--- a/output/result.xlsx
+++ b/output/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,16 @@
           <t>status</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>document_id</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -466,29 +476,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>半導體通膨趨勢成形，晶圓代工、IC 設計紛漲價 | TechNews 科技新報</t>
+          <t>市場報導： 2026年上半年半導體營收竟然達7千億美元，相當於2024年一整年總營收，AI太可怕了！ - 科技產業資訊室</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://finance.technews.tw/2026/05/01/semiconductor-inflation-trend-takes-shape-wafer-foundries-ic-design-price-hikes/</t>
+          <t>https://iknow.stpi.niar.org.tw/Post/Read.aspx?PostID=23258</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Fri, 01 May 2026 07:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>半導體通膨趨勢成形，晶圓代工、IC 設計紛漲價 | TechNews 科技新報 搜尋： 登入 註冊 登出 VIP會員 Menu Skip to content 會員專區 訂閱專區 技術分析 焦點新聞評析 拓墣觀點 TechNews Smart AI 活動專區 常見問題 半導體 晶圓 晶片 IC 設計 封裝測試 處理器 GPU 記憶體 零組件 光電科技 面板 電池 3C周邊 AI 人工智慧 Claude Apple Intelligence DeepSeek Gemini Copilot ChatGPT Perplexity Grok 財經 財報 證券 房地產 Fintech 加密貨幣 金融政策 國際貿易 國際金融 支付方案 尖端科技 奈米 衛星通訊 汽車科技 航太科技 機器人 軍事科技 材料 無人機 環境科學 醫療科技 生物科技 科技生活 科技教育 能源科技 太陽能 風力 核能 電力儲存 企業永續 科技人才 系列專題 Token 戰爭：AI 推論時代的結構性大洗牌 光速革命 2026：矽光子與 CPO 領航 AI 下半場 AI 全方位解析：看懂任務分類、硬體門檻與你的產業卡位戰 能源即算力！2026 資料中心電源保衛戰 川普重返白宮一年，全球科技規則如何改變？ AI 晶片封裝技術革命 晶片戰場的隱形冠軍：先進封裝需求背後，一場決定全球 AI 命脈的設備軍備競賽 財報快訊 企業部落格 市場動態 關於我們 內容合作單位 菁英人才招募中 廣告合作 TN Smart 半導體通膨趨勢成形，晶圓代工、IC 設計紛漲價 作者 中央社 | 發布日期 2026 年 05 月 01 日 9:59 | 分類 IC 設計 , 半導體 , 晶圓 | edit Loading... Now Translating . . . 半導體通膨趨勢成形，因應成本高漲，包括晶圓代工及 IC 設計廠紛紛調漲價格，對於智慧手機等消費產品市場影響逐步顯現，智慧手機等今年出貨量恐面臨衰退壓力。 半導體廠法人說明會陸續登場，成本壓力及產品價格策略成為法人關注的焦點。晶圓代工廠除將持續投入技術開發及擴充產能，中東緊張局勢也造成能源和物流等成本升高。 晶圓代工廠 力積電 已搶先於今年1月調漲驅動IC及感測器代工價格，3月調漲功率元件代工價格， 世界 先進跟進於4月調漲代工價格， 聯電 也於4月通知客戶，將於下半年調整價格。 不僅晶圓代工價格調漲，後段封測價格也傳出漲價消息，IC設計廠紛紛決定調漲產品售價，減緩成本升高的影響， 盛群 3月已通知客戶， 聯發科 透露將藉由嚴謹的定價策略，目標將全年毛利率維持在44.5%至47.5%區間。 觀察目前整體市況依然呈現不同調的態勢，AI相關市場需求持續強勁，消費電子市場需求相對疲弱，IC設計廠不打算全面調漲產品價格。 雅特力-KY認為，近期微控制器（MCU）市場掀起一波漲價潮，並不是終端市場強勁需求所帶動，而是AI需求強勁占用產能，以及原材料漲價所致，雅特力-KY僅會適度漲價，力求毛利率持穩。 盛群認為，目前經濟情勢並未變好，需求僅穩定，因應晶圓代工與封測漲價10%至15%，盛群將僅調漲低毛利產品售價，期能讓毛利回歸合理。 繼記憶體價格飆漲後，晶圓代工和IC設計紛紛調漲價格，半導體通膨趨勢成形，使得智慧手機等消費產品市場，面臨成本升高的壓力進一步加劇。廠商除將資源集中於高階產品因應，需求也開始趨緩，聯發科預估，今年手機出貨量恐減少15%。漲價對市場需求的影響，未來是否進一步擴大，備受市場關注。 （作者：張建中；首圖來源：shutterstock） 文章看完覺得有幫助，何不給我們一個鼓勵 請我們喝杯咖啡 想請我們喝幾杯咖啡？ 每杯咖啡 65 元 x 1 x 3 x 5 x 您的咖啡贊助將是讓我們持續走下去的動力 總金額共新臺幣 0 元 《關於請喝咖啡的 Q &amp; A》 留給我們的話 取消 確認 從這裡可透過《Google 新聞》追蹤 TechNews 科技新知，時時更新 科技新報粉絲團 加入好友 訂閱免費電子報 關鍵字: 半導體通路 , 晶圓代工 , 智慧手機 , 漲價 Post navigation ← 抓無人機不靠雷達，波蘭測試「聲學感測器」揪出隱形威脅 當「好公司」成為一種人設？拆解 B 型企業的道德溢價與認證背後的機制失靈 → 我們偵測 到您有啟用 AD Block 請您暫停使用AD Block，以支持我們持續能提供更多新聞資訊與優質的閱讀環境。 新報特企 焦點動態 系列專題 AI 推論的 Token 戰爭 小龍蝦點燃「算力即營收」新紀元！Vera Rubin 引爆台美供應鏈一次看 代理 AI 重塑晶片架構！「成本才是王道」，ASIC、CPU 與記憶體牆成新戰場 從 SaaS 到 TaaS：AI 時代為何你不是付月費，而是 Token？ VIP 全預觀 本田續約廣汽十年：從技術輸出到技術汲取的合資 2.0 模式 從馬路到水路，小米申請新能源車水下推進器專利 FEV 與微軟部署車端小語言模型，確保離線語音服務與高效運用記憶體 全球儲能產業發展趨勢：政策、法規與標準化 1.6T 世代：通訊關鍵元件洗牌與台灣廠商切入路徑 本週熱門 數學界天翻地覆，代數幾何 87 年懸案「雅可比猜想」遭 Claude 證偽 焦慮、肥胖、不婚不生，研究：人類演化無法適應現代社會 全球水域含氧量迅速流失，科學家警告「水體脫氧」恐不可逆 根本沒有 100%「美國製造」路由器，廠商群起申請豁免使 FCC 禁令漸鬆 海洋蠕蟲超硬顎部揭密，科學家首度定義全新「生體金屬」 一天喝五杯咖啡也無妨？研究揭開咖啡的護肝潛力 喝咖啡能護心？美國心臟協會揭每日黃金杯數，警告避開三大飲用地雷 是太空垃圾也是天然實驗場！SpaceX 火箭殘骸 8/5 將墜入月球表面 財訊快報 宜特6月營收月增10.5% 漢唐6月營收87.43 億元 台灣大6月營收月增5.4% 科嘉-KY6月營收月減17.3% 康控-KY6月營收月減4.3% 漢磊6月營收6.20 億元 嘉晶6月營收月增3.3% 中華電6月營收月增9.3% 中環6月營收6.39 億元 台積電6月營收月增6.2% 更多&gt;&gt; 編輯精選 [ 專欄 ] 美國與中國分居最大出口市場與進口來源國下的台灣貿易結構 [ 專欄 ] 記憶體價格上漲，難成為美國政府鬆綁中國管制的理由 [ 專題 ] 小龍蝦點燃「算力即營收」新紀元！Vera Rubin 引爆台美供應鏈一次看 [ 專題 ] 代理 AI 重塑晶片架構！「成本才是王道」，ASIC、CPU 與記憶體牆成新戰場 [ 專題 ] 從 SaaS 到 TaaS：AI 時代為何你不是付月費，而是 Token？ [ 專欄 ] 「中小微企業多元振興發展計畫」落實，對提高台灣經濟韌性有重大幫助 [ 專訪 ] AI 資料傳輸量暴增！WD 談「兩大儲存挑戰」：關鍵在分層式架構 [ 專欄 ] 鼓勵「不勞而獲」降稅政策只會擴大台灣社會失衡 FB 粉絲團 我的最愛 趕快加入最愛頁面 Facebook 成為我們的小粉絲 RSS 即時更新新知 相關連結 Facebook 功能 文章 RSS 訂閱 迴響 RSS 訂閱 © 2013-2026 TechNews Inc. All rights reserved. | 關於我們 | 使用條款 | 隱私權政策 | 著作權與授權轉載 登入裝置已達上限 親愛的會員, 您的帳戶已經在其他裝置進行登入，於是系統將自動把您的帳戶登出本裝置。 若需要繼續瀏覽網站，請 重新登入 網站 若非您本人的操作，為保障您的帳戶安全，請您儘快至會員中心 修改密碼 × 請您暫停使用AD Block，以支持我們持續能提供更多新聞資訊與優質的閱讀環境。</t>
-        </is>
-      </c>
+          <t>Tue, 16 Jun 2026 02:26:21 GMT</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>科技產業資訊室</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Success</t>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Download failed</t>
         </is>
       </c>
     </row>
@@ -500,25 +516,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-	NYCU and Purdue Launch Global Semiconductor Academy to Advance AI and Chip Talent Development | 中央社訊息平台
-</t>
+          <t>半導體通膨趨勢成形，晶圓代工、IC 設計紛漲價 - TechNews 科技新報</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.cna.com.tw/postwrite/eng/432806</t>
+          <t>https://finance.technews.tw/2026/05/01/semiconductor-inflation-trend-takes-shape-wafer-foundries-ic-design-price-hikes/</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 07:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>Fri, 01 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>TechNews 科技新報</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NYCU and Purdue Launch Global Semiconductor Academy to Advance AI and Chip Talent Development | 中央社訊息平台 財經訊息平台 知訊台 好生活 影像空間 客戶頻道 中文稿 英文稿 電信 簡介 投稿 投稿 中文稿 英文稿 電信 簡介 平台簡介 服務辦法 投稿流程 收款方式 供稿啓事 新聞稿寫作原則 其他服務 財經訊息平台 知訊台 歡迎公司行號投遞新聞訊息！詳洽業務行銷中心 人工服務時間為週一至週六9:30-12:00、14:00-18:30 如有週日發稿需求請於週六18:00前完成刊登程序。 了解更多 訊息來源：國立陽明交通大學 轉載網址 更多訊息 Matsu’s “Blue Tears” Inspire NYCU Breakthrough in Next-Generation Luminescent Materials NYCU Partners with Kneron to Advance Edge AI Education and Real-World Deployment NYCU and Changhua County Launch Smart Agriculture App to Help Farmers Monitor Crops with AI NYCU Team Wins Taiwan Title at Red Bull Basement, Heads to Silicon Valley for Global Finals NYCU Study Finds Belly Fat May Signal Hidden Heart Failure Risk—Even at Normal Weight 首頁 英文稿 NYCU and Purdue Launch Global Semiconductor Academy to Advance AI and Chip Talent Development 發稿時間：2026/05/07 14:14:32 (中央社訊息服務20260507 14:14:32)As the global semiconductor race accelerates in the AI era, National Yang Ming Chiao Tung University (NYCU) and Purdue University have jointly launched the Semiconductor Academy, a new online professional education initiative designed to cultivate next-generation semiconductor talent and expand access to industry-focused learning worldwide. The collaboration brings together two institutions located at the heart of critical semiconductor ecosystems — Taiwan, home to the world’s most advanced chip manufacturing industry, and the United States, a global leader in semiconductor research, design, and innovation. Developed jointly by NYCU and Purdue, the Semiconductor Academy will offer flexible online courses covering key areas across the semiconductor supply chain, including chip design for AI, semiconductor materials and devices, advanced packaging, reliability, IC design, EDA, and semiconductor industry management. The program is designed for working professionals, engineers, and learners seeking to deepen their expertise or enter the rapidly evolving semiconductor field. Courses will be delivered online in a modular, stackable format, allowing learners to tailor their studies to their professional goals and industry needs. The Semiconductor Academy is a flexible, industry-aligned portfolio of Purdue University micro-credentials developed in collaboration with faculty from NYCU in Taiwan to help upskill the global semiconductor workforce. As one of Taiwan’s leading universities in electrical engineering, computer science, photonics, AI, and semiconductor research, NYCU has long played a central role in nurturing talent for Taiwan’s semiconductor industry and the Hsinchu Science Park ecosystem. Through the Semiconductor Academy, NYCU faculty will contribute academic expertise and real-world industry perspectives drawn from Taiwan’s globally influential semiconductor ecosystem, offering international learners a unique window into the technologies and manufacturing practices shaping the future of chips and AI computing. “Semiconductor innovation requires a deep understanding of the entire technology stack,” said Mark Lundstrom, Don and Carol Scifres Distinguished Professor of Electrical and Computer Engineering at Purdue University. “By bringing together the strengths of both Purdue and NYCU, the Semiconductor Academy provides learners with a rigorous, globally informed perspective on the technologies shaping the future of the industry.” The collaboration also reflects NYCU’s broader internationalization strategy and its commitment to strengthening global partnerships in semiconductors, AI, and emerging technologies. Covering topics from chip design and semiconductor materials to packaging and supply chain management, the Semiconductor Academy’s two-hour modular courses allow learners to build industry-relevant skills at their own pace. According to Purdue, the Semiconductor Academy is part of a broader expansion of semiconductor professional education aimed at addressing rising workforce demands across the global chip industry. Each course in the academy will feature approximately 2 hours of focused learning content and be accessible through flexible online formats. The academy will also be featured on SEMI University (SEMI U), a global digital learning platform serving semiconductor professionals and organizations worldwide. Topics planned for the initial course offerings include: 。Chip Design for AI 。Packaging, Reliability and Characterization 。IC Design, EDA and Analog 。Semiconductor Materials and Devices 。Supply Chain Management and Leadership in the Semiconductor Industry Additional semiconductor professional education courses developed by Purdue are expected to launch in summer 2026, including transistor fundamentals, nanolithography, RF design, and data analysis for semiconductor applications. The launch ceremony for the Semiconductor Academy was held via livestream between Purdue and NYCU, underscoring the growing importance of international collaboration in building the future semiconductor workforce. 文章附檔 For more NYCU News, please visit the official NYCU website. 訊息平台 平台簡介 | 服務辦法 | 投稿流程 | 收款方式 | 供稿啟事 | 新聞稿寫作原則 | 其他服務 關於中央社 公司簡介 | 企業識別 | 公開資訊 | 設置條例摘要 | 隱私權聲明 | 聯絡我們 友善連結 曾虛白新聞獎基金會 | 公職人員及關係人補助交易身分關係公開及查詢平臺 中央社網站 中央通訊社 | Focus Taiwan | フォーカス台湾 | Fokus Taiwan 關注更多 iOS app 下載 | Android app 下載 | Focus Taiwan APP | 全球中央雜誌 | 文化+ | 淨零碳排 | 新聞學院 | 中央社電子報 產品與服務 產品總覽 | 客戶頻道 | 影像空間 | 訊息平台 | 財經訊息平台 | 知訊台 本平台資料均由投稿單位輸入後對外公布，資料如有錯誤、遺漏或虛偽不實，均由投稿單位負責 copyright © 2021 中央通訊社版權所有</t>
+          <t>半導體通膨趨勢成形，晶圓代工、IC 設計紛漲價 | TechNews 科技新報 搜尋： 登入 註冊 登出 VIP會員 Menu Skip to content 會員專區 訂閱專區 技術分析 焦點新聞評析 拓墣觀點 TechNews Smart AI 活動專區 常見問題 半導體 晶圓 晶片 IC 設計 封裝測試 處理器 GPU 記憶體 零組件 光電科技 面板 電池 3C周邊 AI 人工智慧 Claude Apple Intelligence DeepSeek Gemini Copilot ChatGPT Perplexity Grok 財經 財報 證券 房地產 Fintech 加密貨幣 金融政策 國際貿易 國際金融 支付方案 尖端科技 奈米 衛星通訊 汽車科技 航太科技 機器人 軍事科技 材料 無人機 環境科學 醫療科技 生物科技 科技生活 科技教育 能源科技 太陽能 風力 核能 電力儲存 企業永續 科技人才 系列專題 Token 戰爭：AI 推論時代的結構性大洗牌 光速革命 2026：矽光子與 CPO 領航 AI 下半場 AI 全方位解析：看懂任務分類、硬體門檻與你的產業卡位戰 能源即算力！2026 資料中心電源保衛戰 川普重返白宮一年，全球科技規則如何改變？ AI 晶片封裝技術革命 晶片戰場的隱形冠軍：先進封裝需求背後，一場決定全球 AI 命脈的設備軍備競賽 財報快訊 企業部落格 市場動態 關於我們 內容合作單位 菁英人才招募中 廣告合作 TN Smart 半導體通膨趨勢成形，晶圓代工、IC 設計紛漲價 作者 中央社 | 發布日期 2026 年 05 月 01 日 9:59 | 分類 IC 設計 , 半導體 , 晶圓 | edit Loading... Now Translating . . . 半導體通膨趨勢成形，因應成本高漲，包括晶圓代工及 IC 設計廠紛紛調漲價格，對於智慧手機等消費產品市場影響逐步顯現，智慧手機等今年出貨量恐面臨衰退壓力。 半導體廠法人說明會陸續登場，成本壓力及產品價格策略成為法人關注的焦點。晶圓代工廠除將持續投入技術開發及擴充產能，中東緊張局勢也造成能源和物流等成本升高。 晶圓代工廠 力積電 已搶先於今年1月調漲驅動IC及感測器代工價格，3月調漲功率元件代工價格， 世界 先進跟進於4月調漲代工價格， 聯電 也於4月通知客戶，將於下半年調整價格。 不僅晶圓代工價格調漲，後段封測價格也傳出漲價消息，IC設計廠紛紛決定調漲產品售價，減緩成本升高的影響， 盛群 3月已通知客戶， 聯發科 透露將藉由嚴謹的定價策略，目標將全年毛利率維持在44.5%至47.5%區間。 觀察目前整體市況依然呈現不同調的態勢，AI相關市場需求持續強勁，消費電子市場需求相對疲弱，IC設計廠不打算全面調漲產品價格。 雅特力-KY認為，近期微控制器（MCU）市場掀起一波漲價潮，並不是終端市場強勁需求所帶動，而是AI需求強勁占用產能，以及原材料漲價所致，雅特力-KY僅會適度漲價，力求毛利率持穩。 盛群認為，目前經濟情勢並未變好，需求僅穩定，因應晶圓代工與封測漲價10%至15%，盛群將僅調漲低毛利產品售價，期能讓毛利回歸合理。 繼記憶體價格飆漲後，晶圓代工和IC設計紛紛調漲價格，半導體通膨趨勢成形，使得智慧手機等消費產品市場，面臨成本升高的壓力進一步加劇。廠商除將資源集中於高階產品因應，需求也開始趨緩，聯發科預估，今年手機出貨量恐減少15%。漲價對市場需求的影響，未來是否進一步擴大，備受市場關注。 （作者：張建中；首圖來源：shutterstock） 文章看完覺得有幫助，何不給我們一個鼓勵 請我們喝杯咖啡 想請我們喝幾杯咖啡？ 每杯咖啡 65 元 x 1 x 3 x 5 x 您的咖啡贊助將是讓我們持續走下去的動力 總金額共新臺幣 0 元 《關於請喝咖啡的 Q &amp; A》 留給我們的話 取消 確認 從這裡可透過《Google 新聞》追蹤 TechNews 科技新知，時時更新 科技新報粉絲團 加入好友 訂閱免費電子報 關鍵字: 半導體通路 , 晶圓代工 , 智慧手機 , 漲價 Post navigation ← 抓無人機不靠雷達，波蘭測試「聲學感測器」揪出隱形威脅 當「好公司」成為一種人設？拆解 B 型企業的道德溢價與認證背後的機制失靈 → 我們偵測 到您有啟用 AD Block 請您暫停使用AD Block，以支持我們持續能提供更多新聞資訊與優質的閱讀環境。 新報特企 焦點動態 系列專題 AI 推論的 Token 戰爭 小龍蝦點燃「算力即營收」新紀元！Vera Rubin 引爆台美供應鏈一次看 代理 AI 重塑晶片架構！「成本才是王道」，ASIC、CPU 與記憶體牆成新戰場 從 SaaS 到 TaaS：AI 時代為何你不是付月費，而是 Token？ VIP 全預觀 本田續約廣汽十年：從技術輸出到技術汲取的合資 2.0 模式 從馬路到水路，小米申請新能源車水下推進器專利 FEV 與微軟部署車端小語言模型，確保離線語音服務與高效運用記憶體 全球儲能產業發展趨勢：政策、法規與標準化 1.6T 世代：通訊關鍵元件洗牌與台灣廠商切入路徑 本週熱門 數學界天翻地覆，代數幾何 87 年懸案「雅可比猜想」遭 Claude 證偽 焦慮、肥胖、不婚不生，研究：人類演化無法適應現代社會 全球水域含氧量迅速流失，科學家警告「水體脫氧」恐不可逆 根本沒有 100%「美國製造」路由器，廠商群起申請豁免使 FCC 禁令漸鬆 海洋蠕蟲超硬顎部揭密，科學家首度定義全新「生體金屬」 一天喝五杯咖啡也無妨？研究揭開咖啡的護肝潛力 喝咖啡能護心？美國心臟協會揭每日黃金杯數，警告避開三大飲用地雷 是太空垃圾也是天然實驗場！SpaceX 火箭殘骸 8/5 將墜入月球表面 財訊快報 宜特6月營收月增10.5% 漢唐6月營收87.43 億元 台灣大6月營收月增5.4% 科嘉-KY6月營收月減17.3% 康控-KY6月營收月減4.3% 漢磊6月營收6.20 億元 嘉晶6月營收月增3.3% 中華電6月營收月增9.3% 中環6月營收6.39 億元 台積電6月營收月增6.2% 更多&gt;&gt; 編輯精選 [ 專欄 ] 美國與中國分居最大出口市場與進口來源國下的台灣貿易結構 [ 專欄 ] 記憶體價格上漲，難成為美國政府鬆綁中國管制的理由 [ 專題 ] 小龍蝦點燃「算力即營收」新紀元！Vera Rubin 引爆台美供應鏈一次看 [ 專題 ] 代理 AI 重塑晶片架構！「成本才是王道」，ASIC、CPU 與記憶體牆成新戰場 [ 專題 ] 從 SaaS 到 TaaS：AI 時代為何你不是付月費，而是 Token？ [ 專欄 ] 「中小微企業多元振興發展計畫」落實，對提高台灣經濟韌性有重大幫助 [ 專訪 ] AI 資料傳輸量暴增！WD 談「兩大儲存挑戰」：關鍵在分層式架構 [ 專欄 ] 鼓勵「不勞而獲」降稅政策只會擴大台灣社會失衡 FB 粉絲團 我的最愛 趕快加入最愛頁面 Facebook 成為我們的小粉絲 RSS 即時更新新知 相關連結 Facebook 功能 文章 RSS 訂閱 迴響 RSS 訂閱 © 2013-2026 TechNews Inc. All rights reserved. | 關於我們 | 使用條款 | 隱私權政策 | 著作權與授權轉載 登入裝置已達上限 親愛的會員, 您的帳戶已經在其他裝置進行登入，於是系統將自動把您的帳戶登出本裝置。 若需要繼續瀏覽網站，請 重新登入 網站 若非您本人的操作，為保障您的帳戶安全，請您儘快至會員中心 修改密碼 × 請您暫停使用AD Block，以支持我們持續能提供更多新聞資訊與優質的閱讀環境。</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -527,6 +545,12 @@
           <t>Success</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>d970a92d732b9934c7e2d6a264f99fc947e20ef78a234dcc7de6a81e794b3864</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -536,23 +560,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>全台首家IC設計獲Arm注資 通寶半導體Q4擬申請IPO - 日報 - 工商時報</t>
+          <t>NYCU and Purdue Launch Global Semiconductor Academy to Advance AI and Chip Talent Development - 中央社 CNA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.ctee.com.tw/news/20260304700096-439901</t>
+          <t>https://www.cna.com.tw/postwrite/eng/432806</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 08:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>Thu, 07 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>中央社 CNA</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>全台首家IC設計獲Arm注資 通寶半導體Q4擬申請IPO - 日報 - 工商時報 前往主要內容 會員 會員中心 登出 電子報 影音特區 讀報區 首頁 即時 開闔次選單 即時首頁 要聞 證券 金融 稅法 產業 房市 國際 兩岸 科技 生活 要聞 開闔次選單 要聞首頁 政經焦點 總經趨勢 稅務法務 綜合要聞 前瞻一周 證券 開闔次選單 證券首頁 上市櫃 陸港股市 國際股市 產業焦點 期貨 權證 亮點個股 專家看盤 台股逐洞賽 重要指數 重大訊息 財經行事曆 金融 開闔次選單 金融首頁 金融話題 外匯市場 牌告匯率 金融科技 銀行動態 保險脈動 數據觀測 金融人物 理財 開闔次選單 理財首頁 理財新訊 基金 ETF 生活消費 信用卡 退休理財 統一發票 產業 開闔次選單 產業首頁 半導體 科技動態 綜合產業 生技醫療 CEO專訪 職場達人 房市 開闔次選單 房市首頁 房市焦點 區域亮點 名家攻略 居住安全 觀點評論 市場動態 國際 開闔次選單 國際首頁 全球政經 全球市場 議題觀點 國際產業 Global Scan 全球財經周報 大宗商品行情 兩岸 開闔次選單 兩岸首頁 政情動向 兩岸焦點 大陸財經 大陸產業 China Scan 陸港市場 觀點分析 言論 開闔次選單 言論首頁 社論 總經經濟 產業脈動 國際經貿 企業管理 社會觀察 奇思妙想 作者群 樂活 開闔次選單 樂活首頁 美食饗宴 旅遊休閒 生活風格 愛車天地 養生保健 時尚消費 藝文特區 書房 開闔次選單 書房首頁 書房嚴選 名人書單 好書推薦 英文進修 雜誌精選 年度好書 專題 開闔次選單 專題首頁 上市櫃6月營收 大陸經濟新局 台灣半導體風雲 上市櫃Q1營收 生技ESG革命 新世代夯話題 財經人物專訪 商情 開闔次選單 商情首頁 智慧機械 大健康 金融理財 房市建材 科技綠能 消費時尚 產學管顧 社企公益 活動 開闔次選單 活動首頁 台南機械展 台中AI展 台灣權王 服務業大評鑑 數位金融獎 ETF論壇 中華電信論壇 多元信託 期貨與選擇權 永續校園徵影 搜尋 首頁 日報 工商時報 全台首家IC設計獲Arm注資 通寶半導體Q4擬申請IPO 全台首家IC設計獲Arm注資 通寶半導體Q4擬申請IPO 2026.03.04 03:00 工商時報 呂雪彗 通寶半導體 安謀 智原科技 IC設計 Arm注資 通寶半導體公司董事長暨執行長沈軾榮表示，通寶半導體為全台唯一獲Arm投資的 IC 設計公司。圖／通寶半導體提供 切換文字大小 複製文章連結 分享至臉書 以Line分享 加入Google來源 參與討論 友善列印 已將目前網頁的網址複製到您的剪貼簿！ 通寶半導體設計公司簡介 台灣IC設計領域傳出國際策略投資合作捷報，通寶半導體（QBit Semiconductor）公司3日宣布，已完成B輪募資，並獲全球半導體架構大廠安謀公司（Arm Limited）參與投資，成為目前全台唯一獲得Arm投資的IC設計公司。 安謀現成為通寶十大股東之一，至於安謀持股比例及金額，4月下旬召開法說會可望對外說明，未來通寶擬計畫跨足無人機及機器人市場。 通寶半導體同時宣布，隨著募資完成營運規模擴大，計畫於今年第四季向臺灣證券交易所申請IPO上市，進一步邁向資本市場新里程碑，實際時程仍須視主管機關核准及市場狀況而定。 通寶半導體為專攻多功能列印機及事務機系統晶片的IC設計公司，其客戶主要市場遍及美國、日本、中國跟台灣。除Arm參與投資外，據悉，通寶半導體在A輪募資時，台灣政府法人機構持有通寶半導體約6％股權，包括國發基金持股2.7％，以及台肥、工研院等公股事業合計持股比例約6％，還有智原科技等半導體產業加入，整體A輪投資人持股比例約為通寶已發行股權10％。 對於這項注資，Arm全球執行副總裁暨商務長Will Abbey表示，透過與通寶的合作，可以結合先進影像處理、控制與安全能力，以支持列印及影像市場的創新。此類合作展現Arm更廣泛的策略，亦即推動具差異化的解決方案，從高效能系統延伸至更具成本效益的裝置，同時為各類產品建立成長基礎。 通寶半導體創辦人暨執行長沈軾榮也表示，很榮幸成為獲得Arm唯一投資的台灣半導體設計公司，未來通寶將持續深化在印表機影像市場的布局，並拓展至更廣泛的影像相關應用領域。 將工商時報加入Google偏好來源 相關新聞 大盤震盪 拉回擇優布局台股ETF 美股走勢分歧 晶片股台積電ADR持續承壓 《基金》6檔國內半導體ETF夯 受益人數突破43.8萬人創新高 您可能感興趣的話題 留言討論 熱門日報新聞 more 台股聞到「洗籌碼、殺斷頭」的味道！「四貸同堂」族哀嚎 指數何時反彈名師劃重點 大摩喊記憶體供需缺口未收斂 Q3漲勢未歇 南亞科、華邦電、旺宏有戲唱 台股融資大退散 短線反彈契機已到？專家估8月有望戰季線 公股逢低撿便宜 重倉大型權值電子股 買超前十強3檔ETF卡位 竟是同一家 金管會出手 嚴管四貸同堂 專題推薦 返回頁首 網站選單開關 顏色主題切換 LOADING 熱門新聞 TOP 3 more 台股崩盤不敢買？孫慶龍股災做對一件事 52萬竟變成8千萬 未來十年最看好這2檔 台股聞到「洗籌碼、殺斷頭」的味道！「四貸同堂」族哀嚎 指數何時反彈名師劃重點 期貨最新報價7／29期交所夜盤行情 本網頁已閒置超過3分鐘。請點撃框外背景，或右側關閉按鈕(X)，即可回到網頁。 關閉 關閉廣告</t>
+          <t>NYCU and Purdue Launch Global Semiconductor Academy to Advance AI and Chip Talent Development | 中央社訊息平台 財經訊息平台 知訊台 好生活 影像空間 客戶頻道 中文稿 英文稿 電信 簡介 投稿 投稿 中文稿 英文稿 電信 簡介 平台簡介 服務辦法 投稿流程 收款方式 供稿啓事 新聞稿寫作原則 其他服務 財經訊息平台 知訊台 歡迎公司行號投遞新聞訊息！詳洽業務行銷中心 人工服務時間為週一至週六9:30-12:00、14:00-18:30 如有週日發稿需求請於週六18:00前完成刊登程序。 了解更多 訊息來源：國立陽明交通大學 轉載網址 更多訊息 Matsu’s “Blue Tears” Inspire NYCU Breakthrough in Next-Generation Luminescent Materials NYCU Partners with Kneron to Advance Edge AI Education and Real-World Deployment NYCU and Changhua County Launch Smart Agriculture App to Help Farmers Monitor Crops with AI NYCU Team Wins Taiwan Title at Red Bull Basement, Heads to Silicon Valley for Global Finals NYCU Study Finds Belly Fat May Signal Hidden Heart Failure Risk—Even at Normal Weight 首頁 英文稿 NYCU and Purdue Launch Global Semiconductor Academy to Advance AI and Chip Talent Development 發稿時間：2026/05/07 14:14:32 (中央社訊息服務20260507 14:14:32)As the global semiconductor race accelerates in the AI era, National Yang Ming Chiao Tung University (NYCU) and Purdue University have jointly launched the Semiconductor Academy, a new online professional education initiative designed to cultivate next-generation semiconductor talent and expand access to industry-focused learning worldwide. The collaboration brings together two institutions located at the heart of critical semiconductor ecosystems — Taiwan, home to the world’s most advanced chip manufacturing industry, and the United States, a global leader in semiconductor research, design, and innovation. Developed jointly by NYCU and Purdue, the Semiconductor Academy will offer flexible online courses covering key areas across the semiconductor supply chain, including chip design for AI, semiconductor materials and devices, advanced packaging, reliability, IC design, EDA, and semiconductor industry management. The program is designed for working professionals, engineers, and learners seeking to deepen their expertise or enter the rapidly evolving semiconductor field. Courses will be delivered online in a modular, stackable format, allowing learners to tailor their studies to their professional goals and industry needs. The Semiconductor Academy is a flexible, industry-aligned portfolio of Purdue University micro-credentials developed in collaboration with faculty from NYCU in Taiwan to help upskill the global semiconductor workforce. As one of Taiwan’s leading universities in electrical engineering, computer science, photonics, AI, and semiconductor research, NYCU has long played a central role in nurturing talent for Taiwan’s semiconductor industry and the Hsinchu Science Park ecosystem. Through the Semiconductor Academy, NYCU faculty will contribute academic expertise and real-world industry perspectives drawn from Taiwan’s globally influential semiconductor ecosystem, offering international learners a unique window into the technologies and manufacturing practices shaping the future of chips and AI computing. “Semiconductor innovation requires a deep understanding of the entire technology stack,” said Mark Lundstrom, Don and Carol Scifres Distinguished Professor of Electrical and Computer Engineering at Purdue University. “By bringing together the strengths of both Purdue and NYCU, the Semiconductor Academy provides learners with a rigorous, globally informed perspective on the technologies shaping the future of the industry.” The collaboration also reflects NYCU’s broader internationalization strategy and its commitment to strengthening global partnerships in semiconductors, AI, and emerging technologies. Covering topics from chip design and semiconductor materials to packaging and supply chain management, the Semiconductor Academy’s two-hour modular courses allow learners to build industry-relevant skills at their own pace. According to Purdue, the Semiconductor Academy is part of a broader expansion of semiconductor professional education aimed at addressing rising workforce demands across the global chip industry. Each course in the academy will feature approximately 2 hours of focused learning content and be accessible through flexible online formats. The academy will also be featured on SEMI University (SEMI U), a global digital learning platform serving semiconductor professionals and organizations worldwide. Topics planned for the initial course offerings include: 。Chip Design for AI 。Packaging, Reliability and Characterization 。IC Design, EDA and Analog 。Semiconductor Materials and Devices 。Supply Chain Management and Leadership in the Semiconductor Industry Additional semiconductor professional education courses developed by Purdue are expected to launch in summer 2026, including transistor fundamentals, nanolithography, RF design, and data analysis for semiconductor applications. The launch ceremony for the Semiconductor Academy was held via livestream between Purdue and NYCU, underscoring the growing importance of international collaboration in building the future semiconductor workforce. 文章附檔 For more NYCU News, please visit the official NYCU website. 訊息平台 平台簡介 | 服務辦法 | 投稿流程 | 收款方式 | 供稿啟事 | 新聞稿寫作原則 | 其他服務 關於中央社 公司簡介 | 企業識別 | 公開資訊 | 設置條例摘要 | 隱私權聲明 | 聯絡我們 友善連結 曾虛白新聞獎基金會 | 公職人員及關係人補助交易身分關係公開及查詢平臺 中央社網站 中央通訊社 | Focus Taiwan | フォーカス台湾 | Fokus Taiwan 關注更多 iOS app 下載 | Android app 下載 | Focus Taiwan APP | 全球中央雜誌 | 文化+ | 淨零碳排 | 新聞學院 | 中央社電子報 產品與服務 產品總覽 | 客戶頻道 | 影像空間 | 訊息平台 | 財經訊息平台 | 知訊台 本平台資料均由投稿單位輸入後對外公布，資料如有錯誤、遺漏或虛偽不實，均由投稿單位負責 copyright © 2021 中央通訊社版權所有</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -561,6 +589,12 @@
           <t>Success</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>f4068be0c01a90821295bd0289181ff02d813688f755753fa888b3135406f94d</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,33 +604,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ICTGCç«¶è³½é¦ç»ç½è°· é²è»CESå»£éå-¨çICæ°åµéçµèºç£åå°é«çæ-é - å°åå¸é»è-¦åæ¥­åæ¥­å-¬æ Taipei Computer Association</t>
+          <t>市場報導： 2026年上半年半導體營收竟然達7千億美元，相當於2024年一整年總營收，AI太可怕了！ - 科技產業資訊室</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.tca.org.tw/news_detail.php?n=2454&amp;t=h</t>
+          <t>https://iknow.stpi.niar.org.tw/Post/Read.aspx?PostID=23258</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Fri, 02 Jan 2026 08:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>ICTGCç«¶è³½é¦ç»ç½è°· é²è»CESå»£éå ¨çICæ°åµéçµèºç£åå°é«çæ é - å°åå¸é»è ¦åæ¥­åæ¥­å ¬æ Taipei Computer Association æå¡ç»å ¥ å å ¥TCA äººææå ç«å §æå° èªè­ TCA æ¬æç°¡ä» å¤§äºç´ çµç¹æ¶æ§ çç£äº å°æ¥­è¯ç æå¡æå ç¢æ¥­æ¨å»£ å±è¦½æé· åé¡ç«¶è³½ æ°åµæ´»å è¨ç«è³æº åå¥½é£çµ æ°èä¸­å¿ ç±éæ°è äººç©æ¡è¨ª æå¡å°è¨ª æ´»åæ å ± å½±åæ«¥çª TCA Video Gallery TCA Photo Gallery ç«å §æå° × æå° éé ç±éæ°è ICTGCç«¶è³½é¦ç»ç½è°· é²è»CESå»£éå ¨çICæ°åµéçµèºç£åå°é«çæ é IC Taiwan Grand Challengeåéæ¼CES 2025å±ä¸­ä¹TTAåå®¶é¤¨ä»ç´¹ç«¶è³½ åå®¶ç§å­¸åæè¡å§å¡æï¼NSTCï¼æå°çåéåµæ°ç«¶è³½IC Taiwan Grand Challengeï¼ICTGCï¼å°èå ¨çæ°åµå±æ InnoVEX ä¸»è¾¦å®ä½âå°åå¸é»è ¦å ¬æï¼TCAï¼æ¼ CES 2026 æéå ±åååä¸ç³»ååéäº¤æµæ´»åã é¢å° AI ç¡¬é«ãæ©å¨äººãå é²æ¶çèé«ç§æåµæ°å¿«éæ¼é²çå ¨çæµªæ½®ï¼InnoVEX æçºä½çºåéæ°åµå°æ¥äºæ´²æå é²ç§æç¢æ¥­çééµå ¥å£ï¼æ­¤æ¬¡ ICTGC x InnoVEX åéæ¨å»£è¡åé¤äºå¨CESå±æäº®ç¸ï¼ä¹å¾å°æ¼ 1 æ 13 æ¥å¨ç½è°·èè¾¦å°å ´æ´»åï¼åå©æ´å¤ç½è°·åéæ·±å ¥äºè§£å¦ä½ä¸²é£å°ç£å¨åå°é«è AI é åçä¸çç´è³æºï¼å±ç¾å°ç£æ¨åè·¨ååä½èæ¯æä¸ä¸ä»£ééµæè¡çæ±ºå¿èæ¿è«¾ã ICTGCãInnoVEXå°æ¼CES 2026é éç»å ´ å»£éå ¨çæ°åµèè¨TTAåå®¶é¤¨ å¨ CES 2026å±ææéï¼ IC Taiwan Grand Challengeï¼ICTGCï¼å°ææå ¨çåµæ°å±æInnoVEX å°äº®ç¸æ¼CES Eureka Park ç Taiwan Tech Arenaï¼TTAï¼åå®¶é¤¨ï¼Booth Venetian Expo, Hall G â 62201ï¼ãTTA çºåç§ææ¼ CES è¨­ç«çå®æ¹å±åï¼éå®å ·åç ç©¶å°åèæªä¾æ·±ç§ææ½åçæ°åµåéï¼æ¯å¹´å¸å¼å ¨çæè³äººãåéåªé«èç§æé è¢åè¨ªã ICTGC åéä¹å°æ¼ TTA Stage æ·±å ¥ä»ç´¹èºç£å¯ä¸å ·æå®æ´è¼å°æ©å¶ãå¯æ·±å ¥å°æ¥ç¢æ¥­éä¹åå°é«æ°åµç«¶è³½ï¼åä»¥ç²çæ°åµæ¡ä¾åäº«ICTGCå¦ä½çºæ°åµæä¾å¾è¨­è¨å°éç¢çå®æ´å éæ¯æã åéè§å±è äº¦æ­¡è¿èè¨ç¾å ´è InnoVEX åICTGC åéäº¤æµï¼ç­è§£è³æºéçµèç«¶è³½çå¾µä»¶åèæ¹å¼ã ICTGC 2026 å ¨çå¾µä»¶éè·ï¼å©æ»åéæ°åµéµçµç½å³¶ ICTGC ç¾æ­£éæ¾å ¨çå ±åï¼ç³è«æªæ­¢æ¥çº 2026 å¹´ 2 æ 28 æ¥ãæ­¡è¿ä¾èª AIãæ©å¨äººãåå°é«æè¡ãææ¸¬ç³»çµ±ãæ¬¡ä¸ä»£éç®ãæ·±ç§æç­é åçæ©ææ°åµãå­¸ç åéèæè¡éç¼è æäº¤å ·æ½åçåµæ°æç¨ææ¡ã çºåå©åéæ°åµæ´å¤§å½±é¿åãå éæè¡è½å°ï¼å ¥é¸åéå°æ¼ 2026 å¹´ 6 æ 2 è³ 5 æ¥å¨å°åèè¡ç COMPUTEX TAIPEI è InnoVEX æ°åµå±ä¸­ï¼ç²å¾å è²»åå±æ©æã ä½çºäºæ´²ææ¨æ§ç B2B ç§æå±ï¼COMPUTEX çµå InnoVEX ä¸ç«å¼çåµæå°æ¥èåéåªåèå°ï¼è®åéææ©æç´æ¥éçµè£½é å¤¥ä¼´ãåå°é«ä¾æéãåµæè³æºèåéè²·ä¸»ï¼çºå¸å±åå°é«ç¢æ¥­éä¹ééµè·³æ¿ãééICTGCè¨ç«ï¼ç²çåéå¯æææå°ç£åå°é«çæ ç³»ï¼å ±åéç¼å ·åéç«¶ç­ååµæ°è§£æ±ºæ¹æ¡ã å ±åç¶²åï¼ictaiwanchallenge.org ICTGCé¦åº¦ç½è°·ç»å ´ã1 æ 13 æ¥ææInnoVEXèè¾¦è«å£æ·±åå°ç½åå°é«èAIåä½ å»¶çºCESåéæ¨å»£åè½ï¼ICTGCå°æ¼2026å¹´1æ13æ¥é¦åº¦å¨ç½è°·Palo AltoçStartup Island TAIWAN â Silicon Valley Hubèè¾¦ãBridging Silicon Valley and Taiwan: Semiconductor &amp; AI Synergiesãè«å£ãè«å£å¯èç½è°·åµæ¥­è ãæè³äººèæè¡å°å®¶ï¼æ¢è¨å¦ä½åç¨å°ç£åå°é«èAIä¾æéè³æºï¼å¼·ååµæ°è½å°èåéåä½ï¼æ´æ¼ç¾å ´çºæèè¶£åèæ·±åº¦ä»ç´¹å°ä»ç´¹ç«¶è³½å¾µä»¶å §å®¹èè©é¸éé»ï¼åæåæ¡ä¾åäº«ã åéåéäº¦å¯èç±åå æ­¤è«å£ï¼äºè§£æ´å¤æ¼å°ç£ COMPUTEX/InnoVEX å±åºè³è¨ï¼åå©å ¶ææ¡æåé²å ¥å¸å ´çè·¯å¾ä¸¦èèºç£ICTç¢æ¥­çæ ç³»å»ºç«å¯¦è³ªé£çµã æ­¤æ¬¡æ´»åè«å£é¤äºéè«åä½è¬è Laura Swan-Silicon Catalyst Ventures å ±ååå¤¥äººï¼Andy Lombard-Tesoro Venture Capital ç®¡çåå¤¥äºº, Janis Skriveris-Plug and Play Ventures æè³ç¸½ç£æ¨é«ç§æè² è²¬äººä»¥åSam Fok-femtoAI å ±ååµè¾¦äººæ¨å·è¡é·ï¼å°åå¸é»è ¦å ¬ææ¥æ«»å§¿å¯ç¸½å¹¹äºå°å¸¶é åéæä¾ç½è°·æ°åµäººå£«æ´å¤éµçµå°ç£çè³æºï¼å ±åèå£¯æé·ã ç¾å ´å°åæé²è¡å ¨çç´æ­ï¼é è¨å°å¸å¼å ¨çç¸éæ°åµäººå£«è§çãç´æ­é£çµçºï¼https://www.youtube.com/live/ruXS6oe7WNA æ´»åè³è¨ Bridging Silicon Valley and Taiwan: Semiconductor &amp; AI Synergies 2026 å¹´ 1 æ 13 æ¥ï¼ææäºï¼ï½ä¸å 5:00ï¼PSTï¼ Startup Island TAIWAN â Silicon Valley Hub 299 California Ave STE 300, Palo Alto, CA 94306 U.S.A. åèç¶²åï¼ ãBridging Silicon Valley and Taiwan: Semiconductor &amp; AI Synergiesãè«å£ ï¼ç¼ä½æéï¼2026-01-02ï¼ ååè¡¨é  è½å¯ ã åå° ã åäº« å»¶ä¼¸é±è® InnoVEX 2026 ç«¶è³½ç»å ´ AVITICãPlug and PlayãPwCé¦æ³¢ç¹å¥çé½ç¼ï¼è¯æè³¦è½æ°åµéæåéçåè½é å®ç¢é³ä¿èè£äºé·æ¥ä»»çäºé· æè¨±å ±åè´åç¢æ¥­åéå äººç©æ¡è¨ª åç§æç¢å­¸èæå¾·çèé· : æ¨åç¢å­¸åä½è®ç ç¼ææè½å° æ°ä»»çç£äºæ¡è¨ªç³»åå ±å°(7)-æ¬æçäºæ¨å®ç¢æºé«é£å æ©è£äºé· : ãè³éè¨çµåçæãæ¯å°ç£æªä¾ç«¶ç­åªå¢ æ°ä»»çç£äºæ¡è¨ªç³»åå ±å°(6)-æ¬æçäºæ¨éææ©å¨äººé»è­å¿ çéé· : Edge AIæ¯å°ç£æ©å¨äººç¢æ¥­å½éè¶ è»çæ©æ ï¼ æ´å¤è¨æ¯ æå¡å°è¨ª TCAæå¡ä¼æ¥­å°è¨ª -å±¹å²ç§æï¼Eleosï¼ TCAæå¡ä¼æ¥­å°è¨ª -é²ä¸æè¾° TCAæå¡ä¼æ¥­å°è¨ª -å°ç£è³æç§æ ï¼ æ´å¤è¨æ¯ å»£å®£æå é±ç§æ¿ç­ è¯çµ¡æå äº¤éä½ç½® æå¡eåé Â© 2002ï¼2026 å°åå¸é»è ¦åæ¥­åæ¥­å ¬æ çæ¬ææ</t>
-        </is>
-      </c>
+          <t>Tue, 16 Jun 2026 02:26:21 GMT</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>科技產業資訊室</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Success</t>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Download failed</t>
         </is>
       </c>
     </row>
@@ -608,23 +644,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>中國 IC 設計市佔已超車台灣！IDC 揭 2026 半導體十大趨勢：地緣政治如何重塑供應鏈？ | TechOrange 科技報橘</t>
+          <t>全台首家IC設計獲Arm注資 通寶半導體Q4擬申請IPO - 工商時報</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://techorange.com/2025/12/05/2026-semiconductor/</t>
+          <t>https://www.ctee.com.tw/news/20260304700096-439901</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Fri, 05 Dec 2025 08:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>Wed, 04 Mar 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>工商時報</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>中國 IC 設計市佔已超車台灣！IDC 揭 2026 半導體十大趨勢：地緣政治如何重塑供應鏈？ | TechOrange 科技報橘 Skip to content Podcast Apple Podcast Spotify Youtube 聯絡我們 活力徵才 Podcast Apple Podcast Spotify Youtube 聯絡我們 活力徵才 Search 最新文章 AI 人工智慧 AI 機器人 智慧製造 新零售 金融科技 資安 主題特展 2026 AI 智慧大工廠論壇——台中場 2026 科技金融論壇 AI 智慧大工廠論壇－高雄場 2026 AI Agent 新工作革命論壇 AI 智慧大工廠論壇－台南場 AI 機器人產業論壇 AI Ready 數據治理論壇 AI 智慧大工廠論壇－台北場 科技風暴金融高峰論壇 AI 人才年會 TO Highlight 直擊 COMPUTEX 2026 台北國際電腦展 透視 NVIDIA GTC 2026 穩定幣新秩序：科技供應鏈與全球新金融的世紀博弈 2026 AI Impacts 趨勢觀察報告 AI 機器人全球 7 大勢力關鍵報告：透視 Global 300+ 企業系統生態 AI Agent 上工中──你準備好和 AI 當同事了嗎？ 資料治理 = AI 時代的戰略基礎設施 你用的 AI 安全嗎？揭開資安攻擊的新破口 2025 AI 工具應用報告 AI 機器人產業生態分布圖：透視台灣 100 大領軍企業 2025 企業主管 AI 技能趨勢報告 全新一週 Youtube Apple Podcast Spotify 最新文章 AI 人工智慧 AI 機器人 智慧製造 新零售 金融科技 資安 主題特展 2026 AI 智慧大工廠論壇——台中場 2026 科技金融論壇 AI 智慧大工廠論壇－高雄場 2026 AI Agent 新工作革命論壇 AI 智慧大工廠論壇－台南場 AI 機器人產業論壇 AI Ready 數據治理論壇 AI 智慧大工廠論壇－台北場 科技風暴金融高峰論壇 AI 人才年會 TO Highlight 直擊 COMPUTEX 2026 台北國際電腦展 透視 NVIDIA GTC 2026 穩定幣新秩序：科技供應鏈與全球新金融的世紀博弈 2026 AI Impacts 趨勢觀察報告 AI 機器人全球 7 大勢力關鍵報告：透視 Global 300+ 企業系統生態 AI Agent 上工中──你準備好和 AI 當同事了嗎？ 資料治理 = AI 時代的戰略基礎設施 你用的 AI 安全嗎？揭開資安攻擊的新破口 2025 AI 工具應用報告 AI 機器人產業生態分布圖：透視台灣 100 大領軍企業 2025 企業主管 AI 技能趨勢報告 全新一週 Youtube Apple Podcast Spotify 最新文章 AI 人工智慧 AI 機器人 智慧製造 新零售 金融科技 資安 主題特展 2026 AI 智慧大工廠論壇——台中場 2026 科技金融論壇 AI 智慧大工廠論壇－高雄場 2026 AI Agent 新工作革命論壇 AI 智慧大工廠論壇－台南場 AI 機器人產業論壇 AI Ready 數據治理論壇 AI 智慧大工廠論壇－台北場 科技風暴金融高峰論壇 AI 人才年會 TO Highlight 直擊 COMPUTEX 2026 台北國際電腦展 透視 NVIDIA GTC 2026 穩定幣新秩序：科技供應鏈與全球新金融的世紀博弈 2026 AI Impacts 趨勢觀察報告 AI 機器人全球 7 大勢力關鍵報告：透視 Global 300+ 企業系統生態 資料治理 = AI 時代的戰略基礎設施 AI Agent 上工中──你準備好和 AI 當同事了嗎？ 你用的 AI 安全嗎？揭開資安攻擊的新破口 2025 AI 工具應用報告 AI 機器人產業生態分布圖：透視台灣 100 大領軍企業 2025 企業主管 AI 技能趨勢報告 機器人新同事已上工！人機互動最新模式 全新一週 Youtube Apple Podcast Spotify About Us 徵才 聯絡我們 最新文章 AI 人工智慧 AI 機器人 智慧製造 新零售 金融科技 資安 主題特展 2026 AI 智慧大工廠論壇——台中場 2026 科技金融論壇 AI 智慧大工廠論壇－高雄場 2026 AI Agent 新工作革命論壇 AI 智慧大工廠論壇－台南場 AI 機器人產業論壇 AI Ready 數據治理論壇 AI 智慧大工廠論壇－台北場 科技風暴金融高峰論壇 AI 人才年會 TO Highlight 直擊 COMPUTEX 2026 台北國際電腦展 透視 NVIDIA GTC 2026 穩定幣新秩序：科技供應鏈與全球新金融的世紀博弈 2026 AI Impacts 趨勢觀察報告 AI 機器人全球 7 大勢力關鍵報告：透視 Global 300+ 企業系統生態 資料治理 = AI 時代的戰略基礎設施 AI Agent 上工中──你準備好和 AI 當同事了嗎？ 你用的 AI 安全嗎？揭開資安攻擊的新破口 2025 AI 工具應用報告 AI 機器人產業生態分布圖：透視台灣 100 大領軍企業 2025 企業主管 AI 技能趨勢報告 機器人新同事已上工！人機互動最新模式 全新一週 Youtube Apple Podcast Spotify About Us 徵才 聯絡我們 Search 半導體/零組件 中國 IC 設計市佔已超車台灣！IDC 揭 2026 半導體十大趨勢：地緣政治如何重塑供應鏈？ 李昀蔚 2025-12-05 分享本文 IDC 在今（12/5）發布 2026 年全球半導體市場十大趨勢預測，預期 2026 年全球半導體市場將維持雙位數成長動能，年成長率達 11%。 「2026 年半導體產業將從爆發性復甦邁向穩健擴張的階段，」IDC 資深研究經理曾冠瑋表示，為了滿足指數級增長的運算需求，從 IC 設計、晶圓製造到先進封裝的整體價值鏈正處於高產能利用率狀態，供應鏈上下游的緊密協作，將是確保 AI 晶片順利量產與效能突破的關鍵。 針對 2026 年全球半導體市場，IDC 歸納十大趨勢。 趨勢一：2026 年半導體市場持續強勁，年成長率將達 11% 根據 IDC 預測，2028 年全球半導體市場規模將突破 1 兆美元，2030 年更將達到 1.2 兆美元。這股由 AI 驅動的投資週期，將抵銷部分總體經濟的不確定性。 不過，市場必須留意記憶體價格上漲的趨勢，若價格持續走高，可能影響 2026 下半年的市場動能。 趨勢二：AI 晶片需求旺盛，運算應用領域年增 18% 領跑市場 曾冠瑋分析，運算類別佔據半導體市場營收比重將持續攀升，預計 2025-2026 年市佔達 60%，其中 AI 伺服器核心晶片受惠於雲端訓練與邊緣推論需求的同步爆發，預計成長 32%。 相對地，車用（Automotive）與消費性（Consumer）市場因庫存調整與成本上升，展望較為保守。 趨勢三：亞太區 IC 設計年成長 11%，中國市佔擴大至 45% 確立領先 IDC 預估 2026 年亞太區 IC 設計市場將成長 11%，不過正面臨歷史性的結構轉變，因為中國 IC 設計產值已於 2025 年正式超越台灣，確立其市場領先地位。 IDC 預測，2026 年中國市佔率將進一步擴大至 45%，台灣則調整至 40%，此消長態勢源自中國在美方制裁下，仍積極發展本土 AI 晶片、高階手機處理器，加上虛擬貨幣與安防晶片需求強勁，因此帶動當地營收呈現倍數級成長。 趨勢四：先進製程帶動晶圓代工市場成長 20%，台積電市佔將達 73% 先進製程是 2026 年晶圓代工市場成長的核心引擎，預計推動整體產值成長 20%。隨著 AI 晶片算力需求增長，台積電預期市佔率將攀升至 73%，且維持 22-26% 的高成長率。 在資本支出方面，IDC 預估台積電將達 480 億至 500 億美元，主要用於擴充 3nm、2nm 產能及為 1.6nm 做準備。台積電 2nm 預計於 2025 年底達到月產能 8 萬片。三星與 Intel 則分別在韓國華城、美國德州及俄亥俄州積極布局，試圖在 2027-2028 年的 AI 晶片商機中搶佔一席之地。 趨勢五：成熟製程市況回溫，產能利用率將穩於八成 IDC 預估 2026 年平均產能利用率將穩定維持在 80% 以上，特別是中國晶圓廠，受惠於國產替代政策以及驅動 IC、PMIC 等訂單回流，產能利用率預期將保持在 90% 以上的高檔水位。至於台灣、韓國等非中國地區，則受惠於消費性電子復甦，利用率約維持在 80%。 趨勢六：地緣政治重塑半導體供應鏈，美中日晶圓代工產能擴張加速 全球半導體產能版圖正走向區域多元化，美國、中國與日本的晶圓產能年複合成長率（CAGR）預計將分別達到 9.8%、9.8% 與 10% 的新高水位。 中國面對美方先進製程設備禁令，將資源集中擴充受限較小的成熟製程，並加速扶植國產設備供應鏈，預計最快在 2028 年其「所有製程總產能」將超越台灣居全球之冠，並於 2029 年達到 37% 的全球市佔率。 在美國方面，台積電亞利桑那州廠進展順利，一廠（P1）已開始量產，二廠（P2A）預計於 2027 年上半年正式量產 3nm 製程，P2B 則鎖定 2027 年底至 2028 年加入 2nm 行列。 日本亦展現重返半導體強國決心，除台積電熊本廠外，日本政府也全力支持新創晶片製造商 Rapidus。雖然目前日本全球產能佔比僅約 2.5% 至 3%，但在先進製程的戰略地位將顯著提升。 趨勢七：2026 OSAT 市場成長 11%，台美 AI 晶片封裝比重持續攀升 地緣政治重塑全球封測版圖，預計 2026 年 OSAT 市場將成長 11%。中國在「半導體自主化」政策推動下，要求 IC 設計與晶圓製造盡量採用在地供應鏈，推動中國 OSAT 市佔率預計將從過去的 30% 攀升至 2029 年的 33%。 然而，高階 AI 晶片封裝仍由台灣與美國大廠掌握優勢。值得注意的是，若以包含晶圓代工廠先進封裝（Foundry-based packaging）的「封裝總市值」重新排名，受惠於 CoWoS 與 InFO 的高價值貢獻，台積電預計將在 2026 年超越傳統封測廠，成為全球封裝市值的實質龍頭。 趨勢八：CoWoS 先進封裝擴張持續，產能年增 72% 仍供不應求 先進封裝產能擴張將是 2026 年的主旋律。IDC 預測，台積電 2026 年底 CoWoS 月產能將來到 11 萬片，但面對 NVIDIA、AMD 等巨頭將主力晶片全數投入 3nm 製程且 100% 採用先進封裝，市場供需依然吃緊。 這股外溢效應將為 OSAT 廠帶來機會：日月光與矽品憑藉與台積電的長期合作，預計在 2025 年中旬開始有明顯的訂單放量；Intel 雖積極推廣封裝代工，但考量玻璃基板與高階封裝的良率需達 90% 以上才具經濟效益，預期要到 2027 年才能在 CSP 自研晶片市場中見到顯著貢獻。 趨勢九：雲端軍備競賽白熱化，AI 伺服器加速器製造市場暴增 78% AI 加速器市場預計迎來爆發性成長。受惠於 Google TPU、AWS Trainium 等 CSP 自研晶片需求，IDC 預估 2026 年 ASIC 市場年增率將高達 173%。 長期而言，為了優化 TCO，CSP 與模型開發商將持續擴大 ASIC 採用比例，推動 ASIC 在 2024-2029 年的年均複合成長率達到 67%。然而，GPU 並不會因此失勢，因為隨著「影像生成」的需求大增，未來的 AI 電影與即時影像運算需要極具彈性的通用算力，這將是 GPU 長期難以被取代的護城河，也讓 GPU 的年均複合成長率仍維持 56% 的高成長動能。 趨勢十：Foundry、non-memory IDM、OSAT、Photomask 產業同步成長，Foundry2.0市 場將成長 14% 針對市場擔憂的「AI 泡沫化」，IDC 認為 2026 年發生機率偏低，主因在於 AI 基礎建設並非無限制擴張，而是受到「電力供應」與「能源網架構」的物理限制。CSP 業者無法在缺乏電力配套下無限採購晶片，這種物理上的「調節閥」反而讓半導體出貨維持在相對健康、理性的成長軌道，避免了過度庫存堆積導致的瞬間崩盤。 2026 年全球半導體產業將延續雙位數成長，從爆發期邁入「穩健擴張」階段。在這段過程中，地緣政治帶來的供應鏈重組、中國產能的強勢崛起，以及 AI 基礎建設是否會因電力瓶頸而調整節奏，將是決定產業走向的關鍵變數。 議題標籤 熱門文章 追蹤我們 追蹤 Google News TO 會員電子報 還在靠社群媒體追新聞嗎？馬上訂閱電子報，最新科技趨勢、熱門活動不漏接！ 點我訂閱 感謝訂閱！請隨時注意信箱的最新資訊 訂閱發生異常，請稍候再試或聯繫客服信箱 [email protected] 訂閱即同意 個資蒐集聲明 ，並允許 Fusionmedium 使用您的個人資料，及接收不定期活動資訊。 更多分類文章 出口暴增 75% 卻僅增千個職缺：南韓半導體高中爆紅，高薪職涯入口背後藏什麼風險？ 李昀蔚 2026-06-29 近 1,000 億電晶體塞進指甲大小晶片：IBM 0.7 奈米技術亮相，靠 3D 堆疊超車先進製程競賽 李昀蔚 2026-06-26 推論成本砍半、9 個月做出來：OpenAI 首款自研 AI 晶片 Jalapeño 想換到什麼？ 廖紹伶 2026-06-25 高通揭 AI 資料中心新藍圖：Meta 買單、Modular 補上軟體層，同步洽談 ByteDance 客製晶片 李昀蔚 2026-06-25 隱私條款 資訊安全政策 聯絡我們 活力徵才 生活報橘 公民報橘 隱私條款 資訊安全政策 聯絡我們 活力徵才 生活報橘 公民報橘 Facebook Youtube Linkedin Instagram Copyright © 2026 流線傳媒股份有限公司 All rights reserved. 為提供您更好的網站服務，本網站會使用 Cookies 及其他相關技術優化用戶體驗，繼續瀏覽本網站即表示您同意上述聲明 了解隱私權政策 同意並關閉視窗 Manage consent Close Privacy Overview This website uses cookies to improve your experience while you navigate through the website. Out of these, the cookies that are categorized as necessary are stored on your browser as they are essential for the working of basic functionalities of the website. We also use third-party cookies that help us analyze and understand how you use this website. These cookies will be stored in your browser only with your consent. You also have the option to opt-out of these cookies. But opting out of some of these cookies may affect your browsing experience. Necessary Necessary Always Enabled Necessary cookies are absolutely essential for the website to function properly. These cookies ensure basic functionalities and security features of the website, anonymously. Cookie Duration Description cookielawinfo-checkbox-analytics 11 months This cookie is set by GDPR Cookie Consent plugin. The cookie is used to store the user consent for the cookies in the category "Analytics". cookielawinfo-checkbox-functional 11 months The cookie is set by GDPR cookie consent to record the user consent for the cookies in the category "Functional". cookielawinfo-checkbox-necessary 11 months This cookie is set by GDPR Cookie Consent plugin. The cookies is used to store the user consent for the cookies in the category "Necessary". cookielawinfo-checkbox-others 11 months This cookie is set by GDPR Cookie Consent plugin. The cookie is used to store the user consent for the cookies in the category "Other. cookielawinfo-checkbox-performance 11 months This cookie is set by GDPR Cookie Consent plugin. The cookie is used to store the user consent for the cookies in the category "Performance". viewed_cookie_policy 11 months The cookie is set by the GDPR Cookie Consent plugin and is used to store whether or not user has consented to the use of cookies. It does not store any personal data. Functional Functional Functional cookies help to perform certain functionalities like sharing the content of the website on social media platforms, collect feedbacks, and other third-party features. Performance Performance Performance cookies are used to understand and analyze the key performance indexes of the website which helps in delivering a better user experience for the visitors. Analytics Analytics Analytical cookies are used to understand how visitors interact with the website. These cookies help provide information on metrics the number of visitors, bounce rate, traffic source, etc. Advertisement Advertisement Advertisement cookies are used to provide visitors with relevant ads and marketing campaigns. These cookies track visitors across websites and collect information to provide customized ads. Others Others Other uncategorized cookies are those that are being analyzed and have not been classified into a category as yet. SAVE &amp; ACCEPT</t>
+          <t>全台首家IC設計獲Arm注資 通寶半導體Q4擬申請IPO - 日報 - 工商時報 前往主要內容 會員 會員中心 登出 電子報 影音特區 讀報區 首頁 即時 開闔次選單 即時首頁 要聞 證券 金融 稅法 產業 房市 國際 兩岸 科技 生活 要聞 開闔次選單 要聞首頁 政經焦點 總經趨勢 稅務法務 綜合要聞 前瞻一周 證券 開闔次選單 證券首頁 上市櫃 陸港股市 國際股市 產業焦點 期貨 權證 亮點個股 專家看盤 台股逐洞賽 重要指數 重大訊息 財經行事曆 金融 開闔次選單 金融首頁 金融話題 外匯市場 牌告匯率 金融科技 銀行動態 保險脈動 數據觀測 金融人物 理財 開闔次選單 理財首頁 理財新訊 基金 ETF 生活消費 信用卡 退休理財 統一發票 產業 開闔次選單 產業首頁 半導體 科技動態 綜合產業 生技醫療 CEO專訪 職場達人 房市 開闔次選單 房市首頁 房市焦點 區域亮點 名家攻略 居住安全 觀點評論 市場動態 國際 開闔次選單 國際首頁 全球政經 全球市場 議題觀點 國際產業 Global Scan 全球財經周報 大宗商品行情 兩岸 開闔次選單 兩岸首頁 政情動向 兩岸焦點 大陸財經 大陸產業 China Scan 陸港市場 觀點分析 言論 開闔次選單 言論首頁 社論 總經經濟 產業脈動 國際經貿 企業管理 社會觀察 奇思妙想 作者群 樂活 開闔次選單 樂活首頁 美食饗宴 旅遊休閒 生活風格 愛車天地 養生保健 時尚消費 藝文特區 書房 開闔次選單 書房首頁 書房嚴選 名人書單 好書推薦 英文進修 雜誌精選 年度好書 專題 開闔次選單 專題首頁 上市櫃6月營收 大陸經濟新局 台灣半導體風雲 上市櫃Q1營收 生技ESG革命 新世代夯話題 財經人物專訪 商情 開闔次選單 商情首頁 智慧機械 大健康 金融理財 房市建材 科技綠能 消費時尚 產學管顧 社企公益 活動 開闔次選單 活動首頁 台南機械展 台中AI展 台灣權王 服務業大評鑑 數位金融獎 ETF論壇 中華電信論壇 多元信託 期貨與選擇權 永續校園徵影 搜尋 首頁 日報 工商時報 全台首家IC設計獲Arm注資 通寶半導體Q4擬申請IPO 全台首家IC設計獲Arm注資 通寶半導體Q4擬申請IPO 2026.03.04 03:00 工商時報 呂雪彗 通寶半導體 安謀 智原科技 IC設計 Arm注資 通寶半導體公司董事長暨執行長沈軾榮表示，通寶半導體為全台唯一獲Arm投資的 IC 設計公司。圖／通寶半導體提供 切換文字大小 複製文章連結 分享至臉書 以Line分享 加入Google來源 參與討論 友善列印 已將目前網頁的網址複製到您的剪貼簿！ 通寶半導體設計公司簡介 台灣IC設計領域傳出國際策略投資合作捷報，通寶半導體（QBit Semiconductor）公司3日宣布，已完成B輪募資，並獲全球半導體架構大廠安謀公司（Arm Limited）參與投資，成為目前全台唯一獲得Arm投資的IC設計公司。 安謀現成為通寶十大股東之一，至於安謀持股比例及金額，4月下旬召開法說會可望對外說明，未來通寶擬計畫跨足無人機及機器人市場。 通寶半導體同時宣布，隨著募資完成營運規模擴大，計畫於今年第四季向臺灣證券交易所申請IPO上市，進一步邁向資本市場新里程碑，實際時程仍須視主管機關核准及市場狀況而定。 通寶半導體為專攻多功能列印機及事務機系統晶片的IC設計公司，其客戶主要市場遍及美國、日本、中國跟台灣。除Arm參與投資外，據悉，通寶半導體在A輪募資時，台灣政府法人機構持有通寶半導體約6％股權，包括國發基金持股2.7％，以及台肥、工研院等公股事業合計持股比例約6％，還有智原科技等半導體產業加入，整體A輪投資人持股比例約為通寶已發行股權10％。 對於這項注資，Arm全球執行副總裁暨商務長Will Abbey表示，透過與通寶的合作，可以結合先進影像處理、控制與安全能力，以支持列印及影像市場的創新。此類合作展現Arm更廣泛的策略，亦即推動具差異化的解決方案，從高效能系統延伸至更具成本效益的裝置，同時為各類產品建立成長基礎。 通寶半導體創辦人暨執行長沈軾榮也表示，很榮幸成為獲得Arm唯一投資的台灣半導體設計公司，未來通寶將持續深化在印表機影像市場的布局，並拓展至更廣泛的影像相關應用領域。 將工商時報加入Google偏好來源 相關新聞 大盤震盪 拉回擇優布局台股ETF 美股走勢分歧 晶片股台積電ADR持續承壓 《基金》6檔國內半導體ETF夯 受益人數突破43.8萬人創新高 您可能感興趣的話題 留言討論 熱門日報新聞 more 台股聞到「洗籌碼、殺斷頭」的味道！「四貸同堂」族哀嚎 指數何時反彈名師劃重點 大摩喊記憶體供需缺口未收斂 Q3漲勢未歇 南亞科、華邦電、旺宏有戲唱 台股融資大退散 短線反彈契機已到？專家估8月有望戰季線 公股逢低撿便宜 重倉大型權值電子股 買超前十強3檔ETF卡位 竟是同一家 金管會出手 嚴管四貸同堂 專題推薦 返回頁首 網站選單開關 顏色主題切換 LOADING 熱門新聞 TOP 3 more 台股崩盤不敢買？孫慶龍股災做對一件事 52萬竟變成8千萬 未來十年最看好這2檔 台股聞到「洗籌碼、殺斷頭」的味道！「四貸同堂」族哀嚎 指數何時反彈名師劃重點 期貨最新報價7／29期交所夜盤行情 本網頁已閒置超過3分鐘。請點撃框外背景，或右側關閉按鈕(X)，即可回到網頁。 關閉 關閉廣告</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -633,6 +673,12 @@
           <t>Success</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>07bad44a832864eb1272dcab2762e4e86697da67fbc05a5934fb00417467b485</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -642,23 +688,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>瑞昱半導體網通音訊IC領先 全球電子產品仰賴台灣實力 - 財經新聞 - PChome Online 新聞</t>
+          <t>ICTGC競賽首登矽谷 進軍CES廣邀全球IC新創鏈結臺灣半導體生態鏈 - tca.org.tw</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://news.pchome.com.tw/finance/sunmedia/20260330/index-77484256473773329003.html</t>
+          <t>https://www.tca.org.tw/news_detail.php?n=2454&amp;t=h</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mon, 30 Mar 2026 07:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>Fri, 02 Jan 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>tca.org.tw</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>瑞昱半導體網通音訊IC領先 全球電子產品仰賴台灣實力 - 財經新聞 - PChome Online 新聞 股市 PChome 合作媒體 說明 (登入) 首頁 專題 政治 社會 財經 科技 國際 職場 運勢 星座 健康 娛樂 體育 生活 上班族 消費 旅遊 雜誌 汽車 政府 大陸 快訊 財部：台版肥咖CRS申報 筆數金額齊增 中國實施跨國鎮壓 總統：與美強化國防合作 友達第2季每股賺0.18元 投入新技術活化資產 熊本強震見台日情誼 台人送鳳梨酥感謝日人伸援手 # 農民曆 # 今日運勢 # 金融股配息 今日天氣 空氣品質 今日運勢 樂透開獎 彰化縣 一週天氣預報(07/30 05:00發布) 臺北市 33° 32° / 34° 週五 34° / 28° 週六 35° / 28° 農曆 丙午年六月十七 宜: 祭祀,求職應聘 忌: 祈福,拜神求子 更多 獅子座 工作運 更多 【幸運色】 淡粉 【小人】 獅子 2026-07-29 樂透彩中獎號碼 更多 大樂透 8 19 24 26 32 43 47 39樂合彩 5 14 32 33 36 115年 05~06月 統一發票中獎號碼 詳情 2026-07-30 空氣品質指標 更多 臺北市士林 普通 AQI : 64 PM2.5 : 15 臺北市松山 普通 AQI : 62 PM2.5 : 14 最新 google熱搜-新竹氣爆 熱門 名人被打臉事件 HOT 人氣新聞 人氣財經新聞 女性失智症盛行率比男性高！醫揭4可能原因 更年期後應警惕 杜拜國際金融中心在 2026 年上半年取得引領業界的佳績，鞏固其於中東、非洲及南亞地區環球金融領域的領先地位 熊本7.1強震後餘震不斷 熊本市西區測得最大震度4 Google個人AI代理 Gemini Spark將在台開放 立委曝綠營幹部親屬赴陸失聯 陸委會：循機制了解 強震後熊本縣內增至14死 其中2人因地震「直接死亡」 熊本7.1強震後餘震不斷 又再兩起有感地震 Lockton 正式成立全球數據中心及數字基礎設施業務部門 曾獲2014世足金手套 德國門神諾伊爾可能下季退休 老針車翻轉新活力！彰化榮家8旬嬤用古董裁縫機實踐自主復能 監院指兩岸教育交流失衡 陸委會：強化中共統戰識讀 紅十字會設熊本地震捐款專區 首波撥1千萬日圓馳援 FIFA擬成立子公司賣股權 歐足總砲轟、亞足聯表失望 2026臺南夏日音樂節-將軍吼 本周六日強勢來襲！ 周邊交通與各項管制措施懶人包全攻略 央廣推新住民共創平台 用AI突破語言隔閡 《鐵拳教育》金武烈首爾見面會秒殺！海外首站9月獻台灣 高國輝肯定悍將上半季撐到最後 打擊找跳出的契機 韓職王彥程連兩場優質先發 奪個人本季第9勝 王順和重感冒大巨蛋開轟 打擊更有力添信心 熊本強震停電斷水又遇酷暑 政府發首批移動式冷氣 【台股盤後】台股多空激戰震盪逾1700點 終場下跌105點失守4萬點 川寶布局TGV 完成成孔後電鍍金屬化設備試機 台股多空激戰震盪逾1700點 終場下跌105點失守4萬點 AI基建掀物流商機 中菲行：高價值空運快速成長 熊本強震衝擊九州製造業 豐田、Sony等持續停工檢查 台北市新案房價抗跌 信義區每坪226萬實登居冠 越南土地革命篇－與鹹水共生 稻蝦輪作逆境求生 AI基建掀物流商機 中菲行：高價值空運快速成長 8月台股期指跌58點 三大法人賣超台股508.73億元 星巴克同店銷售額連4季成長 上調全年財務展望 越南現象篇－九龍江星光不浪漫 海水倒灌成農民夢魘 8月電子期跌 金融期漲 日月光投控第2季獲利同期新高 先進封測營收優預期 夏慕尼哈根達斯聯名推「情人節套餐」 台北市新案房價抗跌 信義區每坪226萬實登居冠 台股4萬點失守！台積電撐盤收2205元 台股震盪 童子賢：別盯著綠紅聖誕樹、AI長期不泡沫 王品集團夏慕尼加速展店 目標明年底達21店 台股震盪 童子賢：別盯著綠紅聖誕樹、AI長期不泡沫 NEW 最新 新聞 最新影音新聞 友達第2季每股賺0.18元 投入新技術活化資產 財部：台版肥咖CRS申報 筆數金額齊增 苦茶油驗出苯駢芘超標！永豐餘生技退費方式 韓國7月出口額估年增59% 晶片熱潮支撐動能不減 央行理事：若台股降溫 憂資金由股轉房推升房價 央行理事：若台股降溫 憂資金由股轉房推升房價 外資賣超483億元 調節元大台灣50逾6萬張居冠 韓國7月出口額估年增59% 晶片熱潮支撐動能不減 阿里山林鐵x台啤5年 開發第五種品牌雙聯名釀造出二萬天晴新品 日月光：目前封測製程重心在台灣 待時機擴展美國 經濟部、勞動部共審 強迫勞動貨品機制公布 台達電今年資本支出上看700億元 擬新增海外營運據點 台達電上半年獲利創高 鄭平：下半年成長沒有太大問題 台灣大有望併凱擘？林之晨：勢必會評估 台達電資本支出上看700億 擬新增海外營運據點 停進巴紐天然氣 經長：現貨可調整、長約仍需履約 市調：明年DRAM供給續吃緊 NAND Flash轉寬鬆 日月光投控資本支出估105億美元 先進封測營收明年再翻倍 日月光資本支出估105億美元 先進封測營收明年再翻倍 台積電洩密案 2前工程師各判10年、6年定讞 苦茶油驗出苯駢芘超標！永豐餘生技退費方式 韓國7月出口額估年增59% 晶片熱潮支撐動能不減 永慶房屋首年72萬收入保障 新鮮人藍婉云零經驗拚出百萬年薪 央行理事：若台股降溫 憂資金由股轉房推升房價 蔣萬安為何提倒閣？他曝3關鍵：當然衝第一 2026咖啡產業職涯論壇8月6日中山堂登場！跨域結合AI與品牌經營 即日起免費報名 豪雨災害農損現金救助 農業處呼籲屏東縣各鄉鎮市公所加速完成初勘 兒少柳營體驗多元學習！以射擊培養專注及自律 中國實施跨國鎮壓 總統：與美強化國防合作 屏東縣衛生局守護青少年健康！全面禁電子煙、未滿20歲嚴禁購菸 夏莉絲案涉案行為人終身不得擔任教保人員、廢照重罰235萬！北市教育局籲停止政治操作：勿抹煞基層努力 阿里山林鐵x台啤5年 開發第五種品牌雙聯名釀造出二萬天晴新品 吳玉琴返鄉參選鹿草鄉長 盼打造健康家園 影／不讓貧窮限制夢想 彰化家扶獎助學金點亮孩子未來 台積電核心關鍵技術內鬼案 主嫌陳力銘判刑10年定讞 梁詠琪現場驚喜「催生」Lulu 許曦文曝媽媽小S吃醋內幕 血跡一路通往森林！7公尺巨蟒肚子鼓鼓 剖開全村嚇壞 融資租賃業納金保法 163件申訴2大類為主 國海院首度發布MDImageNet高品質海廢資料集 鄭淑分體恤高齢長輩 太保市公所x監理所、衛生所推動高齡換照一站式服務 新聞 財經 2026-03-30 11:49:24 新聞來源 : 商傳媒 回應 瑞昱半導體網通音訊IC領先 全球電子產品仰賴台灣實力 圖／本報資料庫 商傳媒 ｜何映辰／台北報導 台灣積體電路設計大廠瑞昱半導體（Realtek Semiconductor Corp）在全球網通與音訊積體電路（IC）市場扮演關鍵角色，其技術實力驅動著個人電腦與消費性電子產品的發展，並連結台灣IC設計產業在全球供應鏈中的重要地位。該公司以無晶圓廠（fabless）模式運作，專精於設計與行銷通訊、多媒體及周邊裝置所需的各類晶片。 瑞昱半導體的產品線多元，涵蓋乙太網路控制器、Wi-Fi解決方案、音訊編解碼器及高畫質多媒體晶片。這些高效能晶片支援數據傳輸、音訊處理與多媒體操控，廣泛應用於全球主機板、筆記型電腦、路由器及智慧裝置中。華碩（Asus）、技嘉（Gigabyte）、微星（MSI）等主要OEM客戶皆將瑞昱的解決方案整合至其產品。在乙太網路晶片領域，瑞昱提供支援 Gigabit、2.5G及5G速度的區域網路（LAN）介面卡，在PC主機板與網通設備市場佔據主導地位。此外，其ALC系列音訊編解碼器則嵌入在數百萬台筆記型電腦與桌上型電腦中，負責處理高傳真音效。 面對英特爾（Intel）、博通（Broadcom）及聯發科（MediaTek）等巨頭的競爭，瑞昱透過快速創新與穩固的OEM客戶關係，在成本效益高且出貨量龐大的消費性及PC市場取得競爭優勢。該公司專注於乙太網路實體層（Ethernet PHY）與音訊數位類比轉換器（DAC）等利基市場，並在這些類別中掌握顯著市佔。北極星市場情報（NorthStar Market Insights）資深財經編輯艾蕾娜·瓦茲奎茲博士（Dr. Elena Vasquez）曾表示，瑞昱半導體將可靠的晶片設計與物聯網（IoT）、5G及消費性電子產品的持久需求連結起來。 當前市場對瑞昱通訊IC的需求，正受惠於5G基礎設施、邊緣運算及物聯網裝置的擴張，而居家及辦公網路升級也持續推動乙太網路晶片的銷售。此外，8K串流與AI工作負載所需的頻寬，亦刺激對高速區域網路解決方案的需求。在供應鏈方面，瑞昱半導體仰賴台灣半導體產業聚落的支援，包括與台積電（TSMC）等晶圓代工夥伴的合作。對於尋求亞洲科技領袖投資機會的北美投資者而言，瑞昱半導體提供了一個穩定且具代表性的選項，能有效平衡以美國為中心的晶片製造商。 然而，瑞昱也面臨多重風險。其中，圍繞台灣的地緣政治緊張局勢，因其地理位置及對區域晶圓代工廠的依賴，被視為主要潛在風險。激烈的市場競爭亦對利潤造成壓力，尤其當競爭對手在高端市場加速創新時。半導體產業的週期性需求則導致營收波動，PC出貨量放緩會直接影響其業績。瑞昱必須持續投入研發，才能在中階市場維持其成本領先地位。該公司目前正積極投入Wi-Fi 7與PCIe Gen5技術的採用進程。 新聞關鍵字： 半導體 、 瑞昱 、 5G 、 AI 、 IC設計 、 intel 、 代工 、 台積電 、 微星 、 技嘉 記者：商傳媒 更多財經新聞 » 延伸閱讀 微星電競主機Woot狂砍900美元 搶攻暑期玩家市場 (商傳媒2026-07-29 09:26:14) MSI 2026 夏季健檢開跑 筆電、掌機等 6 六項產品皆提供免費健檢服務 (巴哈姆特 GNN2026-07-27 18:46:41) 慶祝品牌 40 週年 MSI 微星推出互動體驗小遊戲「超級組裝挑戰賽」 (巴哈姆特 GNN2026-07-27 18:46:23) 微星科技推出《玩具總動員》「蛋頭先生造型顯卡支撐架」 即日起限量開賣 (巴哈姆特 GNN2026-07-24 18:11:08) 微星推第六代 AMD EPYC 伺服器 搶攻 AI 與資料中心市場 (商傳媒2026-07-24 10:48:52) 超微AI大會一次看 Helios機櫃進入量產台廠受惠 (中央社2026-07-24 06:57:06) 聯手搶攻 AI 商機！微星 與 資策會 展開策略合作 共推 AI PC 與 Edge AI 應用 加速企業智慧化升級 (警政時報2026-07-23 13:09:46) 三星 OLED 電競螢幕殺出 300 美元震撼價 搶攻平價遊戲市場 (商傳媒2026-07-21 09:33:58) 微星科技與資策會展開策略合作 共推 AI PC 與 Edge AI 應用 加速企業智慧化升級 (威傳媒2026-07-16 21:44:24) 微星：RTX Spark高階款供不應求 首批貨接近完售 (中央商情2026-07-16 20:00:30) 最新財經新聞 友達第2季每股賺0.18元 投入新技術活化資產 (中央社 2026-07-30 17:38:52) 財部：台版肥咖CRS申報 筆數金額齊增 (中央社 2026-07-30 17:37:50) 苦茶油驗出苯駢芘超標！永豐餘生技退費方式 (今日新聞 2026-07-30 17:36:19) 韓國7月出口額估年增59% 晶片熱潮支撐動能不減 (中央商情 2026-07-30 17:35:48) 央行理事：若台股降溫 憂資金由股轉房推升房價 (中央商情 2026-07-30 17:34:25) 央行理事：若台股降溫 憂資金由股轉房推升房價 (中央社 2026-07-30 17:32:46) 外資賣超483億元 調節元大台灣50逾6萬張居冠 (中央社 2026-07-30 17:31:44) 韓國7月出口額估年增59% 晶片熱潮支撐動能不減 (中央社 2026-07-30 17:30:40) 阿里山林鐵x台啤5年 開發第五種品牌雙聯名釀造出二萬天晴新品 (台灣好報 2026-07-30 17:25:20) 日月光：目前封測製程重心在台灣 待時機擴展美國 (中央社 2026-07-30 17:18:22) 經濟部、勞動部共審 強迫勞動貨品機制公布 (今日新聞 2026-07-30 17:12:40) 台達電今年資本支出上看700億元 擬新增海外營運據點 (中央商情 2026-07-30 17:08:39) 台達電上半年獲利創高 鄭平：下半年成長沒有太大問題 (中央商情 2026-07-30 17:08:37) 台灣大有望併凱擘？林之晨：勢必會評估 (中央社 2026-07-30 17:08:13) 台達電資本支出上看700億 擬新增海外營運據點 (中央社 2026-07-30 17:07:09) 停進巴紐天然氣 經長：現貨可調整、長約仍需履約 (中央社 2026-07-30 16:47:29) 市調：明年DRAM供給續吃緊 NAND Flash轉寬鬆 (中央社 2026-07-30 16:38:22) 日月光投控資本支出估105億美元 先進封測營收明年再翻倍 (中央商情 2026-07-30 16:29:57) 日月光資本支出估105億美元 先進封測營收明年再翻倍 (中央社 2026-07-30 16:29:09) 台積電洩密案 2前工程師各判10年、6年定讞 (中央商情 2026-07-30 16:16:33) 人氣財經新聞 【台股盤後】台股多空激戰震盪逾1700點 終場下跌105點失守4萬點 (中央商情) 川寶布局TGV 完成成孔後電鍍金屬化設備試機 (中央商情) 台股多空激戰震盪逾1700點 終場下跌105點失守4萬點 (中央社) AI基建掀物流商機 中菲行：高價值空運快速成長 (中央商情) 熊本強震衝擊九州製造業 豐田、Sony等持續停工檢查 (中央社) 台北市新案房價抗跌 信義區每坪226萬實登居冠 (中央商情) 越南土地革命篇－與鹹水共生 稻蝦輪作逆境求生 (中央社) AI基建掀物流商機 中菲行：高價值空運快速成長 (中央社) 8月台股期指跌58點 (中央社) 三大法人賣超台股508.73億元 (中央社) 星巴克同店銷售額連4季成長 上調全年財務展望 (中央社) 越南現象篇－九龍江星光不浪漫 海水倒灌成農民夢魘 (中央社) 8月電子期跌 金融期漲 (中央社) 日月光投控第2季獲利同期新高 先進封測營收優預期 (中央商情) 夏慕尼哈根達斯聯名推「情人節套餐」 (今日新聞) 台北市新案房價抗跌 信義區每坪226萬實登居冠 (中央社) 台股4萬點失守！台積電撐盤收2205元 (今日新聞) 台股震盪 童子賢：別盯著綠紅聖誕樹、AI長期不泡沫 (中央社) 王品集團夏慕尼加速展店 目標明年底達21店 (中央社) 台股震盪 童子賢：別盯著綠紅聖誕樹、AI長期不泡沫 (中央商情) 熊本強震 中信銀與東京之星銀捐5千萬日圓 (今日新聞) 日企財報亮眼率日經指數收漲 SK海力士拖累韓股收低 (中央社) 熊本6.8地震 經長：主要受影響半導體業 (今日新聞) 日月光投控資本支出估105億美元 先進封測營收明年再翻倍 (中央商情) 台灣大種福電滿10年 綠能公益收入估破億元 (中央社) 轉虧為盈！友達Q2賺13.4億元 EPS 0.18元 (今日新聞) 日月光第2季獲利210億同期新高 先進封測營收超預期 (中央社) 星巴克同店銷售額連4季成長 上調全年財務展望 (中央商情) 日月光資本支出估105億美元 先進封測營收明年再翻倍 (中央社) 美國消費者信用分數創一年新高 信用卡拖欠率趨緩 (商傳媒) 限制強迫勞動貨品輸入 龔明鑫：審定會由經部勞部共審 (中央商情) 台積電洩密案 2前工程師各判10年、6年定讞 (中央商情) 肯塔基州西部將建AI資料中心 獲逾千億美元私人投資 (商傳媒) 新台幣貶8.8分 收32.454元 (中央商情) 市調：明年DRAM供給續吃緊 NAND Flash轉寬鬆 (中央社) 高通估Q4獲利不如預期 看好AI業務填補蘋果營收下滑 (中央商情) 停進巴紐天然氣 經長：現貨可調整、長約仍需履約 (中央社) 熊本強震衝擊九州製造業 豐田、Sony等持續停工檢查 (中央商情) 限制強迫勞動貨品輸入 龔明鑫：審定會由經部勞部共審 (中央社) 新台幣貶8.8分 收32.454元 (中央社) IBM 報告：AI 驅動網路攻擊暴增 56% 數據外洩成本飆近 500 萬美元 (商傳媒) 助熊本災後重建 中國信託銀行與日本東京之星銀行捐款5000萬日圓 (上報) 華爾街力挺加密永續合約 美國監管立場現轉機 (商傳媒) 台股收跌105點失守4萬點大關 台積電終場2205元、國巨收跌停 (上報) 台達電資本支出上看700億 擬新增海外營運據點 (中央社) 美晶片法注資格芯 3 億美元 強化 AI 晶片光子互連技術 (商傳媒) 台灣大有望併凱擘？林之晨：勢必會評估 (中央社) 歐元走軟助攻美元投資者 居留權計畫成本最高省6萬美元 (商傳媒) 菲國博弈營收受監管與通膨夾擊 今年恐陷7%衰退 (商傳媒) 台新新光金攜手台新銀 捐3000萬日圓馳援日本熊本震災重建 (品觀點) 台達電上半年獲利創高 鄭平：下半年成長沒有太大問題 (中央商情) 輝達擴大AI與先進技術佈局 聖荷西租賃新廠房搶進研發 (商傳媒) 台達電今年資本支出上看700億元 擬新增海外營運據點 (中央商情) 烏克蘭煉油廠攻擊戰術轉變 美法情報助鎖定俄關鍵設施 (商傳媒) 日月光：目前封測製程重心在台灣 待時機擴展美國 (中央社) 從企業經營看房市政策！百夫長集團主席陳志彬博士解析限貸令 (三星傳媒) 經濟部、勞動部共審 強迫勞動貨品機制公布 (今日新聞) 中信銀與東京之星銀行捐5000萬日圓 盼助熊本受災民眾重建家園 (品觀點) 韓國7月出口額估年增59% 晶片熱潮支撐動能不減 (中央社) 阿里山林鐵x台啤5年 開發第五種品牌雙聯名釀造出二萬天晴新品 (台灣好報) 外資賣超483億元 調節元大台灣50逾6萬張居冠 (中央社) 永豐金證券邀巴逆逆、前外資分析師程正樺開講 談AI泡沫迷思與反指標陷阱 (品觀點) 洛克希德馬丁擴廠增700職位 強化美國軍備產能 (商傳媒) 日股7月跌逾11％！法人看好抵禦波動風險 點名「NIPPON」結構性優勢 (品觀點) 央行理事：若台股降溫 憂資金由股轉房推升房價 (中央社) 財部：台版肥咖CRS申報 筆數金額齊增 (中央社) 苦茶油驗出苯駢芘超標！永豐餘生技退費方式 (今日新聞) 友達第2季每股賺0.18元 投入新技術活化資產 (中央社) 國泰世華銀：油價風險加劇美國聯準會9月升息壓力 (中央商情) 台股反彈無力收跌105點 失守4萬點大關 (中央商情) 日經：SpaceX供應鏈去中 排除中國籍員工設備 (中央商情) AI晶片需求強勁 三星電子Q2營利暴增19倍創歷史新高 (中央商情) 三星電子財報報喜 激勵韓股Kospi指數盤中強彈逾5% (中央商情) 日本2027年4月起食品消費稅首次降至1% 為期2年 (中央商情) 韓國電信KT遭駭致未經用戶授權小額支付 遭罰12億元 (中央商情) 開源基金會3年投入3億元 提升台灣供應鏈影響力 (中央商情) 美國限制先進機器人進口 北京稱將反制 (中央商情) 北市攜手美國20州辦商機媒合會 助台美經貿發展 (中央商情) 男女平均所得差距 財政部統計2024年縮小至1.54倍 (中央商情) 英國宣布3636億核潛艦計畫 支持國防與青年就業 (中央商情) 權值股領軍 台股盤中強彈逾千點觸及41000點 (中央社) 緯創布局AI基建 台南算力中心估2027年首季建置完成 (中央社) 研調：熊本地震JASM停機 台積電第3季營收影響應有限 (中央社) 索尼擬收購騰龍 相機鏡頭市場可能洗牌 (中央社) AI晶片需求強勁 三星電子Q2營利暴增19倍創歷史新高 (中央社) AI投資隱憂衝擊亞股 聯準會按兵不動增利率不確定性 (中央社) 高通估Q4獲利不如預期 看好AI業務填補蘋果營收下滑 (中央社) 美國限制先進機器人進口 北京稱將反制 (中央社) 男女平均所得差距 財政部統計2024年縮小至1.54倍 (中央社) 三星電子財報報喜 激勵韓股Kospi指數盤中強彈逾5% (中央社) 台股跌105.88點 (中央社) 國泰世華銀：油價風險加劇美國聯準會9月升息壓力 (中央社) 開源基金會3年投入3億元 提升台灣供應鏈影響力 (中央社) 索尼擬收購騰龍 相機鏡頭市場可能洗牌 (中央商情) Meta 重押 AI 拖累股價大跌 投資人憂回報不如預期 (商傳媒) 台股反彈無力收跌105點 失守4萬點大關 (中央社) 美利率凍！美元跌後反彈 台幣早盤貶快1角 (今日新聞) 美禁國外機器人進口 業者看台廠供應鏈具3大優勢受惠 (中央社) 看台股暴跌 國安基金操盤手：若失序會處理 (今日新聞) 援助熊本災後重建 台新新光金捐3千萬日圓 (今日新聞) 新台幣午盤貶9分 暫收32.456元 (中央社) 【台股盤中】權值股領軍 台股殺完融資後強彈逾千點 (中央商情) momo富昇物流徵百名司機 績優年薪上看百萬元 (中央社) 韓國金融界推4措施應對槓桿ETF 分散再平衡交易 (中央社) AI新十大建設 教育、醫療、司法導入成果 (今日新聞) AI投資隱憂衝擊亞股 聯準會按兵不動增利率不確定性 (中央商情) 紐約聯準銀行：美國高評級公司債市場運作失能達近三年高點 (商傳媒) 慧榮：下半年持續強勁成長 全年營收估增逾100% (中央商情) 台股歷次盤中跌逾2千點 法人：後市表現佳 (今日新聞) 韓國金融界推4措施應對槓桿ETF 分散再平衡交易 (中央商情) 慧榮：下半年持續強勁成長 全年營收估增逾100% (中央社) 緯創布局AI基建 台南算力中心估2027年首季建置完成 (中央商情) 美商藝電執行長年薪3865萬美元 員工平均薪資305倍引議論 (商傳媒) Plaid 推出創新 AI 模型 深層解讀用戶金融軌跡 (商傳媒) 美眾院通過國防法案引爭議 美以軍事合作非「合併」 (商傳媒) 聯準會決策在即 美元面臨下行風險 豐業銀行示警 (商傳媒) 方舟投資連兩日加碼加密概念股 押寶 CLARITY Act 立法利多 (商傳媒) 萊茵河乾旱水位創低 歐洲油化品供應鏈陷停擺危機 (商傳媒) 美國3億美元注資格芯 劍指矽光子技術發展 (商傳媒) 高通膨與中東戰火施壓 美國聯準會連續五次維持利率不變 (商傳媒) 美國利率連5凍 聯準會主席華許：沒有降通膨的魔法棒！ (品觀點) Rhodium Group：美2030年代新增發電量 政策左右再生能源或天然氣 (商傳媒) 美銀證券集團重申維諦技術買入評級 目標價 440 美元 (商傳媒) 美加關稅戰升溫 加拿大總理強調穩定能源供應以維信譽 (商傳媒) NEC首季財報亮眼 AI業務「Blue Stella」營收強勁成長 (商傳媒) AI用電需求噴發 核能發電股重回投資人視線 (商傳媒) 3COINS插旗臺北複製日本平價策略 誓成「雜貨界優衣庫」 (商傳媒) 投資美股領股息需留意 加拿大免稅儲蓄帳戶揭美國預扣稅陷阱 (商傳媒) 看戲兼做公益！創世兒童劇8/15登場 (商傳媒) 傳伊朗採購中國製攜帶型防空飛彈 中國外交部否認軍售消息 (商傳媒) OpenAI奧特曼會晤美國會議員 談AI風險與發布科研用新模型 (商傳媒) 伊朗發射飛彈襲美基地 川普嗆聲、國際油價跳漲 (商傳媒) 美國證管會控地產信託詐欺 創辦人挪用近 500 萬美元 (商傳媒) 伊朗數週內將獲中國製肩射飛彈 最多400套加劇區域失衡 (商傳媒) BMW傳全球裁員8,000人 加速轉型因應中國電動車競爭 (商傳媒) 能源巨頭求售美國 Explorer 輸油管道股權 估值逾 35 億美元 (商傳媒) 美國關稅衝擊巴西雞蛋出口逾四成 禽類業承壓轉向新市場 (商傳媒) 北美REITs第二季財報報喜 Morguard獲利轉正、Primaris戰略奏效 (商傳媒) 加密貨幣基金經理逃稅判囚三年 須賠償逾 340 萬美元 (商傳媒) AI 巨頭聯手呼籲：美國應主導國際 AI 監管減速 (商傳媒) 【金屬盤後】金價漲 銅價跌 (中央商情) 空中光電板1／屋頂光電新制恐有變數？迷糊上路代價高 「這類住宅」衝擊最大 (周刊王) 阿特曼：AI代理失控如科幻事件 真切感受到威脅 (中央商情) 空中光電板2／屋頂種電政策成敗「管委會」扛？ 沒錢維護下場慘淪「空中廢棄物」 (周刊王) 台股早盤震盪逾千點 台積電上漲40元 (中央商情) 聯準會利率連5凍 外界關注華許如何兌現降通膨承諾 (中央商情) 【盤前焦點】美股下挫費半摔逾5% 法人估台股打底時間拉長 (中央商情) Fed按兵不動「3官員、市場皆不買單」！會議5大要點一次看 (周刊王) 台股早盤震盪逾千點 台積電上漲40元 (中央社) 美高梅Q2營收創紀錄 賭城大道與數位業務表現亮眼 (商傳媒) 聯準會利率連5凍 外界關注華許如何兌現降通膨承諾 (中央社) 新台幣開盤貶1.4分 為32.38元 (中央社) Fed按兵不動引發憂慮！道瓊暴跌逾1千點 創去年4月以來最大單日跌幅 (周刊王) 中東情勢推升油價助長通膨擔憂 美股重挫半導體類股承壓 (商傳媒) 台股急拉站回4萬點 開盤後翻紅漲逾360點 (今日新聞) 泰國現象篇－魚販生計受衝擊 漁村世代斷裂 (中央社) 美股下挫費半摔逾5% 法人估台股打底時間拉長 (中央社) 全球矽晶圓出貨創14季新高 AI需求強勁 (中央社) 台股開盤漲9.76點 (中央社) 泰國公民運動篇－保育母親之河 湄公河學校揭露重金屬污染 (中央社) 台股逆轉！早盤跌634點隨後強彈逾千點 (今日新聞) 油價飆漲 VIX 恐慌指數攀升 納斯達克在聯準會前重挫 (商傳媒) 快訊／台股開盤震盪 一度下挫逾600點、失守4萬點大關 (上報) 美國好市多油價為何能壓到極低？ (草根影響力新視野) 新加坡祭出9億坡元振興方案 多管齊下鞏固經濟競爭力 (商傳媒) AI類股賣壓籠罩 台積電盤中重挫4.1%半導體供應鏈受創 (商傳媒) 烏克蘭襲擊俄國兩大煉油廠 全球能源供應隱憂再起 (商傳媒) 伊朗突襲約旦美軍基地與荷莫茲海峽 油價急升美財政部宣布制裁 (商傳媒) 台積電、台灣50還能買嗎？黃世聰曝抄底關鍵條件 (品觀點) 聯準會分歧美元承壓 日銀決策將左右日圓匯率動向 (商傳媒) 美國原油庫存意外驟降720萬桶 市場關注油價走向 (商傳媒) 聯準會會議後美股續跌 那指連六黑 半導體指數重挫逾5% (商傳媒) 聯準會利率按兵不動 9比3分歧投票 市場料9月升息機率降 (商傳媒) 美元指數延續回檔走勢 聯準會凍息推升匯市波動 (商傳媒) 中東空襲推升油價飆漲近7% 埃克森美孚股價揚3.3% (商傳媒) 美國原油庫存銳減720萬桶創多年新低 國際油價應聲勁揚 (商傳媒) 歐洲股市走低：精品業績喜憂參半，油價攀升科技股續弱 (商傳媒) Binance.US 擬申請美 CFTC 牌照 搶攻美國預測市場業務 (商傳媒) 聯準會維持利率不變 全球股市重挫那指跌逾1.7% (商傳媒) 美國原油庫存大幅銳減720萬桶 油價看漲消費者成本增 (商傳媒) 台股勉強站回4萬點 何時止跌先看3大指標 (卡優新聞) 電玩遊戲課金有祕笈 信用卡賺回20%決殺技 (卡優新聞) 學貸利率降至0.775% 臺銀8/1起受理申請 (卡優新聞) 友達ADR29日上漲0.14美元漲幅1.96%折台股23.63元 (中央商情) 日月光投控ADR29日下跌2.81美元跌幅8.28%折台股503.61元 (中央商情) AI軍備競賽開銷驚人 Meta第二季現金流大減91% (中央社) 中華電信ADR29日下跌0.11美元跌幅0.25%折台股139.59元 (中央商情) 聯電ADR29日下跌0.25美元跌幅1.44%折台股110.76元 (中央商情) 美國揚言打擊伊朗 國際油價大幅上揚 (中央社) 【歐股盤後】互有漲跌 (中央商情) 【美股盤後】收低 (中央商情) 台積電ADR29日下跌17.64美元跌幅4.50%折台股2425.31元 (中央商情) 基準利率不動美債殖利率飆高 通膨難解拖累道瓊大跌 (中央社) 聯準會利率不動但分歧加劇 9月升息機率破5成 (中央社) 晶片股拋售潮未止 美股收黑費半跌逾5% (中央社) 聯準會利率不變3票反對 華許形容決策過程如家庭爭吵 (中央社) 【能源盤後】上揚 (中央商情) 美伊戰火推升油價 聯準會續觀望利率連5凍 (中央社) 台灣大攜可樂旅遊搶進BNPL先買後付市場 (自立晚報) 金管會推金融大回饋提22項目 (自立晚報) 行動版 電腦版 分類新聞 最新 政治 社會 財經 科技 娛樂 體育 生活 國際 健康 寵物 情商 星座 職場 流行 新聞人物 政治 社會 娛樂 體育 科技 國際 財經 新聞專題 精選專題 星座 算命 農民曆 擇日 對獎 樂透 統一發票 氣象 今日天氣 一週天氣 旅遊天氣 國際天氣 天氣圖 警特報 影音新聞 政治 社會 財經 科技 娛樂 體育 生活 國際 健康 消費 旅遊 其他 新聞照片 政治 社會 財經 科技 娛樂 生活 國際 健康 消費 旅遊 大陸 其他 雜誌 總覽 政治 投資 管理 消費 好生活 藝文 公益 愛地球 關鍵字 最新關鍵字</t>
+          <t>ICTGCç«¶è³½é¦ç»ç½è°· é²è»CESå»£éå ¨çICæ°åµéçµèºç£åå°é«çæ é - å°åå¸é»è ¦åæ¥­åæ¥­å ¬æ Taipei Computer Association æå¡ç»å ¥ å å ¥TCA äººææå ç«å §æå° èªè­ TCA æ¬æç°¡ä» å¤§äºç´ çµç¹æ¶æ§ çç£äº å°æ¥­è¯ç æå¡æå ç¢æ¥­æ¨å»£ å±è¦½æé· åé¡ç«¶è³½ æ°åµæ´»å è¨ç«è³æº åå¥½é£çµ æ°èä¸­å¿ ç±éæ°è äººç©æ¡è¨ª æå¡å°è¨ª æ´»åæ å ± å½±åæ«¥çª TCA Video Gallery TCA Photo Gallery ç«å §æå° × æå° éé ç±éæ°è ICTGCç«¶è³½é¦ç»ç½è°· é²è»CESå»£éå ¨çICæ°åµéçµèºç£åå°é«çæ é IC Taiwan Grand Challengeåéæ¼CES 2025å±ä¸­ä¹TTAåå®¶é¤¨ä»ç´¹ç«¶è³½ åå®¶ç§å­¸åæè¡å§å¡æï¼NSTCï¼æå°çåéåµæ°ç«¶è³½IC Taiwan Grand Challengeï¼ICTGCï¼å°èå ¨çæ°åµå±æ InnoVEX ä¸»è¾¦å®ä½âå°åå¸é»è ¦å ¬æï¼TCAï¼æ¼ CES 2026 æéå ±åååä¸ç³»ååéäº¤æµæ´»åã é¢å° AI ç¡¬é«ãæ©å¨äººãå é²æ¶çèé«ç§æåµæ°å¿«éæ¼é²çå ¨çæµªæ½®ï¼InnoVEX æçºä½çºåéæ°åµå°æ¥äºæ´²æå é²ç§æç¢æ¥­çééµå ¥å£ï¼æ­¤æ¬¡ ICTGC x InnoVEX åéæ¨å»£è¡åé¤äºå¨CESå±æäº®ç¸ï¼ä¹å¾å°æ¼ 1 æ 13 æ¥å¨ç½è°·èè¾¦å°å ´æ´»åï¼åå©æ´å¤ç½è°·åéæ·±å ¥äºè§£å¦ä½ä¸²é£å°ç£å¨åå°é«è AI é åçä¸çç´è³æºï¼å±ç¾å°ç£æ¨åè·¨ååä½èæ¯æä¸ä¸ä»£ééµæè¡çæ±ºå¿èæ¿è«¾ã ICTGCãInnoVEXå°æ¼CES 2026é éç»å ´ å»£éå ¨çæ°åµèè¨TTAåå®¶é¤¨ å¨ CES 2026å±ææéï¼ IC Taiwan Grand Challengeï¼ICTGCï¼å°ææå ¨çåµæ°å±æInnoVEX å°äº®ç¸æ¼CES Eureka Park ç Taiwan Tech Arenaï¼TTAï¼åå®¶é¤¨ï¼Booth Venetian Expo, Hall G â 62201ï¼ãTTA çºåç§ææ¼ CES è¨­ç«çå®æ¹å±åï¼éå®å ·åç ç©¶å°åèæªä¾æ·±ç§ææ½åçæ°åµåéï¼æ¯å¹´å¸å¼å ¨çæè³äººãåéåªé«èç§æé è¢åè¨ªã ICTGC åéä¹å°æ¼ TTA Stage æ·±å ¥ä»ç´¹èºç£å¯ä¸å ·æå®æ´è¼å°æ©å¶ãå¯æ·±å ¥å°æ¥ç¢æ¥­éä¹åå°é«æ°åµç«¶è³½ï¼åä»¥ç²çæ°åµæ¡ä¾åäº«ICTGCå¦ä½çºæ°åµæä¾å¾è¨­è¨å°éç¢çå®æ´å éæ¯æã åéè§å±è äº¦æ­¡è¿èè¨ç¾å ´è InnoVEX åICTGC åéäº¤æµï¼ç­è§£è³æºéçµèç«¶è³½çå¾µä»¶åèæ¹å¼ã ICTGC 2026 å ¨çå¾µä»¶éè·ï¼å©æ»åéæ°åµéµçµç½å³¶ ICTGC ç¾æ­£éæ¾å ¨çå ±åï¼ç³è«æªæ­¢æ¥çº 2026 å¹´ 2 æ 28 æ¥ãæ­¡è¿ä¾èª AIãæ©å¨äººãåå°é«æè¡ãææ¸¬ç³»çµ±ãæ¬¡ä¸ä»£éç®ãæ·±ç§æç­é åçæ©ææ°åµãå­¸ç åéèæè¡éç¼è æäº¤å ·æ½åçåµæ°æç¨ææ¡ã çºåå©åéæ°åµæ´å¤§å½±é¿åãå éæè¡è½å°ï¼å ¥é¸åéå°æ¼ 2026 å¹´ 6 æ 2 è³ 5 æ¥å¨å°åèè¡ç COMPUTEX TAIPEI è InnoVEX æ°åµå±ä¸­ï¼ç²å¾å è²»åå±æ©æã ä½çºäºæ´²ææ¨æ§ç B2B ç§æå±ï¼COMPUTEX çµå InnoVEX ä¸ç«å¼çåµæå°æ¥èåéåªåèå°ï¼è®åéææ©æç´æ¥éçµè£½é å¤¥ä¼´ãåå°é«ä¾æéãåµæè³æºèåéè²·ä¸»ï¼çºå¸å±åå°é«ç¢æ¥­éä¹ééµè·³æ¿ãééICTGCè¨ç«ï¼ç²çåéå¯æææå°ç£åå°é«çæ ç³»ï¼å ±åéç¼å ·åéç«¶ç­ååµæ°è§£æ±ºæ¹æ¡ã å ±åç¶²åï¼ictaiwanchallenge.org ICTGCé¦åº¦ç½è°·ç»å ´ã1 æ 13 æ¥ææInnoVEXèè¾¦è«å£æ·±åå°ç½åå°é«èAIåä½ å»¶çºCESåéæ¨å»£åè½ï¼ICTGCå°æ¼2026å¹´1æ13æ¥é¦åº¦å¨ç½è°·Palo AltoçStartup Island TAIWAN â Silicon Valley Hubèè¾¦ãBridging Silicon Valley and Taiwan: Semiconductor &amp; AI Synergiesãè«å£ãè«å£å¯èç½è°·åµæ¥­è ãæè³äººèæè¡å°å®¶ï¼æ¢è¨å¦ä½åç¨å°ç£åå°é«èAIä¾æéè³æºï¼å¼·ååµæ°è½å°èåéåä½ï¼æ´æ¼ç¾å ´çºæèè¶£åèæ·±åº¦ä»ç´¹å°ä»ç´¹ç«¶è³½å¾µä»¶å §å®¹èè©é¸éé»ï¼åæåæ¡ä¾åäº«ã åéåéäº¦å¯èç±åå æ­¤è«å£ï¼äºè§£æ´å¤æ¼å°ç£ COMPUTEX/InnoVEX å±åºè³è¨ï¼åå©å ¶ææ¡æåé²å ¥å¸å ´çè·¯å¾ä¸¦èèºç£ICTç¢æ¥­çæ ç³»å»ºç«å¯¦è³ªé£çµã æ­¤æ¬¡æ´»åè«å£é¤äºéè«åä½è¬è Laura Swan-Silicon Catalyst Ventures å ±ååå¤¥äººï¼Andy Lombard-Tesoro Venture Capital ç®¡çåå¤¥äºº, Janis Skriveris-Plug and Play Ventures æè³ç¸½ç£æ¨é«ç§æè² è²¬äººä»¥åSam Fok-femtoAI å ±ååµè¾¦äººæ¨å·è¡é·ï¼å°åå¸é»è ¦å ¬ææ¥æ«»å§¿å¯ç¸½å¹¹äºå°å¸¶é åéæä¾ç½è°·æ°åµäººå£«æ´å¤éµçµå°ç£çè³æºï¼å ±åèå£¯æé·ã ç¾å ´å°åæé²è¡å ¨çç´æ­ï¼é è¨å°å¸å¼å ¨çç¸éæ°åµäººå£«è§çãç´æ­é£çµçºï¼https://www.youtube.com/live/ruXS6oe7WNA æ´»åè³è¨ Bridging Silicon Valley and Taiwan: Semiconductor &amp; AI Synergies 2026 å¹´ 1 æ 13 æ¥ï¼ææäºï¼ï½ä¸å 5:00ï¼PSTï¼ Startup Island TAIWAN â Silicon Valley Hub 299 California Ave STE 300, Palo Alto, CA 94306 U.S.A. åèç¶²åï¼ ãBridging Silicon Valley and Taiwan: Semiconductor &amp; AI Synergiesãè«å£ ï¼ç¼ä½æéï¼2026-01-02ï¼ ååè¡¨é  è½å¯ ã åå° ã åäº« å»¶ä¼¸é±è® InnoVEX 2026 ç«¶è³½ç»å ´ AVITICãPlug and PlayãPwCé¦æ³¢ç¹å¥çé½ç¼ï¼è¯æè³¦è½æ°åµéæåéçåè½é å®ç¢é³ä¿èè£äºé·æ¥ä»»çäºé· æè¨±å ±åè´åç¢æ¥­åéå äººç©æ¡è¨ª åç§æç¢å­¸èæå¾·çèé· : æ¨åç¢å­¸åä½è®ç ç¼ææè½å° æ°ä»»çç£äºæ¡è¨ªç³»åå ±å°(7)-æ¬æçäºæ¨å®ç¢æºé«é£å æ©è£äºé· : ãè³éè¨çµåçæãæ¯å°ç£æªä¾ç«¶ç­åªå¢ æ°ä»»çç£äºæ¡è¨ªç³»åå ±å°(6)-æ¬æçäºæ¨éææ©å¨äººé»è­å¿ çéé· : Edge AIæ¯å°ç£æ©å¨äººç¢æ¥­å½éè¶ è»çæ©æ ï¼ æ´å¤è¨æ¯ æå¡å°è¨ª TCAæå¡ä¼æ¥­å°è¨ª -å±¹å²ç§æï¼Eleosï¼ TCAæå¡ä¼æ¥­å°è¨ª -é²ä¸æè¾° TCAæå¡ä¼æ¥­å°è¨ª -å°ç£è³æç§æ ï¼ æ´å¤è¨æ¯ å»£å®£æå é±ç§æ¿ç­ è¯çµ¡æå äº¤éä½ç½® æå¡eåé Â© 2002ï¼2026 å°åå¸é»è ¦åæ¥­åæ¥­å ¬æ çæ¬ææ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -667,74 +717,12 @@
           <t>Success</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>IC semiconductor</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ç¾è¡ç¦é»ï¼ON Semiconductor(ON.US) | 23:32:11(GMT+8) - å°è¦è²¡ç¶</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://www.ttv.com.tw/finance/view/042026232332134174FF5E00432693B2142340DE48AAE792/587</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Fri, 24 Apr 2026 07:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ç¾è¡ç¦é»ï¼ON Semiconductor(ON.US) | 23:32:11(GMT+8) - å°è¦è²¡ç¶ é»æé¡¯ç¤º è²¡ç¶å°ç¯ç®è¡¨ å°è¦è²¡ç¶å°ç²çµ²å å°è¦æ°è ç¾è¡ç¦é»ï¼ON Semiconductor(ON.US) | 23:32:11(GMT+8) 2026/4/24 åéè¡å¸ MoneyDJæ°è 2026-04-23 23:32:13 æ¸ä½å §å®¹ä¸­å¿ ç¼ä½ON Semiconductorï¼ON.USï¼è¡å¹ç¤ä¸­è¡¨ç¾å¼·å¢ï¼æäº¤å¹ä¾å°97.78ç¾å ï¼æ¼²å¹ é9.87%ï¼ç¤ä¸­æé«è§¸å98.62ç¾å ï¼æäº¤éçº649,794è¡ï¼åå¹96.30ç¾å ã å¾ç¤ä¸­èµ°å¢ä¾çï¼è³éæé¡¯ç©æ¥µæ¹§å ¥ï¼ä¹åæ å¸å ´å°å ¬å¸å¾å¸è¡¨ç¾æ±æåå¤æå¾ ãON Semiconductoræ¯ä¸å®¶æä¾é»æºç®¡çèææ¸¬è§£æ±ºæ¹æ¡çåå°é«å ¬å¸ï¼ç¢åæ¶µèSiCèGaNåçåå°é«ãåé¡ææ¸¬å¨ä»¥åé¡æ¯ICï¼æç¨ç¯åéåæ±½è»ãå·¥æ¥­èè³æä¸­å¿ç­é åã æ­¤æ¬¡è¡å¹ä¸æï¼åæ åºå¸å ´çå¥½å ¶å¨AIè³æä¸­å¿èé«å£é»åè½æé åçæé·æ½åãé¨èé«æè½éç®èé»åæçéæ±æçºæåï¼ON Semiconductoræèåçå ä»¶èææ¸¬æè¡å¸å±ï¼å ·ååå ¥é«æé·æç¨å¸å ´çåªå¢ï¼ä¹è®æè³äººå°å ¶æªä¾çéç©ºéç¢çæ´å¤æ³åã å¾ç¢æ¥­è¶¨å¢ä¾çï¼åå°é«éæ±æ­£åæ æ¼AIä¼ºæå¨èè³æä¸­å¿æ´å»ºå¸¶åï¼ç¸éä¾æéä¸­çå å­¸æª¢æ¸¬ãæ¸¬è©¦ä»¥åé«å£é é»é åä¹åæ­¥è½è¶¨æ´»çµ¡ãå¦ä¸æ¹é¢ï¼SiemensèTSMCå¨AIé© åæ¶çè¨­è¨ä¸çåä½æçºæ´å¤§ï¼åéåºå£æ¸æèåéåªé«å ±å°äº¦é¡¯ç¤ºï¼åå°é«è¨å®åè½æ­£å¨ååãå¨æ´é«å¸æ³éæ­¥æ¹åä¹ä¸ï¼ä¹é²ä¸æ­¥æ¯æON Semiconductorå¨æè¡å¯¦åèå®¢æ¶å¸å±ä¸çåªå¢ï¼ä¸¦å¼·åå¸å ´å°å ¶å¾çºç²å©è¡¨ç¾çæå¾ ã è³æä¾æºï¼ MoneyDJçè²¡ç¶² æ­¡è¿å å ¥ å°è¦è²¡ç¶å°ç²çµ²å ï¼ ç±éé»é± » ä¸æGalaxyæ°åç¼è¡¨ ç§ä¸æ¬¾æºçæ©åå ¨æ°æºæ §æé¶ ãç¾è¡ãéçææ¸æ¶é« AIææå¼ç§æè¡ä¸è· åçå ä»¶ä¾éæªè®ï¼å¼·èä¸åå¹´çæ¶å¢å¹ æåªä¸åå¹´ ç·¯åµæ´å¤§æ°äºæ¥­ï¼ç¼æåé·æç²å©è½å çæ¬çç¼7.1å¼·é å°ç©é»åæäº æ¥BBUå¤§å®¢æ¶è¡åºï¼é ç¥¥æªä¾ä¸å¹´AIæç¨æä¿è­ å¸å±AIãHPCåæ© è¶ è±æå¹´çºæ´Flip Chipç¢è½ ç¾ç³»CPUæ°å¹³å°äº¦å°ååï¼éé´»åç±çè¿æé· ç¤¾ç¾¤åäº« » èºç£é»è¦äºæ¥­è¡ä»½æéå ¬å¸ çæ¬ææã©2015 Taiwan Television Enterprise, Ltd. All Rights Reserved. é»æé¡¯ç¤º åéè¡å¸ ç§æèå éèå¸å ´ ç¢æ¥­åæ  è²¡ç¶è³è¨ çæ´»è¬è±¡ ç¾é£æ¶è²» â²TOPâ²</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>IC semiconductor</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>【即時新聞】這「1檔」半導體轉強，NVTS最新漲2.94%還能追嗎？ | CMoney投資網誌</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://cmnews.com.tw/article/newsyoudeservetoknow-d463d065-3823-11f1-bf7c-8951ef46c39f</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Wed, 15 Apr 2026 07:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>【即時新聞】這「1檔」半導體轉強，NVTS最新漲2.94%還能追嗎？ | CMoney投資網誌 清空 搜尋紀錄 全部清除 取消 開始使用 投資網誌 登入 台股 新聞快訊 盤中獵報 籌碼k線專欄 ETF/期貨/原物料 美股 美股研究報告 美股新聞 美股財報會議 美股入門 大師選股 美股K線 Alpha's Newsletter 基金 基金新聞 基金排行 熱門 研究報告 理財達人 小資女艾蜜莉 不敗教主陳重銘 權證小哥 林恩如 阿格力 沈萬鈞 愛德恩小朋友 朱家泓x林穎 大俠武林 張捷 股市隱者 老簡免費文章 不魯 順流小畢 BC股倉 股人阿勳 Sara 無聊詹 蔡斯 怪博士 Dr.Selena好老公選股 美股夢想家施雅棠 尼克萊 春燕來了 新手入門 投資策略 基本分析 技術分析 籌碼分析 生活理財 生活理財 投資心得 退休規劃 CMoney官方 Money錢 林奇芬 狄驤 葉芷娟 李勛 金融人類學徒 清流君 美股航海王 游庭皓 張遠 存股攻城獅-聰聰 學投資，也學人生 人生學習 【即時新聞】這「1檔」半導體轉強，NVTS最新漲2.94%還能追嗎？ 首頁 美股 美股新聞 【即時新聞】這「1檔」半導體轉強，NVTS最新漲2.94%還能追嗎？ 權知道 我們重視「知」的權利 不惜抽絲剝繭、深入調查 只為讓投資人不錯過重要的投資訊息 權知道 2026-04-15 01:03 405 NVTS 近期市場對次世代半導體技術的關注度持續提升，其中專注於純粹次世代半導體技術的 Navitas Semiconductor (NVTS) 成為焦點。該公司致力推動「電氣化世界」願景，以全球首創的氮化鎵（GaN）功率 IC 及獨特的溝槽式平面碳化矽（SiC）技術在產業中佔據一席之地，旨在支援更高效能與潔淨能源的永續發展。 隨著市場熱度增加，相關衍生性金融商品也受到資金留意，例如 Tradr 每日2倍做多 NVTS 主動型 ETF（代號：NVTX）。最新資料顯示，該檔 ETF 預計於 2025 年 12 月 17 日進行除息，配息總額約為 3.5155 美元，這為關注該個股波動性與資金流向的資深投資人，提供了另一個觀察市場情緒與籌碼動能的參考指標。 Navitas Semiconductor (NVTS) ：近期個股表現 基本面亮點 Navitas Semiconductor (NVTS) 主要研發超高效能的半導體解決方案，其營運與業務重點包含： 核心技術：專注於氮化鎵（GaN）與碳化矽（SiC）技術，提供高功率密度的解決方案。 產品應用：功率 IC 高度整合了驅動、控制與保護功能，主要應用於行動裝置、消費性電子、企業級應用及電動車（eMobility）等新能源領域。 營收結構：目前公司營運版圖涵蓋美國、歐洲與亞洲等地，其中最大宗的營收來源為中國市場。 近期股價變化 根據 2026 年 4 月 13 日的最新交易數據顯示，該股價呈現震盪走高的格局。當日開盤價為 9.37 美元，盤中最高觸及 9.86 美元，最低來到 9.12 美元，終場收在 9.82 美元，單日上漲 0.28 美元，漲幅達 2.94%。在交易量方面，當日成交量為 13,571,257 股，較前一交易日的成交量變動幅度為 -8.25%。 總結而言，Navitas Semiconductor 在次世代功率半導體領域具備明確的技術佈局，相關主動型 ETF 亦反映出市場對其資金動能的關注。後續投資人可持續追蹤該公司在中國市場的營收表現，以及終端消費電子與電動車市場的供需動態，作為評估 (NVTS) 長期營運發展與潛在風險的重要依據。 文章相關標籤 Top50美股新聞 美股 美股新聞快訊 本文內容轉載 於此 關於作者 權知道 我們重視「知」的權利 不惜抽絲剝繭、深入調查 只為讓投資人不錯過重要的投資訊息 作者文章 【即時新聞】台達電(2308)獲利狂增88%！法說前夕，這「5檔概念股」多空交戰？ 【即時新聞】晶豪科(3006)爆量震盪多空激戰！這「3檔概念股」資金輪動誰接棒？ 【即時新聞】宇瞻(8271)爆量急跌逾7%，這「2檔記憶體概念股」盤中多空激戰！ 更多文章 今日最熱 1 【台股盤後】漲價題材陸續追繳，加權一度回測半年線 2 輝達「循環融資」疑慮發酵，牽動全球晶片股，這7檔重挫台股一度大跌逾2,000點 3 【股市爆料同學會專屬】－開戶領 30 天籌碼 K 線 VIP 4 記憶體股重挫解析：長鑫科技（CXMT）掛牌引爆全球賣壓 5 崩盤怎麼辦？「腳麻動不了」也要活下來：顧好情緒4步驟＋看懂大盤籌碼訊號 全站最新 【00405A】07/30 操作日報｜揮刀出清國巨，資金轉進台達電 19minutes ago 【00406A】07/30 操作日報｜資金轉向金融傳產避險？ 20minutes ago 【ETF籌碼日報】官股大買0050，外資、自營商大賣0050達119億 31minutes ago 2026.7.29 期指實戰錄 - VVIP 限定 anhour ago 2026.7.28 期指實戰錄 - VVIP 限定 anhour ago 最熱 最新 作者 1 【即時新聞】台達電(2308)獲利狂增88%！法說前夕，這「5檔概念股」多空交戰？ 2 【即時新聞】晶豪科(3006)爆量震盪多空激戰！這「3檔概念股」資金輪動誰接棒？ 3 【即時新聞】宇瞻(8271)爆量急跌逾7%，這「2檔記憶體概念股」盤中多空激戰！ 更多文章 1 【00405A】07/30 操作日報｜揮刀出清國巨，資金轉進台達電 2 【00406A】07/30 操作日報｜資金轉向金融傳產避險？ 3 【ETF籌碼日報】官股大買0050，外資、自營商大賣0050達119億 1 【台股盤後】漲價題材陸續追繳，加權一度回測半年線 2 輝達「循環融資」疑慮發酵，牽動全球晶片股，這7檔重挫台股一度大跌逾2,000點 3 【股市爆料同學會專屬】－開戶領 30 天籌碼 K 線 VIP 收藏內容 讓好文不錯過 立即收藏 取消 前往綁定 取消 確定購買 要永久刪除文章嗎 「」將被永久刪除，且這項操作無法復原。 取消 永久刪除 您尚未登入 登入會員才能編輯或管理文章，請先登入再進入此頁 取消 登入</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3ccc8d408c7b8b6a576a6c109f4331f3fdb5cb914a2a24b036a161f9c12492a9</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/result.xlsx
+++ b/output/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,37 +476,53 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>市場報導： 2026年上半年半導體營收竟然達7千億美元，相當於2024年一整年總營收，AI太可怕了！ - 科技產業資訊室</t>
+          <t>半導體通膨趨勢成形，晶圓代工、IC 設計紛漲價 - TechNews 科技新報</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://iknow.stpi.niar.org.tw/Post/Read.aspx?PostID=23258</t>
+          <t>https://finance.technews.tw/2026/05/01/semiconductor-inflation-trend-takes-shape-wafer-foundries-ic-design-price-hikes/</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tue, 16 Jun 2026 02:26:21 GMT</t>
+          <t>Fri, 01 May 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>科技產業資訊室</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>半導體通膨趨勢成形，因應成本高漲，包括晶圓代工及 IC 設計廠紛紛調漲價格，對於智慧手機等消費產品市場影響逐步顯現，智慧手機等今年出貨量恐面臨衰退壓力。
+半導體廠法人說明會陸續登場，成本壓力及產品價格策略成為法人關注的焦點。晶圓代工廠除將持續投入技術開發及擴充產能，中東緊張局勢也造成能源和物流等成本升高。
+晶圓代工廠
+已搶先於今年1月調漲驅動IC及感測器代工價格，3月調漲功率元件代工價格，
+先進跟進於4月調漲代工價格，
+也於4月通知客戶，將於下半年調整價格。
+不僅晶圓代工價格調漲，後段封測價格也傳出漲價消息，IC設計廠紛紛決定調漲產品售價，減緩成本升高的影響，
+3月已通知客戶，
+透露將藉由嚴謹的定價策略，目標將全年毛利率維持在44.5%至47.5%區間。
+觀察目前整體市況依然呈現不同調的態勢，AI相關市場需求持續強勁，消費電子市場需求相對疲弱，IC設計廠不打算全面調漲產品價格。
+雅特力-KY認為，近期微控制器（MCU）市場掀起一波漲價潮，並不是終端市場強勁需求所帶動，而是AI需求強勁占用產能，以及原材料漲價所致，雅特力-KY僅會適度漲價，力求毛利率持穩。
+盛群認為，目前經濟情勢並未變好，需求僅穩定，因應晶圓代工與封測漲價10%至15%，盛群將僅調漲低毛利產品售價，期能讓毛利回歸合理。
+繼記憶體價格飆漲後，晶圓代工和IC設計紛紛調漲價格，半導體通膨趨勢成形，使得智慧手機等消費產品市場，面臨成本升高的壓力進一步加劇。廠商除將資源集中於高階產品因應，需求也開始趨緩，聯發科預估，今年手機出貨量恐減少15%。漲價對市場需求的影響，未來是否進一步擴大，備受市場關注。</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Download failed</t>
-        </is>
-      </c>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4e78b80beb620f39c678da1b8dd8d665db0c4dc4072aef4c8de7eb9abd8d246e</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -516,27 +532,45 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>半導體通膨趨勢成形，晶圓代工、IC 設計紛漲價 - TechNews 科技新報</t>
+          <t>NYCU and Purdue Launch Global Semiconductor Academy to Advance AI and Chip Talent Development - 中央社 CNA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://finance.technews.tw/2026/05/01/semiconductor-inflation-trend-takes-shape-wafer-foundries-ic-design-price-hikes/</t>
+          <t>https://www.cna.com.tw/postwrite/eng/432806</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Fri, 01 May 2026 07:00:00 GMT</t>
+          <t>Thu, 07 May 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TechNews 科技新報</t>
+          <t>中央社 CNA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>半導體通膨趨勢成形，晶圓代工、IC 設計紛漲價 | TechNews 科技新報 搜尋： 登入 註冊 登出 VIP會員 Menu Skip to content 會員專區 訂閱專區 技術分析 焦點新聞評析 拓墣觀點 TechNews Smart AI 活動專區 常見問題 半導體 晶圓 晶片 IC 設計 封裝測試 處理器 GPU 記憶體 零組件 光電科技 面板 電池 3C周邊 AI 人工智慧 Claude Apple Intelligence DeepSeek Gemini Copilot ChatGPT Perplexity Grok 財經 財報 證券 房地產 Fintech 加密貨幣 金融政策 國際貿易 國際金融 支付方案 尖端科技 奈米 衛星通訊 汽車科技 航太科技 機器人 軍事科技 材料 無人機 環境科學 醫療科技 生物科技 科技生活 科技教育 能源科技 太陽能 風力 核能 電力儲存 企業永續 科技人才 系列專題 Token 戰爭：AI 推論時代的結構性大洗牌 光速革命 2026：矽光子與 CPO 領航 AI 下半場 AI 全方位解析：看懂任務分類、硬體門檻與你的產業卡位戰 能源即算力！2026 資料中心電源保衛戰 川普重返白宮一年，全球科技規則如何改變？ AI 晶片封裝技術革命 晶片戰場的隱形冠軍：先進封裝需求背後，一場決定全球 AI 命脈的設備軍備競賽 財報快訊 企業部落格 市場動態 關於我們 內容合作單位 菁英人才招募中 廣告合作 TN Smart 半導體通膨趨勢成形，晶圓代工、IC 設計紛漲價 作者 中央社 | 發布日期 2026 年 05 月 01 日 9:59 | 分類 IC 設計 , 半導體 , 晶圓 | edit Loading... Now Translating . . . 半導體通膨趨勢成形，因應成本高漲，包括晶圓代工及 IC 設計廠紛紛調漲價格，對於智慧手機等消費產品市場影響逐步顯現，智慧手機等今年出貨量恐面臨衰退壓力。 半導體廠法人說明會陸續登場，成本壓力及產品價格策略成為法人關注的焦點。晶圓代工廠除將持續投入技術開發及擴充產能，中東緊張局勢也造成能源和物流等成本升高。 晶圓代工廠 力積電 已搶先於今年1月調漲驅動IC及感測器代工價格，3月調漲功率元件代工價格， 世界 先進跟進於4月調漲代工價格， 聯電 也於4月通知客戶，將於下半年調整價格。 不僅晶圓代工價格調漲，後段封測價格也傳出漲價消息，IC設計廠紛紛決定調漲產品售價，減緩成本升高的影響， 盛群 3月已通知客戶， 聯發科 透露將藉由嚴謹的定價策略，目標將全年毛利率維持在44.5%至47.5%區間。 觀察目前整體市況依然呈現不同調的態勢，AI相關市場需求持續強勁，消費電子市場需求相對疲弱，IC設計廠不打算全面調漲產品價格。 雅特力-KY認為，近期微控制器（MCU）市場掀起一波漲價潮，並不是終端市場強勁需求所帶動，而是AI需求強勁占用產能，以及原材料漲價所致，雅特力-KY僅會適度漲價，力求毛利率持穩。 盛群認為，目前經濟情勢並未變好，需求僅穩定，因應晶圓代工與封測漲價10%至15%，盛群將僅調漲低毛利產品售價，期能讓毛利回歸合理。 繼記憶體價格飆漲後，晶圓代工和IC設計紛紛調漲價格，半導體通膨趨勢成形，使得智慧手機等消費產品市場，面臨成本升高的壓力進一步加劇。廠商除將資源集中於高階產品因應，需求也開始趨緩，聯發科預估，今年手機出貨量恐減少15%。漲價對市場需求的影響，未來是否進一步擴大，備受市場關注。 （作者：張建中；首圖來源：shutterstock） 文章看完覺得有幫助，何不給我們一個鼓勵 請我們喝杯咖啡 想請我們喝幾杯咖啡？ 每杯咖啡 65 元 x 1 x 3 x 5 x 您的咖啡贊助將是讓我們持續走下去的動力 總金額共新臺幣 0 元 《關於請喝咖啡的 Q &amp; A》 留給我們的話 取消 確認 從這裡可透過《Google 新聞》追蹤 TechNews 科技新知，時時更新 科技新報粉絲團 加入好友 訂閱免費電子報 關鍵字: 半導體通路 , 晶圓代工 , 智慧手機 , 漲價 Post navigation ← 抓無人機不靠雷達，波蘭測試「聲學感測器」揪出隱形威脅 當「好公司」成為一種人設？拆解 B 型企業的道德溢價與認證背後的機制失靈 → 我們偵測 到您有啟用 AD Block 請您暫停使用AD Block，以支持我們持續能提供更多新聞資訊與優質的閱讀環境。 新報特企 焦點動態 系列專題 AI 推論的 Token 戰爭 小龍蝦點燃「算力即營收」新紀元！Vera Rubin 引爆台美供應鏈一次看 代理 AI 重塑晶片架構！「成本才是王道」，ASIC、CPU 與記憶體牆成新戰場 從 SaaS 到 TaaS：AI 時代為何你不是付月費，而是 Token？ VIP 全預觀 本田續約廣汽十年：從技術輸出到技術汲取的合資 2.0 模式 從馬路到水路，小米申請新能源車水下推進器專利 FEV 與微軟部署車端小語言模型，確保離線語音服務與高效運用記憶體 全球儲能產業發展趨勢：政策、法規與標準化 1.6T 世代：通訊關鍵元件洗牌與台灣廠商切入路徑 本週熱門 數學界天翻地覆，代數幾何 87 年懸案「雅可比猜想」遭 Claude 證偽 焦慮、肥胖、不婚不生，研究：人類演化無法適應現代社會 全球水域含氧量迅速流失，科學家警告「水體脫氧」恐不可逆 根本沒有 100%「美國製造」路由器，廠商群起申請豁免使 FCC 禁令漸鬆 海洋蠕蟲超硬顎部揭密，科學家首度定義全新「生體金屬」 一天喝五杯咖啡也無妨？研究揭開咖啡的護肝潛力 喝咖啡能護心？美國心臟協會揭每日黃金杯數，警告避開三大飲用地雷 是太空垃圾也是天然實驗場！SpaceX 火箭殘骸 8/5 將墜入月球表面 財訊快報 宜特6月營收月增10.5% 漢唐6月營收87.43 億元 台灣大6月營收月增5.4% 科嘉-KY6月營收月減17.3% 康控-KY6月營收月減4.3% 漢磊6月營收6.20 億元 嘉晶6月營收月增3.3% 中華電6月營收月增9.3% 中環6月營收6.39 億元 台積電6月營收月增6.2% 更多&gt;&gt; 編輯精選 [ 專欄 ] 美國與中國分居最大出口市場與進口來源國下的台灣貿易結構 [ 專欄 ] 記憶體價格上漲，難成為美國政府鬆綁中國管制的理由 [ 專題 ] 小龍蝦點燃「算力即營收」新紀元！Vera Rubin 引爆台美供應鏈一次看 [ 專題 ] 代理 AI 重塑晶片架構！「成本才是王道」，ASIC、CPU 與記憶體牆成新戰場 [ 專題 ] 從 SaaS 到 TaaS：AI 時代為何你不是付月費，而是 Token？ [ 專欄 ] 「中小微企業多元振興發展計畫」落實，對提高台灣經濟韌性有重大幫助 [ 專訪 ] AI 資料傳輸量暴增！WD 談「兩大儲存挑戰」：關鍵在分層式架構 [ 專欄 ] 鼓勵「不勞而獲」降稅政策只會擴大台灣社會失衡 FB 粉絲團 我的最愛 趕快加入最愛頁面 Facebook 成為我們的小粉絲 RSS 即時更新新知 相關連結 Facebook 功能 文章 RSS 訂閱 迴響 RSS 訂閱 © 2013-2026 TechNews Inc. All rights reserved. | 關於我們 | 使用條款 | 隱私權政策 | 著作權與授權轉載 登入裝置已達上限 親愛的會員, 您的帳戶已經在其他裝置進行登入，於是系統將自動把您的帳戶登出本裝置。 若需要繼續瀏覽網站，請 重新登入 網站 若非您本人的操作，為保障您的帳戶安全，請您儘快至會員中心 修改密碼 × 請您暫停使用AD Block，以支持我們持續能提供更多新聞資訊與優質的閱讀環境。</t>
+          <t>NYCU and Purdue Launch Global Semiconductor Academy to Advance AI and Chip Talent Development
+發稿時間：2026/05/07 14:14:32
+(中央社訊息服務20260507 14:14:32)As the global semiconductor race accelerates in the AI era, National Yang Ming Chiao Tung University (NYCU) and Purdue University have jointly launched the Semiconductor Academy, a new online professional education initiative designed to cultivate next-generation semiconductor talent and expand access to industry-focused learning worldwide.
+The collaboration brings together two institutions located at the heart of critical semiconductor ecosystems — Taiwan, home to the world’s most advanced chip manufacturing industry, and the United States, a global leader in semiconductor research, design, and innovation. Developed jointly by NYCU and Purdue, the Semiconductor Academy will offer flexible online courses covering key areas across the semiconductor supply chain, including chip design for AI, semiconductor materials and devices, advanced packaging, reliability, IC design, EDA, and semiconductor industry management.
+The program is designed for working professionals, engineers, and learners seeking to deepen their expertise or enter the rapidly evolving semiconductor field. Courses will be delivered online in a modular, stackable format, allowing learners to tailor their studies to their professional goals and industry needs.
+The Semiconductor Academy is a flexible, industry-aligned portfolio of Purdue University micro-credentials developed in collaboration with faculty from NYCU in Taiwan to help upskill the global semiconductor workforce.
+As one of Taiwan’s leading universities in electrical engineering, computer science, photonics, AI, and semiconductor research, NYCU has long played a central role in nurturing talent for Taiwan’s semiconductor industry and the Hsinchu Science Park ecosystem.
+Through the Semiconductor Academy, NYCU faculty will contribute academic expertise and real-world industry perspectives drawn from Taiwan’s globally influential semiconductor ecosystem, offering international learners a unique window into the technologies and manufacturing practices shaping the future of chips and AI computing.
+“Semiconductor innovation requires a deep understanding of the entire technology stack,” said Mark Lundstrom, Don and Carol Scifres Distinguished Professor of Electrical and Computer Engineering at Purdue University. “By bringing together the strengths of both Purdue and NYCU, the Semiconductor Academy provides learners with a rigorous, globally informed perspective on the technologies shaping the future of the industry.” The collaboration also reflects NYCU’s broader internationalization strategy and its commitment to strengthening global partnerships in semiconductors, AI, and emerging technologies.
+Covering topics from chip design and semiconductor materials to packaging and supply chain management, the Semiconductor Academy’s two-hour modular courses allow learners to build industry-relevant skills at their own pace.
+According to Purdue, the Semiconductor Academy is part of a broader expansion of semiconductor professional education aimed at addressing rising workforce demands across the global chip industry. Each course in the academy will feature approximately 2 hours of focused learning content and be accessible through flexible online formats. The academy will also be featured on SEMI University (SEMI U), a global digital learning platform serving semiconductor professionals and organizations worldwide.
+Topics planned for the initial course offerings include:
+。Chip Design for AI
+。Packaging, Reliability and Characterization
+。IC Design, EDA and Analog
+。Semiconductor Materials and Devices
+。Supply Chain Management and Leadership in the Semiconductor Industry
+Additional semiconductor professional education courses developed by Purdue are expected to launch in summer 2026, including transistor fundamentals, nanolithography, RF design, and data analysis for semiconductor applications. The launch ceremony for the Semiconductor Academy was held via livestream between Purdue and NYCU, underscoring the growing importance of international collaboration in building the future semiconductor workforce.
+For more NYCU News, please visit the official NYCU website.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -547,7 +581,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>d970a92d732b9934c7e2d6a264f99fc947e20ef78a234dcc7de6a81e794b3864</t>
+          <t>99c1b51e2e4344e6fd4461f48b7839df56167ecec2c97ec84fb1251345ae320e</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -560,41 +594,37 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NYCU and Purdue Launch Global Semiconductor Academy to Advance AI and Chip Talent Development - 中央社 CNA</t>
+          <t>市場報導： 2026年上半年半導體營收竟然達7千億美元，相當於2024年一整年總營收，AI太可怕了！ - 科技產業資訊室</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.cna.com.tw/postwrite/eng/432806</t>
+          <t>https://iknow.stpi.niar.org.tw/Post/Read.aspx?PostID=23258</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 07:00:00 GMT</t>
+          <t>Tue, 16 Jun 2026 02:26:21 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>中央社 CNA</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>NYCU and Purdue Launch Global Semiconductor Academy to Advance AI and Chip Talent Development | 中央社訊息平台 財經訊息平台 知訊台 好生活 影像空間 客戶頻道 中文稿 英文稿 電信 簡介 投稿 投稿 中文稿 英文稿 電信 簡介 平台簡介 服務辦法 投稿流程 收款方式 供稿啓事 新聞稿寫作原則 其他服務 財經訊息平台 知訊台 歡迎公司行號投遞新聞訊息！詳洽業務行銷中心 人工服務時間為週一至週六9:30-12:00、14:00-18:30 如有週日發稿需求請於週六18:00前完成刊登程序。 了解更多 訊息來源：國立陽明交通大學 轉載網址 更多訊息 Matsu’s “Blue Tears” Inspire NYCU Breakthrough in Next-Generation Luminescent Materials NYCU Partners with Kneron to Advance Edge AI Education and Real-World Deployment NYCU and Changhua County Launch Smart Agriculture App to Help Farmers Monitor Crops with AI NYCU Team Wins Taiwan Title at Red Bull Basement, Heads to Silicon Valley for Global Finals NYCU Study Finds Belly Fat May Signal Hidden Heart Failure Risk—Even at Normal Weight 首頁 英文稿 NYCU and Purdue Launch Global Semiconductor Academy to Advance AI and Chip Talent Development 發稿時間：2026/05/07 14:14:32 (中央社訊息服務20260507 14:14:32)As the global semiconductor race accelerates in the AI era, National Yang Ming Chiao Tung University (NYCU) and Purdue University have jointly launched the Semiconductor Academy, a new online professional education initiative designed to cultivate next-generation semiconductor talent and expand access to industry-focused learning worldwide. The collaboration brings together two institutions located at the heart of critical semiconductor ecosystems — Taiwan, home to the world’s most advanced chip manufacturing industry, and the United States, a global leader in semiconductor research, design, and innovation. Developed jointly by NYCU and Purdue, the Semiconductor Academy will offer flexible online courses covering key areas across the semiconductor supply chain, including chip design for AI, semiconductor materials and devices, advanced packaging, reliability, IC design, EDA, and semiconductor industry management. The program is designed for working professionals, engineers, and learners seeking to deepen their expertise or enter the rapidly evolving semiconductor field. Courses will be delivered online in a modular, stackable format, allowing learners to tailor their studies to their professional goals and industry needs. The Semiconductor Academy is a flexible, industry-aligned portfolio of Purdue University micro-credentials developed in collaboration with faculty from NYCU in Taiwan to help upskill the global semiconductor workforce. As one of Taiwan’s leading universities in electrical engineering, computer science, photonics, AI, and semiconductor research, NYCU has long played a central role in nurturing talent for Taiwan’s semiconductor industry and the Hsinchu Science Park ecosystem. Through the Semiconductor Academy, NYCU faculty will contribute academic expertise and real-world industry perspectives drawn from Taiwan’s globally influential semiconductor ecosystem, offering international learners a unique window into the technologies and manufacturing practices shaping the future of chips and AI computing. “Semiconductor innovation requires a deep understanding of the entire technology stack,” said Mark Lundstrom, Don and Carol Scifres Distinguished Professor of Electrical and Computer Engineering at Purdue University. “By bringing together the strengths of both Purdue and NYCU, the Semiconductor Academy provides learners with a rigorous, globally informed perspective on the technologies shaping the future of the industry.” The collaboration also reflects NYCU’s broader internationalization strategy and its commitment to strengthening global partnerships in semiconductors, AI, and emerging technologies. Covering topics from chip design and semiconductor materials to packaging and supply chain management, the Semiconductor Academy’s two-hour modular courses allow learners to build industry-relevant skills at their own pace. According to Purdue, the Semiconductor Academy is part of a broader expansion of semiconductor professional education aimed at addressing rising workforce demands across the global chip industry. Each course in the academy will feature approximately 2 hours of focused learning content and be accessible through flexible online formats. The academy will also be featured on SEMI University (SEMI U), a global digital learning platform serving semiconductor professionals and organizations worldwide. Topics planned for the initial course offerings include: 。Chip Design for AI 。Packaging, Reliability and Characterization 。IC Design, EDA and Analog 。Semiconductor Materials and Devices 。Supply Chain Management and Leadership in the Semiconductor Industry Additional semiconductor professional education courses developed by Purdue are expected to launch in summer 2026, including transistor fundamentals, nanolithography, RF design, and data analysis for semiconductor applications. The launch ceremony for the Semiconductor Academy was held via livestream between Purdue and NYCU, underscoring the growing importance of international collaboration in building the future semiconductor workforce. 文章附檔 For more NYCU News, please visit the official NYCU website. 訊息平台 平台簡介 | 服務辦法 | 投稿流程 | 收款方式 | 供稿啟事 | 新聞稿寫作原則 | 其他服務 關於中央社 公司簡介 | 企業識別 | 公開資訊 | 設置條例摘要 | 隱私權聲明 | 聯絡我們 友善連結 曾虛白新聞獎基金會 | 公職人員及關係人補助交易身分關係公開及查詢平臺 中央社網站 中央通訊社 | Focus Taiwan | フォーカス台湾 | Fokus Taiwan 關注更多 iOS app 下載 | Android app 下載 | Focus Taiwan APP | 全球中央雜誌 | 文化+ | 淨零碳排 | 新聞學院 | 中央社電子報 產品與服務 產品總覽 | 客戶頻道 | 影像空間 | 訊息平台 | 財經訊息平台 | 知訊台 本平台資料均由投稿單位輸入後對外公布，資料如有錯誤、遺漏或虛偽不實，均由投稿單位負責 copyright © 2021 中央通訊社版權所有</t>
-        </is>
-      </c>
+          <t>科技產業資訊室</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Success</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>f4068be0c01a90821295bd0289181ff02d813688f755753fa888b3135406f94d</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Download failed</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -604,37 +634,48 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>市場報導： 2026年上半年半導體營收竟然達7千億美元，相當於2024年一整年總營收，AI太可怕了！ - 科技產業資訊室</t>
+          <t>全台首家IC設計獲Arm注資 通寶半導體Q4擬申請IPO - 工商時報</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://iknow.stpi.niar.org.tw/Post/Read.aspx?PostID=23258</t>
+          <t>https://www.ctee.com.tw/news/20260304700096-439901</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Tue, 16 Jun 2026 02:26:21 GMT</t>
+          <t>Wed, 04 Mar 2026 08:00:00 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>科技產業資訊室</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>工商時報</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>通寶半導體設計公司簡介
+台灣IC設計領域傳出國際策略投資合作捷報，通寶半導體（QBit Semiconductor）公司3日宣布，已完成B輪募資，並獲全球半導體架構大廠安謀公司（Arm Limited）參與投資，成為目前全台唯一獲得Arm投資的IC設計公司。
+安謀現成為通寶十大股東之一，至於安謀持股比例及金額，4月下旬召開法說會可望對外說明，未來通寶擬計畫跨足無人機及機器人市場。
+通寶半導體同時宣布，隨著募資完成營運規模擴大，計畫於今年第四季向臺灣證券交易所申請IPO上市，進一步邁向資本市場新里程碑，實際時程仍須視主管機關核准及市場狀況而定。
+通寶半導體為專攻多功能列印機及事務機系統晶片的IC設計公司，其客戶主要市場遍及美國、日本、中國跟台灣。除Arm參與投資外，據悉，通寶半導體在A輪募資時，台灣政府法人機構持有通寶半導體約6％股權，包括國發基金持股2.7％，以及台肥、工研院等公股事業合計持股比例約6％，還有智原科技等半導體產業加入，整體A輪投資人持股比例約為通寶已發行股權10％。
+對於這項注資，Arm全球執行副總裁暨商務長Will Abbey表示，透過與通寶的合作，可以結合先進影像處理、控制與安全能力，以支持列印及影像市場的創新。此類合作展現Arm更廣泛的策略，亦即推動具差異化的解決方案，從高效能系統延伸至更具成本效益的裝置，同時為各類產品建立成長基礎。
+通寶半導體創辦人暨執行長沈軾榮也表示，很榮幸成為獲得Arm唯一投資的台灣半導體設計公司，未來通寶將持續深化在印表機影像市場的布局，並拓展至更廣泛的影像相關應用領域。
+將工商時報加入Google偏好來源</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Download failed</t>
-        </is>
-      </c>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>aff1f2ed85b1eadb7b7db5280b1d2c6999979931eb2ac141ac79151a4983936d</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -644,27 +685,51 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>全台首家IC設計獲Arm注資 通寶半導體Q4擬申請IPO - 工商時報</t>
+          <t>ICTGC競賽首登矽谷 進軍CES廣邀全球IC新創鏈結臺灣半導體生態鏈 - tca.org.tw</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.ctee.com.tw/news/20260304700096-439901</t>
+          <t>https://www.tca.org.tw/news_detail.php?n=2454&amp;t=h</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Wed, 04 Mar 2026 08:00:00 GMT</t>
+          <t>Fri, 02 Jan 2026 08:00:00 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>工商時報</t>
+          <t>tca.org.tw</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>全台首家IC設計獲Arm注資 通寶半導體Q4擬申請IPO - 日報 - 工商時報 前往主要內容 會員 會員中心 登出 電子報 影音特區 讀報區 首頁 即時 開闔次選單 即時首頁 要聞 證券 金融 稅法 產業 房市 國際 兩岸 科技 生活 要聞 開闔次選單 要聞首頁 政經焦點 總經趨勢 稅務法務 綜合要聞 前瞻一周 證券 開闔次選單 證券首頁 上市櫃 陸港股市 國際股市 產業焦點 期貨 權證 亮點個股 專家看盤 台股逐洞賽 重要指數 重大訊息 財經行事曆 金融 開闔次選單 金融首頁 金融話題 外匯市場 牌告匯率 金融科技 銀行動態 保險脈動 數據觀測 金融人物 理財 開闔次選單 理財首頁 理財新訊 基金 ETF 生活消費 信用卡 退休理財 統一發票 產業 開闔次選單 產業首頁 半導體 科技動態 綜合產業 生技醫療 CEO專訪 職場達人 房市 開闔次選單 房市首頁 房市焦點 區域亮點 名家攻略 居住安全 觀點評論 市場動態 國際 開闔次選單 國際首頁 全球政經 全球市場 議題觀點 國際產業 Global Scan 全球財經周報 大宗商品行情 兩岸 開闔次選單 兩岸首頁 政情動向 兩岸焦點 大陸財經 大陸產業 China Scan 陸港市場 觀點分析 言論 開闔次選單 言論首頁 社論 總經經濟 產業脈動 國際經貿 企業管理 社會觀察 奇思妙想 作者群 樂活 開闔次選單 樂活首頁 美食饗宴 旅遊休閒 生活風格 愛車天地 養生保健 時尚消費 藝文特區 書房 開闔次選單 書房首頁 書房嚴選 名人書單 好書推薦 英文進修 雜誌精選 年度好書 專題 開闔次選單 專題首頁 上市櫃6月營收 大陸經濟新局 台灣半導體風雲 上市櫃Q1營收 生技ESG革命 新世代夯話題 財經人物專訪 商情 開闔次選單 商情首頁 智慧機械 大健康 金融理財 房市建材 科技綠能 消費時尚 產學管顧 社企公益 活動 開闔次選單 活動首頁 台南機械展 台中AI展 台灣權王 服務業大評鑑 數位金融獎 ETF論壇 中華電信論壇 多元信託 期貨與選擇權 永續校園徵影 搜尋 首頁 日報 工商時報 全台首家IC設計獲Arm注資 通寶半導體Q4擬申請IPO 全台首家IC設計獲Arm注資 通寶半導體Q4擬申請IPO 2026.03.04 03:00 工商時報 呂雪彗 通寶半導體 安謀 智原科技 IC設計 Arm注資 通寶半導體公司董事長暨執行長沈軾榮表示，通寶半導體為全台唯一獲Arm投資的 IC 設計公司。圖／通寶半導體提供 切換文字大小 複製文章連結 分享至臉書 以Line分享 加入Google來源 參與討論 友善列印 已將目前網頁的網址複製到您的剪貼簿！ 通寶半導體設計公司簡介 台灣IC設計領域傳出國際策略投資合作捷報，通寶半導體（QBit Semiconductor）公司3日宣布，已完成B輪募資，並獲全球半導體架構大廠安謀公司（Arm Limited）參與投資，成為目前全台唯一獲得Arm投資的IC設計公司。 安謀現成為通寶十大股東之一，至於安謀持股比例及金額，4月下旬召開法說會可望對外說明，未來通寶擬計畫跨足無人機及機器人市場。 通寶半導體同時宣布，隨著募資完成營運規模擴大，計畫於今年第四季向臺灣證券交易所申請IPO上市，進一步邁向資本市場新里程碑，實際時程仍須視主管機關核准及市場狀況而定。 通寶半導體為專攻多功能列印機及事務機系統晶片的IC設計公司，其客戶主要市場遍及美國、日本、中國跟台灣。除Arm參與投資外，據悉，通寶半導體在A輪募資時，台灣政府法人機構持有通寶半導體約6％股權，包括國發基金持股2.7％，以及台肥、工研院等公股事業合計持股比例約6％，還有智原科技等半導體產業加入，整體A輪投資人持股比例約為通寶已發行股權10％。 對於這項注資，Arm全球執行副總裁暨商務長Will Abbey表示，透過與通寶的合作，可以結合先進影像處理、控制與安全能力，以支持列印及影像市場的創新。此類合作展現Arm更廣泛的策略，亦即推動具差異化的解決方案，從高效能系統延伸至更具成本效益的裝置，同時為各類產品建立成長基礎。 通寶半導體創辦人暨執行長沈軾榮也表示，很榮幸成為獲得Arm唯一投資的台灣半導體設計公司，未來通寶將持續深化在印表機影像市場的布局，並拓展至更廣泛的影像相關應用領域。 將工商時報加入Google偏好來源 相關新聞 大盤震盪 拉回擇優布局台股ETF 美股走勢分歧 晶片股台積電ADR持續承壓 《基金》6檔國內半導體ETF夯 受益人數突破43.8萬人創新高 您可能感興趣的話題 留言討論 熱門日報新聞 more 台股聞到「洗籌碼、殺斷頭」的味道！「四貸同堂」族哀嚎 指數何時反彈名師劃重點 大摩喊記憶體供需缺口未收斂 Q3漲勢未歇 南亞科、華邦電、旺宏有戲唱 台股融資大退散 短線反彈契機已到？專家估8月有望戰季線 公股逢低撿便宜 重倉大型權值電子股 買超前十強3檔ETF卡位 竟是同一家 金管會出手 嚴管四貸同堂 專題推薦 返回頁首 網站選單開關 顏色主題切換 LOADING 熱門新聞 TOP 3 more 台股崩盤不敢買？孫慶龍股災做對一件事 52萬竟變成8千萬 未來十年最看好這2檔 台股聞到「洗籌碼、殺斷頭」的味道！「四貸同堂」族哀嚎 指數何時反彈名師劃重點 期貨最新報價7／29期交所夜盤行情 本網頁已閒置超過3分鐘。請點撃框外背景，或右側關閉按鈕(X)，即可回到網頁。 關閉 關閉廣告</t>
+          <t>ICTGC競賽首登矽谷 進軍CES廣邀全球IC新創鏈結臺灣半導體生態鏈
+IC Taiwan Grand Challenge團隊於CES 2025展中之TTA國家館介紹競賽
+國家科學及技術委員會（NSTC）指導的國際創新競賽IC Taiwan Grand Challenge（ICTGC）將與全球新創展會 InnoVEX 主辦單位—台北市電腦公會（TCA）於 CES 2026 期間共同啟動一系列國際交流活動。
+面對 AI 硬體、機器人、先進晶片與高科技創新快速演進的全球浪潮，InnoVEX 持續作為國際新創對接亞洲最先進科技產業的關鍵入口，此次 ICTGC x InnoVEX 國際推廣行動除了在CES展會亮相，之後將於 1 月 13 日在矽谷舉辦專場活動，協助更多矽谷團隊深入了解如何串連台灣在半導體與 AI 領域的世界級資源，展現台灣推動跨國合作與支持下一代關鍵技術的決心與承諾。
+ICTGC、InnoVEX將於CES 2026領銜登場 廣邀全球新創蒞臨TTA國家館
+在 CES 2026展會期間， IC Taiwan Grand Challenge（ICTGC）將攜手全球創新展會InnoVEX 將亮相於CES Eureka Park 的 Taiwan Tech Arena（TTA）國家館（Booth Venetian Expo, Hall G — 62201）。TTA 為國科會於 CES 設立的官方展區，鎖定具備研究導向與未來深科技潛力的新創團隊，每年吸引全球投資人、國際媒體與科技領袖參訪。
+ICTGC 團隊也將於 TTA Stage 深入介紹臺灣唯一具有完整輔導機制、可深入對接產業鏈之半導體新創競賽，及以獲獎新創案例分享ICTGC如何為新創提供從設計到量產的完整加速支持。
+國際觀展者亦歡迎蒞臨現場與 InnoVEX 及ICTGC 團隊交流，瞭解資源鏈結與競賽的徵件參與方式。
+ICTGC 2026 全球徵件開跑！助攻國際新創鍵結矽島
+ICTGC 現正開放全球報名，申請截止日為 2026 年 2 月 28 日。歡迎來自 AI、機器人、半導體技術、感測系統、次世代運算、深科技等領域的早期新創、學研團隊與技術開發者提交具潛力的創新應用提案。
+為協助國際新創擴大影響力、加速技術落地，入選團隊將於 2026 年 6 月 2 至 5 日在台北舉行的 COMPUTEX TAIPEI 與 InnoVEX 新創展中，獲得免費參展機會。
+作為亞洲指標性的 B2B 科技展，COMPUTEX 結合 InnoVEX 一站式的創投對接與國際媒合舞台，讓團隊有機會直接鏈結製造夥伴、半導體供應鏈、創投資源與國際買主，為布局半導體產業鏈之關鍵跳板。透過ICTGC計畫，獲獎團隊可望攜手台灣半導體生態系，共同開發具國際競爭力創新解決方案。
+報名網址：ictaiwanchallenge.org
+ICTGC首度矽谷登場　1 月 13 日攜手InnoVEX舉辦論壇深化台矽半導體與AI合作
+延續CES國際推廣動能，ICTGC將於2026年1月13日首度在矽谷Palo Alto的Startup Island TAIWAN – Silicon Valley Hub舉辦「Bridging Silicon Valley and Taiwan: Semiconductor &amp; AI Synergies」論壇。論壇匯聚矽谷創業者、投資人與技術專家，探討如何善用台灣半導體與AI供應鏈資源，強化創新落地與國際合作，更於現場為有興趣參與深度介紹將介紹競賽徵件內容與評選重點，及成功案例分享。
+國際團隊亦可藉由參加此論壇，了解更多於台灣 COMPUTEX/InnoVEX 展出資訊，協助其掌握成功進入市場的路徑並與臺灣ICT產業生態系建立實質連結。
+此次活動論壇除了邀請四位講者Laura Swan-Silicon Catalyst Ventures 共同合夥人，Andy Lombard-Tesoro Venture Capital 管理合夥人, Janis Skriveris-Plug and Play Ventures 投資總監暨高科技負責人以及Sam Fok-femtoAI 共同創辦人暨執行長，台北市電腦公會楊櫻姿副總幹事將帶領團隊提供矽谷新創人士更多鍵結台灣的資源，共同茁壯成長。
+現場將同時進行全球直播，預計將吸引全球相關新創人士觀看。直播連結為：
+Bridging Silicon Valley and Taiwan: Semiconductor &amp; AI Synergies
+2026 年 1 月 13 日（星期二）｜下午 5:00（PST）
+Startup Island TAIWAN – Silicon Valley Hub
+299 California Ave STE 300, Palo Alto, CA 94306 U.S.A.
+參考網址：
+「Bridging Silicon Valley and Taiwan: Semiconductor &amp; AI Synergies」論壇
+（發佈時間：2026-01-02）</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -675,7 +740,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>07bad44a832864eb1272dcab2762e4e86697da67fbc05a5934fb00417467b485</t>
+          <t>3e2cc7646f4acb278718f9a379e3fb9ff2aef32d2c4329d4a62d582c839ad49d</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -688,27 +753,50 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ICTGC競賽首登矽谷 進軍CES廣邀全球IC新創鏈結臺灣半導體生態鏈 - tca.org.tw</t>
+          <t>NYCU and Purdue Launch Global Semiconductor Academy to Advance AI and Chip Talent Development - 中央社 CNA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.tca.org.tw/news_detail.php?n=2454&amp;t=h</t>
+          <t>https://www.cna.com.tw/postwrite/eng/432806</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Fri, 02 Jan 2026 08:00:00 GMT</t>
+          <t>Thu, 07 May 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>tca.org.tw</t>
+          <t>中央社 CNA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ICTGCç«¶è³½é¦ç»ç½è°· é²è»CESå»£éå ¨çICæ°åµéçµèºç£åå°é«çæ é - å°åå¸é»è ¦åæ¥­åæ¥­å ¬æ Taipei Computer Association æå¡ç»å ¥ å å ¥TCA äººææå ç«å §æå° èªè­ TCA æ¬æç°¡ä» å¤§äºç´ çµç¹æ¶æ§ çç£äº å°æ¥­è¯ç æå¡æå ç¢æ¥­æ¨å»£ å±è¦½æé· åé¡ç«¶è³½ æ°åµæ´»å è¨ç«è³æº åå¥½é£çµ æ°èä¸­å¿ ç±éæ°è äººç©æ¡è¨ª æå¡å°è¨ª æ´»åæ å ± å½±åæ«¥çª TCA Video Gallery TCA Photo Gallery ç«å §æå° × æå° éé ç±éæ°è ICTGCç«¶è³½é¦ç»ç½è°· é²è»CESå»£éå ¨çICæ°åµéçµèºç£åå°é«çæ é IC Taiwan Grand Challengeåéæ¼CES 2025å±ä¸­ä¹TTAåå®¶é¤¨ä»ç´¹ç«¶è³½ åå®¶ç§å­¸åæè¡å§å¡æï¼NSTCï¼æå°çåéåµæ°ç«¶è³½IC Taiwan Grand Challengeï¼ICTGCï¼å°èå ¨çæ°åµå±æ InnoVEX ä¸»è¾¦å®ä½âå°åå¸é»è ¦å ¬æï¼TCAï¼æ¼ CES 2026 æéå ±åååä¸ç³»ååéäº¤æµæ´»åã é¢å° AI ç¡¬é«ãæ©å¨äººãå é²æ¶çèé«ç§æåµæ°å¿«éæ¼é²çå ¨çæµªæ½®ï¼InnoVEX æçºä½çºåéæ°åµå°æ¥äºæ´²æå é²ç§æç¢æ¥­çééµå ¥å£ï¼æ­¤æ¬¡ ICTGC x InnoVEX åéæ¨å»£è¡åé¤äºå¨CESå±æäº®ç¸ï¼ä¹å¾å°æ¼ 1 æ 13 æ¥å¨ç½è°·èè¾¦å°å ´æ´»åï¼åå©æ´å¤ç½è°·åéæ·±å ¥äºè§£å¦ä½ä¸²é£å°ç£å¨åå°é«è AI é åçä¸çç´è³æºï¼å±ç¾å°ç£æ¨åè·¨ååä½èæ¯æä¸ä¸ä»£ééµæè¡çæ±ºå¿èæ¿è«¾ã ICTGCãInnoVEXå°æ¼CES 2026é éç»å ´ å»£éå ¨çæ°åµèè¨TTAåå®¶é¤¨ å¨ CES 2026å±ææéï¼ IC Taiwan Grand Challengeï¼ICTGCï¼å°ææå ¨çåµæ°å±æInnoVEX å°äº®ç¸æ¼CES Eureka Park ç Taiwan Tech Arenaï¼TTAï¼åå®¶é¤¨ï¼Booth Venetian Expo, Hall G â 62201ï¼ãTTA çºåç§ææ¼ CES è¨­ç«çå®æ¹å±åï¼éå®å ·åç ç©¶å°åèæªä¾æ·±ç§ææ½åçæ°åµåéï¼æ¯å¹´å¸å¼å ¨çæè³äººãåéåªé«èç§æé è¢åè¨ªã ICTGC åéä¹å°æ¼ TTA Stage æ·±å ¥ä»ç´¹èºç£å¯ä¸å ·æå®æ´è¼å°æ©å¶ãå¯æ·±å ¥å°æ¥ç¢æ¥­éä¹åå°é«æ°åµç«¶è³½ï¼åä»¥ç²çæ°åµæ¡ä¾åäº«ICTGCå¦ä½çºæ°åµæä¾å¾è¨­è¨å°éç¢çå®æ´å éæ¯æã åéè§å±è äº¦æ­¡è¿èè¨ç¾å ´è InnoVEX åICTGC åéäº¤æµï¼ç­è§£è³æºéçµèç«¶è³½çå¾µä»¶åèæ¹å¼ã ICTGC 2026 å ¨çå¾µä»¶éè·ï¼å©æ»åéæ°åµéµçµç½å³¶ ICTGC ç¾æ­£éæ¾å ¨çå ±åï¼ç³è«æªæ­¢æ¥çº 2026 å¹´ 2 æ 28 æ¥ãæ­¡è¿ä¾èª AIãæ©å¨äººãåå°é«æè¡ãææ¸¬ç³»çµ±ãæ¬¡ä¸ä»£éç®ãæ·±ç§æç­é åçæ©ææ°åµãå­¸ç åéèæè¡éç¼è æäº¤å ·æ½åçåµæ°æç¨ææ¡ã çºåå©åéæ°åµæ´å¤§å½±é¿åãå éæè¡è½å°ï¼å ¥é¸åéå°æ¼ 2026 å¹´ 6 æ 2 è³ 5 æ¥å¨å°åèè¡ç COMPUTEX TAIPEI è InnoVEX æ°åµå±ä¸­ï¼ç²å¾å è²»åå±æ©æã ä½çºäºæ´²ææ¨æ§ç B2B ç§æå±ï¼COMPUTEX çµå InnoVEX ä¸ç«å¼çåµæå°æ¥èåéåªåèå°ï¼è®åéææ©æç´æ¥éçµè£½é å¤¥ä¼´ãåå°é«ä¾æéãåµæè³æºèåéè²·ä¸»ï¼çºå¸å±åå°é«ç¢æ¥­éä¹ééµè·³æ¿ãééICTGCè¨ç«ï¼ç²çåéå¯æææå°ç£åå°é«çæ ç³»ï¼å ±åéç¼å ·åéç«¶ç­ååµæ°è§£æ±ºæ¹æ¡ã å ±åç¶²åï¼ictaiwanchallenge.org ICTGCé¦åº¦ç½è°·ç»å ´ã1 æ 13 æ¥ææInnoVEXèè¾¦è«å£æ·±åå°ç½åå°é«èAIåä½ å»¶çºCESåéæ¨å»£åè½ï¼ICTGCå°æ¼2026å¹´1æ13æ¥é¦åº¦å¨ç½è°·Palo AltoçStartup Island TAIWAN â Silicon Valley Hubèè¾¦ãBridging Silicon Valley and Taiwan: Semiconductor &amp; AI Synergiesãè«å£ãè«å£å¯èç½è°·åµæ¥­è ãæè³äººèæè¡å°å®¶ï¼æ¢è¨å¦ä½åç¨å°ç£åå°é«èAIä¾æéè³æºï¼å¼·ååµæ°è½å°èåéåä½ï¼æ´æ¼ç¾å ´çºæèè¶£åèæ·±åº¦ä»ç´¹å°ä»ç´¹ç«¶è³½å¾µä»¶å §å®¹èè©é¸éé»ï¼åæåæ¡ä¾åäº«ã åéåéäº¦å¯èç±åå æ­¤è«å£ï¼äºè§£æ´å¤æ¼å°ç£ COMPUTEX/InnoVEX å±åºè³è¨ï¼åå©å ¶ææ¡æåé²å ¥å¸å ´çè·¯å¾ä¸¦èèºç£ICTç¢æ¥­çæ ç³»å»ºç«å¯¦è³ªé£çµã æ­¤æ¬¡æ´»åè«å£é¤äºéè«åä½è¬è Laura Swan-Silicon Catalyst Ventures å ±ååå¤¥äººï¼Andy Lombard-Tesoro Venture Capital ç®¡çåå¤¥äºº, Janis Skriveris-Plug and Play Ventures æè³ç¸½ç£æ¨é«ç§æè² è²¬äººä»¥åSam Fok-femtoAI å ±ååµè¾¦äººæ¨å·è¡é·ï¼å°åå¸é»è ¦å ¬ææ¥æ«»å§¿å¯ç¸½å¹¹äºå°å¸¶é åéæä¾ç½è°·æ°åµäººå£«æ´å¤éµçµå°ç£çè³æºï¼å ±åèå£¯æé·ã ç¾å ´å°åæé²è¡å ¨çç´æ­ï¼é è¨å°å¸å¼å ¨çç¸éæ°åµäººå£«è§çãç´æ­é£çµçºï¼https://www.youtube.com/live/ruXS6oe7WNA æ´»åè³è¨ Bridging Silicon Valley and Taiwan: Semiconductor &amp; AI Synergies 2026 å¹´ 1 æ 13 æ¥ï¼ææäºï¼ï½ä¸å 5:00ï¼PSTï¼ Startup Island TAIWAN â Silicon Valley Hub 299 California Ave STE 300, Palo Alto, CA 94306 U.S.A. åèç¶²åï¼ ãBridging Silicon Valley and Taiwan: Semiconductor &amp; AI Synergiesãè«å£ ï¼ç¼ä½æéï¼2026-01-02ï¼ ååè¡¨é  è½å¯ ã åå° ã åäº« å»¶ä¼¸é±è® InnoVEX 2026 ç«¶è³½ç»å ´ AVITICãPlug and PlayãPwCé¦æ³¢ç¹å¥çé½ç¼ï¼è¯æè³¦è½æ°åµéæåéçåè½é å®ç¢é³ä¿èè£äºé·æ¥ä»»çäºé· æè¨±å ±åè´åç¢æ¥­åéå äººç©æ¡è¨ª åç§æç¢å­¸èæå¾·çèé· : æ¨åç¢å­¸åä½è®ç ç¼ææè½å° æ°ä»»çç£äºæ¡è¨ªç³»åå ±å°(7)-æ¬æçäºæ¨å®ç¢æºé«é£å æ©è£äºé· : ãè³éè¨çµåçæãæ¯å°ç£æªä¾ç«¶ç­åªå¢ æ°ä»»çç£äºæ¡è¨ªç³»åå ±å°(6)-æ¬æçäºæ¨éææ©å¨äººé»è­å¿ çéé· : Edge AIæ¯å°ç£æ©å¨äººç¢æ¥­å½éè¶ è»çæ©æ ï¼ æ´å¤è¨æ¯ æå¡å°è¨ª TCAæå¡ä¼æ¥­å°è¨ª -å±¹å²ç§æï¼Eleosï¼ TCAæå¡ä¼æ¥­å°è¨ª -é²ä¸æè¾° TCAæå¡ä¼æ¥­å°è¨ª -å°ç£è³æç§æ ï¼ æ´å¤è¨æ¯ å»£å®£æå é±ç§æ¿ç­ è¯çµ¡æå äº¤éä½ç½® æå¡eåé Â© 2002ï¼2026 å°åå¸é»è ¦åæ¥­åæ¥­å ¬æ çæ¬ææ</t>
+          <t>Matsu’s “Blue Tears” Inspire NYCU Breakthrough in Next-Generation Luminescent Materials
+NYCU Partners with Kneron to Advance Edge AI Education and Real-World Deployment
+NYCU and Changhua County Launch Smart Agriculture App to Help Farmers Monitor Crops with AI
+NYCU Team Wins Taiwan Title at Red Bull Basement, Heads to Silicon Valley for Global Finals
+NYCU Study Finds Belly Fat May Signal Hidden Heart Failure Risk—Even at Normal Weight
+NYCU and Purdue Launch Global Semiconductor Academy to Advance AI and Chip Talent Development
+發稿時間：2026/05/07 14:14:32
+(中央社訊息服務20260507 14:14:32)As the global semiconductor race accelerates in the AI era, National Yang Ming Chiao Tung University (NYCU) and Purdue University have jointly launched the Semiconductor Academy, a new online professional education initiative designed to cultivate next-generation semiconductor talent and expand access to industry-focused learning worldwide.
+The collaboration brings together two institutions located at the heart of critical semiconductor ecosystems — Taiwan, home to the world’s most advanced chip manufacturing industry, and the United States, a global leader in semiconductor research, design, and innovation. Developed jointly by NYCU and Purdue, the Semiconductor Academy will offer flexible online courses covering key areas across the semiconductor supply chain, including chip design for AI, semiconductor materials and devices, advanced packaging, reliability, IC design, EDA, and semiconductor industry management.
+The program is designed for working professionals, engineers, and learners seeking to deepen their expertise or enter the rapidly evolving semiconductor field. Courses will be delivered online in a modular, stackable format, allowing learners to tailor their studies to their professional goals and industry needs.
+The Semiconductor Academy is a flexible, industry-aligned portfolio of Purdue University micro-credentials developed in collaboration with faculty from NYCU in Taiwan to help upskill the global semiconductor workforce.
+As one of Taiwan’s leading universities in electrical engineering, computer science, photonics, AI, and semiconductor research, NYCU has long played a central role in nurturing talent for Taiwan’s semiconductor industry and the Hsinchu Science Park ecosystem.
+Through the Semiconductor Academy, NYCU faculty will contribute academic expertise and real-world industry perspectives drawn from Taiwan’s globally influential semiconductor ecosystem, offering international learners a unique window into the technologies and manufacturing practices shaping the future of chips and AI computing.
+“Semiconductor innovation requires a deep understanding of the entire technology stack,” said Mark Lundstrom, Don and Carol Scifres Distinguished Professor of Electrical and Computer Engineering at Purdue University. “By bringing together the strengths of both Purdue and NYCU, the Semiconductor Academy provides learners with a rigorous, globally informed perspective on the technologies shaping the future of the industry.” The collaboration also reflects NYCU’s broader internationalization strategy and its commitment to strengthening global partnerships in semiconductors, AI, and emerging technologies.
+Covering topics from chip design and semiconductor materials to packaging and supply chain management, the Semiconductor Academy’s two-hour modular courses allow learners to build industry-relevant skills at their own pace.
+According to Purdue, the Semiconductor Academy is part of a broader expansion of semiconductor professional education aimed at addressing rising workforce demands across the global chip industry. Each course in the academy will feature approximately 2 hours of focused learning content and be accessible through flexible online formats. The academy will also be featured on SEMI University (SEMI U), a global digital learning platform serving semiconductor professionals and organizations worldwide.
+Topics planned for the initial course offerings include:
+。Chip Design for AI
+。Packaging, Reliability and Characterization
+。IC Design, EDA and Analog
+。Semiconductor Materials and Devices
+。Supply Chain Management and Leadership in the Semiconductor Industry
+Additional semiconductor professional education courses developed by Purdue are expected to launch in summer 2026, including transistor fundamentals, nanolithography, RF design, and data analysis for semiconductor applications. The launch ceremony for the Semiconductor Academy was held via livestream between Purdue and NYCU, underscoring the growing importance of international collaboration in building the future semiconductor workforce.
+For more NYCU News, please visit the official NYCU website.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -719,10 +807,50 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3ccc8d408c7b8b6a576a6c109f4331f3fdb5cb914a2a24b036a161f9c12492a9</t>
+          <t>18fb0777c7251bbf53690d6e918ab35a43212a286e270a47638a96b4e1d35bf9</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>市場報導： 2026年上半年半導體營收竟然達7千億美元，相當於2024年一整年總營收，AI太可怕了！ - 科技產業資訊室</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://iknow.stpi.niar.org.tw/Post/Read.aspx?PostID=23258</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Tue, 16 Jun 2026 02:26:21 GMT</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>科技產業資訊室</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Download failed</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/result.xlsx
+++ b/output/result.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,10 +488,8 @@
           <t>https://finance.technews.tw/2026/05/01/semiconductor-inflation-trend-takes-shape-wafer-foundries-ic-design-price-hikes/</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Fri, 01 May 2026 07:00:00 GMT</t>
-        </is>
+      <c r="D2" s="1" t="n">
+        <v>46143.29166666666</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -552,7 +554,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NYCU and Purdue Launch Global Semiconductor Academy to Advance AI and Chip Talent Development
+          <t>Matsu’s “Blue Tears” Inspire NYCU Breakthrough in Next-Generation Luminescent Materials
+NYCU Partners with Kneron to Advance Edge AI Education and Real-World Deployment
+NYCU and Changhua County Launch Smart Agriculture App to Help Farmers Monitor Crops with AI
+NYCU Team Wins Taiwan Title at Red Bull Basement, Heads to Silicon Valley for Global Finals
+NYCU Study Finds Belly Fat May Signal Hidden Heart Failure Risk—Even at Normal Weight
+NYCU and Purdue Launch Global Semiconductor Academy to Advance AI and Chip Talent Development
 發稿時間：2026/05/07 14:14:32
 (中央社訊息服務20260507 14:14:32)As the global semiconductor race accelerates in the AI era, National Yang Ming Chiao Tung University (NYCU) and Purdue University have jointly launched the Semiconductor Academy, a new online professional education initiative designed to cultivate next-generation semiconductor talent and expand access to industry-focused learning worldwide.
 The collaboration brings together two institutions located at the heart of critical semiconductor ecosystems — Taiwan, home to the world’s most advanced chip manufacturing industry, and the United States, a global leader in semiconductor research, design, and innovation. Developed jointly by NYCU and Purdue, the Semiconductor Academy will offer flexible online courses covering key areas across the semiconductor supply chain, including chip design for AI, semiconductor materials and devices, advanced packaging, reliability, IC design, EDA, and semiconductor industry management.
@@ -581,7 +588,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>99c1b51e2e4344e6fd4461f48b7839df56167ecec2c97ec84fb1251345ae320e</t>
+          <t>18fb0777c7251bbf53690d6e918ab35a43212a286e270a47638a96b4e1d35bf9</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -753,100 +760,33 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NYCU and Purdue Launch Global Semiconductor Academy to Advance AI and Chip Talent Development - 中央社 CNA</t>
+          <t>市場報導： 2026年上半年半導體營收竟然達7千億美元，相當於2024年一整年總營收，AI太可怕了！ - 科技產業資訊室</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.cna.com.tw/postwrite/eng/432806</t>
+          <t>https://iknow.stpi.niar.org.tw/Post/Read.aspx?PostID=23258</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Thu, 07 May 2026 07:00:00 GMT</t>
+          <t>Tue, 16 Jun 2026 02:26:21 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>中央社 CNA</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Matsu’s “Blue Tears” Inspire NYCU Breakthrough in Next-Generation Luminescent Materials
-NYCU Partners with Kneron to Advance Edge AI Education and Real-World Deployment
-NYCU and Changhua County Launch Smart Agriculture App to Help Farmers Monitor Crops with AI
-NYCU Team Wins Taiwan Title at Red Bull Basement, Heads to Silicon Valley for Global Finals
-NYCU Study Finds Belly Fat May Signal Hidden Heart Failure Risk—Even at Normal Weight
-NYCU and Purdue Launch Global Semiconductor Academy to Advance AI and Chip Talent Development
-發稿時間：2026/05/07 14:14:32
-(中央社訊息服務20260507 14:14:32)As the global semiconductor race accelerates in the AI era, National Yang Ming Chiao Tung University (NYCU) and Purdue University have jointly launched the Semiconductor Academy, a new online professional education initiative designed to cultivate next-generation semiconductor talent and expand access to industry-focused learning worldwide.
-The collaboration brings together two institutions located at the heart of critical semiconductor ecosystems — Taiwan, home to the world’s most advanced chip manufacturing industry, and the United States, a global leader in semiconductor research, design, and innovation. Developed jointly by NYCU and Purdue, the Semiconductor Academy will offer flexible online courses covering key areas across the semiconductor supply chain, including chip design for AI, semiconductor materials and devices, advanced packaging, reliability, IC design, EDA, and semiconductor industry management.
-The program is designed for working professionals, engineers, and learners seeking to deepen their expertise or enter the rapidly evolving semiconductor field. Courses will be delivered online in a modular, stackable format, allowing learners to tailor their studies to their professional goals and industry needs.
-The Semiconductor Academy is a flexible, industry-aligned portfolio of Purdue University micro-credentials developed in collaboration with faculty from NYCU in Taiwan to help upskill the global semiconductor workforce.
-As one of Taiwan’s leading universities in electrical engineering, computer science, photonics, AI, and semiconductor research, NYCU has long played a central role in nurturing talent for Taiwan’s semiconductor industry and the Hsinchu Science Park ecosystem.
-Through the Semiconductor Academy, NYCU faculty will contribute academic expertise and real-world industry perspectives drawn from Taiwan’s globally influential semiconductor ecosystem, offering international learners a unique window into the technologies and manufacturing practices shaping the future of chips and AI computing.
-“Semiconductor innovation requires a deep understanding of the entire technology stack,” said Mark Lundstrom, Don and Carol Scifres Distinguished Professor of Electrical and Computer Engineering at Purdue University. “By bringing together the strengths of both Purdue and NYCU, the Semiconductor Academy provides learners with a rigorous, globally informed perspective on the technologies shaping the future of the industry.” The collaboration also reflects NYCU’s broader internationalization strategy and its commitment to strengthening global partnerships in semiconductors, AI, and emerging technologies.
-Covering topics from chip design and semiconductor materials to packaging and supply chain management, the Semiconductor Academy’s two-hour modular courses allow learners to build industry-relevant skills at their own pace.
-According to Purdue, the Semiconductor Academy is part of a broader expansion of semiconductor professional education aimed at addressing rising workforce demands across the global chip industry. Each course in the academy will feature approximately 2 hours of focused learning content and be accessible through flexible online formats. The academy will also be featured on SEMI University (SEMI U), a global digital learning platform serving semiconductor professionals and organizations worldwide.
-Topics planned for the initial course offerings include:
-。Chip Design for AI
-。Packaging, Reliability and Characterization
-。IC Design, EDA and Analog
-。Semiconductor Materials and Devices
-。Supply Chain Management and Leadership in the Semiconductor Industry
-Additional semiconductor professional education courses developed by Purdue are expected to launch in summer 2026, including transistor fundamentals, nanolithography, RF design, and data analysis for semiconductor applications. The launch ceremony for the Semiconductor Academy was held via livestream between Purdue and NYCU, underscoring the growing importance of international collaboration in building the future semiconductor workforce.
-For more NYCU News, please visit the official NYCU website.</t>
-        </is>
-      </c>
+          <t>科技產業資訊室</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Success</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>18fb0777c7251bbf53690d6e918ab35a43212a286e270a47638a96b4e1d35bf9</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>IC semiconductor</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>市場報導： 2026年上半年半導體營收竟然達7千億美元，相當於2024年一整年總營收，AI太可怕了！ - 科技產業資訊室</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://iknow.stpi.niar.org.tw/Post/Read.aspx?PostID=23258</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Tue, 16 Jun 2026 02:26:21 GMT</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>科技產業資訊室</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
         <is>
           <t>Download failed</t>
         </is>

--- a/output/result.xlsx
+++ b/output/result.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,46 @@
       <c r="J1" t="inlineStr">
         <is>
           <t>error</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ai_summary</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ai_category</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ai_keywords</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ai_importance</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ai_model</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ai_version</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ai_analyze_time</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ai_confidence</t>
         </is>
       </c>
     </row>
@@ -525,6 +565,14 @@
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -592,6 +640,14 @@
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -632,6 +688,14 @@
           <t>Download failed</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -683,6 +747,14 @@
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -751,6 +823,14 @@
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -760,37 +840,376 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>市場報導： 2026年上半年半導體營收竟然達7千億美元，相當於2024年一整年總營收，AI太可怕了！ - 科技產業資訊室</t>
+          <t>中國 IC 設計市佔已超車台灣！IDC 揭 2026 半導體十大趨勢：地緣政治如何重塑供應鏈？ - TechOrange 科技報橘</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://iknow.stpi.niar.org.tw/Post/Read.aspx?PostID=23258</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Tue, 16 Jun 2026 02:26:21 GMT</t>
-        </is>
+          <t>https://techorange.com/2025/12/05/2026-semiconductor/</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45996.33333333334</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>科技產業資訊室</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>TechOrange 科技報橘</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>IDC 在今（12/5）發布 2026 年全球半導體市場十大趨勢預測，預期 2026 年全球半導體市場將維持雙位數成長動能，年成長率達 11%。
+「2026 年半導體產業將從爆發性復甦邁向穩健擴張的階段，」IDC 資深研究經理曾冠瑋表示，為了滿足指數級增長的運算需求，從 IC 設計、晶圓製造到先進封裝的整體價值鏈正處於高產能利用率狀態，供應鏈上下游的緊密協作，將是確保 AI 晶片順利量產與效能突破的關鍵。
+針對 2026 年全球半導體市場，IDC 歸納十大趨勢。
+根據 IDC 預測，2028 年全球半導體市場規模將突破 1 兆美元，2030 年更將達到 1.2 兆美元。這股由 AI 驅動的投資週期，將抵銷部分總體經濟的不確定性。
+不過，市場必須留意記憶體價格上漲的趨勢，若價格持續走高，可能影響 2026 下半年的市場動能。
+曾冠瑋分析，運算類別佔據半導體市場營收比重將持續攀升，預計 2025-2026 年市佔達 60%，其中 AI 伺服器核心晶片受惠於雲端訓練與邊緣推論需求的同步爆發，預計成長 32%。
+相對地，車用（Automotive）與消費性（Consumer）市場因庫存調整與成本上升，展望較為保守。
+IDC 預估 2026 年亞太區 IC 設計市場將成長 11%，不過正面臨歷史性的結構轉變，因為中國 IC 設計產值已於 2025 年正式超越台灣，確立其市場領先地位。
+IDC 預測，2026 年中國市佔率將進一步擴大至 45%，台灣則調整至 40%，此消長態勢源自中國在美方制裁下，仍積極發展本土 AI 晶片、高階手機處理器，加上虛擬貨幣與安防晶片需求強勁，因此帶動當地營收呈現倍數級成長。
+先進製程是 2026 年晶圓代工市場成長的核心引擎，預計推動整體產值成長 20%。隨著 AI 晶片算力需求增長，台積電預期市佔率將攀升至 73%，且維持 22-26% 的高成長率。
+在資本支出方面，IDC 預估台積電將達 480 億至 500 億美元，主要用於擴充 3nm、2nm 產能及為 1.6nm 做準備。台積電 2nm 預計於 2025 年底達到月產能 8 萬片。三星與 Intel 則分別在韓國華城、美國德州及俄亥俄州積極布局，試圖在 2027-2028 年的 AI 晶片商機中搶佔一席之地。
+IDC 預估 2026 年平均產能利用率將穩定維持在 80% 以上，特別是中國晶圓廠，受惠於國產替代政策以及驅動 IC、PMIC 等訂單回流，產能利用率預期將保持在 90% 以上的高檔水位。至於台灣、韓國等非中國地區，則受惠於消費性電子復甦，利用率約維持在 80%。
+全球半導體產能版圖正走向區域多元化，美國、中國與日本的晶圓產能年複合成長率（CAGR）預計將分別達到 9.8%、9.8% 與 10% 的新高水位。
+中國面對美方先進製程設備禁令，將資源集中擴充受限較小的成熟製程，並加速扶植國產設備供應鏈，預計最快在 2028 年其「所有製程總產能」將超越台灣居全球之冠，並於 2029 年達到 37% 的全球市佔率。
+在美國方面，台積電亞利桑那州廠進展順利，一廠（P1）已開始量產，二廠（P2A）預計於 2027 年上半年正式量產 3nm 製程，P2B 則鎖定 2027 年底至 2028 年加入 2nm 行列。
+日本亦展現重返半導體強國決心，除台積電熊本廠外，日本政府也全力支持新創晶片製造商 Rapidus。雖然目前日本全球產能佔比僅約 2.5% 至 3%，但在先進製程的戰略地位將顯著提升。
+地緣政治重塑全球封測版圖，預計 2026 年 OSAT 市場將成長 11%。中國在「半導體自主化」政策推動下，要求 IC 設計與晶圓製造盡量採用在地供應鏈，推動中國 OSAT 市佔率預計將從過去的 30% 攀升至 2029 年的 33%。
+然而，高階 AI 晶片封裝仍由台灣與美國大廠掌握優勢。值得注意的是，若以包含晶圓代工廠先進封裝（Foundry-based packaging）的「封裝總市值」重新排名，受惠於 CoWoS 與 InFO 的高價值貢獻，台積電預計將在 2026 年超越傳統封測廠，成為全球封裝市值的實質龍頭。
+先進封裝產能擴張將是 2026 年的主旋律。IDC 預測，台積電 2026 年底 CoWoS 月產能將來到 11 萬片，但面對 NVIDIA、AMD 等巨頭將主力晶片全數投入 3nm 製程且 100% 採用先進封裝，市場供需依然吃緊。
+這股外溢效應將為 OSAT 廠帶來機會：日月光與矽品憑藉與台積電的長期合作，預計在 2025 年中旬開始有明顯的訂單放量；Intel 雖積極推廣封裝代工，但考量玻璃基板與高階封裝的良率需達 90% 以上才具經濟效益，預期要到 2027 年才能在 CSP 自研晶片市場中見到顯著貢獻。
+AI 加速器市場預計迎來爆發性成長。受惠於 Google TPU、AWS Trainium 等 CSP 自研晶片需求，IDC 預估 2026 年 ASIC 市場年增率將高達 173%。
+長期而言，為了優化 TCO，CSP 與模型開發商將持續擴大 ASIC 採用比例，推動 ASIC 在 2024-2029 年的年均複合成長率達到 67%。然而，GPU 並不會因此失勢，因為隨著「影像生成」的需求大增，未來的 AI 電影與即時影像運算需要極具彈性的通用算力，這將是 GPU 長期難以被取代的護城河，也讓 GPU 的年均複合成長率仍維持 56% 的高成長動能。
+針對市場擔憂的「AI 泡沫化」，IDC 認為 2026 年發生機率偏低，主因在於 AI 基礎建設並非無限制擴張，而是受到「電力供應」與「能源網架構」的物理限制。CSP 業者無法在缺乏電力配套下無限採購晶片，這種物理上的「調節閥」反而讓半導體出貨維持在相對健康、理性的成長軌道，避免了過度庫存堆積導致的瞬間崩盤。
+2026 年全球半導體產業將延續雙位數成長，從爆發期邁入「穩健擴張」階段。在這段過程中，地緣政治帶來的供應鏈重組、中國產能的強勢崛起，以及 AI 基礎建設是否會因電力瓶頸而調整節奏，將是決定產業走向的關鍵變數。</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Download failed</t>
-        </is>
-      </c>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2ff7ce7ea89916c1195ccf726a2cbe400b942f1532cf8c7e112d739602e99d8f</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>半導體通膨趨勢成形，晶圓代工、IC 設計紛漲價 - TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://finance.technews.tw/2026/05/01/semiconductor-inflation-trend-takes-shape-wafer-foundries-ic-design-price-hikes/</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Fri, 01 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>半導體通膨趨勢成形，因應成本高漲，包括晶圓代工及 IC 設計廠紛紛調漲價格，對於智慧手機等消費產品市場影響逐步顯現，智慧手機等今年出貨量恐面臨衰退壓力。
+半導體廠法人說明會陸續登場，成本壓力及產品價格策略成為法人關注的焦點。晶圓代工廠除將持續投入技術開發及擴充產能，中東緊張局勢也造成能源和物流等成本升高。
+晶圓代工廠
+已搶先於今年1月調漲驅動IC及感測器代工價格，3月調漲功率元件代工價格，
+先進跟進於4月調漲代工價格，
+也於4月通知客戶，將於下半年調整價格。
+不僅晶圓代工價格調漲，後段封測價格也傳出漲價消息，IC設計廠紛紛決定調漲產品售價，減緩成本升高的影響，
+3月已通知客戶，
+透露將藉由嚴謹的定價策略，目標將全年毛利率維持在44.5%至47.5%區間。
+觀察目前整體市況依然呈現不同調的態勢，AI相關市場需求持續強勁，消費電子市場需求相對疲弱，IC設計廠不打算全面調漲產品價格。
+雅特力-KY認為，近期微控制器（MCU）市場掀起一波漲價潮，並不是終端市場強勁需求所帶動，而是AI需求強勁占用產能，以及原材料漲價所致，雅特力-KY僅會適度漲價，力求毛利率持穩。
+盛群認為，目前經濟情勢並未變好，需求僅穩定，因應晶圓代工與封測漲價10%至15%，盛群將僅調漲低毛利產品售價，期能讓毛利回歸合理。
+繼記憶體價格飆漲後，晶圓代工和IC設計紛紛調漲價格，半導體通膨趨勢成形，使得智慧手機等消費產品市場，面臨成本升高的壓力進一步加劇。廠商除將資源集中於高階產品因應，需求也開始趨緩，聯發科預估，今年手機出貨量恐減少15%。漲價對市場需求的影響，未來是否進一步擴大，備受市場關注。</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>46237.86427756945</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>c892500cb00e9052a353b06c891bd622ea32067b72b66139cc189e69c86dfbd3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>全台首家IC設計獲Arm注資 通寶半導體Q4擬申請IPO - 工商時報</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.ctee.com.tw/news/20260304700096-439901</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Wed, 04 Mar 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>工商時報</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>通寶半導體設計公司簡介
+台灣IC設計領域傳出國際策略投資合作捷報，通寶半導體（QBit Semiconductor）公司3日宣布，已完成B輪募資，並獲全球半導體架構大廠安謀公司（Arm Limited）參與投資，成為目前全台唯一獲得Arm投資的IC設計公司。
+安謀現成為通寶十大股東之一，至於安謀持股比例及金額，4月下旬召開法說會可望對外說明，未來通寶擬計畫跨足無人機及機器人市場。
+通寶半導體同時宣布，隨著募資完成營運規模擴大，計畫於今年第四季向臺灣證券交易所申請IPO上市，進一步邁向資本市場新里程碑，實際時程仍須視主管機關核准及市場狀況而定。
+通寶半導體為專攻多功能列印機及事務機系統晶片的IC設計公司，其客戶主要市場遍及美國、日本、中國跟台灣。除Arm參與投資外，據悉，通寶半導體在A輪募資時，台灣政府法人機構持有通寶半導體約6％股權，包括國發基金持股2.7％，以及台肥、工研院等公股事業合計持股比例約6％，還有智原科技等半導體產業加入，整體A輪投資人持股比例約為通寶已發行股權10％。
+對於這項注資，Arm全球執行副總裁暨商務長Will Abbey表示，透過與通寶的合作，可以結合先進影像處理、控制與安全能力，以支持列印及影像市場的創新。此類合作展現Arm更廣泛的策略，亦即推動具差異化的解決方案，從高效能系統延伸至更具成本效益的裝置，同時為各類產品建立成長基礎。
+通寶半導體創辦人暨執行長沈軾榮也表示，很榮幸成為獲得Arm唯一投資的台灣半導體設計公司，未來通寶將持續深化在印表機影像市場的布局，並拓展至更廣泛的影像相關應用領域。
+將工商時報加入Google偏好來源</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>46237.8643865162</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ab0ba52b718011d084d7791b678dec6ea2fcabe421fbf2d21d47ffbe4c3e8366</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ICTGC競賽首登矽谷 進軍CES廣邀全球IC新創鏈結臺灣半導體生態鏈 - tca.org.tw</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.tca.org.tw/news_detail.php?n=2454&amp;t=h</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Fri, 02 Jan 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>tca.org.tw</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ICTGC競賽首登矽谷 進軍CES廣邀全球IC新創鏈結臺灣半導體生態鏈
+IC Taiwan Grand Challenge團隊於CES 2025展中之TTA國家館介紹競賽
+國家科學及技術委員會（NSTC）指導的國際創新競賽IC Taiwan Grand Challenge（ICTGC）將與全球新創展會 InnoVEX 主辦單位—台北市電腦公會（TCA）於 CES 2026 期間共同啟動一系列國際交流活動。
+面對 AI 硬體、機器人、先進晶片與高科技創新快速演進的全球浪潮，InnoVEX 持續作為國際新創對接亞洲最先進科技產業的關鍵入口，此次 ICTGC x InnoVEX 國際推廣行動除了在CES展會亮相，之後將於 1 月 13 日在矽谷舉辦專場活動，協助更多矽谷團隊深入了解如何串連台灣在半導體與 AI 領域的世界級資源，展現台灣推動跨國合作與支持下一代關鍵技術的決心與承諾。
+ICTGC、InnoVEX將於CES 2026領銜登場 廣邀全球新創蒞臨TTA國家館
+在 CES 2026展會期間， IC Taiwan Grand Challenge（ICTGC）將攜手全球創新展會InnoVEX 將亮相於CES Eureka Park 的 Taiwan Tech Arena（TTA）國家館（Booth Venetian Expo, Hall G — 62201）。TTA 為國科會於 CES 設立的官方展區，鎖定具備研究導向與未來深科技潛力的新創團隊，每年吸引全球投資人、國際媒體與科技領袖參訪。
+ICTGC 團隊也將於 TTA Stage 深入介紹臺灣唯一具有完整輔導機制、可深入對接產業鏈之半導體新創競賽，及以獲獎新創案例分享ICTGC如何為新創提供從設計到量產的完整加速支持。
+國際觀展者亦歡迎蒞臨現場與 InnoVEX 及ICTGC 團隊交流，瞭解資源鏈結與競賽的徵件參與方式。
+ICTGC 2026 全球徵件開跑！助攻國際新創鍵結矽島
+ICTGC 現正開放全球報名，申請截止日為 2026 年 2 月 28 日。歡迎來自 AI、機器人、半導體技術、感測系統、次世代運算、深科技等領域的早期新創、學研團隊與技術開發者提交具潛力的創新應用提案。
+為協助國際新創擴大影響力、加速技術落地，入選團隊將於 2026 年 6 月 2 至 5 日在台北舉行的 COMPUTEX TAIPEI 與 InnoVEX 新創展中，獲得免費參展機會。
+作為亞洲指標性的 B2B 科技展，COMPUTEX 結合 InnoVEX 一站式的創投對接與國際媒合舞台，讓團隊有機會直接鏈結製造夥伴、半導體供應鏈、創投資源與國際買主，為布局半導體產業鏈之關鍵跳板。透過ICTGC計畫，獲獎團隊可望攜手台灣半導體生態系，共同開發具國際競爭力創新解決方案。
+報名網址：ictaiwanchallenge.org
+ICTGC首度矽谷登場　1 月 13 日攜手InnoVEX舉辦論壇深化台矽半導體與AI合作
+延續CES國際推廣動能，ICTGC將於2026年1月13日首度在矽谷Palo Alto的Startup Island TAIWAN – Silicon Valley Hub舉辦「Bridging Silicon Valley and Taiwan: Semiconductor &amp; AI Synergies」論壇。論壇匯聚矽谷創業者、投資人與技術專家，探討如何善用台灣半導體與AI供應鏈資源，強化創新落地與國際合作，更於現場為有興趣參與深度介紹將介紹競賽徵件內容與評選重點，及成功案例分享。
+國際團隊亦可藉由參加此論壇，了解更多於台灣 COMPUTEX/InnoVEX 展出資訊，協助其掌握成功進入市場的路徑並與臺灣ICT產業生態系建立實質連結。
+此次活動論壇除了邀請四位講者Laura Swan-Silicon Catalyst Ventures 共同合夥人，Andy Lombard-Tesoro Venture Capital 管理合夥人, Janis Skriveris-Plug and Play Ventures 投資總監暨高科技負責人以及Sam Fok-femtoAI 共同創辦人暨執行長，台北市電腦公會楊櫻姿副總幹事將帶領團隊提供矽谷新創人士更多鍵結台灣的資源，共同茁壯成長。
+現場將同時進行全球直播，預計將吸引全球相關新創人士觀看。直播連結為：
+Bridging Silicon Valley and Taiwan: Semiconductor &amp; AI Synergies
+2026 年 1 月 13 日（星期二）｜下午 5:00（PST）
+Startup Island TAIWAN – Silicon Valley Hub
+299 California Ave STE 300, Palo Alto, CA 94306 U.S.A.
+參考網址：
+「Bridging Silicon Valley and Taiwan: Semiconductor &amp; AI Synergies」論壇
+（發佈時間：2026-01-02）</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>46237.864415625</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>e4ac11cb4fcbfe85b0cee5b80deaf1b76ee2e40c21af99a317cd4a3a94cab310</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>中國 IC 設計市佔已超車台灣！IDC 揭 2026 半導體十大趨勢：地緣政治如何重塑供應鏈？ - TechOrange 科技報橘</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://techorange.com/2025/12/05/2026-semiconductor/</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Fri, 05 Dec 2025 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>TechOrange 科技報橘</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>IDC 在今（12/5）發布 2026 年全球半導體市場十大趨勢預測，預期 2026 年全球半導體市場將維持雙位數成長動能，年成長率達 11%。
+「2026 年半導體產業將從爆發性復甦邁向穩健擴張的階段，」IDC 資深研究經理曾冠瑋表示，為了滿足指數級增長的運算需求，從 IC 設計、晶圓製造到先進封裝的整體價值鏈正處於高產能利用率狀態，供應鏈上下游的緊密協作，將是確保 AI 晶片順利量產與效能突破的關鍵。
+針對 2026 年全球半導體市場，IDC 歸納十大趨勢。
+根據 IDC 預測，2028 年全球半導體市場規模將突破 1 兆美元，2030 年更將達到 1.2 兆美元。這股由 AI 驅動的投資週期，將抵銷部分總體經濟的不確定性。
+不過，市場必須留意記憶體價格上漲的趨勢，若價格持續走高，可能影響 2026 下半年的市場動能。
+曾冠瑋分析，運算類別佔據半導體市場營收比重將持續攀升，預計 2025-2026 年市佔達 60%，其中 AI 伺服器核心晶片受惠於雲端訓練與邊緣推論需求的同步爆發，預計成長 32%。
+相對地，車用（Automotive）與消費性（Consumer）市場因庫存調整與成本上升，展望較為保守。
+IDC 預估 2026 年亞太區 IC 設計市場將成長 11%，不過正面臨歷史性的結構轉變，因為中國 IC 設計產值已於 2025 年正式超越台灣，確立其市場領先地位。
+IDC 預測，2026 年中國市佔率將進一步擴大至 45%，台灣則調整至 40%，此消長態勢源自中國在美方制裁下，仍積極發展本土 AI 晶片、高階手機處理器，加上虛擬貨幣與安防晶片需求強勁，因此帶動當地營收呈現倍數級成長。
+先進製程是 2026 年晶圓代工市場成長的核心引擎，預計推動整體產值成長 20%。隨著 AI 晶片算力需求增長，台積電預期市佔率將攀升至 73%，且維持 22-26% 的高成長率。
+在資本支出方面，IDC 預估台積電將達 480 億至 500 億美元，主要用於擴充 3nm、2nm 產能及為 1.6nm 做準備。台積電 2nm 預計於 2025 年底達到月產能 8 萬片。三星與 Intel 則分別在韓國華城、美國德州及俄亥俄州積極布局，試圖在 2027-2028 年的 AI 晶片商機中搶佔一席之地。
+IDC 預估 2026 年平均產能利用率將穩定維持在 80% 以上，特別是中國晶圓廠，受惠於國產替代政策以及驅動 IC、PMIC 等訂單回流，產能利用率預期將保持在 90% 以上的高檔水位。至於台灣、韓國等非中國地區，則受惠於消費性電子復甦，利用率約維持在 80%。
+全球半導體產能版圖正走向區域多元化，美國、中國與日本的晶圓產能年複合成長率（CAGR）預計將分別達到 9.8%、9.8% 與 10% 的新高水位。
+中國面對美方先進製程設備禁令，將資源集中擴充受限較小的成熟製程，並加速扶植國產設備供應鏈，預計最快在 2028 年其「所有製程總產能」將超越台灣居全球之冠，並於 2029 年達到 37% 的全球市佔率。
+在美國方面，台積電亞利桑那州廠進展順利，一廠（P1）已開始量產，二廠（P2A）預計於 2027 年上半年正式量產 3nm 製程，P2B 則鎖定 2027 年底至 2028 年加入 2nm 行列。
+日本亦展現重返半導體強國決心，除台積電熊本廠外，日本政府也全力支持新創晶片製造商 Rapidus。雖然目前日本全球產能佔比僅約 2.5% 至 3%，但在先進製程的戰略地位將顯著提升。
+地緣政治重塑全球封測版圖，預計 2026 年 OSAT 市場將成長 11%。中國在「半導體自主化」政策推動下，要求 IC 設計與晶圓製造盡量採用在地供應鏈，推動中國 OSAT 市佔率預計將從過去的 30% 攀升至 2029 年的 33%。
+然而，高階 AI 晶片封裝仍由台灣與美國大廠掌握優勢。值得注意的是，若以包含晶圓代工廠先進封裝（Foundry-based packaging）的「封裝總市值」重新排名，受惠於 CoWoS 與 InFO 的高價值貢獻，台積電預計將在 2026 年超越傳統封測廠，成為全球封裝市值的實質龍頭。
+先進封裝產能擴張將是 2026 年的主旋律。IDC 預測，台積電 2026 年底 CoWoS 月產能將來到 11 萬片，但面對 NVIDIA、AMD 等巨頭將主力晶片全數投入 3nm 製程且 100% 採用先進封裝，市場供需依然吃緊。
+這股外溢效應將為 OSAT 廠帶來機會：日月光與矽品憑藉與台積電的長期合作，預計在 2025 年中旬開始有明顯的訂單放量；Intel 雖積極推廣封裝代工，但考量玻璃基板與高階封裝的良率需達 90% 以上才具經濟效益，預期要到 2027 年才能在 CSP 自研晶片市場中見到顯著貢獻。
+AI 加速器市場預計迎來爆發性成長。受惠於 Google TPU、AWS Trainium 等 CSP 自研晶片需求，IDC 預估 2026 年 ASIC 市場年增率將高達 173%。
+長期而言，為了優化 TCO，CSP 與模型開發商將持續擴大 ASIC 採用比例，推動 ASIC 在 2024-2029 年的年均複合成長率達到 67%。然而，GPU 並不會因此失勢，因為隨著「影像生成」的需求大增，未來的 AI 電影與即時影像運算需要極具彈性的通用算力，這將是 GPU 長期難以被取代的護城河，也讓 GPU 的年均複合成長率仍維持 56% 的高成長動能。
+針對市場擔憂的「AI 泡沫化」，IDC 認為 2026 年發生機率偏低，主因在於 AI 基礎建設並非無限制擴張，而是受到「電力供應」與「能源網架構」的物理限制。CSP 業者無法在缺乏電力配套下無限採購晶片，這種物理上的「調節閥」反而讓半導體出貨維持在相對健康、理性的成長軌道，避免了過度庫存堆積導致的瞬間崩盤。
+2026 年全球半導體產業將延續雙位數成長，從爆發期邁入「穩健擴張」階段。在這段過程中，地緣政治帶來的供應鏈重組、中國產能的強勢崛起，以及 AI 基礎建設是否會因電力瓶頸而調整節奏，將是決定產業走向的關鍵變數。</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>46237.86443957176</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>c2c888cdc2d8914d55b2a9bb7e967671464e5d36db98adfd86fd9fe4d8cf4879</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/result.xlsx
+++ b/output/result.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:U54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -533,7 +533,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>b3b4ad83b48702ce2ea2055f535e5d4b8ca5a70c50ef915e3c62756f15346df4</t>
+          <t>0ac76262e3803be4963f9143832b061295d6c5a580ed0a1ab054cee036600710</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -543,92 +543,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>台灣IC設計產業：年營收破千億美元，蟄伏於供應鏈背後的全球王者 - 報新聞</t>
+          <t>施振榮看好NEO Semiconductor推動AI記憶體創新- 產業 - 工商時報</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.contentplatform.info/articles/492757/taiwan-ic-design-industry-mediatek-realtek-novatek-ai-semiconductor/</t>
+          <t>https://www.ctee.com.tw/news/20260806701438-430502</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>報新聞</t>
+          <t>工商時報</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fri, 07 Aug 2026 17:23:43 GMT</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" s="1" t="n">
-        <v>46242.57756180505</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>0ac76262e3803be4963f9143832b061295d6c5a580ed0a1ab054cee036600710</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>IC semiconductor</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>施振榮看好NEO Semiconductor推動AI記憶體創新- 產業 - 工商時報</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>https://www.ctee.com.tw/news/20260806701438-430502</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>工商時報</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
           <t>Thu, 06 Aug 2026 08:26:00 GMT</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>由矽谷華人許富菖創立的AI記憶體公司NEO Semiconductor，今（6）日於全球記憶體與儲存產業年度盛會Future Memory and Storage（FMS 2026），發表新一代AI晶片內建記憶體技術X-SRAM，並同步推出NEO.AI平台。
 該平台整合X-SRAM與3D X-DRAM兩項核心技術，致力解決AI晶片內建記憶體容量不足，以及高頻寬記憶體（HBM）容量與功耗限制等兩大挑戰。
@@ -645,8 +578,75 @@
 將工商時報加入Google偏好來源</t>
         </is>
       </c>
+      <c r="I2" s="1" t="n">
+        <v>46244.62251445602</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>b3b4ad83b48702ce2ea2055f535e5d4b8ca5a70c50ef915e3c62756f15346df4</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>台灣IC設計產業：年營收破千億美元，蟄伏於供應鏈背後的全球王者 - 報新聞</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://www.contentplatform.info/articles/492757/taiwan-ic-design-industry-mediatek-realtek-novatek-ai-semiconductor/</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>報新聞</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:23:43 GMT</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" s="1" t="n">
-        <v>46242.57759101647</v>
+        <v>46244.62257930556</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="I4" s="1" t="n">
-        <v>46242.57761462817</v>
+        <v>46244.62260273148</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="I5" s="1" t="n">
-        <v>46242.57763964016</v>
+        <v>46244.62263523148</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" s="1" t="n">
-        <v>46242.57766593536</v>
+        <v>46244.62265920139</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -920,6 +920,4555 @@
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>e4ac11cb4fcbfe85b0cee5b80deaf1b76ee2e40c21af99a317cd4a3a94cab310</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ICTGC競賽首登矽谷 進軍CES廣邀全球IC新創鏈結臺灣半導體生態鏈 - tca.org.tw</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://www.tca.org.tw/news_detail.php?n=2454&amp;t=h</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>tca.org.tw</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fri, 02 Jan 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ICTGC競賽首登矽谷 進軍CES廣邀全球IC新創鏈結臺灣半導體生態鏈
+IC Taiwan Grand Challenge團隊於CES 2025展中之TTA國家館介紹競賽
+國家科學及技術委員會（NSTC）指導的國際創新競賽IC Taiwan Grand Challenge（ICTGC）將與全球新創展會 InnoVEX 主辦單位—台北市電腦公會（TCA）於 CES 2026 期間共同啟動一系列國際交流活動。
+面對 AI 硬體、機器人、先進晶片與高科技創新快速演進的全球浪潮，InnoVEX 持續作為國際新創對接亞洲最先進科技產業的關鍵入口，此次 ICTGC x InnoVEX 國際推廣行動除了在CES展會亮相，之後將於 1 月 13 日在矽谷舉辦專場活動，協助更多矽谷團隊深入了解如何串連台灣在半導體與 AI 領域的世界級資源，展現台灣推動跨國合作與支持下一代關鍵技術的決心與承諾。
+ICTGC、InnoVEX將於CES 2026領銜登場 廣邀全球新創蒞臨TTA國家館
+在 CES 2026展會期間， IC Taiwan Grand Challenge（ICTGC）將攜手全球創新展會InnoVEX 將亮相於CES Eureka Park 的 Taiwan Tech Arena（TTA）國家館（Booth Venetian Expo, Hall G — 62201）。TTA 為國科會於 CES 設立的官方展區，鎖定具備研究導向與未來深科技潛力的新創團隊，每年吸引全球投資人、國際媒體與科技領袖參訪。
+ICTGC 團隊也將於 TTA Stage 深入介紹臺灣唯一具有完整輔導機制、可深入對接產業鏈之半導體新創競賽，及以獲獎新創案例分享ICTGC如何為新創提供從設計到量產的完整加速支持。
+國際觀展者亦歡迎蒞臨現場與 InnoVEX 及ICTGC 團隊交流，瞭解資源鏈結與競賽的徵件參與方式。
+ICTGC 2026 全球徵件開跑！助攻國際新創鍵結矽島
+ICTGC 現正開放全球報名，申請截止日為 2026 年 2 月 28 日。歡迎來自 AI、機器人、半導體技術、感測系統、次世代運算、深科技等領域的早期新創、學研團隊與技術開發者提交具潛力的創新應用提案。
+為協助國際新創擴大影響力、加速技術落地，入選團隊將於 2026 年 6 月 2 至 5 日在台北舉行的 COMPUTEX TAIPEI 與 InnoVEX 新創展中，獲得免費參展機會。
+作為亞洲指標性的 B2B 科技展，COMPUTEX 結合 InnoVEX 一站式的創投對接與國際媒合舞台，讓團隊有機會直接鏈結製造夥伴、半導體供應鏈、創投資源與國際買主，為布局半導體產業鏈之關鍵跳板。透過ICTGC計畫，獲獎團隊可望攜手台灣半導體生態系，共同開發具國際競爭力創新解決方案。
+報名網址：ictaiwanchallenge.org
+ICTGC首度矽谷登場　1 月 13 日攜手InnoVEX舉辦論壇深化台矽半導體與AI合作
+延續CES國際推廣動能，ICTGC將於2026年1月13日首度在矽谷Palo Alto的Startup Island TAIWAN – Silicon Valley Hub舉辦「Bridging Silicon Valley and Taiwan: Semiconductor &amp; AI Synergies」論壇。論壇匯聚矽谷創業者、投資人與技術專家，探討如何善用台灣半導體與AI供應鏈資源，強化創新落地與國際合作，更於現場為有興趣參與深度介紹將介紹競賽徵件內容與評選重點，及成功案例分享。
+國際團隊亦可藉由參加此論壇，了解更多於台灣 COMPUTEX/InnoVEX 展出資訊，協助其掌握成功進入市場的路徑並與臺灣ICT產業生態系建立實質連結。
+此次活動論壇除了邀請四位講者Laura Swan-Silicon Catalyst Ventures 共同合夥人，Andy Lombard-Tesoro Venture Capital 管理合夥人, Janis Skriveris-Plug and Play Ventures 投資總監暨高科技負責人以及Sam Fok-femtoAI 共同創辦人暨執行長，台北市電腦公會楊櫻姿副總幹事將帶領團隊提供矽谷新創人士更多鍵結台灣的資源，共同茁壯成長。
+現場將同時進行全球直播，預計將吸引全球相關新創人士觀看。直播連結為：
+Bridging Silicon Valley and Taiwan: Semiconductor &amp; AI Synergies
+2026 年 1 月 13 日（星期二）｜下午 5:00（PST）
+Startup Island TAIWAN – Silicon Valley Hub
+299 California Ave STE 300, Palo Alto, CA 94306 U.S.A.
+參考網址：
+「Bridging Silicon Valley and Taiwan: Semiconductor &amp; AI Synergies」論壇
+（發佈時間：2026-01-02）</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>46244.62278165509</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>858c62d825b27cd022cdc524a608aa9f87e352944400bbdf64555e4511a193c6</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>瑞昱半導體網通音訊IC領先 全球電子產品仰賴台灣實力 - 財經新聞 - PChome Online 新聞 - news.pchome.com.tw</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://news.pchome.com.tw/finance/sunmedia/20260330/index-77484256473773329003.html</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>news.pchome.com.tw</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Mon, 30 Mar 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>圖／本報資料庫
+｜何映辰／台北報導
+台灣積體電路設計大廠瑞昱半導體（Realtek Semiconductor Corp）在全球網通與音訊積體電路（IC）市場扮演關鍵角色，其技術實力驅動著個人電腦與消費性電子產品的發展，並連結台灣IC設計產業在全球供應鏈中的重要地位。該公司以無晶圓廠（fabless）模式運作，專精於設計與行銷通訊、多媒體及周邊裝置所需的各類晶片。
+瑞昱半導體的產品線多元，涵蓋乙太網路控制器、Wi-Fi解決方案、音訊編解碼器及高畫質多媒體晶片。這些高效能晶片支援數據傳輸、音訊處理與多媒體操控，廣泛應用於全球主機板、筆記型電腦、路由器及智慧裝置中。華碩（Asus）、技嘉（Gigabyte）、微星（MSI）等主要OEM客戶皆將瑞昱的解決方案整合至其產品。在乙太網路晶片領域，瑞昱提供支援 Gigabit、2.5G及5G速度的區域網路（LAN）介面卡，在PC主機板與網通設備市場佔據主導地位。此外，其ALC系列音訊編解碼器則嵌入在數百萬台筆記型電腦與桌上型電腦中，負責處理高傳真音效。
+面對英特爾（Intel）、博通（Broadcom）及聯發科（MediaTek）等巨頭的競爭，瑞昱透過快速創新與穩固的OEM客戶關係，在成本效益高且出貨量龐大的消費性及PC市場取得競爭優勢。該公司專注於乙太網路實體層（Ethernet PHY）與音訊數位類比轉換器（DAC）等利基市場，並在這些類別中掌握顯著市佔。北極星市場情報（NorthStar Market Insights）資深財經編輯艾蕾娜·瓦茲奎茲博士（Dr. Elena Vasquez）曾表示，瑞昱半導體將可靠的晶片設計與物聯網（IoT）、5G及消費性電子產品的持久需求連結起來。
+當前市場對瑞昱通訊IC的需求，正受惠於5G基礎設施、邊緣運算及物聯網裝置的擴張，而居家及辦公網路升級也持續推動乙太網路晶片的銷售。此外，8K串流與AI工作負載所需的頻寬，亦刺激對高速區域網路解決方案的需求。在供應鏈方面，瑞昱半導體仰賴台灣半導體產業聚落的支援，包括與台積電（TSMC）等晶圓代工夥伴的合作。對於尋求亞洲科技領袖投資機會的北美投資者而言，瑞昱半導體提供了一個穩定且具代表性的選項，能有效平衡以美國為中心的晶片製造商。
+然而，瑞昱也面臨多重風險。其中，圍繞台灣的地緣政治緊張局勢，因其地理位置及對區域晶圓代工廠的依賴，被視為主要潛在風險。激烈的市場競爭亦對利潤造成壓力，尤其當競爭對手在高端市場加速創新時。半導體產業的週期性需求則導致營收波動，PC出貨量放緩會直接影響其業績。瑞昱必須持續投入研發，才能在中階市場維持其成本領先地位。該公司目前正積極投入Wi-Fi 7與PCIe Gen5技術的採用進程。
+新聞關鍵字：
+intel
+記者：商傳媒
+更多財經新聞 »</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>46244.62280597222</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>5e2150db004a7711293be698d35503f37f1430da74b1cbad0d35736d127bb684</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>中國 IC 設計市佔已超車台灣！IDC 揭 2026 半導體十大趨勢：地緣政治如何重塑供應鏈？ - techorange.com</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://techorange.com/2025/12/05/2026-semiconductor/</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>techorange.com</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fri, 05 Dec 2025 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>IDC 在今（12/5）發布 2026 年全球半導體市場十大趨勢預測，預期 2026 年全球半導體市場將維持雙位數成長動能，年成長率達 11%。
+「2026 年半導體產業將從爆發性復甦邁向穩健擴張的階段，」IDC 資深研究經理曾冠瑋表示，為了滿足指數級增長的運算需求，從 IC 設計、晶圓製造到先進封裝的整體價值鏈正處於高產能利用率狀態，供應鏈上下游的緊密協作，將是確保 AI 晶片順利量產與效能突破的關鍵。
+針對 2026 年全球半導體市場，IDC 歸納十大趨勢。
+根據 IDC 預測，2028 年全球半導體市場規模將突破 1 兆美元，2030 年更將達到 1.2 兆美元。這股由 AI 驅動的投資週期，將抵銷部分總體經濟的不確定性。
+不過，市場必須留意記憶體價格上漲的趨勢，若價格持續走高，可能影響 2026 下半年的市場動能。
+曾冠瑋分析，運算類別佔據半導體市場營收比重將持續攀升，預計 2025-2026 年市佔達 60%，其中 AI 伺服器核心晶片受惠於雲端訓練與邊緣推論需求的同步爆發，預計成長 32%。
+相對地，車用（Automotive）與消費性（Consumer）市場因庫存調整與成本上升，展望較為保守。
+IDC 預估 2026 年亞太區 IC 設計市場將成長 11%，不過正面臨歷史性的結構轉變，因為中國 IC 設計產值已於 2025 年正式超越台灣，確立其市場領先地位。
+IDC 預測，2026 年中國市佔率將進一步擴大至 45%，台灣則調整至 40%，此消長態勢源自中國在美方制裁下，仍積極發展本土 AI 晶片、高階手機處理器，加上虛擬貨幣與安防晶片需求強勁，因此帶動當地營收呈現倍數級成長。
+先進製程是 2026 年晶圓代工市場成長的核心引擎，預計推動整體產值成長 20%。隨著 AI 晶片算力需求增長，台積電預期市佔率將攀升至 73%，且維持 22-26% 的高成長率。
+在資本支出方面，IDC 預估台積電將達 480 億至 500 億美元，主要用於擴充 3nm、2nm 產能及為 1.6nm 做準備。台積電 2nm 預計於 2025 年底達到月產能 8 萬片。三星與 Intel 則分別在韓國華城、美國德州及俄亥俄州積極布局，試圖在 2027-2028 年的 AI 晶片商機中搶佔一席之地。
+IDC 預估 2026 年平均產能利用率將穩定維持在 80% 以上，特別是中國晶圓廠，受惠於國產替代政策以及驅動 IC、PMIC 等訂單回流，產能利用率預期將保持在 90% 以上的高檔水位。至於台灣、韓國等非中國地區，則受惠於消費性電子復甦，利用率約維持在 80%。
+全球半導體產能版圖正走向區域多元化，美國、中國與日本的晶圓產能年複合成長率（CAGR）預計將分別達到 9.8%、9.8% 與 10% 的新高水位。
+中國面對美方先進製程設備禁令，將資源集中擴充受限較小的成熟製程，並加速扶植國產設備供應鏈，預計最快在 2028 年其「所有製程總產能」將超越台灣居全球之冠，並於 2029 年達到 37% 的全球市佔率。
+在美國方面，台積電亞利桑那州廠進展順利，一廠（P1）已開始量產，二廠（P2A）預計於 2027 年上半年正式量產 3nm 製程，P2B 則鎖定 2027 年底至 2028 年加入 2nm 行列。
+日本亦展現重返半導體強國決心，除台積電熊本廠外，日本政府也全力支持新創晶片製造商 Rapidus。雖然目前日本全球產能佔比僅約 2.5% 至 3%，但在先進製程的戰略地位將顯著提升。
+地緣政治重塑全球封測版圖，預計 2026 年 OSAT 市場將成長 11%。中國在「半導體自主化」政策推動下，要求 IC 設計與晶圓製造盡量採用在地供應鏈，推動中國 OSAT 市佔率預計將從過去的 30% 攀升至 2029 年的 33%。
+然而，高階 AI 晶片封裝仍由台灣與美國大廠掌握優勢。值得注意的是，若以包含晶圓代工廠先進封裝（Foundry-based packaging）的「封裝總市值」重新排名，受惠於 CoWoS 與 InFO 的高價值貢獻，台積電預計將在 2026 年超越傳統封測廠，成為全球封裝市值的實質龍頭。
+先進封裝產能擴張將是 2026 年的主旋律。IDC 預測，台積電 2026 年底 CoWoS 月產能將來到 11 萬片，但面對 NVIDIA、AMD 等巨頭將主力晶片全數投入 3nm 製程且 100% 採用先進封裝，市場供需依然吃緊。
+這股外溢效應將為 OSAT 廠帶來機會：日月光與矽品憑藉與台積電的長期合作，預計在 2025 年中旬開始有明顯的訂單放量；Intel 雖積極推廣封裝代工，但考量玻璃基板與高階封裝的良率需達 90% 以上才具經濟效益，預期要到 2027 年才能在 CSP 自研晶片市場中見到顯著貢獻。
+AI 加速器市場預計迎來爆發性成長。受惠於 Google TPU、AWS Trainium 等 CSP 自研晶片需求，IDC 預估 2026 年 ASIC 市場年增率將高達 173%。
+長期而言，為了優化 TCO，CSP 與模型開發商將持續擴大 ASIC 採用比例，推動 ASIC 在 2024-2029 年的年均複合成長率達到 67%。然而，GPU 並不會因此失勢，因為隨著「影像生成」的需求大增，未來的 AI 電影與即時影像運算需要極具彈性的通用算力，這將是 GPU 長期難以被取代的護城河，也讓 GPU 的年均複合成長率仍維持 56% 的高成長動能。
+針對市場擔憂的「AI 泡沫化」，IDC 認為 2026 年發生機率偏低，主因在於 AI 基礎建設並非無限制擴張，而是受到「電力供應」與「能源網架構」的物理限制。CSP 業者無法在缺乏電力配套下無限採購晶片，這種物理上的「調節閥」反而讓半導體出貨維持在相對健康、理性的成長軌道，避免了過度庫存堆積導致的瞬間崩盤。
+2026 年全球半導體產業將延續雙位數成長，從爆發期邁入「穩健擴張」階段。在這段過程中，地緣政治帶來的供應鏈重組、中國產能的強勢崛起，以及 AI 基礎建設是否會因電力瓶頸而調整節奏，將是決定產業走向的關鍵變數。</t>
+        </is>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>46244.62283685185</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>c26182506dccbffae3fbede2667f6b57b42e2b670d91e4b15a978b817696108b</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>美股焦點：ON Semiconductor(ON.US) | 23:32:11(GMT+8) - 台視全球資訊網</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://www.ttv.com.tw/finance/view/042026232332134174FF5E00432693B2142340DE48AAE792/587</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>台視全球資訊網</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Fri, 24 Apr 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" s="1" t="n">
+        <v>46244.62286261574</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>5d1d6ef625a4bb9cd01eae5a76b6b531620f326d595b56bfffa47b317874bc2f</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>【即時新聞】這「1檔」半導體轉強，NVTS最新漲2.94%還能追嗎？ - CMoney投資網誌</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://cmnews.com.tw/article/newsyoudeservetoknow-d463d065-3823-11f1-bf7c-8951ef46c39f</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CMoney投資網誌</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Wed, 15 Apr 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>【即時新聞】這「1檔」半導體轉強，NVTS最新漲2.94%還能追嗎？ | CMoney投資網誌
+【即時新聞】這「1檔」半導體轉強，NVTS最新漲2.94%還能追嗎？
+2026-04-15 01:03
+核心技術：專注於氮化鎵（GaN）與碳化矽（SiC）技術，提供高功率密度的解決方案。
+產品應用：功率 IC 高度整合了驅動、控制與保護功能，主要應用於行動裝置、消費性電子、企業級應用及電動車（eMobility）等新能源領域。
+營收結構：目前公司營運版圖涵蓋美國、歐洲與亞洲等地，其中最大宗的營收來源為中國市場。
+文章相關標籤
+Top50美股新聞
+美股新聞快訊
+本文內容轉載
+【即時新聞】台達電(2308)直衝漲停！大戶搶卡位，這「4檔概念股」接棒上攻？
+【即時新聞】川湖(2059)EPS狂飆74元！資金排擠，這「2檔概念股」現分歧？
+兩個APP年代結束了！在美股K線上同時掌握台美股損益
+【股市爆料同學會專屬】－開戶領 30 天籌碼 K 線 VIP
+【每日簽到領獎】最高送 500 元超商禮券 + LINE Points
+【台股盤後】台積撐場等非農，加權多空搶月線
+【籌碼K線 1月登入禮】籌碼集中股(4)
+anhour ago
+非農爆冷點燃全球股市：從總經事件看台股AI供應鏈三雄
+國巨只是第一棒？MLCC搶貨、長約全來了，被動元件整排點火！
+4hours ago
+川湖連兩天攻漲停衝破1.2萬，GB300、ASIC還能推多高？
+5hours ago
+要永久刪除文章嗎
+「」將被永久刪除，且這項操作無法復原。</t>
+        </is>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>46244.62335300926</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>6d715a21756bd9fbfdd919f65a10e8d540d8cef461a7f80ebab26a4eb889a351</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>從追趕到突圍：中國半導體轉向成熟製程，力奪全球供應鏈話語權 - TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://technews.tw/2026/05/11/china-semiconductor-industry-shifts-to-mature-nodes/</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" s="1" t="n">
+        <v>46244.62337538195</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ab0ba52b718011d084d7791b678dec6ea2fcabe421fbf2d21d47ffbe4c3e8366</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>全台首家IC設計獲Arm注資 通寶半導體Q4擬申請IPO - 工商時報</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://www.ctee.com.tw/news/20260304700096-439901</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>工商時報</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Wed, 04 Mar 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>通寶半導體設計公司簡介
+台灣IC設計領域傳出國際策略投資合作捷報，通寶半導體（QBit Semiconductor）公司3日宣布，已完成B輪募資，並獲全球半導體架構大廠安謀公司（Arm Limited）參與投資，成為目前全台唯一獲得Arm投資的IC設計公司。
+安謀現成為通寶十大股東之一，至於安謀持股比例及金額，4月下旬召開法說會可望對外說明，未來通寶擬計畫跨足無人機及機器人市場。
+通寶半導體同時宣布，隨著募資完成營運規模擴大，計畫於今年第四季向臺灣證券交易所申請IPO上市，進一步邁向資本市場新里程碑，實際時程仍須視主管機關核准及市場狀況而定。
+通寶半導體為專攻多功能列印機及事務機系統晶片的IC設計公司，其客戶主要市場遍及美國、日本、中國跟台灣。除Arm參與投資外，據悉，通寶半導體在A輪募資時，台灣政府法人機構持有通寶半導體約6％股權，包括國發基金持股2.7％，以及台肥、工研院等公股事業合計持股比例約6％，還有智原科技等半導體產業加入，整體A輪投資人持股比例約為通寶已發行股權10％。
+對於這項注資，Arm全球執行副總裁暨商務長Will Abbey表示，透過與通寶的合作，可以結合先進影像處理、控制與安全能力，以支持列印及影像市場的創新。此類合作展現Arm更廣泛的策略，亦即推動具差異化的解決方案，從高效能系統延伸至更具成本效益的裝置，同時為各類產品建立成長基礎。
+通寶半導體創辦人暨執行長沈軾榮也表示，很榮幸成為獲得Arm唯一投資的台灣半導體設計公司，未來通寶將持續深化在印表機影像市場的布局，並拓展至更廣泛的影像相關應用領域。
+將工商時報加入Google偏好來源</t>
+        </is>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>46244.62340170139</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>72032f20594b3c259a665f43d3f6e959904d49cc721acc33fb83396feb7f13de</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ICTGC 攜手 InnoVEX，首次串接矽谷創新能量 打造台灣與矽谷之間的半導體與 AI 創新橋樑 - tca.org.tw</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://www.tca.org.tw/news_detail.php?n=2449&amp;t=h</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>tca.org.tw</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fri, 12 Dec 2025 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ICTGC 攜手 InnoVEX，首次串接矽谷創新能量 打造台灣與矽谷之間的半導體與 AI 創新橋樑
+ICTGC第三梯次得獎團隊來自美國、瑞典、臺灣，由國科會吳誠文主委親自頒獎。
+在人工智慧（AI）驅動世界的時代，台灣被譽為「矽島（Silicon Island）」，是全球半導體技術的核心引擎，2026年以「連結矽谷與矽島台灣的半導體與 AI 實力」為核心主題，由國科會指導、台北市電腦公會執行的IC Taiwan Grand Challenge（ICTGC）競賽，將攜手全球創新展會 InnoVEX，於 2026 年 1 月 13 日在 Startup Island Taiwan Silicon Valley Hub（美國 Palo Alto）舉辦 「Bridging Silicon Valley and Taiwan: Semiconductor &amp; AI Synergies」 活動，打造跨境科技合作的新舞台，此次活動將向矽谷新創分享競賽資訊與獎助資源。ICTGC 不僅提供三萬美元獎金，更結合業師輔導、企業合作與技術資源，是矽谷新創拓展事業版圖、切入全球半導體與 AI 生態系的難得機會。
+ICTGC海外推廣活動繼2024年在日本推廣，2026年ICTGC與InnoVEX團隊於CES 展後延伸國際交流，首度深入矽谷新創圈，開啟台灣與矽谷於半導體科技領域的全新對話，深化台美科技互動，拓展國際新創合作。
+活動匯聚多位引領半導體、人工智慧與未來科技發展的重量級領袖前來分享。講者包含Silicon Catalyst 的共同合夥人、同時也是 Sand Hill Angels 投資人 Laura Swan，擁有多年協助早期半導體新創的深厚經驗。Tesoro Ventures 管理合夥人 Andy Lombard 觸及全球市場，協助 AI 與半導體新創透過資本與供應鏈資源加速成長。
+Plug and Play Ventures 的資深投資合夥人暨高科技領域負責人 Janis Skriveris，主導過數十項早期投資，涵蓋具變革性的技術，並曾投資獨角獸 Einride，長期深耕 AI、清潔科技與基礎建設等領域的新創合作。
+此外，femtoAI 執行長暨共同創辦人、亦是 IC Taiwan Grand Challenge（ICTGC）前屆得獎者的 Sam Fok，正致力於打造超高效嵌入式 AI 解決方案，讓智慧功能走入日常電子產品中，同時也將分享獲獎過程，鼓勵新創團隊申請ICTGC藉此擴展產品。
+本次活動也特別邀請 Hardware User Group（HUG）全球負責人 Michael Raspuzzi 主持路演環節，邀集早期新創團隊分享創新技術，將呈現硬體、AI 與機器人領域中最前瞻、大膽的創新構想，以串聯矽谷新創與台灣的量能為核心，展現兩地生態系的協作潛力，凸顯台灣作為推動創新落地的關鍵樞紐角色。
+對矽谷創業家而言，什麼是 IC Taiwan Grand Challenge?
+台灣政府廣發英雄帖，打造國際創新挑戰賽
+人工智慧的運行，決勝點依舊是晶片！從晶圓代工到完整的精密電子供應鏈，台灣構築了支撐全球數位經濟的硬體基礎。IC Taiwan Grand Challenge（ICTGC）是台灣為凝聚全球創新者、並串接其獨步全球的半導體與硬體生態系所打造的旗艦計畫，此次2026 年 1 月 13 日活動也向矽谷創業者與研究者揭示台灣半導體與ICT產業如何成為創新的最佳夥伴，讓全球團隊能夠在台灣「打造、驗證、加速」前瞻技術，並推動跨國合作，以共同實現跨越國界的創新願景。
+ICTGC 為創業者提供：
+●連結台灣半導體與硬體供應鏈的機會
+●提供頂尖研究機構及指標廠商的業師計畫
+●全球指標新創展會InnoVEX展出機會，提升國際能見度與成長速度
+●三萬美金獎助以及後續原型製作與試產投資
+Bridging Silicon Valley and Taiwan: Semiconductor &amp; AI Synergies
+日期：2026 年 1 月 13 日（週二）
+時間：下午 5:30 – 晚上 8:00（PST）
+地點：Startup Island Taiwan – Silicon Valley Hub
+299 California Ave, STE 300, Palo Alto, CA 94306
+報名連結：
+邀請您前來共同見證 台灣矽谷聯手在半導體與AI領域的合作新篇章。
+參考網址：
+（發佈時間：2025-12-12）</t>
+        </is>
+      </c>
+      <c r="I14" s="1" t="n">
+        <v>46244.62342738426</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>f19113e887dfbe08f3df29ee989d20774e0fa8193d0ee01d97cd2a0e74d647aa</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>通寶成Arm唯一注資台灣IC設計 鎖定無人機與機器人 - 科技新聞 - PChome Online 新聞 - news.pchome.com.tw</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://news.pchome.com.tw/science/technice/20260305/index-77267807313741338005.html</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>news.pchome.com.tw</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Thu, 05 Mar 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>台灣IC設計領域近期傳出重大的國際策略投資捷報，專注於多功能列印機與事務機系統晶片的通寶半導體（QBit Semiconductor），於3日正式宣布完成B輪募資。本次募資最受市場矚目的焦點，在於全球半導體架構巨頭安謀（Arm Limited）的參與投資，使通寶成為目前全台唯一獲得Arm直接注資的IC設計公司，為台灣半導體產業寫下新頁。
+記者鄧天心／台北報導
+通寶獲Arm注資，衝刺影像處理新商機。（圖／擷取自通寶半導體官方網站）
+國際大廠策略入股 產官研結構紮實
+隨著B輪募資的圓滿達成，Arm已正式列入通寶半導體的前十大股東。儘管目前關於Arm的具體持股比例與投資金額尚未公開，但外界預期在4月下旬召開的法說會中，公司將有更詳盡的說明。
+事實上，通寶半導體自創立以來便擁有極為穩健的股東結構。在早前的A輪募資中，已有包含國發基金（持股2.7%）在內的台灣政府法人機構進駐，結合台肥、工研院等公股事業，合計持股約6%。此外，半導體指標大廠智原科技也早已加入投資行列，顯示通寶在技術與市場潛力上深受國內外產官研各界的認可。
+更多科技工作請上科技專區：
+從影像控制跨足無人機與機器人
+通寶半導體長期深耕多功能列印機（MFP）與事務機系統晶片，市場版圖橫跨美國、日本、中國與台灣。針對此次注資，Arm全球執行副總裁暨商務長Will Abbey指出，透過與通寶的合作，能將先進的影像處理、控制與安全能力相結合，支持影像市場的持續創新。這也反映了Arm的廣泛策略：從高效能系統延伸至更具成本效益的裝置，為多元產品建立成長基礎。
+通寶半導體創辦人暨執行長沈軾榮則表示，對於能成為Arm在台唯一的注資對象深感榮幸，未來通寶不僅將持續強化在印表機影像市場的領先地位，更計畫將技術觸角延伸至無人機及機器人等新興影像應用市場，利用既有的核心競爭力開拓更多元的商機。
+邁向資本市場 Q4啟動IPO申請
+隨著營運規模的擴張與國際大廠的背書，通寶半導體宣布已做好進入資本市場的準備，計畫於今年第四季向臺灣證券交易所正式申請IPO上市。雖然實際的掛牌時程仍須視主管機關核准及市場狀況而定，但這項上市計畫已無疑成為今年台灣IC設計產業中最受關注的里程碑之一。
+延伸閱讀：
+黃仁勳：投資OpenAI「可能是最後一次」 IPO前資金布局逐步收尾
+通寶成Arm唯一注資台灣IC設計 鎖定無人機與機器人
+最早出現於
+科技島-掌握科技新聞、科技職場最新資訊
+新聞關鍵字：
+記者：鄧天心
+更多科技新聞 »</t>
+        </is>
+      </c>
+      <c r="I15" s="1" t="n">
+        <v>46244.6234515625</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>91843debf041fc741aba79dec6df216f652db20173c389f6278cae3a27ce0f85</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>通寶半導體獲 Arm 投資、完成 B 輪募資，規劃 Q426 申請上市 - TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://finance.technews.tw/2026/03/03/qbit-semiconductor/</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tue, 03 Mar 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>台灣 IC 設計產業再添資本市場動態。通寶半導體（QBit Semiconductor）宣布完成 B 輪募資，並獲得 Arm Limited 參與投資，成為目前國內少數獲得 Arm 投資的 IC 設計業者之一。該公司同時規劃於 2026 年第四季向台灣證券交易所申請上市。
+據該公司說明，Arm 此次投資著眼於雙方在影像處理、控制與安全技術上的合作潛力，應用範圍涵蓋列印與影像相關市場。Arm 全球執行副總裁暨商務長 Will Abbey 指出，相關合作有助於擴展從高效能系統到成本導向裝置的技術應用，強化不同產品線的解決方案布局。
+通寶半導體創辦人暨執行長沈軾榮表示，此次引進 Arm 資金與策略資源，將有助於該公司深化既有市場並拓展影像相關應用領域。不過該公司並未對募資金額與估值細節對外揭露。
+除 Arm 外，台灣政府法人機構目前亦持有通寶半導體約 6% 股權，顯示其在國內半導體產業鏈中具一定政策與策略意涵。
+通寶半導體成立於 2016 年，總部設於台北，並於美國波士頓及日本東京設有據點。創辦團隊來自高通體系，具備系統單晶片（SoC）開發背景，專注於高速影像處理與精密動件控制技術整合。該公司指出，其技術核心包括影像智慧運算、精密動件控制與能源管理。
+目前通寶 SoC 平台已導入國際印表機品牌產品，應用範圍涵蓋多功能事務機（MFP）、醫療印表機、相片印表機、掃描器與工業印表機等設備。未來規劃將產品線延伸至自助服務機（Kiosk）、機器人與無人機等領域。
+隨著本輪募資完成與營運規模擴張，通寶半導體預計於 2026 年第四季推進上市申請。
+（首圖來源：
+通寶半導體
+文章看完覺得有幫助，何不給我們一個鼓勵
+請我們喝杯咖啡
+想請我們喝幾杯咖啡？
+每杯咖啡 65 元
+您的咖啡贊助將是讓我們持續走下去的動力
+總金額共新臺幣
+《關於請喝咖啡的 Q &amp; A》
+留給我們的話
+從這裡可透過《Google 新聞》追蹤 TechNews</t>
+        </is>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>46244.62356418982</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>784c1b2acbfd3c05e8b785afa12e3ff56d4ffc5ba3ac6e855ca008c36246fbb0</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>30 人團隊搶下全球半壁江山，君曜科技如何成為橋接 IC 王者？ - TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://finance.technews.tw/2025/11/08/leading-bridging-chip-supplier-zeitec-semiconductor/</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sat, 08 Nov 2025 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>君曜科技靠自行研發的手機螢幕橋接晶片，成為橋接晶片供應商龍頭。證明以靈活的小團隊、貼近市場的策略，在競爭激烈的驅動 IC 市場，也可以找到一片天。
+一家員工不過30人、年營收從未達到10億元的IC設計公司，為何能在強敵環伺、價格殺到見骨的驅動IC戰場上穩健存活？答案是，洞察市場供需缺口，找出獨門生意。
+即將在年底上櫃的君曜科技，營收規模相較於聯詠、奇景等大廠，幾乎可用「微不足道」來形容，但它靠著自行研發的手機螢幕用橋接晶片，每年穩健獲利，如今在全球售後維修市場市占率已達五成，穩居橋接晶片供應商王座。
+根據法人推估，全球每年出貨約13億支智慧手機中，其中多達四億支會送進維修站。如果問題是螢幕故障，原本的OLED螢幕，可能會被成本較低的LCD螢幕取代，但置換上的LCD面板，因為廠牌、規格差異，常會出現螢幕訊號不相容或「黑邊」問題，此時就需要一顆專門轉換訊號的橋接晶片，讓螢幕功能維持正常。
+解決手機換螢幕黑邊問題
+招牌商品成維修必備元件
+這項維修必備的元件，正是由君曜率業界之先開發的招牌產品。
+2010年創立君曜之前，君曜科技董事長林澤琦曾任職台灣IC設計龍頭
+的電視晶片部門，但在大企業穩定晉升並非他的夢想，「我從小就想創業，不想每天坐辦公室」，32歲那年，他與朋友湊出1,000萬元創業，主攻因智慧手機和平板電腦興起而需求大增的觸控IC。
+▲ 君曜董事長林澤琦指出，研發團隊人雖少，但能快速決策和調整規格，適應市場多變需求，具有大型IC公司難以模仿的效率。
+剛成立不久，君曜推出的觸控IC就成功打入中國白牌平板市場與韓國SK集團等客戶，單月出貨突破百萬顆。這樣的成績立刻引起全球電子製造服務霸主
+注意，在2015年投資3,000萬元成為股東，並在多項產品中採用君曜晶片。
+然而，白牌平板市場2015年以後急速萎縮，再加上競爭者湧入、價格戰激烈，君曜因此力圖轉型，與鴻海合作開發高階觸控IC，計劃用於鴻海操刀的Nokia與InFocus智慧手機，但隨著相關產品開發進度停滯，也讓想藉著進入供應鏈翻身的君曜營運陷入困難。
+為求生存，林澤琦努力發掘新商機。2016年他注意到手機維修業者的零件來源，正從原本的「拆舊料」轉為「換新料」，因此嘗試與售後方案設計公司合作，提供觸控IC，勉強做到損益兩平。
+但林澤琦沒有輕易放棄，進一步調查後發現，手機維修還需橋接晶片因應新舊螢幕規格差異，利潤又高於觸控IC。且當時橋接晶片採取的開發技術難度高、價格又貴，幾乎沒有競爭者。但他有微控制器（MCU）設計經驗，自信可設計出成本可控的客製化晶片（ASIC）取而代之。</t>
+        </is>
+      </c>
+      <c r="I17" s="1" t="n">
+        <v>46244.62358853009</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>69219fd53db5db6409b4bbe269736870f303828840cd614c846cfd05558ad169</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>GaN 功率晶片商 Navitas 營收展望超優、股價飆 19% - TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://finance.technews.tw/2026/02/26/navitas-semiconductor-announces-fourth-quarter-and-full-year-2025-financial-results/</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Thu, 26 Feb 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>第三代半導體氮化鎵（GaN）功率 IC 領導大廠納微半導體（Navitas Semiconductor）抓住新崛起的 AI 資料中心商機，本季營收展望有望呈現季增，股價應聲飆高。
+The Motley Fool、Benzinga報導，Navitas 24日盤後公布第四季（2025年10-12月）財報：營收年減將近60%至730萬美元（擊敗分析師預期的695萬美元）；經調整的非一般公認會計原則（Non-GAAP）每股虧損為0.05美元（符合預期），略優於去年同期的每股虧損0.06美元。
+（Source：
+納微半導體
+展望本季（1-3月），Navitas預測營收將介於800~850萬美元之間，遠優於分析師預期的734.5萬美元，主要受到高功率市場貢獻增加、行動與消費者業務的曝險降低帶動。
+Navitas總裁兼執行長Chris Allexandre指出，Q4期間，該公司加速朝「Navitas 2.0」進行戰略轉型，並運用旗下領先業界的氮化鎵與高壓碳化矽（SiC）解決方案，滿足高功率市場的需求。
+值得注意的是，高功率市場對Navitas整體營收占比首次居所有業務之冠，而行動裝置相關的營收占比則降至不到25%。
+Navitas把重點放在成長快速的領域，當中包括AI資料中心、電網與能源基礎建設、高效能運算以及工業電氣化等。預計到了2030年，這些領域的可用市場規模總計將達到35億美元。
+Navitas 25日聞訊飆漲19.61%、收9.88美元，創1月28日以來收盤新高；年初迄今漲幅來到38.38%。
+MoneyDJ新聞
+授權轉載；首圖來源：
+文章看完覺得有幫助，何不給我們一個鼓勵
+請我們喝杯咖啡
+想請我們喝幾杯咖啡？
+每杯咖啡 65 元
+您的咖啡贊助將是讓我們持續走下去的動力
+總金額共新臺幣
+《關於請喝咖啡的 Q &amp; A》
+留給我們的話
+從這裡可透過《Google 新聞》追蹤 TechNews
+AI 資料中心
+Navitas</t>
+        </is>
+      </c>
+      <c r="I18" s="1" t="n">
+        <v>46244.62361392361</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>c5cd36811da64e7927563ac2608067d5e2031c9fded56cb75be6b7935f2fa6b3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>中國急起直追，台灣2029年將失晶圓代工寶座？IDC揭半導體新變局 - 數位時代</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://www.bnext.com.tw/article/85426/idc-2025-semiconductor-predict</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>數位時代</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Fri, 12 Dec 2025 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>AI NAS 何時才值得部署？QNAP 拆解地端 AI 的成本、算力與資料門檻
+2026.08.05
+AI與大數據
+sponsored
+威聯通科技股份有限公司
+當資料不能離開企業，運算就得靠近：AI 先改寫儲存架構
+AI 帶來的第一個變化，不只是運算能力提高，而是企業必須重新決定資料放在哪裡。
+儲存架構大致分為雲端與地端兩塊，QNAP 身為資料安全的守護者，長期發展的是地端網路儲存設備（NAS），並擴展至 25GbE、100GbE 高速網路交換器產品線，提供完整的儲存與高速網路基礎架構。威聯通科技（QNAP）總經理劉文義解釋，當資料因合規要求或敏感度不能上雲，就必須留在靠近使用者與應用的地方；運算需求一旦增加，承接資料的裝置也自然被推向地端 AI。
+不能上雲的名單比想像中長。醫療業持有大量醫療個資，金融與保險業受到合規與法規限制，部分大學院校與設計公司也不希望資料被雲端存取。對這些組織而言，問題並不是雲端好不好用，而是一開始就沒有把核心資料全面上雲的選項。
+威聯通科技（QNAP）總經理暨威強電集團（IEI）董事長 劉文義
+真正讓更多企業回頭計算的，則是長期成本。劉文義指出，資料上傳雲端可能免費，下載卻會按流量收費；當企業把一年、兩年、三年的費用加總回推，可能會發現，購買一台同等容量的 NAS，還能使用 7-10 年。資料規模愈大、存取愈頻繁，總持有成本的差距就愈值得評估。
+這並不代表雲端與地端只能二選一。雲端仍適合模型訓練、程式開發與波動大的工作負載；地端則較適合高頻存取、對延遲敏感，或不能離開企業邊界的資料。企業真正要回答的，是每一類資料與任務應該放在哪裡。
+依 QNAP 觀察，客戶過去關心的是需要幾 TB、幾 PB，或備份速度有多快；現在更常問的是，機器裡的資料要如何被 AI 活用。QNAP 也從 2021 年起，把公司發展定調在 AI 與高速網路的融合，試圖讓 NAS 從資料保存的位置，進一步成為資料被調用的位置。
+當資料量持續擴大，搜尋與管理方式也會跟著改變。「在 NAS 裡放入 AI Agent 會越來越不可或缺。」劉文義舉例，當照片累積到 10 萬、20 萬張，要找出其中幾張特定畫面，已不可能只靠人工翻找。此時，能理解內容、接受自然語言指令的 AI 工具，會從加分功能逐漸變成必要條件。
+從資料治理到地端推論：AI NAS 如何進入企業工作流？
+AI NAS 不是「多了 AI 功能的 NAS」，而是 NAS 在企業工作流裡換了位置。
+依 QNAP 觀察，目前客戶大致分布在一條導入光譜上。人數最多的一群，仍在把資料集中、分類、清理與建立權限。這一步看似與 AI 無關，卻決定後續系統能不能找到正確資料、辨識版本，並把答案交給有權限的人。
+中間一群開始建置私有的檢索增強生成（RAG）知識庫。RAG 並不是重新訓練一個模型，而是在模型回答前，先從企業的 SOP、合約、法規或技術文件中取回相關內容，再產生附有來源依據的答案。QNAP 以 Qsirch 的語意搜尋能力協助建構這類應用，協助企業建立私有知識庫；而走在最前面的少數企業，則已經嘗試地端推論與 AI Agent。
+模型的選擇權，QNAP 刻意留給客戶。知識庫背後採用哪一個模型，可由企業依需求決定，不綁定單一 AI 供應商。QNAP 也以 QuAgent AI 助理與模型情境協定（MCP）相關能力，讓管理者透過自然語言查詢狀態、調整設定，並讓 NAS 成為 AI Agent 可調用的資料節點。
+不過，劉文義沒有把這條路說得太容易。他坦言，目前 NAS 硬體的 AI 運算能力仍有限。一般企業期待的應用，可能需要約 300 到 800 TOPS，甚至 1,000 TOPS，因此多數方案會以 NVIDIA 顯示卡補足算力；一張卡約需新台幣 10 萬至 12 萬元，一張算不完，就得配置 2 張或 4 張。
+「整體成本可能是過去單獨一台 NAS 的 5 倍到 10 倍，並不是大部分中小企業都能接受。」除了硬體，使用者還需要 AI 應用的 Know-how、程式背景與開發資源，這些都是落地成本。
+QNAP 則是透過算力分級讓各規模與需求的企業都可以有適合的解決方案。在 Computex 2026 搶先亮相的 QNAP AI NAS 中，一類是採用含有 iGPU 與專屬 NPU 的處理器平台，以一百多 TOPS 的範圍，可順暢使用 AI 應用程式；另一類機種則可安裝 1 張或 2 張 NVIDIA 顯示卡，處理更大的運算量。
+同時 QNAP 也在軟體端也持續開發，目標是讓 NAS 裡的資料更有效率地被 AI 工具調用，讓資料成為有價值的知識。
+從規格走到現場：能源公司如何導入私有 LLM？
+本地 AI 實際落地部署會是什麼模樣？劉文義舉了一家約 50 多人的能源公司為例。這家公司原本想用 NAS 搭配雲端 AI 建置內部資料庫，但很快遇到兩個瓶頸：一是員工查詢時明顯出現卡頓；二是專利、技術與合約都高度敏感，高層不願上傳至公有雲，擔心機密資料會有外洩的疑慮。
+後來，該公司導入 QNAP AI NAS 的旗艦機種 QAI-h1290FX，搭配顯示卡與全快閃 SSD，在地端部署私有大型語言模型，把數十年來封存的靜態檔案交給 AI 調用，進行跨檔案摘要與精準搜尋。員工因此省下翻找合約與報告的時間，核心機密也能留在企業內部。
+這個案例說明，若任務範圍明確，有些應用不必動用雲端大型模型，地端運算量就可能足以支應。
+但不同企業的資料量、查詢方式與模型大小不同，導入前仍需要概念驗證（POC）與技術人員評估。
+而且，資料留在地端並不等於自動安全。企業仍要處理帳號權限、網路隔離、備份復原、漏洞修補與日常維運。地端的價值，是讓資料邊界與控制權回到企業手上；相對地，安全責任也會更直接地回到企業。
+哪些企業現在該做，哪些再等？先看重複性與三個條件
+能不能導入地端 AI，不只由產業標籤決定，也要看工作是否重複，以及場景能不能被清楚定義。劉文義觀察，第一批走進來的，除了受法規限制的醫療、金融與保險業，也包括利用地端 AI 加速資料處理的科技業，以及會計、律師等有大量重複文書工作的專業服務業，因為效益較容易被看見。
+工廠也是可預期的場景。一條生產線可能有　10　台、20　台機器，每台處理與儲存資料的 Protocol 都不同，需要相對應的儲存裝置；生產過程累積的影像與紀錄可能要保存 3 年到 5 年。當企業要跨設備調用這些資料，AI Agent 與地端資料節點就有發揮空間。
+「重複性資料處理越多，或重複性動作越多的產業，越容易透過導入 AI 提高工作效率。」反過來說，較傳統、人力密集，或仍高度依賴人工判斷的製造業，短期內未必能快速導入地端 AI。
+依 QNAP 提供的資料，企業也可用「高頻、大量、敏感」三個條件做第一輪判斷：資料是否被頻繁調用？規模是否大到雲端傳輸與長期費用開始變得明顯？內容是否涉及個資、法規、智慧財產或商業機密？三個條件愈集中，地端部署愈值得評估；三者都不成立時，使用雲端 API 往往更簡單，也可能更划算。
+可以先等的企業，大致也有三種。第一，資料仍分散、版本混亂、權限不清，急著上 AI 只會把混亂放大，先完成集中與治理，效率就可能先提升。第二，找不到一個具體且反覆發生的業務痛點，只因為「別人都在做」而採購，設備很可能變成昂貴的展示品。第三，使用量仍小、需求偶發，現階段雲端的彈性反而更有優勢。
+因此，POC 不應只驗證「模型答不答得出來」，還要回答三個問題：資料由誰負責，誰可以存取？導入後能節省多少查找時間、傳輸成本或人工作業？正式上線後，誰負責資料、模型與資安維運？只有當效益與責任都能被量化，才適合從展示走向正式部署。
+企業願意把部分資料留在自己的機房，動力最終仍回到資料主權。QNAP 的主要市場分布在歐洲、美洲與亞太，其中歐洲占比將近一半，而歐洲也正是全球推動資料主權的最大動力。
+QNAP 的產品已取得 ISO 27001、ISO 27017 與 ISO 27018 等多項認證，並滿足 GDPR、HIPAA 等資料保護與法規遵循需求；累積至今，已售出約數百萬台裝置，協助企業打造智慧、安全的儲存方案。
+至於普及時間點，劉文義提出一個明確的價格與效能交會點：地端應用若要順暢運作，運算量可能至少要達到 300 至 600 TOPS，甚至 800 TOPS，同時價格要落在新台幣 5 萬至 8 萬元。目前符合這些條件的硬體方案仍很有限。
+「AI NAS 不是多了 AI 功能，而是改寫了資料在工作流的位置。」威聯通科技總經理劉文義坦言，地端算力成本高昂，QNAP 透過「算力分級」與開放模型架構，助企業逐步建構私有 RAG 知識庫與 AI 團隊。
+「預測約兩、三年後，應該很快會看到符合一般大眾期待、具備合理 CP 值的產品。那個時間點，就會是 AI 落地最蓬勃發展的時候。」在此之前，企業真正能先做的，不是搶著買最大的模型或最昂貴的顯示卡，而是把資料治理、使用權限與高價值場景準備好。
+QNAP 以「資料煉油廠」比喻自己的角色：原油再多，沒有整理、提煉與配送的過程，也無法成為可用的能源。這個定位也點出地端 AI 的競賽條件——不是誰先買到算力，而是誰的資料先準備好被調用。模型會持續更換，但企業自己的資料層則會長期存在。
+AI NAS 不是把模型塞進儲存設備，而是在資料必須留在企業內時，讓搜尋、推論與管理靠近資料的地端節點。
+QNAP World Tour 2026 台北場將於 2026 年 9 月 18 日（五）舉行，現場將聚焦 AI 應用、儲存備份、網通產品、資安與監控，並安排 Live Demo，適合 IT 管理者、系統整合商與企業決策者參加。
+活動地點：新板希爾頓酒店｜如意 AB 廳
+活動時間：09:20–16:00
+地址：新北市板橋區民權路 88 號 2F
+立即報名：
+2026 QNAP 台灣企業資安韌性大調查，填問券抽好禮，倒數計時：
+即時熱門文章
+全球AI伺服器幾乎都靠台廠做！鴻海、廣達、緯穎⋯19檔AI基建概念股全拆解
+告別「極速迷思」！Opensignal 國際評比揭密：什麼才是 5G 時代的好網路？
+Gemini完整教學地圖！37篇實測整理，Notebooks、Spark、提示詞架構全打包
+黃仁勳再喊下一波AI浪潮是機器人！輝達Jetson Thor台鏈名單曝光，這些可望成受惠族群
+AI已經做得到20%的題目，反而不要碰！Google首席科學家給創業者的「1%法則」
+0到18歲成長津貼來了！可領多少？2027上路規劃、最新進度一次看</t>
+        </is>
+      </c>
+      <c r="I19" s="1" t="n">
+        <v>46244.6237478125</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>219376d9cb16ba8c93224bc86bce6e724c8062ef7fc9283f00ac3448736c22ba</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Nordic Semiconductor推出nRF54LV10A —— 一款突破性的低電壓藍牙低功耗系統單晶片，專為新一代醫療保健穿戴式設備設計_COMPOTECH ASIA - COMPOTECH Asia</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://www.compotechasia.com/a/new_product/2025/1209/62429.html</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>COMPOTECH Asia</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tue, 09 Dec 2025 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" s="1" t="n">
+        <v>46244.62377064815</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>fc89988ac380bea990e6415a7c7ed13a54ad8b53e884d7e640d64c325ff1f9f3</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>台灣第一家！通寶半導體獲ARM 投資打造AI生態圈擬於2026年Q4申請上市 - 三立新聞</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://inews.setn.com/news/1801759</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>三立新聞</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tue, 03 Mar 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026/03/03 14:56
+財經中心／綜合報導
+通寶半導體宣布完成B輪募資，並獲全球半導體架構大廠安謀公司（Arm Limited）參與投資，成為目前全台唯一獲Arm投資的 IC 設計公司。（圖／翻攝畫面）
+台灣 IC 設計領域再添策略合作新指標，通寶半導體（QBit Semiconductor）宣布完成B輪募資，並獲全球半導體架構大廠安謀公司（Arm Limited）參與投資，成為目前全台唯一獲Arm投資的 IC 設計公司。通寶同時宣布，計畫於2026年第四季向台灣證券交易所申請上市，實際時程仍須視主管機關核准及市場狀況而定。
+Arm 全球執行副總裁暨商務長 Will Abbey 表示：「透過與通寶的合作，我們可以結合先進影像處理、控制與安全能力，以支持列印及影像市場的創新。此類合作展現了 Arm 更廣泛的策略，即推動具差異化的解決方案，從高效能系統延伸至更具成本效益的裝置，同時為各類產品建立成長基礎。」
+通寶半導體創辦人暨執行長沈軾榮表示：「很榮幸成為獲得Arm唯一投資的台灣半導體設計公司，衷心感謝 Arm 對 QBit 技術與產品潛力的高度肯定。未來將持續深化在印表機影像市場的布局，並拓展至更廣泛的影像相關應用領域。」
+除Arm投資外，台灣政府法人機構目前亦持有通寶半導體約6%股權，顯示其在台灣半導體產業鏈中的策略角色。
+通寶成立於2016年，總部位於台北，並於美國波士頓及日本東京設有據點。創辦團隊源自高通（Qualcomm）體系，具備長期系統單晶片（SoC）開發經驗，專注於高速智慧影像處理與精密動件控制技術，是業界少數成功整合「影像智慧運算」、「精密動件控制」與「能源感知管理」三大核心技術的廠商。
+通寶SoC平台已獲國際一線印表機品牌採用，除多功能事務機（MFP）市場外，亦廣泛用於醫療印表機、相片印表機、掃描器、條碼印表機及工業印表機。未來，通寶半導體亦計畫將 SoC 開發拓展至互動式多媒體自動服務機（Kiosk）、機器人及無人機等新興應用領域。隨著募資完成與營運規模擴大，公司將依計畫於2026年第四季推進上市申請，邁向資本市場新里程碑。</t>
+        </is>
+      </c>
+      <c r="I21" s="1" t="n">
+        <v>46244.62379607639</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>a40adbc2c2b8875e017498c2b2e7e8a6a209d0b29298f9429681cdb2c86348cf</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>MOSFET 是什麼？功率半導體崛起？為何近期熱度提升？安世事件帶來哪些利多？ - StockFeel 股感</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://www.stockfeel.com.tw/mosfet-%E6%87%89%E7%94%A8-%E6%A6%82%E5%BF%B5%E8%82%A1/</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>StockFeel 股感</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Wed, 27 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>MOSFET 的全稱為，「金屬氧化物半導體場效電晶體」（Metal-Oxide-Semiconductor Field-Effect Transistor ，以下簡稱 MOSFET），是現代電子工業中應用最為廣泛的基礎元件之一。無論是在複雜的積體電路（IC）設計中，還是在終端的電路板（PCB）應用上，重要性不可替代。特別是在大功率半導體，MOSFET 可以精準的控制電源電子，可以直觀的理解成電子電路中的「精密開關」。但為何近期 Mosfet 的熱度如此之高呢？
+MOSFET 是什麼？
+上看，MOSFET 是一種利用電場效應來控制電流導通的元件。其三端結構包含閘極（Gate）、源極（Source）與汲極（Drain）。其透過施加電壓於閘極，在下方的半導體表面感應出導電通道，從而允許電流在源極與汲極之間流動 。根據導電特性與內部摻雜通道的差異，MOSFET 演化出三種最基本的技術形式：NMOS、PMOS 與 CMOS 。
+股感資料庫整理
+MOSFET 基本結構類型
+運作機制說明
+技術優勢與限制
+(N-type)
+N 型通道
+閘極施加正電壓吸引電子形成通道，使電流導通。
+電子遷移率高，開關速度快，是功率元件的首選，但在靜態時較耗電。
+(P-type)
+P 型通道
+閘極施加負電壓吸引電洞形成通道，與 NMOS 導電特性相反。
+製造工藝成熟，但電洞移動速度較電子慢，效率較低，通常不單獨用於高頻。
+CMOS (Complementary)
+電子與電洞
+由一個 NMOS 與一個 PMOS 對稱組合而成，是目前數位電路的主流。
+靜態功耗極低，僅在 0 與 1 切換時耗電，是現代行動裝置長效續航的基礎。
+晶片從平面到 3D
+當閘極長度縮短至極限，閘極對通道的控制力會大幅減弱，導致即使在「關閉」狀態，電子還是會透過基板滲漏，產生漏電。為了克服這一點，半導體工程師把電晶體從「平面」拉向「三維」，把它想像成電線放在地上接觸到導電物就會漏電，但如果今天使用絕緣體包覆，就不會漏電了。
+股感資料庫整理 ; 資料來源：
+EDN TAIWAN
+MOSFET 技術演進與結構差異
+主要製程節點
+結構特點描述
+漏電抑制能力
+（PlanarFET）
+28nm 以上
+傳統 2D 結構，閘極僅從上方控制通道
+低（易產生漏電）
+鰭式場效電晶體 (FinFET)
+22nm – 3nm
+3D 結構，通道如魚鰭般立起，閘極從三面包裹通道
+高（顯著減少漏電）
+全環繞閘極 (GAAFET)
+3nm 以下
+奈米片 (Nanosheet) 結構，閘極全方位 360 度包裹通道
+極高（支撐 2nm 以下微縮）
+FinFET 的導入是半導體史上的重大突破。它將通道設計成垂直垂直的薄膜（鰭片），讓閘極能夠從左、右、上三面進行控制，大幅增強了靜電吸引力並抑制了漏電。而目前最先進的 GAAFET（Gate-All-Around）將通道設計成多層水平疊放的奈米線或奈米片，閘極則完全包裹住通道的四個側面。這種「全環繞」的設計提供了近乎完美的電力控制，是目前 3 奈米及未來 2 奈米、1 奈米製程得以實現的關鍵技術支撐。
+💡更多關於 MOSFET 的分類以及應用，股感站上已相關文章，本文就不做過多解釋。有興趣的讀者歡迎點擊下方連結看更多！
+延伸閱讀 &gt;&gt;&gt;
+MOSFET 是什麼？MOSFET應用有哪些？
+為何 MOSFET 近期的熱度再次提升？
+我們將話題回到 MOSFET ，雖然是成熟技術，但 MOSFET 在 2024 年至 2026 年間，熱度重新爆發，主要由以下原因推動。
+MOSFET 應用在 AI 伺服器
+AI 伺服器（如搭載 NVIDIA H100、Blackwell 架構的系統）對電力需求極高，傳統的 12V 電源系統在輸送強大電流時會產生巨大的熱損耗。因此，全球資料中心正大規模轉向 48V 供電架構。
+這種轉變對 MOSFET 產業產生龐大需求需求，為什麼呢？因為，
+48V 系統需要更多的電壓轉換
+導致單台伺服器內部的 MOSFET 數量增加 2 至 3 倍
+。而為了應對高效率與高功率密度要求，系統需要導入更先進的中壓與低壓 MOSFET 封裝技術及材料。
+AI 伺服器與傳統伺服器 MOSFET 需求對比
+傳統伺服器
+AI 伺服器
+(如 NVIDIA 平台)
+對 MOSFET 的影響
+500W – 1000W
+3000W – 12000W
+功率承載能力需顯著提升 。
+12V 系統
+48V 系統
+需更多中壓 (30V-100V) MOSFET。
+MOSFET 使用量
+約 40 – 60 顆
+超過 150 – 200 顆
+帶動出貨量呈倍數成長 。
+轉換效率要求
+92% – 94%
+97.5% 以上
+驅動 MOSFET 往低導通阻抗方向演進
+MOSFET 應用在電動車與再生能源
+電動車（EV）的滲透率在 2024 年的全球銷量超過 1700 萬輛，而一輛電動車在牽引逆變器、車載充電器（OBC）、DC-DC 轉換器以及電池管理系統（BMS）中，需要使用上千個功率 MOSFET。跟傳統燃油車相比，電動車對 MOSFET 的需求價值量提升了 5 至 10 倍 。同時，太陽能與風能系統中不可或缺的逆變器，也極度依賴高壓 MOSFET 進行直流與交流電的轉換 。
+2025 年安世半導體（Nexperia）事件
+在 2025 年，全球 MOSFET 產業發生一場震驚業界的風暴，總部位於荷蘭的功率半導體龍頭安世半導體（Nexperia）在 2019 年被中資聞泰科技（Wingtech）收購。這場事件改寫全球供應鏈，也為台灣廠商帶來結構性轉單機會。
+安世之亂事件起因
+2024 年底，當時美國商務部把聞泰科技列入美國出口管制清單。到了 2025 年 9 月 30 日，荷蘭政府罕見地引用冷戰時期的《商品供應法》（Goods Availability Act），以維護國家安全及供應鏈治理缺陷為由，強制接管安世半導體。
+緊接著 2025 年 10 月，荷蘭法院裁定暫停聞泰創辦人張學政的 CEO 職務，並凍結中資母公司的投票權，由法院指派的臨時管理層接手營運。中國政府隨即展開強力反擊。2025 年 10 月 4 日，中國商務部宣布對安世位於東莞等地的中國廠區實施嚴格的出口管制，禁止成品與組件運往歐洲及美國。
+原先晶片都是先在歐洲設計及前端生產，再送到中國進行封裝出貨。也導致安世在全球汽車供應鏈中（安世供應歐洲車廠約 40% 需求的 MOSFET 與二極體）瞬間面臨斷鏈。高度依賴安世的嵌入式組件的車廠像福斯、BMW、賓士及本田，不得不面臨減產或停產。
+截至 2026 年初，安世半導體實際上已經分裂成兩個實體：歐洲的總部（EMEA）與中國的生產子公司。歐洲總部指控中國廠區將原定出口的庫存私自轉賣給中國本地客戶，並試圖繞過歐洲技術授權另起爐灶。雖然 2025 年底雙方曾短暫透過豁免，放寬部分限制以緩解斷鏈壓力，直到目前 2026/05 為止事情還沒有定案，雙方仍在法院攻防。
+這種不確定性引發了全球車廠大規模的「去風險化（De-risking）」浪潮。由於車用電子元件需經過嚴苛的 AEC-Q101 認證，且導入週期長達 5 至 10 年，一旦某個供應商被標記為「地緣政治高風險」，車廠會毫不猶豫地尋找具備同樣認證、且「非中資背景」的替代方案，這也讓台灣功率元件廠商迎來的黃金時刻。
+台廠轉單效應
+台灣 MOSFET 與功率元件廠商因長期深耕車規市場，且擁有完整的自主產能，成為此波危機中全球車廠的首選。
+安世事件後受益台廠
+受益關鍵原因
+轉單與市場動態描述
+車用營收佔比逾 50%，具備齊全的車規 TVS/MOSFET 認證。
+2025 年底營收年增顯著，股價提前反應市場預期。
+產品線與安世高度重疊，具備從晶圓到封裝的完整 IDM 能力。
+成功切入歐洲高階車廠供應鏈，填補安世留下的空缺，營運朝高壓、高頻升級。
+專精於 48V 系統 MOSFET 模組，
+車用布局較深。
+受惠於車用系統升級與安世供貨不穩，加速擴建產線以應對歐洲與日本車廠的急單。
+具備 PMIC+MOSFET 的 SPS 整合能力，打入伺服器與網通。
+雖然主力在運算平台，但也受惠於整體供應鏈對非中資電源管理方案的需求提升。
+由於更換供應商涉及極高的驗證成本與風險，一旦歐美車廠在 2025 年將訂單轉向台廠並完成驗證，這些產能將在未來 5 到 10 年的車型週期中穩定貢獻，讓台廠晉升主要供應商。
+全球 MOSFET 市場現況與台廠地位
+全球 MOSFET 市場主要由歐、美、日的大型垂直整合製造商（IDM）主導。這些大廠擁有自己的晶圓廠、封測廠與研發中心，能夠垂直整合技術與產能。
+2024-2025 全球功率 MOSFET 市占排名
+2024 市佔率估計
+關鍵動態與技術亮點
+英飛凌 (Infineon)
+23.53%
+全球龍頭，收購 GaN Systems 強化氮化鎵布局，引領 300mm 功率晶圓技術 。
+安森美 (ONsemi)
+12.02%
+專注汽車與工業領域，與全球多家 EV 巨頭簽署 SiC MOSFET 長期供應合約 。
+意法半導體 (STMicro)
+6.58%
+碳化矽 (SiC) 領域的先驅，與特斯拉有深厚的供貨關係 。
+安世半導體(Nexperia)
+6.17%
+低壓和中壓 MOSFET 被廣泛應用於汽車和行動應用領域。
+威世 (Vishay)
+5.26%
+推出 Gen 4.5 系列高壓 MOSFET，有極低導通電阻與高耐用性 。
+台廠的市場份額與切入點
+台灣 MOSFET 業者在早期主要集中在「低壓（30V 以下）」市場，尤其是在主機板與筆記型電腦應用中佔有極高市佔率。然而，隨著消費性電子利潤趨薄，台廠正積極轉向中高壓與高性能市場。
+目前，台廠在全球 MOSFET 產值的佔比約在 10% 至 15% 之間，但在特定的 PC 相關領域，台廠供應全球超過 50% 的需求。近年台廠的策略明確轉向「去消費化」，開始切入伺服器 V-Core、工業馬達驅動以及電動車電源管理。
+例如，力智 (6719) 與大中 (6435) 等公司，成功打入全球主流伺服器與資料中心供應鏈 。台灣有全球最完整的半導體生態系，透過與世界先進 (5347) 或台積電等代工廠的合作，台廠能快速導入最先進的溝槽式（Trench）或屏蔽閘極技術（SGT），展現極強的成本與技術競爭力 。
+MOSFET 台灣概念股
+台灣 MOSFET 產業鏈主要由設計公司（Fabless）與相關的晶圓代工、封測廠組成。在這一波 AI 與 EV 浪潮中，相關個股的表現與公司技術轉型深度密切相關，除了以下公司外還有其他相關概念股，礙於篇幅股感就沒有一一列出。
+台灣 MOSFET 概念股
+電源管理 IC 與 MOSFET 整合 (SPS)
+深耕 AI 伺服器供電，網通平台營收佔比提升，目標伺服器營收突破 5% 。
+高壓、中壓 MOSFET 設計
+受益於 48V 資料中心架構升級，中壓 SGT MOSFET 出貨穩健。
+PC 與消費性 MOSFET
+積極布局高壓產品與第三類半導體 (SiC) 研發，切入能源管理領域。
+功率半導體元件
+隸屬鴻海集團，具備電動車平台 (MIH) 內供優勢，發展高壓 MOSFET 與 SiC 技術。
+NB 與消費性功率元件
+轉向高效能運算 (HPC) 與穿戴式裝置電源管理，優化產品組合以提升毛利。
+功率半導體晶圓代工
+與漢磊合作開發 8 吋 SiC 產能，預計 2026 年量產，搶佔 WBG 元件代工先機 。
+功率半導體導線架
+英飛凌、意法半導體等國際大廠合作夥伴，掌握高階電力模組的物理基礎（散熱）。
+整流二極體、MOSFET
+擁有自有封裝技術與中低壓 MOSFET 產品線
+MOSFET、二極體
+成功從消費性轉入伺服器與工控，具備溝槽式 (Trench) 技術，產品效率更穩定
+二極體、功率半導體
+美商Diodesy子公司，轉型高階 TVS (瞬態電壓抑制器) 與 SiC 封裝
+車用發電機二極體、SiC 模組
+強項在車用，高功率 IGBT/SiC 模組技術
+轉向伺服器電源
+碳化矽 (SiC)、氮化鎵 (GaN) 代工
+台灣第三代半導體純代工龍頭，
+擁有全台灣最成熟的 SiC 產線，具備 6 吋產能
+碳化矽 (SiC)、氮化鎵 (GaN) 磊晶 (Epi)
+唯一具備 SiC/GaN 磊晶量產能力的供應商
+力智 (6719) 的高價值轉型
+力智電子是台灣 MOSFET 領域中，少數具備將電源管理 IC (PMIC) 與功率元件 (MOSFET) 整合為「智慧功率級」(Smart Power Stage, SPS) 能力的公司。在 AI 運算中 GPU 需要極高能量密度的供電，力智的 SPS 產品具備高電流承載（達 90A 以上）與優異的熱管理，成為 AI 伺服器供應鏈中的重要參與者。2026Q1 法說會透露，雖然短期內受庫存調整影響，但其高價值產品佔比持續提升，推升毛利率回升至 35% 以上，公司從消費性電子轉向高效能運算。
+強茂（2481）轉單挹注
+強茂是全球第五大整流元件製造商，產線從晶片設計、製造、封裝測試到銷售，旗下有三座晶圓廠以及 5 座封裝廠。主要產品包含
+MOSFET
+33% 、
+19% 以及
+高階產品 BJT
+1%。產品佔比則為
+3%。25 年底的安世之亂也讓強茂獲得歐洲車用 MOSFET 轉單機會，產品驗證期縮短至兩季， 預計 26Q2 就會有營收挹注。
+嘉晶（3016）
+嘉晶隸屬漢磊集團，是全球矽及化合物磊晶片代工龍頭 。產品結構以矽磊晶佔 90% 為核心 ，功率 MOSFET 則是下游應用。前面提到 AI 伺服器電源轉向 800V 高壓直流架構，帶動 MOSFET 用矽磊晶需求，促使 8 吋產品佔比在 26Q1 飆升至 70% 。近期更切入矽光子光偵測器（
+）磊晶代工，同時跨足兩大話題。
+MOSFET 產業從過去被視為低階、低毛利的基礎零件，到如今成為 AI 伺服器電力心臟與電動車效能關鍵，相關技術門檻還有商業價值也隨之提升。
+AI 驅動的量價齊揚
+：48V 供電架構的升級，增加 MOSFET 的使用數量，也驅動高階封裝與中壓高性能產品的市場需求，提高產品單價。
+第三類半導體的替代效應
+：SiC 與 GaN MOSFET 的普及將重新定義高壓與高頻電路的設計，而具備提前布局能力的國際 IDM 廠與台灣代工廠（如世界先進）將成為最大受益者 。
+台廠的升級機遇
+：台灣 MOSFET 個股脫離單一的消費性循環，透過與 AI 伺服器品牌廠及車用電子供應鏈的深度綁定，預計會有更強的獲利與成長潛力。
+【延伸閱讀】
+矽谷晶片危機解密：美國擺脫台灣半導體依賴的幕後角力與談判內幕
+IC 設計是什麼？半導體產業鏈有哪些？IC 設計、IC 製造、IC 封測全解析！
+第三代半導體是什麼？碳化矽（SIC）概念股、第三代半導體概念股有哪些？
+270666</t>
+        </is>
+      </c>
+      <c r="I22" s="1" t="n">
+        <v>46244.6238288426</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>f6fd556ce7e06082903a08836771552e9a863fb20d553ec3baa79b6b22fca37d</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>【獨家專訪】SAPIEN Semiconductors：從大型Micro LED 顯示器到近眼顯示裝置的全方位解決方案 - ledinside.com.tw</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://www.ledinside.com.tw/interview/20251017-40226.html</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ledinside.com.tw</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Fri, 17 Oct 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>SAPIEN Semiconductors致力於與全球 Micro LED 顯示器產業的關鍵客戶緊密合作，提供創新的解決方案。此外，該公司在2024年成功於韓國KOSDAQ掛牌上市，創下79.9億韓元的營收佳績，年成長率高達149%。SAPIEN Semiconductors為了更完善服務客戶也在矽谷設立辦公室，而客戶們也包含多家美國科技巨頭。TrendForce 很榮幸與 SAPIEN Semiconductors執行長李明熙（Myunghee Lee）及策略長 Ethan Jin 進行電話專訪。他們分享了對 Micro LED 市場展望的寶貴見解，並討論了公司目前的發展狀況。
+SAPIEN Semiconductors Inc. 成立於 2017 年，是一家無廠半導體設計公司，專注於為 Micro LED 顯示驅動器開發客製化 ASIC 產品與解決方案。該公司運用創新且已經在矽晶圓片上驗證的設計IP，為客戶提供完整為客戶提供涵蓋各種Micro LED顯示解析度及尺寸的完整解決方案。這些解決方案適用於從元宇宙到大型顯示器等各類應用領域。根據 SAPIEN Semiconductors 的專利組合，在近眼顯示應用中採用具備 PWM 的主動驅動 CMOS 架構，可有效降低功耗。此外，就大型顯示器而言，採用具備 PWM 驅動的Micro IC，不僅能更容易點亮 LED，還能避免驅動電流過低的問題。
+李明熙表示，SAPIEN Semiconductors已成功提供標準化與客製化的 CMOS 產品，以滿足不同客戶的需求。例如，該公司目前已向市場提供採用 28nm 節點的標準全彩 CMOS產品，以及採用 22nm／28nm 節點的客製化單色 CMOS 背板 IC，支援 2.5µm 的像素間距，解析度達 800×600 至最高 2K。未來，公司規劃突破22nm製程節點與2µm像素間距的技術門檻，以實現1280x720 或更高的 FHD解析度。針對大型顯示器，SAPIEN Semiconductors正致力開發Micro IC，為美國主要科技公司提供具附加價值的解決方案，產品主要鎖定新一代筆電顯示器應用。這些解決方案旨在提升亮度均勻性、提高對比度並降低功耗，從而實現更卓越的靜態與動態畫質。
+李明熙認為，Micro LED 技術結合 CMOS 可廣泛應用於近眼顯示、筆電顯示、車用顯示與大型顯示器，將引領新一代顯示技術進入非凡的新時代。</t>
+        </is>
+      </c>
+      <c r="I23" s="1" t="n">
+        <v>46244.6238612963</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>840706a5bdb3730b7ee331116b12d747e3b5e516c12211f189d3480622602686</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Arm 首度在台領投！專家分析：通寶半導體憑尖端技術獲全球矽智財IP龍頭入股 - ETtoday財經雲</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://finance.ettoday.net/news/3129203</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ETtoday財經雲</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Mon, 09 Mar 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>▲通寶半導體憑尖端技術獲全球矽智財IP龍頭入股 。（圖／通寶提供）
+記者陳弘修／台北報導
+台灣半導體產業再傳佳音！通寶半導體（QBit Semiconductor）宣布獲得全球半導體技術龍頭Arm的策略性入股，正式成為台灣首家獲其直接投資之 IC 設計夥伴。另外，通寶已規畫於 2026 年第四季正式申請 IPO 上市。
+隨著技術實力與營運規模，通寶半導體的成長過程相當受到財經與科技界關注。創辦人暨董事長沈軾榮在第一波募資中，通寶公司便吸引國發基金等國家級單位資金挹注；而在最新一輪募資中，Arm 更決定直接參股，成為通寶邁向國際市場的重要推手。
+針對此項投資，Arm 全球執行副總裁暨商務長 Will Abbey 表示，透過與通寶的合作，Arm 能結合先進的影像處理與安全能力，支持列印及影像市場的創新。這也展現了 Arm 的廣泛策略：將其架構從高效能系統延伸至更具成本效益的裝置，建立差異化的解決方案。
+通寶半導體的專業優勢，有助於 Arm 在特定垂直領域（如列印、掃描、影像辨識、AI 生態圈） 開發出更具成本競爭力的產品。此次投資不僅代表 Arm 對通寶技術積澱的肯定，更象徵雙方將共同為未來的影像處理精密控制市場奠定堅實的基礎，開創台灣 IC 設計走向全球戰略合作的新模式。
+▲通寶半導體公司董事長暨執行長沈軾榮。
+財經專家汪潔民在廣播節目中也表示，全球矽智財IP龍頭Arm正式投資通寶半導體，這不僅是 Arm 在台灣的首例直接投資案，更顯示出台灣在特殊應用領域（SoC &amp; ASIC）的研發實力已獲國際頂尖大廠認可。
+汪潔民分析，Arm過去並未投資台灣任何一家公司，為何特別選擇通寶，關鍵在於通寶具備「可怕的先進影像處理技術」。通寶是全球極少數能自主開發並成功整合以下三大核心技術的公司：AI 智慧影像處理運算、精密動件控制、節能感知管理，特別是在多功能事務機（MFP）產業，晶片設計必須同時應對極其複雜的影像還原、精密機構運作及高度資安防護，技術壁壘極高。通寶憑藉先進影像處理功能，在競爭激烈的 IC 設計市場中脫穎而出。
+※本文版權所有，非經授權，不得轉載。
+[ETtoday著作權聲明]
+A-Lin誇曾國城「下麵好吃」　狂開車他笑瘋：你在說什麼
+快訊／台積電開獎！　7月、前7月營收雙創紀錄
+晶圓代工龍頭台積電（2330）今日公佈 2026 年 7 月營收報告。台積電 7 月合併營收約為新台幣 4,675 億 8,000 萬元，較上月增加了 5.6%，較去年同期增加了 44.7%，續創單月歷史新高。
+2026-08-10 13:42
+國票金副董年薪2千萬掀波　大股東一銀出手！2聲明促檢討薪酬
+國票金（2889）副董事長年薪高達2,000萬元引發爭議，身為大股東之一的第一銀行今（10）日出手表態，針對國票金高階主管薪酬議題提出2項聲明，除已促請所推舉董事透過董事會檢討國票金及子公司薪酬結構合理性，也要求持續精進公司治理，以保障股東權益。
+2026-08-10 14:09
+記憶體缺貨兩樣情！3檔亮燈漲停　千金股勤誠挫6%
+記憶體缺貨題材今（10）日呈現兩樣情，上游記憶體族群買氣火熱，南亞科（2408）、華邦電（2344）、巨虹（8084）盤中一度亮燈漲停，旺宏（2337）漲逾8%，晶豪科（3006）更大漲9.75%、距離漲停僅一步之遙；相較之下，下游通路族群走勢偏弱，威剛（3260）、十銓（4967）、宇瞻（8271）、創見（2451）股價全面走疲，千金股勤誠（8210）也受記憶體缺料、營收認列遞延影響，盤中跌幅一度達6.73%。
+2026-08-10 11:47
+2.5兆股利放大術！0050橫掃3世代　2檔主動式ETF擠進前10強
+上市櫃企業獲利創高帶動下，今年現金股利發放規模可望突破2.5兆，凱基證券觀察，愈來愈多投資人已不再將股利視為一次性的收入，而是把股利再投入，經統計元大台灣50（0050）成為所有年齡層股利再投入主要標的，尤其Z世代（19～30歲）投入占比高達29%，展現年輕族群「先存市值、再談收益」的理財觀念。
+2026-08-10 11:35
+禾伸堂處置出關奔漲停　被動元件5檔齊亮燈
+處置股新制於今（10）日上路，禾伸堂（3026）處置提前解禁，股價跳空直奔588元漲停，其他遭處置被動元件全數恢復正常交易，日電貿（3090）、天二科技（6834）、光頡（3624）、雷科（6207）、富致（6642）等五檔一度亮燈攻漲停，國巨*（2327）漲幅逾半根停板。
+2026-08-10 11:10
+處置新制來了！南電明提前出關今漲逾半根　景碩、欣興紅盤同慶
+台股處置新制今（10）日正式上路，ABF載板景碩（3189）、欣興（3037）、因股價波動過大，每2分鐘撮合一次，處置至8月14日止，欣興漲逾3%，來到985元，景碩則是漲逾1%，南電（8046）適用銜接制度提前明（11）日出關結束處置，股價開高走高，漲逾半根停板，上攻1150元，突破季線，臻鼎-KY（4958）則是盤上震盪。
+2026-08-10 10:20
+台股6千金齊亮燈　權值股台達電帶旺指數漲近千點
+台股今（10）日在權值股、高價股奮力上攻下，多頭信心滿滿，特別是權值股「三哥」台達電（2308）、萬金股后川湖（2059）等6檔亮燈漲停，開盤1小時後加權指數漲近千點。
+2026-08-10 10:18
+面板雙雄齊亮燈！台積電遭爆搶購友達廠房　公司：不回應傳聞
+護國神山台積電（2330）爆出有意向面板廠購地擴廠，受此消息影響，面板股友達（2409）、群創（3481）早盤雙雙亮燈漲停，開盤不到半小時皆湧入逾18萬張成交量，居成交排行前2大。
+2026-08-10 10:14
+川湖處置首日再飆漲停！一張爽賺111萬　本土投顧喊17500元
+伺服器滑軌大廠、股后川湖（2059）今（10）日迎來處置首日，股價開盤直攻漲停價12,220元，連續2個交易日亮燈漲停，再刷掛牌以來歷史天價，盤中一度大漲1,110元，等於每張帳面多賺111萬元。不過漲停並未鎖牢，開盤約10分鐘後打開，漲幅快速收斂。
+2026-08-10 09:17
+首檔聚焦PCB供應鏈龍頭的ETF　 009828於8／17開募
+隨著AI伺服器、高速運算及資料中心建置需求持續升溫，市場投資焦點正由晶片與伺服器，逐步擴散至PCB、載板及高階材料等關鍵供應鏈，瞄準此趨勢，中國信託投信推出國內首檔聚焦PCB供應鏈的「中信台日韓PCB ETF（009828）將於8月17日至20日展開募集，助投資人一次布局台灣、日本及韓國PCB產業龍頭，掌握AI硬體規格升級所帶動的長期成長商機。
+2026-08-10 14:31
+我也要留言，快前往新聞雲App！</t>
+        </is>
+      </c>
+      <c r="I24" s="1" t="n">
+        <v>46244.62388615741</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>6707a17d53879fe3227e2c9c22edabb69bbb83ed41f96e0833d8927ec8c45514</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AI x 半導體下的新契機，《AI核心驅動全球半導體競局》研討會成功解密 - TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://technews.tw/2026/04/13/trendforce-2026-hsinchu-semiconductor-forum/</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Mon, 13 Apr 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>集邦科技與科技新報於 2026 年 3 月 31 日假新竹暐順國際會議中心盛大舉辦《AI核心驅動全球半導體競局》研討會。來自產官學研的專家們嘗試從半導體新聚落、晶圓代工、半導體價值鏈升級、邊緣 AI 落地、DRAM 創新、CPO 新趨勢等專題發表，共同探索在 AI 算力掛帥時代下，半導體產業得以致勝的關鍵下一步。
+AI 成為晶圓代工主要驅動力，強勁 PMIC 需求拉高 8 吋廠利用率
+集邦科技研究經理喬安表示，記憶體、電源（包含與 AI 相關的 PMIC 電源管理 IC 與 Power Discrete 功率離散元件）及先進技術（包含與 AI 相關的先進製程、先進封裝）成為 2026 年的三大關鍵字。
+根據 TrendForce 集邦研究數據指出，2026 年全球晶圓代工市場營收預估達 2,187.74 億美元，其中台灣占比高達 79%（光台積電便占了 74%，聯電 3.7%），中國 8%（中芯國際 4.6%，華虹集團 2.4%），韓國 7%（三星 6.2%）。受到市場全面轉向 AI 影響，2026 年先進製程（16 奈米以下）YoY 年增率達 36%，超越 2025 年的 28%。反觀成熟製程則因 AI 擴大擠壓消費性產品需求而導致成長受抑，年增率從 2025 年的 15%，腰斬至 2026 年的 6%。
+今年由於記憶體價格大漲，嚴重壓縮消費性產品成本，其中尤以智慧手機（YoY -11%）、筆電（-9%）、平板電腦（-6%）的出貨量遭到重挫，受到衝擊的還包括 TV 與顯示器（皆為 -1%）。撐起市場半邊天的半導體終端產品主力是伺服器（出貨量年增率突破 13% 新高）、AI 伺服器（28%）與新能源車（16%）。
+喬安最後總結 5 個值得持續關注的重點：（1）AI 已然成為晶圓代工產業自 2024 年到 2026 年的主要驅動力。（2）更強勁的 PMIC 需求持續拉高 8 吋廠的利用率。（3）在多廠區產能規劃與多次 Tape-out 設計定案策略下，成本持續攀升。（4）價格持續攀升的先進製造仍屬稀缺資源。（5）隨著區域市場分化加劇，成熟製程獲利壓力持續上升。
+算力平台已成半導體下一個主戰場，攜手業界共建 AI 算力新生態
+隨著 AI 運算需求快速成長，GPU 採購成本增加了 10 倍。除了 AI 開發涉及非常多階段且複雜的全生命週期外，當前 AI 基礎設施更面臨諸多管理挑戰，包括異構硬體環的整合與管理困難、缺乏視覺化儀錶板以做出更佳決策、高昂基礎設施成本與低 GPU 利用率，以及複雜且耗時的 AI 環境建置與模型開發。
+數位無限執行長陳文裕表示，數位無限推出的核心產品 AI-Stack 即為業界頂尖 AI 基礎設施管理平台，整合了第三代 GPU 切割技術、GPU 多片聚合、跨節點運算、全新操作介面、多雲管理、開源深度學習工具、 HPC 高效運算、RCS 環境部署等功能。
+該公司並另推 ixCSP AI 雲端服務與營運解決方案，為 AI-Stack 延伸的商用算力服務平台，能協助企業快速建置 GPU 即服務（GaaS）、模型即服務（MaaS）及 Token 即服務（TaaS），實現算力的商品化、服務化與可營運能力。
+陳文裕強調指出，「算力平台」已是下一個半導體競爭的主戰場，數位無限旗下 AI-Stack 集結了支援 GPU / ASIC 異質算力的 AI 運算層；展現算力調度、效能最佳化及 TCO 降低效益的優化層；打造企業資料湖、RAG 及 MLOps 的資料 / 模型層，以及實現智慧製造的應用層，正好站在這個價值鏈升級的交叉點上。
+半導體價值的未來在於「協作」，其中晶片提供了靈魂的載體，算力平台則賦予其運行的智慧。數位無限將持續深耕 AI-Stack，成為台灣半導體產業升級的最佳夥伴，並與業界共建 AI 算力新生態。
+AI 成功導入關鍵在於軟硬協同，助攻台灣從「矽島」走向「光電島」
+除了前面談到的精采議題外，參與本次盛會的主講者也為與會佳賓們採討邊緣 AI 落地的實踐訣竅、滿足 AI 高效能運算的 DRAM 記憶體創新，以及 CPO 設計關鍵與商機。
+擷發科技技術長暨 IC 設計事業群總經理吳展良表示，AI 的成功導入關鍵在於「軟硬體協同」。從整體的系統層設計，到軟硬體的協同運作，再到跨平台的靈活部署，這三者都至關重要。AI 的落地不應僅僅聚焦於單一晶片的性能或單一模型的優劣，而是一個系統性的工程。
+愛普科技 VHM 產品處處長闕欣男表示，卓越的能耗與算力是目前 AI 及高速運算的必要的條件。該公司提供的 VHM（very high bandwidth memory）產品，是第一個透過 WoW 3D 堆疊的寬頻記憶體方案，提供比傳統記憶體超過 10 倍的頻寬，並達成 70% 以上的能耗優化，不僅能因應 AI 應用需求，並能支持未來運算技術的突破。
+恩萊特科技總經理蘇正宇表示，光電共封裝（CPO）不再是「是否」的問題，而是「現在式」的最佳光互連方案。該公司並提出支持台灣產業搶佔 CPO 商機的四項行動建議：搶佔 2026 量產窗口、建立亞洲最完整 PDK 平台、服務南部矽光子聚落、推動設計流程標準化。總之，恩萊特科技將掌握工具、賦能產業、共創未來地支援台灣半導體生態從「矽島」走向「光電島」。
+（首圖來源：TrendForce）
+文章看完覺得有幫助，何不給我們一個鼓勵
+請我們喝杯咖啡
+想請我們喝幾杯咖啡？
+每杯咖啡 65 元
+您的咖啡贊助將是讓我們持續走下去的動力
+總金額共新臺幣
+《關於請喝咖啡的 Q &amp; A》
+留給我們的話
+從這裡可透過《Google 新聞》追蹤 TechNews</t>
+        </is>
+      </c>
+      <c r="I25" s="1" t="n">
+        <v>46244.62435674768</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>795c8f4a6a73a784ae2822b9bedadb516b4a30d0253d2c61ba9e16b5dfbaedd3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>「落後國際 5~10 年」，中國半導體高層罕見坦承 AI 晶片差距 - TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://technews.tw/2026/03/31/china-semiconductor-ai-chip-tech-lags-5-10-years-equipment-talent-bottlenecks-worsen/</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tue, 31 Mar 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>在今年 3 月 25 日至 27 日於上海舉行的 SEMICON China 2026 相關論壇上，多位中國半導體業界高層罕見坦言，當地在 AI 資料中心晶片領域與國際領先者之間仍有約五到十年的差距。與此同時，AI 應用快速擴張也正把設備、被動元件與人才供應推向緊繃狀態。
+根據與會者說法，AI 熱潮雖然推動晶片技術與投資持續升溫，但下一階段的突破更仰賴半導體製造設備的進展。ACM Research 執行長 David Wang 表示，AI 浪潮帶動了晶片進步，但未來運算效能的演進路徑，很大程度上將由新一代製造設備決定，而目前這些下一代工具尚未開發完成。
+在需求端，國家矽產業集團資深副總裁李偉提到，記憶體、資料中心電源管理 IC，以及光電技術的需求正在上升，資料傳輸與 6G 也逐漸成為焦點。Sino IC Leasing 執行副總裁袁以沛（Daniel Yuan）則指出，隨著資料中心建設加速，多層陶瓷電容器出現供應吃緊，反映支撐 AI 伺服器建置的被動元件正面臨更大壓力。
+在製造與人才方面，重慶芯聯微電子資深副總裁李海明表示，AI 成長迫使中國晶圓廠加快擴產，但人才留任與設備利用率仍是關鍵瓶頸。他直言，中國在消費性晶片仍具競爭力，但在車用與資料中心半導體方面，與外部領先水準仍相差五到十年。不過，他也認為，將 AI 導入製造流程，可能是縮小差距的可行途徑。
+論壇同時聚焦中國半導體企業的國際化策略。與會高層認為，持續投資與市場規模是維持全球競爭力的基礎，而差異化技術則是走向海外的關鍵。儘管地緣政治限制仍在，業者普遍認為，只要能提供具價值的產品與方案，仍有機會爭取海外客戶；而國內競爭加劇，也正在迫使更多公司把目光轉向出口市場。
+整體而言，這場論壇凸顯中國晶片產業正一邊加速追趕 AI 浪潮，一邊承受供應鏈與人才的雙重壓力。業界共識是，AI 將持續推升資本支出，而只有在設備升級、製造效率與技術投資同步跟進的情況下，相關企業才有機會縮短與國際先進水準的距離。
+Chinese chip industry leaders admit the country lags five to ten years behind in AI data center chips — AI demand is straining equipment and talent supply
+（首圖來源：shutterstock）
+文章看完覺得有幫助，何不給我們一個鼓勵
+請我們喝杯咖啡
+想請我們喝幾杯咖啡？
+每杯咖啡 65 元
+您的咖啡贊助將是讓我們持續走下去的動力
+總金額共新臺幣
+《關於請喝咖啡的 Q &amp; A》
+留給我們的話
+從這裡可透過《Google 新聞》追蹤 TechNews
+AI 資料中心</t>
+        </is>
+      </c>
+      <c r="I26" s="1" t="n">
+        <v>46244.62438107639</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>3e4e570dc5e57385463f20950b03756693c3b3a1e174a7661378e6de86fe8b38</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>WSTS：2026 年全球半導體營收增 26.3%，逼近 1 兆美元 - TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://technews.tw/2025/12/02/global-semiconductor-revenue-nears-1-trillion-by-2026/</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tue, 02 Dec 2025 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>世界半導體貿易統計組織（WSTS）發布全球半導體市場最新預測報告，預期 2025 年全球半導體營收可望成長 22.5%，2026 年再增長 26.3%，逼近 1 兆美元關卡。
+（Source：
+WSTS預估，2025年全球半導體營收可望達7,720億美元，較先前預估高出近450億美元，年增22.5%。主要受惠邏輯和記憶體市場得益於人工智慧應用及資料中心基礎設施強勁需求。
+2025年邏輯IC營收可望增長37.1%，是增幅最大的產品類別，其次是記憶體營收成長27.8%，感測器營收成長10.4%、微處理器營收成長7.9%、類比IC營收成長7.5%、光電子元件營收成長3.7%；受汽車領域需求疲軟影響，分離式元件營收恐下滑0.4%。
+美洲和亞太地區營收可望分別增長29.1%及24.9%，主要是受惠邏輯IC和記憶體業務強勁成長；歐洲營收成長5.6%，日本恐下滑4.1%。
+展望2026年，WSTS預期，全球半導體營收可望再成長26.3%，達到9,750億美元，記憶體和邏輯IC仍是主要成長動能，分別成長39.4%及32.1%；美洲和亞太地區是成長最強勁的地區，分別成長34.4%及24.9%。</t>
+        </is>
+      </c>
+      <c r="I27" s="1" t="n">
+        <v>46244.62440524306</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>b3fcc0ab81072690e082b4cb78aa52d73ad66d06a60932ac81969b70cc6942e2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>礼鼎半导体冲刺港股，中国内地IC载板排名第三 - FX168财经</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://news.fx168news.com/cooperate/2607/7469152.shtml</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>FX168财经</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Thu, 02 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" s="1" t="n">
+        <v>46244.62454228009</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>470674249962a799c89eb1334da0c3195b7d7f00248425e72020ce9da2b6f162</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>工研院先進半導體研發基地破土，台積電捐助設備定 2027 年完工 - TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://technews.tw/2026/02/10/the-industrial-technology-research-institute-itri-advanced-semiconductor-rd-base-broke-ground/</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tue, 10 Feb 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>經濟部攜手國發會、國科會共同打造的「先進半導體研發基地」，10 日於工研院中興院區正式動土、藉由晶創台灣方案的支持，基地內將設有「先進半導體試產線」，2027 年底完工後，將提供「IC 設計創新試產驗證」、「先進半導體製程開發」、「設備材料在地化驗證」三項服務，有效降低中小型 IC 設計公司與新創公司的驗證門檻，協助國內材料及設備業者強化競爭力，並超前部署 AI 晶片、矽光子、量子等前瞻技術，開創半導體創新研發生態系，並強化台灣在全球半導體產業的關鍵地位。
+當場致詞的行政院院長卓榮泰表示，AI驅動下使得半導體需求激增，半導體不僅是當前世界各國全力爭取發展的產業，也是台灣連結世界的關鍵樞紐，同時更是總統賴清德提出的AI新十大建設、五大信賴產業政策的核心項目。隨著 算力需求越來越大，政府積極打造台灣從「半導體製造大國」升級為「AI智慧島」，在基礎建設上超前部署，而這座「先進半導體研發基地」，就是國家戰略拼圖中不可或缺的一塊，同時，政府也會扮演產業最強力的後盾，確保產業在研發創新的路上，沒有後顧之憂。
+經濟部部長龔明鑫表示，面對國際局勢變動與全球供應鏈重組，在全球賽跑中持續領先的關鍵就在於強化研發韌性與自主技術，經濟部積極推動「先進半導體研發基地」，有三大亮點，第一是培育生態系、鎖定中小型IC設計公司、新創，或本土設備、材料商，提供新材料、設備、製程反覆驗證機會，例如少量多樣、可彈性調整之「新型態晶圓共乘服務」、縮短研發週期、加快商品化。讓產業生態系更完整、更有韌性。
+第二是技術多樣性，將鎖定目前應用最廣、需求最穩定的 28 到 90 奈米市場，也是AI 邊緣運算(Edge Al)與高效能運算需求最迫切的節點。突破、助攻AI 百工百業。第三是研發更前瞻，智慧醫療、自駕車、工廠自動化都需要特殊製程晶片，在工研院研發團隊全力配合下，基地將超前部署 AI晶片、矽光子、量子科技的尖端開發，扮演百工百業數位轉型的核心引擎，此外要特別感謝
+，不僅慷慨捐贈關鍵半導體設備，還派出專業團隊，提供最頂尖的建廠諮詢與技術指導，充分展現台灣半導體產業最珍貴的共好精神。
+經濟部長期深耕高階半導體技術研發，從材料、元件、製程、晶片設計、封裝到測試完整布局，積極建構我國半導體產業上中下游的一條龍開發能量，在晶創台灣方案政策推動下，已設置 3DIC 先進封裝試產線、八吋次微米感測晶片兩大試產線，並設置「檢量測驗證實驗室」，協助業界進行技術驗證與快速試製。現在進一步建設「先進半導體研發基地」，為國內研究機構首座新形態高科技半導體廠房，設有十二吋先進半導體後製程試產線，並升級現有八吋產線，預計2027年底完工。
+未來，基地將提供28至90奈米後段製程的研發與試產服務，串聯晶片設計、製造與封裝試量產，及測試驗證一條龍服務，協助中小型IC設計業者、半導體業者將產品開發時程縮短30%，並支援量子運算、矽光子、客製化晶片(ASIC)、整合型 3D 架構與下世代記憶體等前瞻技術。國內廠商可於本地完成研發、驗證、迭代的完整流程，強化半導體供應鏈的自主性與韌性；基地也將促進與大專校院合作，協助學生熟悉製程與業界需求，提升半導體人才量能與競爭力。期盼透過三大試產線與一座實驗室的整合，超前部署基礎建設，打造下世代半導體創新研發生態系。
+(首圖來源：科技新報攝)
+文章看完覺得有幫助，何不給我們一個鼓勵
+請我們喝杯咖啡
+想請我們喝幾杯咖啡？
+每杯咖啡 65 元
+您的咖啡贊助將是讓我們持續走下去的動力
+總金額共新臺幣
+《關於請喝咖啡的 Q &amp; A》
+留給我們的話
+從這裡可透過《Google 新聞》追蹤 TechNews
+先進半導體</t>
+        </is>
+      </c>
+      <c r="I29" s="1" t="n">
+        <v>46244.62456527778</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>9a7dc224540514f6744339f4ebfa33b103459d718bf62dec876901a104efd077</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>功率半導體(Power Semiconductor)-8 一文看懂，先進功率半導體技術路線圖：SiC、GaN與先進封裝| 科技 - 鉅亨號</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://hao.cnyes.com/post/256845</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>鉅亨號</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Mon, 29 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>功率半導體(Power Semiconductor)-8 一文看懂，先進功率半導體技術路線圖：SiC、GaN與先進封裝
+2026/06/29
+功率半導體產業將在 2026-2030 年迎來系統性躍遷。SiC 與 GaN 將全面邁向 8 英吋晶圓時代以降低成本，並透過溝槽柵與縱向結構突破電壓與性能極限。同時，先進封裝將從傳統模式轉向 2.5D/3D 異構整合，目標實現極低寄生電感 (&lt;3nH) 與極低熱阻，以支持 800V 高壓電動車平台與 AI 伺服器電源。未來 GaN 將主導高頻高密度場景，SiC 則在超高壓與高魯棒性領域保持優勢，兩者共同驅動電力電子系統的極致小型化與智能化。
+展望2026至2030年，碳化矽（SiC）功率半導體技術將圍繞“大尺寸、高整合、極致性能與高可靠性”的核心目標，在材料與襯底、器件結構與工藝、性能指標以及應用生態等方面，實現從技術攻堅到產業成熟的系統性躍遷。
+1. 材料與襯底技術：邁向低成本、高品質的8英吋時代
+2026-2030年將是8英吋（200mm）SiC襯底從量產匯入走向產業主流的決定性時期，其發展將顯著降低器件成本並支撐更大的晶片面積與更高產量。
+襯底缺陷控制與質量提升
+：基面位錯（BPDs）作為影響器件可靠性的主要殘留缺陷，其控制仍是技術攻堅重點。通過採用重複a面生長（RAF）等先進襯底製備技術，並持續最佳化物理氣相傳輸（PVT）法生長工藝的熱場設計與原料純度，目標是將8英吋襯底的缺陷密度（尤其是BPDs）穩定控制在約
+1×10¹¹ cm⁻³
+的極低水平，以滿足高壓大電流器件（如3.3kV及以上MOSFET）的製造需求。同時，雷射輔助切割（KABRA）與冷裂等低損耗晶圓切片技術將逐步替代傳統多線切割，以減少亞表面損傷，提高可用晶圓質量和材料利用率。
+成本下降路徑與量產化
+：8英吋晶圓面積約為6英吋的1.8倍，能顯著提升每片晶圓的晶片產出數量，這是降低
+單位晶片成本（Cost per Die）
+的核心驅動力。行業預測，從6英吋向8英吋襯底的遷移，在初期即可帶來
+超過20%
+的器件成本降低。到2028-2029年，隨著意法半導體、芯聯整合、羅姆、安森美等主要廠商產能的全面爬坡與良率提升，8英吋SiC襯底的供應將趨於穩定，其單位面積製造成本有望接近成熟的6英吋水平。屆時，8英吋襯底將成為SiC功率器件生產的
+，市場份額預計超過50%，建構起多元化、規模化的全球供應鏈，為SiC器件在電動汽車、太陽能等成本敏感市場的普及奠定基礎。
+2. 器件結構與製造工藝：從平面到立體的性能革命
+器件結構的創新與工藝的微縮化是持續提升SiC器件性能的關鍵。溝槽柵與超結結構將成為中高壓領域的主流技術方向。
+溝槽柵MOSFET的結構定型與可靠性突破
+：平面柵結構正加速被具有更低比導通電阻（R_on,sp）的溝槽柵MOSFET（UMOSFET）所取代。為解決傳統溝槽底部電場集中導致的柵氧可靠性問題，
+P+遮蔽區、雙溝槽（DT MOS）及非對稱保護注入
+等柵氧保護結構已從實驗室驗證走向大規模商業化應用。這些結構能將高電場從脆弱的柵氧化層轉移，同時顯著降低米勒電容（Cgd），最佳化開關性能。到2030年，結合
+柵氧介面工程
+（如氮化退火）的持續最佳化，商用溝槽柵SiC MOSFET的柵氧壽命（TDDB）在175°C下的平均故障間隔時間（MTTF）有望達到
+10⁹小時
+量級，滿足最嚴苛的車規級可靠性要求。
+超結（SJ）技術的產業化突破
+：超結結構通過在漂移區形成交替的N/P柱，能突破傳統單極器件的“矽極限”，實現極低的R_on,sp。其關鍵技術路徑依賴於
+深槽填充外延
+多步外延生長
+工藝，以在SiC材料中實現高深寬比溝槽的均勻摻雜填充。實驗室已展示出優異的性能潛力，例如3.3kV超結器件實現了
+3.3 mΩ·cm²
+的超低比導通電阻。預計在2027-2029年間，SiC超結MOSFET（特別是1200V-3300V平台）將從研發走向小批次量產，並在電動汽車主驅逆變器、大功率太陽能逆變器等高端應用中，展現出相較於傳統SiC MOSFET和矽基IGBT的顯著效率與功率密度優勢。
+3. 性能指標與可靠性：逼近理論極限的系統性最佳化
+隨著材料和器件結構的進步，SiC功率器件的關鍵性能指標將持續逼近4H-SiC材料的理論極限，同時系統級的可靠性得到全方位強化。
+靜態與動態性能的持續提升
+：通過溝槽節距微縮、超結最佳化以及歐姆接觸電阻的降低，商用SiC MOSFET的比導通電阻預計每年將有顯著改進。以1200V器件為例，其R_on,sp目標將從2026年的約
+2 mΩ·cm²
+向2030年的
+1 mΩ·cm²
+乃至更低邁進。開關性能方面，通過最佳化器件結構以降低所有寄生電容（Cgs, Cgd, Cds），並結合
+先進低寄生電感封裝
+（寄生電感目標
+&lt;3 nH
+），開關頻率支援能力將從當前的數百kHz向
+MHz等級
+邁進，從而顯著降低系統無源元件體積和開關損耗。
+高溫與可靠性壁壘的突破
+：目前商用SiC MOSFET的最高結溫（Tj_max）普遍為175-200°C。通過
+高k柵介質材料
+的探索、介面鈍化技術的改進以及
+耐高溫封裝材料
+（如AMB活性金屬釺焊基板）的應用，到2030年，商用器件的
+最高工作結溫有望提升至225°C-250°C
+。在可靠性方面，除了柵氧壽命的延長，
+短路耐受時間（SCWT）
+通過最佳化器件飽和電流與散熱路徑，目標從目前的幾微秒提升至
+以上。此外，在雙面冷卻等先進封裝支援下，功率模組的
+功率循環壽命
+（ΔTj=100°C）目標將達到
+量級，以滿足電動汽車全生命周期的高可靠性需求。
+4. 應用拓展與系統整合：從器件到解決方案
+技術演進最終將服務於應用場景的深化與拓展。SiC器件的高頻、高效特性將驅動系統架構的變革。
+核心應用場景的全面滲透
+：在電動汽車領域，SiC MOSFET將從主逆變器、車載充電機（OBC）向直流-直流轉換器（DC-DC）全面滲透，助力實現800V甚至更高電壓平台，縮短充電時間並提升續航。在可再生能源領域，基於SiC的太陽能逆變器和儲能變流器將因其更高的轉換效率和功率密度而成為主流選擇。此外，資料中心伺服器電源、工業電機驅動、軌道交通及智能電網等領域，都將因SiC技術的成熟而迎來能效的顯著提升。
+整合化與智能化趨勢
+：未來SiC技術的發展將不僅限於單顆器件性能的提升，更側重於
+系統級協同最佳化
+。具體表現為：
+智能功率模組（IPM）
+將SiC晶片與驅動、保護、感測電路乃至無源元件整合在單一封裝內，簡化系統設計並提升可靠性；
+晶片級互連技術
+（如銀燒結）替代傳統焊料，提高連接可靠性和散熱能力；器件設計與
+先進封裝技術
+（如雙面冷卻、嵌入式封裝）及
+專用柵極驅動晶片
+的深度協同，以徹底釋放SiC的高頻高速潛力，並解決電磁干擾（EMI）等問題。
+綜上所述，2026-2030年的SiC功率半導體技術路線圖描繪了一條從材料基底到系統應用的清晰升級路徑。通過8英吋襯底量產實現成本突破，借助溝槽與超結結構創新逼近性能極限，並依託整合化與可靠性提升滿足高端應用需求，SiC技術將完成從“優質選項”到“必然選擇”的關鍵跨越，全面賦能能源革命與電氣化未來。
+承接SiC技術在高壓大功率領域確立的“高品質-大尺寸-高可靠”技術範式，GaN功率半導體的演進路徑則呈現出鮮明的差異化特徵：其核心驅動力在於挖掘氮化鎵材料固有的高電子遷移率與高臨界電場優勢，在
+高頻、高效、高功率密度
+的應用場景中建構核心競爭力。2026-2030年，GaN技術將圍繞材料、器件、整合與系統四大維度展開深度攻堅，其路線圖的核心在於解決從實驗室性能到產業級可靠性的關鍵瓶頸，實現從消費電子向工業、汽車及資料中心等高性能市場的規模化滲透。以下將基於現有技術進展，系統梳理GaN功率半導體在未來五年的結構化演進路徑。
+（一） 材料基石：大尺寸矽基GaN外延的應力與缺陷協同調控
+GaN-on-Si作為當前產業主導技術平台，其向8英吋及更大尺寸晶圓過渡的處理程序，直接關係到製造成本下降與產能擴張。然而，矽與GaN之間高達
+約17%的晶格失配
+和顯著的熱膨脹係數（CTE）差異，導致外延層存在高位錯密度（
+10⁸–10¹⁰ cm⁻²
+）和開裂風險，這是尺寸放大處理程序中必須攻克的首要物理障礙。
+1. 應力控制與缺陷抑制的核心技術叢集
+多層緩衝層與超晶格工程
+簡單單層緩衝已演進為複雜的
+多疊層超晶格結構
+（如GaN/AlN序列）。通過精心設計緩衝層的材料序列、厚度與生長溫度，有效打亂並阻斷穿透位錯（Threading Dislocation）向有源區的傳播，這是降低缺陷密度的最核心工藝手段。
+CTE匹配的工程化襯底
+為從根本上解決因CTE失配導致的外延層應力開裂，特別是生長用於高壓器件的厚膜（&gt;10 µm）外延層，
+QST™（Qromis襯底技術）
+等專用襯底被開發出來。其CTE與GaN高度匹配，已實現
+無裂紋的厚膜GaN外延生長
+，為開發擊穿電壓超過650V乃至達到2.2kV的器件提供了關鍵的材料基礎。
+精密化的MOCVD工藝控制
+面向8英吋晶圓，金屬有機化學氣相沉積（MOCVD）技術通過
+兩流生長法
+分離惰性氣體與反應氣體，顯著改善了晶圓範圍內外延層厚度與摻雜濃度的均勻性。結合
+熱預算管理
+（精確控制升降溫速率），能夠動態調整生長條件，緩解熱應力累積，降低晶圓翹曲與破裂機率。
+2. 尺寸升級路徑與挑戰
+當前，6英吋GaN-on-Si晶圓已是量產標準，8英吋晶圓已在部分代工廠實現可用性。向12英吋邁進是長期目標，但面臨更嚴峻挑戰：
+均勻性控制
+晶圓面積倍增，對厚度、摻雜及缺陷分佈的全域均勻性提出極限要求。
+應力與翹曲管理
+襯底破裂構成了最大困難
+”（substrate fracturing poses the greatest difficulty），大尺寸下熱應力導致的機械失效風險非線性增加。
+裝置與工藝相容性
+現有6英吋和8英吋產線裝置需進行重大調整或更新，以適配12英吋工藝，這是一項巨大的資本與技術工程。
+因此，2026-2030年間，8英吋GaN-on-Si外延技術將通過
+緩衝層最佳化設計
+CTE匹配襯底的局部應用
+（針對高壓產品）實現穩定量產與良率提升，而12英吋技術將主要處於研發與中試驗證階段，全面量產預計在此時間窗口之後。
+（二） 器件核心：p-GaN柵HEMT的可靠性躍遷與魯棒性設計
+增強型（E-mode）操作是功率開關器件安全應用的前提，p-GaN柵高電子遷移率電晶體（HEMT）是目前最具前景的商業化增強型方案。然而，其固有的“脆弱柵極”（低柵壓耐受）和動態性能退化（如動態Ron）問題，是制約其在高可靠性領域應用的瓶頸。未來五年的技術路線將圍繞系統性提升器件魯棒性展開。
+1. 柵極介面工程與智能整合驅動
+柵極穩健性擴展
+傳統p-GaN柵HEMT雖提供約
++1.3V的正閾值電壓
+，但其柵極電壓上限通常被限制在
+，易受過壓衝擊而失效。革新性的
+ICeGaN™
+等技術路徑通過在晶片上單片整合輔助HEMT與感測保護電路，將有效閾值電壓提升至
+約2.5V
+，並將柵極電壓窗口大幅擴展至
+靜態30V、動態耐受超過70V
+。這不僅消除了對負壓關斷電源的需求，更通過積體電路主動吸收電壓尖峰，從根本上解決了柵極脆性問題。
+動態Ron與陷阱管理
+GaN HEMT開啟後導通電阻高於靜態值的現象（動態Ron）主要源於材料介面及體內的電荷陷阱。技術路徑包括：最佳化外延生長質量、改進
+p-GaN/AlGaN介面處理工藝
+以及採用特定的
+以降低陷阱密度。在系統層面，
+單片整合驅動電路
+可實現即時的開關斜率（dv/dt, di/dt）控制與死區時間最佳化，減輕瞬態電場應力，從而抑制動態Ron的加劇。
+2. 熱管理及可靠性驗證體系
+結溫與熱設計
+遵循主流的JEDEC標準，GaN功率器件的最高結溫通常設定為
+150°C
+。由於導通電阻和跨導隨溫度升高而顯著惡化，先進的封裝技術（如高熱性能的
+TOLL/TOLT封裝
+）與PCB級散熱設計（如採用
+6層板及雙面冷卻佈局
+）至關重要，用以分散熱點的溫度積累，防止熱失控。
+標準化測試與失效機理研究
+GaN器件的可靠性評估已形成專門框架，需全面遵循
+JEP173、JEP180、JEP182
+等一系列JEDEC測試指南，進行高溫反偏（HTRB）、高溫柵偏（HTGB）、開關應力、短路耐受等嚴苛測試。特別是短路能力，傳統離散GaN HEMT的耐受時間普遍
+低於1微秒
+，而整合了智能保護功能的
+GaNSafe™等功率IC
+，可在檢測到故障後
+30納秒內實現安全關斷
+，極大提升了系統生存能力。
+（三） 電壓邊界拓展：縱向GaN結構突破與高壓終端技術
+當前商業化GaN HEMT產品主要集中於650V電壓等級，
+尚無額定電壓超過900V的GaN HEMT實現商業發佈
+。為了進軍更高壓的應用市場（如800V母線電動汽車、工業電機驅動），必須突破橫向結構的電壓限制。
+1. 從橫向到縱向的結構性變革
+橫向HEMT的侷
+基於GaN-on-Si的橫向結構雖易於實現驅動、保護電路的單片整合，但其電場沿表面分佈，在高壓下會產生嚴重的電場擁擠效應，限制了電壓的進一步提升。
+縱向GaN-on-GaN的崛起
+縱向結構利用GaN材料高達
+3.3 MV/cm的臨界擊穿電場
+，通過控制外延漂移區的厚度來直接設定擊穿電壓，理論上可實現從
+100V至4kV
+的寬範圍電壓覆蓋。實驗室已展示的縱向GaN器件（如JFET、MOSFET）表現出與矽基和SiC器件相當的
+雪崩能量承受能力
+30微秒的短路耐受時間
+，在魯棒性上取得了質的飛躍。
+2. 高壓終端保護與系統設計創新
+對於縱向器件，其電場沿垂直方向分佈，天然適合採用
+p-n結終端
+技術來最佳化邊緣電場。結合前文提及的
+CTE匹配襯底
+（如QST）以生長厚外延層，已實現器件擊穿電壓達到
+2.2kV
+，為開發1.2kV商用器件提供了充足的可靠性設計余量。
+系統級電壓拓展
+在縱向高壓GaN器件完全成熟之前，系統架構創新提供了過渡路徑。例如，採用
+三電平拓撲
+（如飛跨電容多電平變換器，FCML）可以使用現有的650V GaN器件來高效、可靠地處理800V直流母線電壓，從而在不等待器件本身電壓等級突破的情況下，率先在800V系統中發揮GaN的高頻優勢。
+（四） 系統整合：GaN功率IC與異構整合的深度演進
+整合化是GaN技術發揮其高頻、高效率潛能，並最終實現超高功率密度的必然選擇。其演進路徑從最初的晶片級協同，正向更複雜的片上系統（SoC）和異構整合方向發展。
+1. GaN功率積體電路的成熟與普及
+GaN功率IC將GaN FET、基於GaN的驅動電路、邏輯控制及保護功能（過流、短路、欠壓鎖定）整合於單一表面貼裝封裝內。這種“
+AllGaN™
+GaNFast™
+”方案創造了
+接近零阻抗的柵極驅動回路
+，基本消除了由寄生電感引起的關斷損耗和電壓過沖，使得開關頻率輕鬆邁入
+。自2015年首款低壓GaN功率IC展示以來，該技術已快速商業化，其系統級價值在於：
+省去外部柵極電阻、自舉電路等數十個分立元件，PCB面積可縮小
+提升可靠性
+整合保護功能（如
+GaNSense™
+技術的無損電流感測，響應時間快至30ns）使系統在面對故障時更為健壯。
+已廣泛應用於手機快充充電器，並正快速向資料中心（48V/12V匯流排轉換）、車載充電器（OBC）和伺服器電源等高價值領域滲透。
+2. 未來整合化方向
+從目前的半橋整合，向
+全橋甚至三相逆變器
+的單片整合晶片發展，進一步壓縮功率轉換系統的體積。
+將GaN HEMT與成熟的
+矽基CMOS
+技術通過晶圓級鍵合（如TSMC的SoIC™技術）進行異質整合。這允許在同一個封裝內，用高性能的GaN器件處理功率，而用高密度、低功耗的矽CMOS實現複雜的數字控制、通訊和保護功能，實現性能與功能性的最優組合。
+垂直器件整合
+隨著高品質、低成本GaN襯底製備技術的進步，縱向GaN功率器件有望實現規模化。未來，基於縱向GaN的功率IC可能在高電壓（&gt;1kV）、大電流應用中，與SiC功率模組展開直接競爭。
+總結與展望（2026-2030）
+綜上所述，GaN功率半導體2026-2030年的技術路線圖是一條圍繞“
+材料可控、器件可靠、電壓可擴、系統可集
+”四重目標協同推進的路徑。
+8英吋GaN-on-Si外延將在
+超晶格緩衝層
+工程化襯底
+的輔助下，實現缺陷密度控制與產能爬坡，為成本下降奠定基礎；縱向GaN-on-GaN外延技術將從研發走向中試，瞄準1.2kV及以上高壓市場。
+p-GaN柵HEMT將通過
+ICeGaN™等智能柵極技術
+深度整合的功率IC方案
+，全面解決柵極脆弱性和動態可靠性問題，滿足汽車、工業等領域的嚴苛認證要求。
+縱向GaN器件結構將成為突破650V電壓天花板、挑戰中高壓市場的主力，初期通過系統級拓撲（如三電平）與現有器件結合，後期依靠縱向器件本身實現電壓等級的躍升。
+GaN功率IC將從消費級向工業級和車規級快速迭代，並從簡單的功率開關整合向包含複雜控制功能的
+異構整合系統
+演進，最終實現功率轉換系統的極致小型化與智能化。
+在此期間，GaN與SiC將在應用市場形成明確的互補與競爭格局：在600-900V區間，尤其是在追求MHz級開關頻率、超高功率密度和極高效率的應用中（如資料中心電源、車載DC-DC、高端消費電子），GaN將憑藉其整合化優勢佔據主導；而在1.2kV及以上、側重於高結溫、高短路魯棒性及更高單管電流能力的領域（如電動汽車主驅逆變器、大功率太陽能逆變器），SiC仍將保持其結構上的優勢。兩者技術的平行發展，共同推動著整個電力電子產業向更高效、更緊湊、更智能的未來邁進。
+為充分發揮SiC與GaN等寬禁帶半導體器件的性能潛力，並應對電動汽車、資料中心等高增長應用對功率密度、效率及可靠性的極致要求，先進功率半導體封裝技術在2026-2030年間將沿著明確的技術路徑加速演進。本路線圖基於市場預測、技術平台發展與底層使能創新，系統勾勒未來五年的關鍵里程碑與性能指標。
+1. 整體市場與技術發展趨勢
+先進封裝（AP）市場結構將在2028年發生根本性轉變。根據預測，
+先進封裝營收預計在2028年首次超越傳統封裝
+，佔據市場主導地位。具體而言，2026年先進封裝營收預計達到約
+520億美元
+，佔封裝總市場的47.7%；到2029年，這一數字將增長至
+695億美元
+，佔比提升至約50.9%，2019-2029年間的復合年增長率（CAGR）約為8.9。市場價值正加速向高端技術平台集中，預計到2029年，
+高端性能封裝（如2.5D/3D）的價值佔比將從2023年的7%提升至約26%
+在技術平台層面，增長呈現顯著分化。
+2.5D/3D整合
+是增長最快的領域，其等效12英吋晶圓產量在2023-2029年間的CAGR高達
+30.5%
+嵌入式晶片（Embedded Die）
+平台則在營收增長上表現最為突出，同期CAGR預計達到
+。這些趨勢共同指向一個核心目標：通過封裝技術的系統性創新，實現系統級性能、功率密度和能效的跨越式提升。
+2. 關鍵封裝平台技術演進路徑
+2.1 2.5D/3D整合與異構整合
+2.5D/3D技術是實現超高算力與高功率密度異構整合的核心路徑，其發展將由人工智慧/機器學習（AI/ML）和高性能計算（HPC）強力驅動。
+產量與架構演進
+2.5D/3D封裝的單元出貨量在2023-2029年間保持約
+的CAGR。技術架構持續演進，矽中介層面積向
+2800 mm²
+發展，以支援更多高頻寬記憶體（HBM）堆疊（例如從8顆HBM增至12顆）。模塑中介層（Mold Interposer）配合矽橋技術預計在2025-2027年間開始上量。
+互連技術突破
+混合鍵合（Hybrid Bonding）
+是實現超高密度垂直互連的關鍵。該技術預計於
+2026年底/2027年初
+匯入HBM4E的量產，並自2024年底起逐步應用於3D NAND儲存晶片的堆疊。
+銅-銅直接鍵合
+的研發將聚焦於在
+低於400°C
+的更低溫度下實現高可靠性鍵合，以滿足更嚴苛的熱預算要求。
+2.2 扇出型封裝（Fan-Out）
+扇出型封裝因其高整合度和靈活性，正從消費電子向高端應用滲透。
+其晶圓產量在2023-2029年間的CAGR約為
+13.6%
+扇出型系統級封裝（FO SiP）
+扇出型基板（FO-on-Substrate）
+以及整合矽橋的
+高密度扇出
+演進，以滿足網路、HPC及汽車電子領域對性能與整合度的更高要求。
+2.3 嵌入式晶片與系統級封裝（SiP）
+嵌入式封裝通過將晶片埋入基板，顯著縮短互連、最佳化散熱，是高功率密度整合的理想選擇。
+高增長動力
+嵌入式晶片平台在2023-2029年間的營收與單元出貨量CAGR分別高達
+，增長動力主要來自汽車電子、5G基站等對尺寸、熱性能和可靠性有嚴苛要求的領域。
+系統級整合
+系統級封裝（SiP）穩步發展，2029年營收預計達93億美元。其趨勢是採用雙面貼裝、整合遮蔽技術，並向
+2.5D/3D SiP
+架構演進，以最佳化射頻性能和系統尺寸。
+3. 功率半導體專用封裝技術路線
+針對SiC和GaN功率器件的獨特需求，先進封裝技術路線聚焦於攻克寄生參數、熱管理和整合度三大核心挑戰。
+3.1 超低寄生電感封裝
+為實現MHz級高頻開關並抑制電壓過沖與電磁干擾（EMI），功率模組的寄生電感必須降至極低水平。
+功率回路寄生電感的目標是向
+邁進，部分先進GaN模組原型已驗證了
+0.94 nH
+的極低電感值。
+全面淘汰傳統的引線鍵合，採用
+平面互連技術
+，如銅夾扣、銅帶、柔性印刷電路（如SKiN技術）。通過
+緊湊型換流回路佈局
+磁場抵消設計
+最佳化內部電磁場。在模組內部
+整合去耦電容器
+，將其貼近功率晶片以抵消端子寄生電感的影響。
+3.2 高效熱管理與雙面冷卻
+高功率密度帶來的散熱挑戰要求熱阻的持續降低。
+在採用雙面冷卻結構時，結到殼熱阻（R_th(j-c)）的目標是達到
+&lt;0.1 °C/W
+，當前先進模組已實現
+0.14 °C/W
+雙面散熱（DSC）
+將成為中高功率模組的標準配置。更激進的技術包括
+直接液體冷卻
+微通道冷卻層
+直接製造在器件襯底或基板（如DBC）內部，使冷卻液無限貼近熱源。同時，採用
+活性金屬釺焊（AMB）氮化矽基板
+高性能熱介面材料（TIM）
+，如奈米銀燒結層，以降低各介面熱阻。
+3.3 高密度整合與智能化
+封裝正從單純的“器件保護”向“系統功能整合”演變。
+整合度提升
+利用SiC/GaN晶片面積小的優勢，在單一封裝內整合功率開關、
+柵極驅動器
+、電流/溫度
+，形成智能功率模組（IPM）或功率IC。例如，GaN功率IC將驅動、邏輯和保護功能單片整合，實現了“零阻抗”柵極回路。
+先進互連材料
+奈米銀燒結
+奈米銅燒結
+作為高導熱、高可靠性的晶片貼裝材料，將逐步替代傳統錫基焊料，滿足高溫應用需求。其中，奈米銅漿料因其更低成本和抗電遷移特性成為重要發展方向。
+4. 底層使能技術與材料創新
+底層技術的突破是上述封裝路線圖得以實現的基石。
+玻璃核心基板
+開始商用化，為超大尺寸、高I/O數封裝提供更優的平整度與高頻性能。先進有機基板的線寬/線距持續微縮。
+Chiplet（小晶片）架構
+成為主流設計理念，驅動對2.5D/3D和扇出型等先進封裝平台的需求。
+背部供電網路（BSPDN）
+等晶片級新架構開始部署，與先進封裝協同最佳化系統能效。
+可靠性驗證
+針對&gt;200°C的高溫封裝，可靠性驗證體系將更加完善。除了遵循JEDEC、AEC-Q101等標準進行高溫儲存、溫度循環、功率循環測試外，將更注重
+電-熱-力多物理場耦合
+的模擬與測試，並利用資料驅動方法進行壽命預測。
+5. 總結與展望
+2026-2030年，先進功率半導體封裝技術將沿著“
+更高密度、更低寄生、更強散熱、更智能整合
+”的軌跡快速發展。市場結構的顛覆性變化（先進封裝超越傳統）與技術價值的向上集中（高端平台佔比提升）相輔相成。對於功率應用，技術演進的核心量化目標明確：實現
+功率回路寄生電感&lt;1-3 nH
+結到殼熱阻&lt;0.1 °C/W
+，並通過異構整合將功率密度推升至新高度。
+實現該路線圖仍面臨一系列挑戰，包括混合鍵合等先進工藝的製造成本與良率、嵌入式微通道的長期可靠性、多材料介面在極端熱循環下的穩定性等。然而，在電動汽車800V平台、AI資料中心48V母線轉換等強勁需求的牽引下，產學界將持續投入，推動這些創新技術從實驗室原型走向規模化商用，最終支撐下一代電力電子系統在性能、能效與體積上的全面突破。
+(半導體先進技術與模擬)</t>
+        </is>
+      </c>
+      <c r="I30" s="1" t="n">
+        <v>46244.62459576389</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>99282990254295f23b6069f22bd9729761bc9de2ce214a4cd8fa8522ae22fb79</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>砸近8億元取得8吋晶圓廠！新唐終止與以色列大廠合資 旗下子公司完全持有TPSCo - FTNN 新聞網</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://www.ftnn.com.tw/news/533337</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>FTNN 新聞網</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Thu, 26 Mar 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>記者張書翰／綜合報導
+記憶體巨頭華邦電（2344）旗下半導體暨IC設計大廠新唐（4919）昨（25）日發布重訊，公告董事會決議通過對由子公司Nuvoton Technology Corporation Japan（NTCJ）與以色列商Tower Semiconductor（高塔半導體）合資之Tower Partners Semiconductor Co., Ltd.（TPSCo）進行策略性業務重組，並終止合資關係。
+新唐宣布旗下子公司NTCJ將取得TPSCo公司100%股權。（示意圖／截取自新唐官網影片）
+新唐表示，TPSCo營運項目包含12吋及8吋晶圓廠相關業務。目前由新唐旗下子公司NTCJ持有49%股權計49,539股，以色列商Tower則持有51%股權；當交易完成後預計累積持有TPSCo公司100%股份共101,100股。
+廣告 更多內容請繼續往下閱讀
+新唐說明，該公司與Tower計畫對TPSCo進行策略性業務重組，並結束與Tower之合資安排；新唐指出，重組後Tower將取得TPSCo之12吋晶圓廠及相關業務，TPSCo之8吋晶圓廠及相關業務將由TPSCo持續經營，並成為NTCJ之全資子公司，NTCJ將於交易完成日支付2500萬美元（約新台幣7.98億元）予Tower作為對價。該交易預計於2027年4月1日完成，惟仍須符合相關交割條件及主管機關核准。
+今日新唐開高後一路震盪，最終翻黑下跌7.8元，以93.2元作收，跌幅7.72%，成交量來到1萬7276張。
+◎《FTNN新聞網》提醒您：本資料僅供參考，投資人應獨立判斷，審慎評估並自負投資風險。</t>
+        </is>
+      </c>
+      <c r="I31" s="1" t="n">
+        <v>46244.62462010416</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>651cba9a1261da00ca71b45d4f40eb85f6e1966de0791d4e8479969fe09c67e1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>聯發科半導體、人工智慧及通訊領域論文 入選全球頂尖學術會議 - 自由財經</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://ec.ltn.com.tw/article/breakingnews/5257196</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>自由財經</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tue, 25 Nov 2025 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>台股收盤》記憶體領逾1300家同樂 指數收漲702點
+台積電7月營收4675億元 月增5.6％再飆新高
+聯發科半導體、人工智慧及通訊領域論文 入選全球頂尖學術會議
+2025/11/25 12:52
+聯發科半導體、人工智慧及通訊領域論文入選全球頂尖學術會議。（記者卓怡君攝）
+〔記者卓怡君／台北報導〕IC設計龍頭聯發科（2454）今日宣布，今年旗下多篇論文入選ISSCC、NeurIPS、CVPR、ICLR、ICML、ICC、GLOBECOM等全球半導體、人工智慧及通訊領域的頂尖國際學術會議。其中，入選有IC設計界奧林匹克之稱的ISSCC 2026論文中，有兩篇由台灣總部研發團隊發表，這也讓聯發科成為台灣業界唯一連續23年累計超過百篇論文入選的企業，展現深厚的技術實力。此外，聯發科副董事長暨執行長蔡力行也受邀於明年二月在美國舊金山舉行的ISSCC 2026，以「拓展AI新視野：半導體創新觀點」（Advancing Horizons for AI: Perspectives on Semiconductor Innovations）為題，分享如何持續透過半導體技術創新，推動AI邁向新境界。
+聯發科集團包含聯發科各前瞻技術研發單位、集團旗下專精人工智慧領域的研究單位聯發創新基地，2025年至今有20篇論文入選積體電路設計、AI、通訊領域的全球頂尖國際學術會議與期刊，另有上百篇論文由聯發科技前瞻研發中心（MediaTek Advanced Research Center；MARC）與全球頂尖學術機構共同發表或贊助發表。聯發科技集團獨立發表的論文，研究內容涵蓋提升行動處理器效能、系統能效、AI標準單元優化與DTCO整合、矽光子異質整合、記憶體設計、邊緣生成式影像處理、增進基礎模型運算效率、通訊與運算網路架構融合、FR3頻譜部署、衛星與地面網路頻譜共享、綠色通訊與運算、天線設計等後續可應用在積體電路設計精進、邊緣AI運算、資料中心、6G、ESG等領域，展現創新突破與前瞻技術之實力。
+請繼續往下閱讀...
+蔡力行也受邀於半導體IC設計領域的最高殿堂ISSCC 2026進行大會演講，將深入探討先進封裝、電力供應、散熱管理、高頻寬記憶體、高速介面及無線通訊等半導體關鍵技術，如何影響未來十年 AI 系統的發展。此外，也將說明半導體產業生態系和供應鏈如何透過效能、效率、擴展性架構，以及跨層次系統的創新合作，推動運算能力、頻寬和能源效率的快速成長，進而加速 agentic AI 和 physical AI 的普及。
+聯發科長期專注前瞻技術的研發與關鍵技術的深耕，近年研發投入已超過千億新台幣，此外，也持續透過MARC與國內外頂尖學術機構展開產學合作，並積極參與國際產業標準的制定，以進一步擴大產業影響力，鞏固在技術領域的領導地位。
+一手掌握經濟脈動
+點我訂閱自由財經Youtube頻道
+不用抽 不用搶 現在用APP看新聞 保證天天中獎
+點我下載APP
+按我看活動辦法
+今日熱門新聞</t>
+        </is>
+      </c>
+      <c r="I32" s="1" t="n">
+        <v>46244.62473276621</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>9d26820d0d4c5cdd0ffcee101e09a8a4420b68665a736989844872b104470034</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Cadence 攜手台積電擴大 AI 半導體創新，範圍涵蓋 N3、N2、A16 及 A14 先進製程 - TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://technews.tw/2026/05/12/cadence-partners-with-tsmc-to-expand-ai-semiconductor-innovation/</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" s="1" t="n">
+        <v>46244.62476368056</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2db8fa800bbc0eeb8c86f4b71d8c7b7711dc2003bcf334ace465b6abc3f9ff37</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>為何印度理工人才不願來台？ 台IC設計業者揭背後原因 - digitimes.com.tw</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://www.digitimes.com.tw/tech/dt/n/shwnws.asp?id=0000733683_OB45OBTN9ZSIJS26YI5IY</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>digitimes.com.tw</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Wed, 08 Oct 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" s="1" t="n">
+        <v>46244.62480554398</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>60b0ca63494564649596daa2b53702c6954758a16f0563a75662e3b53ad89dd4</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Dialog Semiconductor成為AST＆Science先進通訊客製IC的首選供應商 - CIO Taiwan</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://www.cio.com.tw/dialog-semiconductors-as-preferred-provider-for-asts-advanced-communications-custom-ic/</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>CIO Taiwan</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Thu, 17 Dec 2020 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Dialog Semiconductor成為AST＆Science先進通訊客製IC的首選供應商 | CIO Taiwan
+查看所有結果
+上一篇文章
+專訪光田綜合醫院總院長王乃弘
+下一篇文章
+Toppan投資 iDGate (蓋特資訊)深化其在數位ID領域的全球領先地位
+【專訪】中國信託商業銀行數位科技處處長王俊權：數據與 AI 治理體系，三層金字塔規模化
+【專訪】台達電子資訊長暨資安長曾立峰：企業架構思維，驅動全球營運
+匯豐銀行 AI 防堵金融犯罪的十年轉骨
+【編輯室札記】開源大模型讓 AI ROI 露曙光
+【專訪】萬事達卡台灣區董事總經理陳懿文：Agentic Commerce 時代 重塑金融信任架構
+直擊製造業 AI 轉型深水區！Dell Technologies、勤業眾信、BIG DATA 聯手推一站式 Agentic AI 架構，助攻企業從 PoC 邁向規模化生產
+臺安醫院重構數位韌性基石：攜手思科佈局零信任智慧醫療新階段
+邁向 Physical AI 無人載具成企業 AI、通訊韌性與資安整合新戰場
+經濟股市爆發 民眾無感如何解決？
+【金融業】金融犯罪偵測系統的十年演進 ─ HSBC 反洗錢系統的 AI 路徑
+FDE 前線部署工程師，讓 AI 真正落地的角色
+未治理 AI 將付出代價
+避免盲追流行，「主權 AI」徹底剖析
+從缺料、缺工到缺貨：企業為什麼需要 BCM 商業持續管理？
+邊 AI 邊裁員　企業正在重寫成長的規則
+供應商視野
+CIO 雜誌</t>
+        </is>
+      </c>
+      <c r="I35" s="1" t="n">
+        <v>46244.62483115741</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>41fa99a30b4653f2e09824373cea6b9080e72bc96a09d726f765675c71bfd52e</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Semiconductor sector output forecast to rise by double digits in 2025|English News - ocacnews.net</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://ocacnews.net/article/398583</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>ocacnews.net</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tue, 20 May 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" s="1" t="n">
+        <v>46244.62487055556</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>cda17a2ec00dcd3e7a2b6649f4da1e1ef6ee3d832d202576a667d6c37e60fcac</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>大摩對射頻半導體市場保持謹慎，點名持續觀察穩懋、全新、聯電狀況 - TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://finance.technews.tw/2025/12/12/morgan-stanley-remains-cautious-about-the-radio-frequency-semiconductor-market/</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Fri, 12 Dec 2025 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>外資大摩在最新研究報告中表示，儘管受惠於強勁的 iPhone 功率放大器（PA）需求與光通訊潛在機會，多家主要射頻（RF）半導體和晶圓代工廠的獲利預期獲得上修，但分析師仍維持謹慎態度。報告對台系廠商
+光電維持「落後大盤」投資評等，並對
+維持「持有」的評等。
+大摩維持穩懋的「落後大盤」投資評等，但將目標價從每股新台幣70元，大幅上調至115元。原因是考量到2025年至2027年EPS預測的變動，其中同時將穩懋在2025年和2026年的EPS預測分別調高8%和11%。另外，根據通路調查儘管2025年下半年智慧型手機需求平淡，但Apple已增加對
+的iPhone產能訂單，其中包含iPhone 17和iPhone 17 Pro的增量訂單。特別是隨著Sony停產iPhone VCSEL（垂直腔面發射雷射），預計將為穩懋帶來進一步的成長潛力。
+不過，儘管iPhone訂單增加，報告仍認為這部分利多已「大致反映在股價中」。市場對穩懋在光通訊業務的期望，特別是與Lumentum合作生產連續波雷射（CW laser）或電吸收調制雷射（EML）的期待，被認為過高且未經證實。而穩懋正在爭取CW laser和EML的認證，但目前消息來源指出，公司尚未獲得Lumentum的委外訂單或量產資格。
+而針對大摩對聯電維持「持有」投資評等，目標價從48元上調至新台幣52.5元的情況，是基於聯電受惠於iPhone供應鏈，通過聯詠和Qorvo PA供應驅動IC和3DIC封裝，預計第四季營收將優於公司財測。因此，聯電 2025年EPS預測被上調了25%。
+然而，儘管短期利多，分析師對聯電的長期前景保持謹慎。主要在於預計2026年消費電子需求（包括智慧型手機和PC）可能因供應短缺和潛在的價格上漲而走弱。加上由於消費市場疲軟，預計上升的製造成本難以轉嫁給客戶。因此，大摩下調了聯電 2026年和2027年的毛利率假設。不過，聯電在成熟製程節點具有與台積電相當的品質和專業技術，這是其長期優勢之一，因此 2026年預期EPS為3.37元，毛利率預計為28.6%。
+至於全新光電則因為市占率提升難擋市場下滑，維持「落後大盤」投資評等，目標價從65元上調至新台幣85元。但由於全新光電在Android智慧型手機市場（包括三星）持續取得市占率，因其品質優於三安，且定價低於穩懋，報告將其2025年至2027年EPS預測上調90%、36%和34%，反映其在Android市場的市占率成長。
+不過，2026年智慧型手機出貨量預計將因先進製程晶圓、記憶體和BT基板等供應短缺而承壓。此外，Skyworks與Qorvo合併後是否會將更多訂單外包給全新光電目前仍存在不確定性，目前兩者占其營收占全新光電不到1%，且預計合併後會更聚焦於iPhone生產。所以，預期2026年全新光電營收為44.03億元，毛利率預計為26.1%。
+整體來說，大摩認為2026年智慧型手機需求將持續疲軟，導致其他零組件規格下降。對於穩懋和全新而言，整體2026年智慧型手機需求仍是主要的風險。但儘管市場面臨挑戰，部分結構性增長仍值得關注。其中，隨著向Wi-Fi 7時代遷移，GaAs晶圓消耗量將增加，是因為Wi-Fi 7有三個頻段（2.4 GHz, 5 GHz, 和 6 GHz），而Wi-Fi 6只有兩個頻段。穩懋其在GaAs領域的領先地位，有望從Wi-Fi 7遷移中獲利。另外，市場一直在等待AI智慧型手機引發換機需求，但目前尚未實現，未來市場也還要進一步觀察。
+(首圖來源：
+Freepik
+文章看完覺得有幫助，何不給我們一個鼓勵
+請我們喝杯咖啡
+想請我們喝幾杯咖啡？
+每杯咖啡 65 元
+您的咖啡贊助將是讓我們持續走下去的動力
+總金額共新臺幣
+《關於請喝咖啡的 Q &amp; A》
+留給我們的話
+從這裡可透過《Google 新聞》追蹤 TechNews
+功率放大器</t>
+        </is>
+      </c>
+      <c r="I37" s="1" t="n">
+        <v>46244.62489186342</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>bef16fabb298f3831569573533c5522478a9db9044a02e0dcd049f99ad6e8ccb</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Taiwan ranked No. 1 semiconductor material buyer in 2022|English News - ocacnews.net</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://ocacnews.net/article/342674</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>ocacnews.net</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jun 2023 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" s="1" t="n">
+        <v>46244.62491994213</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>911b56f42cecaa50b9187146b6f3bfec0ac4b2893b908dad5f7a530d2f0b995e</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ITRI raises output growth forecast for Taiwan semiconductors|English News - ocacnews.net</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://ocacnews.net/article/405790</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>ocacnews.net</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Sat, 16 Aug 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" s="1" t="n">
+        <v>46244.62494292824</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>639f8ebbece786f86813e938d0ccf98ab3d08bba30540e5b1f9592b0b65641fc</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>IC Taiwan Grand Challenge 攜手國際新創InnoVEX亮相技術發表會熱鬧登場展現跨國創新能量 - tca.org.tw</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://www.tca.org.tw/news_detail.php?n=2334&amp;t=h</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>tca.org.tw</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Thu, 22 May 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>IC Taiwan Grand Challenge 攜手國際新創 InnoVEX亮相 技術發表會熱鬧登場 展現跨國創新能量
+行政院卓榮泰院長參觀IC Taiwan Grand Challenge主題館
+我國致力挖掘吸引全球的IC設計創新、晶片創新應用及系統整合人才，而由國家科學及技術委員會（國科會）自2024年主辦的IC Taiwan Grand Challenge，今（22）日在亞洲最具代表性的創新科技平台InnoVEX 舉辦技術發表會，由7 家橫跨法國、瑞典、新加坡、英國及臺灣的國際新創團隊登場，和逾百位產業界、投資人等面對面交流，氣氛熱絡，充份展現跨國創新能量。
+此次IC Taiwan Grand Challenge在 COMPUTEX / InnoVEX設有主題專館，開幕首日行政院卓榮泰院長蒞館參觀團隊攤位時，聽取團隊現場解說，留下深刻印象，更在今天舉辦技術發表活動，吸引產業界、投資人等面對面交流，7 家新創團隊分別是：
+法國 WISE-INTEGRATION｜氮化鎵電源元件技術
+瑞典 NSS Water｜奈米級純水處理方案
+新加坡 JMEM TEK｜後量子時代資安防護
+新加坡 TurboNext.ai｜大語言模型基礎架構
+英國 Genenet Technology｜AI與量子驅動器官晶片
+英國 QuinAs Technology｜量子驅動通用記憶體
+臺灣 Voltraware Semiconductor｜城市連結中距無線充電方案
+國科會表示，ICTGC競賽至今辦理共兩梯次，選出了10隊國內外新創及學研團隊獲獎，獲選新創已有2家進駐南港IC育成中心，來自美國的新創公司GalaVerse在國科會的促成下，完成與國內外大廠對接合作；在資金媒合面向，亦獲得IC設計大廠種子輪投資，反映市場對新創技術應用前景的高度肯定。
+隨著AI技術持續成長，帶動半導體躍升為驅動AI產業創新的核心引擎，為讓臺灣成為「人工智慧之島」，同時把握這波AI浪潮中的獨特優勢與市場契機，國科會指出，第三梯次IC Taiwan Grand Challenge更擴大競賽領域，納入AI核心技術與晶片，期望促成國內外人才來臺落地合作，協助建設本國的AI運算系統，並使百工百業都能應用發展。
+過去臺灣在製造上有明顯優勢，IC Taiwan Grand Challenge可補足臺灣在AI創新應用端的發展能量。這項比賽不只是比賽，包括今年的技術發表活動，也更是產業媒合對接的一環，希望最後能打造出具產業化價值的成果。第三梯次競賽徵件至6月30日止，獲選團隊將於2025臺灣創新技術博覽會展出，鼓勵國內外新創報名，共同促進產業創新轉型，驅動全球IC與AI創新應用發展。
+■《關於 COMPUTEX TAIPEI 及 InnoVEX》
+COMPUTEX TAIPEI 是台北市電腦公會施振榮理事長任內開辦及命名，1985 年邀請外貿協會共同主辦。InnoVEX 是兩會 2016 年開辦的新創展會，以科技新創公司為核心，透過多元展覽形式與媒合平台，加速 ICT 產業創新，並協助各階段新創尋找商業夥伴，期盼打造具影響力的全球新創生態圈。
+參考網址：
+IC Taiwan Grand Challenge
+（發佈時間：2025-05-22）</t>
+        </is>
+      </c>
+      <c r="I40" s="1" t="n">
+        <v>46244.62496851852</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>03ea2e084138cc326cdd2524ea646239092663a5223569afb7f4c05e0fa286c6</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TSMC's Liu expects Taiwan IC output to grow by over 24% in 2021 - ocacnews.net</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://ocacnews.net/article/294059</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>ocacnews.net</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Fri, 29 Oct 2021 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" s="1" t="n">
+        <v>46244.62499065972</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>90510c2b81ff073ff963d951442ba7ac0475f9f3eecbaafc3dbd4e9297962780</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CT Semiconductor 完成組裝、測試和封裝 (ATP) 半導體晶片的首期「種子培訓」課程 - globenewswire.com</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/news-release/2025/01/25/3015182/0/zh-hant/ct-semiconductor-%E5%AE%8C%E6%88%90%E7%B5%84%E8%A3%9D-%E6%B8%AC%E8%A9%A6%E5%92%8C%E5%B0%81%E8%A3%9D-atp-%E5%8D%8A%E5%B0%8E%E9%AB%94%E6%99%B6%E7%89%87%E7%9A%84%E9%A6%96%E6%9C%9F-%E7%A8%AE%E5%AD%90%E5%9F%B9%E8%A8%93-%E8%AA%B2%E7%A8%8B.html</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>globenewswire.com</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Sat, 25 Jan 2025 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>河內，越南, Jan. 25, 2025 (GLOBE NEWSWIRE) -- CT Group 旗下的 CT Semiconductor 正式結束了組裝、測試和封裝 (ATP) 半導體晶片的首期「種子培訓 - 培訓導師」課程。 該課程於 2025 年 1 月 13 日至 19 日在河內國家創新中心 (NIC) 舉行。
+主辦方開設該課程的宗旨是與政府合作，培養半導體產業的優秀人才。 這個項目遵循總理第 1018/QD-TTg 號決定。該決定概述了越南半導體產業從現在到 2030 年期間的發展策略，以及展望至 2050 年的願景。
+CT Semiconductor 的「種子培訓 - 培訓導師」課程
+該課程由擁有 20 多年行業經驗的外國專家設計並提供直接指導。 課程的亮點之一，是所有參與者都獲得了
+CT Semiconductor
+的全力支持，包括學費、生活費和交通費。 這顯示該公司堅定致力為越南半導體產業的可持續發展作出貢獻，同時緊貼政府的產業發展策略。
+Le Xuan Luc 博士 (越南河內國立大學 - 工程技術大學，奈米資訊科技融合工程博士) 表示：
+「我參加了『種子培訓 - 培訓導師』首期課程，覺得這門課程非常有意義。 CT Semiconductor 具有無畏的開創性視野，為培養測試、組裝和封裝 IC 晶片的高水平實踐型學生而提供支援，這是一項長期策略，在全國範圍內推動越南半導體生態系統蓬勃發展。 自越南確立科技是國家發展核心以來，這是為業界帶來重大效益的實際舉措。」
+國家創新中心 (NIC) 的代表分享說：
+「像『種子培訓 - 培訓導師』這樣的課程，是培養技術熟練的人才隊伍的第一步，以滿足國內外半導體產業的龐大需求。 CT Semiconductor 在人力資源培訓計劃方面發揮領導作用，有助實現國家設立的目標：到 2030 年，將有 50,000 名工程師和本科生為半導體行業服務。」
+CT Semiconductor 的代表補充說：
+「我們明白，人力資源是關鍵，以實現『越南成為地區性領先的半導體技術中心』的願景。 透過這項課程，CT Semiconductor 不僅滿足了我們廠房的人力需求，更可為外國半導體公司在越南投資和擴展業務而提供支援。 這是長期策略的一部分，旨在確保越南不僅是投資項目的理想地點，而且還能提供符合國際標準的優秀人才。」
+CT Semiconductor 開設課程是為越南半導體產業培養優秀人才邁出了策略性的一步。 CT Semiconductor 大力投資於教育和技術開發，致力為半導體產業打好可持續發展的基礎，與各界人士攜手合作，逐步將越南打造為地區性及全球的重要半導體技術中心。</t>
+        </is>
+      </c>
+      <c r="I42" s="1" t="n">
+        <v>46244.62556239584</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>d9516ceb392700aba05ac3588dda0bad4b7cb2b4b9dfd03d00b1e349a1f310cf</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>半導體產業趨勢的反轉（1）：從垂直整合到價值鏈的解構 - digitimes.com.tw</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://www.digitimes.com.tw/col/article/?id=15760</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>digitimes.com.tw</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Wed, 19 Feb 2025 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>在半導體產業發展迄今的70幾個年頭，有一甲子的時間整個產業的動向是解構產業價值鏈，變成單獨的價值鏈節點（value chain node）。
+在1950~70年代，最早期的半導體公司如仙童半導體（Fairchild Semiconductor；1957）、美國無線電公司（RCA Semiconductor；1960s）、通用儀器（General Instrument；1960s）、德州儀器（Texas Instrument；1951）、摩托羅拉半導體（Motorola Semiconductor；1949）等，這些公司在今日半導體產業的分類都是清一色的整合設備製造商（IDM；Integrated Device Manufacturer）。
+現在的IDM多指從晶片設計、晶片製造、晶片封測一路走到底的垂直整合公司，但是彼時的IDM更名符其實—它們連半導體製造及封測設備都可以一併自己製造，在50年代，這是主流。60年代，才逐漸轉向使用專業設備製造商的產品；70年代後，使用協力廠商製作的半導體製造設備才成為業界的主流業態。現在重要的半導體設備廠商如東京威力科創（Tokyo Electron；1963）、應用材料（Applied Materials；1967）等就是在60年代才成立的。
+更有甚者，這些半導體晶片製造廠商本身就是電子系統廠商的一部分或者子公司，其本身成立的部分目的就是進入新科技領域以及垂直整合零、元件部分進入系統。以後進入半導體製造業的日韓廠商更是如此，其母公司幾乎清一色都是電子系統的製造商。
+至於IC線路設計，當然在公司內部完成，而且因為當時的IC線路相對簡單，人工設計是常見做法（common practice）。
+只有在化學用品上，半導體公司才委外向一般的化學材料公司訂制，譬如信越化學（Shin-Etsu Silicon；1953）和勝高（Sumco；1953）等。
+所以在半導體產業發展的初期，現今所看到半導體產業價值鏈各節點譬如IC設計、製造設備、晶圓製造、封裝測試等，在早期的半導體產業的競爭樣態中主要以垂直整合的方式在價值鏈中獲取儘最多的價值節點以擴大競爭優勢，而反映出的公司型態就是IDM。
+日月光（ASE Technology Holding；1984）和矽品（SPIL；Siliconware Precision Industries；1984）出現後開始將封裝測試從垂直整合的半導體價值鏈分割出來；雖然艾克爾（Amkor Technology；1969）很早就成立以委外組裝和測試（OSAT；Outsourced Semiconductor Assembly &amp; Test）為主要業務的公司，但是到了日月光和矽品等出現之後，OSAT才為半導體產業的主流。
+台積電（TSMC；1987）的出現讓製造價值鏈節點的分割更進一步。代工不是創新，專業代工（pure-play foundry）才是。
+其實之前的IDM廠很多也都兼營代工，用以提高製造設備的稼動率（utilization rate），增加收入。如果不是這樣，也很難理解為什麼在80年代初、中期的IC設計、無晶圓廠（fabless）公司如高通（Qualcomm；1985）等如何開展他們的產品製造了。
+專業代工模式初期的優勢比較，展現於客戶信賴與生態系的打造。一直到2000年後，DRAM先因為電容微縮的困難，拱手讓出半導體產業技術驅動者（technology driver）的位置、Flash短暫的替手後，邏輯製程成最終的半導產業技術驅動者。這時候專業代工模式的技術研發規模經濟開始發揮顯著效益，與IDM的商業模式競爭，在多個半導體次領域中取得優勢。
+在半導體產業發展的一甲子中，產業發展的方向朝向解構產業高度整合的價值鏈，變成單獨存在的價值鏈節點，如電子設計自動化（EDA；Electronics Design Automation）、製造設備、材料、晶圓製造代工、委外組裝及測試等，並且在各價值鏈節點上，利用專注所造成的規模經濟取得競爭優勢。
+特別是在邏輯線路的領域中，這個專注於單一價值節點的策略逐漸取得優勢。但是這個模式並不是在所有半導體次領域中都靈光。譬如在功率元件令域中，IDM廠商還是主流，並且大多主要廠商都是從線路設計一路做到模組（module）；記憶體產品到目前也還是以IDM為主要經營型態，原因另外為文論述。
+裂解垂直整合的價值鏈成為各自獨立的價值鏈節點還能取得更高效率的運作和利潤，自有它的深層技術原因：此時的半導體發展在核心的環節如設計、製造、封測等都還留有相當的物性和電性的餘裕，各相鄰的價值節點之間可以靠共同約定的標準介面來協作，毋需太多額外的溝通，因此獨立、專注的價值節點經營可行，並且可以建立規模經濟，特別是在技術研發方面。這一點對於以後產業型態的發展持續佔有重要的影響力。</t>
+        </is>
+      </c>
+      <c r="I43" s="1" t="n">
+        <v>46244.62560547454</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>48d605b54fce7180a1174c7d39c71f52500f46950e0f62787045acf849ce26b2</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Manufacturing sector's Q2 fixed asset investments up on IC expansion|English News - ocacnews.net</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://ocacnews.net/article/408310</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>ocacnews.net</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Thu, 18 Sep 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" s="1" t="n">
+        <v>46244.62562869213</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>f0d83ebd3a8f068f24b94463dfedca4e4d5ff26f56c07a1a491ba6fce3d2fda6</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2023年半導體平均月薪5.6萬元年增幅3.1% 高薪職務出列！挑戰月薪上看10萬 - 104職場力</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://blog.104.com.tw/104data-2023-semiconductor-salary/</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>104職場力</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Tue, 05 Sep 2023 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" s="1" t="n">
+        <v>46244.6257383449</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>f84824d4d97b46a78bcb3d2aa4262369827025f0d1503af80fdd981ca4bc1c21</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>【2025最新】半導體業平均薪資前10揭曉！瑞昱年薪475萬奪冠、台積電排第9｜工作機會 - 104職場力</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://blog.104.com.tw/top-10-semiconductor-industry-salary-2024/</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>104職場力</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Wed, 04 Jun 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" s="1" t="n">
+        <v>46244.62576335648</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>cf227a2c8d065c9423155b9660e657159b2ae3801c130ba1c9d46cbf3370b37f</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>鴻海研究院研發先進晶片獲IEEE ISPSD肯定 突破AI伺服器關鍵技術 - 鴻海科技集團</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://www.foxconn.com/zh-tw/press-center/press-releases/latest-news/1769</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>鴻海科技集團</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Mon, 16 Jun 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>鴻海研究院研發先進晶片獲IEEE ISPSD肯定 突破AI伺服器關鍵技術
+2025/06/16
+3+3+3佈局
+解決高溫性能衰退問題
+諧振轉換控制器性能 突破伺服器電源控制技術限制
+【台灣台北–
+日】鴻海科技集團旗下，鴻海研究院半導體研究所最新兩項前瞻性研究成果再獲肯定，包括應用於
+伺服器的單晶片整合電路關鍵技術，以及
+伺服器所需的高效電源控制技術領域，同時獲得國際功率半導體頂級會議
+IEEE ISPSD 2025
+International Symposium on
+Power Semiconductor Devices and ICs
+》接受並且於今年六月初在日本熊本市發表！
+鴻海研究院半導體研究所郭浩中所長與蕭逸楷博士與陽明交通大學及中央大學合作，成功開發出基於半導體所自主研發的碳化矽製程，應用於
+伺服器的單晶片整合電路關鍵技術，克服傳統矽基電路在高溫（超過
+）下效能衰減限制。此外，研究團隊亦在
+伺服器所需的高效電源控制技術領域，開發出一款整合
+Burst Mode
+Soft-Start
+諧振轉換器控制器，將可有效降低輕載功耗並提升系統啟動穩定性。
+鴻海研究院在導入
+加速碳化矽技術開發，建立
+AI for Semiconductor
+的基礎後，進一步與陽明交通大學吳添立副教授、陳柏宏教授、國立中央大學杜長慶副教授展開跨校前瞻技術研究，結合鴻揚半導體碳化矽製程代工平台，成功開發出基於半導體所自主研發的碳化矽製程，可應用於極端環境的單晶片整合電路技術，以及可提升
+伺服器效能的
+控制器技術，實踐
+Semiconductor
+for AI
+圖一 鴻海研究院半導體研究所郭浩中所長（左三）與蕭逸楷組長（左五）及陽明交通大學吳添立教授（左四）研究團隊。
+鴻海研究院自主開發的碳化矽製程，運用在
+單晶片整合電路設計
+上，開發基於碳化矽元件的單晶片整合電路技術，成功克服傳統矽基電路在高溫（超過
+）下效能衰減的限制。相較於傳統電阻負載與二極體連接負載，該技術透過
+結構實現更高的線性度與更廣的輸出電壓範圍。此設計不僅與現有碳化矽元件製程相容，無需額外製程步驟，更在高溫環境中實現精準的類比訊號處理，適用於極端環境下的感測與控制系統。這個單晶片整合電路技術的研究成果，實現高線性度、高頻寬與高溫穩定的優異性能，可在
+環境下穩定運作，克服傳統矽電路高溫限制。
+吳添立教授表示：「這項技術充分利用了碳化矽的寬能隙與高熱導性優勢，為高溫環境下的類比電路設計開闢新路徑。」郭浩中所長則指出：「此成果展現了鴻海研究院在半導體技術上的深厚實力，未來將持續深化產學合作，加速技術落地。」未來，鴻海研究院將與吳教授展開更積極的合作，除上述研究成果外，近期與吳教授在第四代化合物半導體的學術成果也發表在今年的
+VLSI-TSA
+，並獲得相當廣泛的關注。
+圖二 單晶片整合電路設計結構示意圖、光罩圖以及實際電路圖。
+此外，在近期最夯的
+伺服器議題上，半導體所與陽明交通大學的陳柏宏教授研究團隊、中央大學的杜長慶教授研究團隊展開跨校合作，成功設計出整合
+控制器架構
+控制下，於輕載時可減少開關損耗，提升待機效率；於
+可平滑啟動系統，避免大電流衝擊元件。並採用
+（零電流切換）控制技術，減少
+與能量損耗，展現集團在智慧電源控制領域創新能量。
+圖三 整合
+控制器架構及能源效率比較。
+鴻海積極布局前瞻技術，致力於成為全球科技創新的領導者。鴻海研究院作為集團的技術研發核心，持續與學術及產業界合作，推動半導體技術的突破。此次的跨校合作成果，不僅彰顯鴻海在高性能半導體領域的研發實力，也為集團在電動車、智慧製造與航太應用等領域的發展奠定堅實基礎。
+鴻海精密工業股份有限公司（臺灣證券交易所代碼：
+年肇基於臺灣，以模具為根基，擴展為高科技服務企業。在電子代工服務領域（
+）市占率超過四成，排名世界第一，涵蓋消費性電子、雲端網路、電腦終端、元件及其他等四大產品領域。在全球
+個國家地區設有據點，員工總人數於季節性高峰時約九十萬人。
+年合併營收新臺幣
+兆元，名列《財富雜誌》（
+Fortune
+大企業排行榜第
+近年來，鴻海積極投入「電動車、數位健康、機器人」三大新興產業以及「人工智慧、半導體、新世代通訊技術」三項新技術領域，以「三加三」結合作為集團重要的長期發展策略，為全球標竿客戶提供完整解決方案，成為全方位智慧生活提供者。如需更多資訊，請參觀
+www.honhai.com</t>
+        </is>
+      </c>
+      <c r="I47" s="1" t="n">
+        <v>46244.6258053588</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>e097dd1868ea3b466a96ee9b8ac9699a142d2a30879e7b14e8aedad5cf8be7e8</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>「全球IC設計供應商大展」首度增闢臺北場 - iThome</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://www.ithome.com.tw/news/24694</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>iThome</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Thu, 30 Sep 2021 07:36:05 GMT</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>繼去年10月宣布擴大在亞太地區的布局之後，由全球主要IC設計業者組成的全球IC設計與委外代工協會（Fabless Semiconductor Association；簡稱FSA）又有最新決議，該協會日前宣布，今年11月11日將在臺北舉辦一場「全球IC設計供應商大展」，同時並舉行「半導體領域論壇」，會中更擬邀請聯發科技董事長蔡明介進行專題演講。
+「全球IC設計供應商大展」是FSA每年例行的大型展覽活動，在美國已經連續舉辦了7年，今年第8屆的展覽活動將於10月舉行。緊接著在11月，針對亞太地區的業者，另外增闢一場同樣類型的展覽及論壇活動，這是該協會第1次在其它區域增闢展覽場次。
+至於為何選擇在臺北舉辦，FSA亞太地區執行長王智立表示：「最主要是因為臺灣目前是僅次於美國第2大的IC設計大國，臺灣佔有全球IC設計25％的產值，而且還在逐漸成長當中，是一個非常重要的IC設計重鎮。」除此之外，也是為了服務臺灣的IC設計及半導體業者，因為每年「全球IC設計供應商大展」在美國舉辦時，業者能派去參觀這個展覽的人數有限，如果在臺北展出，則可以參與的人將會有更多。
+去年美國的「全球IC設計供應商大展」，總共吸引了917家公司參與了這個活動，參觀人數約有1800人。IC產業的中高階主管、工程師及業務行銷人員佔了絕大多數。今年臺北的首場展覽，佔地面積有150攤位，預計吸引1500名參觀者。
+FSA目前共有450個會員公司，亞太區有29家業者，亞太會員數近來成長快速，王智立表示，今年6月亞太會員將達到55個公司。臺灣業者包括聯發科、鈺創、揚智、凌陽、威盛等多家知名IC業者都是會員。
+鈺創董事長盧超群指出，在半導體業界有許多大大小小的協會，他認為大略可分成3個體系，一個是以半導體製造業者為主的半導體協會，如：美國半導體協會（SIA），另一個是是學術與業界結合的IEEE，負責業界標準的制訂等工作。另外一股勢力就是由IC設計業者組成的FSA，而FSA在業界希望能達到整合上下游供應練資源的功能。</t>
+        </is>
+      </c>
+      <c r="I48" s="1" t="n">
+        <v>46244.62583908565</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>dc74c2edc22c1b22e6eeea02d48cb561d61918edfe005fcff817a913e2828802</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2023 年全球前十大 IC 設計業者營收合計年增 12%，NVIDIA 首度奪冠 - TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://finance.technews.tw/2024/05/09/total-revenue-of-the-worlds-top-ten-ic-design-companies-in-2023/</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Thu, 09 May 2024 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" s="1" t="n">
+        <v>46244.62586155093</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>c8ccdc5fe4b9178247a1974381170690c33b6fb683d74a9ca93d1c289751896b</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>【專欄】中芯國際7奈米真抄襲台積電？被爆早用挖礦專用IC「練兵」 - 數位時代</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://www.bnext.com.tw/article/70875/smic-7nm</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>數位時代</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Thu, 28 Jul 2022 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>AI NAS 何時才值得部署？QNAP 拆解地端 AI 的成本、算力與資料門檻
+2026.08.05
+AI與大數據
+sponsored
+威聯通科技股份有限公司
+當資料不能離開企業，運算就得靠近：AI 先改寫儲存架構
+AI 帶來的第一個變化，不只是運算能力提高，而是企業必須重新決定資料放在哪裡。
+儲存架構大致分為雲端與地端兩塊，QNAP 身為資料安全的守護者，長期發展的是地端網路儲存設備（NAS），並擴展至 25GbE、100GbE 高速網路交換器產品線，提供完整的儲存與高速網路基礎架構。威聯通科技（QNAP）總經理劉文義解釋，當資料因合規要求或敏感度不能上雲，就必須留在靠近使用者與應用的地方；運算需求一旦增加，承接資料的裝置也自然被推向地端 AI。
+不能上雲的名單比想像中長。醫療業持有大量醫療個資，金融與保險業受到合規與法規限制，部分大學院校與設計公司也不希望資料被雲端存取。對這些組織而言，問題並不是雲端好不好用，而是一開始就沒有把核心資料全面上雲的選項。
+威聯通科技（QNAP）總經理暨威強電集團（IEI）董事長 劉文義
+真正讓更多企業回頭計算的，則是長期成本。劉文義指出，資料上傳雲端可能免費，下載卻會按流量收費；當企業把一年、兩年、三年的費用加總回推，可能會發現，購買一台同等容量的 NAS，還能使用 7-10 年。資料規模愈大、存取愈頻繁，總持有成本的差距就愈值得評估。
+這並不代表雲端與地端只能二選一。雲端仍適合模型訓練、程式開發與波動大的工作負載；地端則較適合高頻存取、對延遲敏感，或不能離開企業邊界的資料。企業真正要回答的，是每一類資料與任務應該放在哪裡。
+依 QNAP 觀察，客戶過去關心的是需要幾 TB、幾 PB，或備份速度有多快；現在更常問的是，機器裡的資料要如何被 AI 活用。QNAP 也從 2021 年起，把公司發展定調在 AI 與高速網路的融合，試圖讓 NAS 從資料保存的位置，進一步成為資料被調用的位置。
+當資料量持續擴大，搜尋與管理方式也會跟著改變。「在 NAS 裡放入 AI Agent 會越來越不可或缺。」劉文義舉例，當照片累積到 10 萬、20 萬張，要找出其中幾張特定畫面，已不可能只靠人工翻找。此時，能理解內容、接受自然語言指令的 AI 工具，會從加分功能逐漸變成必要條件。
+從資料治理到地端推論：AI NAS 如何進入企業工作流？
+AI NAS 不是「多了 AI 功能的 NAS」，而是 NAS 在企業工作流裡換了位置。
+依 QNAP 觀察，目前客戶大致分布在一條導入光譜上。人數最多的一群，仍在把資料集中、分類、清理與建立權限。這一步看似與 AI 無關，卻決定後續系統能不能找到正確資料、辨識版本，並把答案交給有權限的人。
+中間一群開始建置私有的檢索增強生成（RAG）知識庫。RAG 並不是重新訓練一個模型，而是在模型回答前，先從企業的 SOP、合約、法規或技術文件中取回相關內容，再產生附有來源依據的答案。QNAP 以 Qsirch 的語意搜尋能力協助建構這類應用，協助企業建立私有知識庫；而走在最前面的少數企業，則已經嘗試地端推論與 AI Agent。
+模型的選擇權，QNAP 刻意留給客戶。知識庫背後採用哪一個模型，可由企業依需求決定，不綁定單一 AI 供應商。QNAP 也以 QuAgent AI 助理與模型情境協定（MCP）相關能力，讓管理者透過自然語言查詢狀態、調整設定，並讓 NAS 成為 AI Agent 可調用的資料節點。
+不過，劉文義沒有把這條路說得太容易。他坦言，目前 NAS 硬體的 AI 運算能力仍有限。一般企業期待的應用，可能需要約 300 到 800 TOPS，甚至 1,000 TOPS，因此多數方案會以 NVIDIA 顯示卡補足算力；一張卡約需新台幣 10 萬至 12 萬元，一張算不完，就得配置 2 張或 4 張。
+「整體成本可能是過去單獨一台 NAS 的 5 倍到 10 倍，並不是大部分中小企業都能接受。」除了硬體，使用者還需要 AI 應用的 Know-how、程式背景與開發資源，這些都是落地成本。
+QNAP 則是透過算力分級讓各規模與需求的企業都可以有適合的解決方案。在 Computex 2026 搶先亮相的 QNAP AI NAS 中，一類是採用含有 iGPU 與專屬 NPU 的處理器平台，以一百多 TOPS 的範圍，可順暢使用 AI 應用程式；另一類機種則可安裝 1 張或 2 張 NVIDIA 顯示卡，處理更大的運算量。
+同時 QNAP 也在軟體端也持續開發，目標是讓 NAS 裡的資料更有效率地被 AI 工具調用，讓資料成為有價值的知識。
+從規格走到現場：能源公司如何導入私有 LLM？
+本地 AI 實際落地部署會是什麼模樣？劉文義舉了一家約 50 多人的能源公司為例。這家公司原本想用 NAS 搭配雲端 AI 建置內部資料庫，但很快遇到兩個瓶頸：一是員工查詢時明顯出現卡頓；二是專利、技術與合約都高度敏感，高層不願上傳至公有雲，擔心機密資料會有外洩的疑慮。
+後來，該公司導入 QNAP AI NAS 的旗艦機種 QAI-h1290FX，搭配顯示卡與全快閃 SSD，在地端部署私有大型語言模型，把數十年來封存的靜態檔案交給 AI 調用，進行跨檔案摘要與精準搜尋。員工因此省下翻找合約與報告的時間，核心機密也能留在企業內部。
+這個案例說明，若任務範圍明確，有些應用不必動用雲端大型模型，地端運算量就可能足以支應。
+但不同企業的資料量、查詢方式與模型大小不同，導入前仍需要概念驗證（POC）與技術人員評估。
+而且，資料留在地端並不等於自動安全。企業仍要處理帳號權限、網路隔離、備份復原、漏洞修補與日常維運。地端的價值，是讓資料邊界與控制權回到企業手上；相對地，安全責任也會更直接地回到企業。
+哪些企業現在該做，哪些再等？先看重複性與三個條件
+能不能導入地端 AI，不只由產業標籤決定，也要看工作是否重複，以及場景能不能被清楚定義。劉文義觀察，第一批走進來的，除了受法規限制的醫療、金融與保險業，也包括利用地端 AI 加速資料處理的科技業，以及會計、律師等有大量重複文書工作的專業服務業，因為效益較容易被看見。
+工廠也是可預期的場景。一條生產線可能有　10　台、20　台機器，每台處理與儲存資料的 Protocol 都不同，需要相對應的儲存裝置；生產過程累積的影像與紀錄可能要保存 3 年到 5 年。當企業要跨設備調用這些資料，AI Agent 與地端資料節點就有發揮空間。
+「重複性資料處理越多，或重複性動作越多的產業，越容易透過導入 AI 提高工作效率。」反過來說，較傳統、人力密集，或仍高度依賴人工判斷的製造業，短期內未必能快速導入地端 AI。
+依 QNAP 提供的資料，企業也可用「高頻、大量、敏感」三個條件做第一輪判斷：資料是否被頻繁調用？規模是否大到雲端傳輸與長期費用開始變得明顯？內容是否涉及個資、法規、智慧財產或商業機密？三個條件愈集中，地端部署愈值得評估；三者都不成立時，使用雲端 API 往往更簡單，也可能更划算。
+可以先等的企業，大致也有三種。第一，資料仍分散、版本混亂、權限不清，急著上 AI 只會把混亂放大，先完成集中與治理，效率就可能先提升。第二，找不到一個具體且反覆發生的業務痛點，只因為「別人都在做」而採購，設備很可能變成昂貴的展示品。第三，使用量仍小、需求偶發，現階段雲端的彈性反而更有優勢。
+因此，POC 不應只驗證「模型答不答得出來」，還要回答三個問題：資料由誰負責，誰可以存取？導入後能節省多少查找時間、傳輸成本或人工作業？正式上線後，誰負責資料、模型與資安維運？只有當效益與責任都能被量化，才適合從展示走向正式部署。
+企業願意把部分資料留在自己的機房，動力最終仍回到資料主權。QNAP 的主要市場分布在歐洲、美洲與亞太，其中歐洲占比將近一半，而歐洲也正是全球推動資料主權的最大動力。
+QNAP 的產品已取得 ISO 27001、ISO 27017 與 ISO 27018 等多項認證，並滿足 GDPR、HIPAA 等資料保護與法規遵循需求；累積至今，已售出約數百萬台裝置，協助企業打造智慧、安全的儲存方案。
+至於普及時間點，劉文義提出一個明確的價格與效能交會點：地端應用若要順暢運作，運算量可能至少要達到 300 至 600 TOPS，甚至 800 TOPS，同時價格要落在新台幣 5 萬至 8 萬元。目前符合這些條件的硬體方案仍很有限。
+「AI NAS 不是多了 AI 功能，而是改寫了資料在工作流的位置。」威聯通科技總經理劉文義坦言，地端算力成本高昂，QNAP 透過「算力分級」與開放模型架構，助企業逐步建構私有 RAG 知識庫與 AI 團隊。
+「預測約兩、三年後，應該很快會看到符合一般大眾期待、具備合理 CP 值的產品。那個時間點，就會是 AI 落地最蓬勃發展的時候。」在此之前，企業真正能先做的，不是搶著買最大的模型或最昂貴的顯示卡，而是把資料治理、使用權限與高價值場景準備好。
+QNAP 以「資料煉油廠」比喻自己的角色：原油再多，沒有整理、提煉與配送的過程，也無法成為可用的能源。這個定位也點出地端 AI 的競賽條件——不是誰先買到算力，而是誰的資料先準備好被調用。模型會持續更換，但企業自己的資料層則會長期存在。
+AI NAS 不是把模型塞進儲存設備，而是在資料必須留在企業內時，讓搜尋、推論與管理靠近資料的地端節點。
+QNAP World Tour 2026 台北場將於 2026 年 9 月 18 日（五）舉行，現場將聚焦 AI 應用、儲存備份、網通產品、資安與監控，並安排 Live Demo，適合 IT 管理者、系統整合商與企業決策者參加。
+活動地點：新板希爾頓酒店｜如意 AB 廳
+活動時間：09:20–16:00
+地址：新北市板橋區民權路 88 號 2F
+立即報名：
+2026 QNAP 台灣企業資安韌性大調查，填問券抽好禮，倒數計時：
+即時熱門文章
+全球AI伺服器幾乎都靠台廠做！鴻海、廣達、緯穎⋯19檔AI基建概念股全拆解
+告別「極速迷思」！Opensignal 國際評比揭密：什麼才是 5G 時代的好網路？
+Gemini完整教學地圖！37篇實測整理，Notebooks、Spark、提示詞架構全打包
+黃仁勳再喊下一波AI浪潮是機器人！輝達Jetson Thor台鏈名單曝光，這些可望成受惠族群
+AI已經做得到20%的題目，反而不要碰！Google首席科學家給創業者的「1%法則」
+0到18歲成長津貼來了！可領多少？2027上路規劃、最新進度一次看</t>
+        </is>
+      </c>
+      <c r="I50" s="1" t="n">
+        <v>46244.62739863426</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>b25ce6310ea574f011477b6dbe960921afda78558d82c5931236c24dac4a08f2</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2024全球前十大IC設計公司最新排名！NVIDIA市占50％稱霸、聯發科排第5 - wealth.com.tw</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://www.wealth.com.tw/articles/86af32a3-c705-48de-b242-0ebfbc657f0f</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>wealth.com.tw</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Tue, 18 Mar 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" s="1" t="n">
+        <v>46244.62742038194</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>d0455bacbf23a7968e443b7e65e45901fa7e104e12e9c57e7c10bb6e85228895</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>一顆IC、3兆產值！解析台灣半導體大軍創下的全球奇蹟 - 數位時代</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://www.bnext.com.tw/article/60280/taiwan%27s-semiconductor-industry</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>數位時代</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Tue, 01 Dec 2020 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>根據世界半導體貿易統計組織（WSTS）預估，雖受到疫情干擾，但仍樂觀預估2020年全球半導體產值約4,260億美元（約新台幣12.78兆元），增幅3.3％；相較之下，台灣因疫情控制得宜產能未受影響，工研院產科國際所（IEK）更上修今年台灣半導體產值年成長高達20.7％，並將首度突破新台幣3兆元大關，在暌違3年後，重奪全球第2大半導體產值國地位。
+過去3年，也是台灣半導體產業風起雲湧的關鍵時期：台積電創辦人張忠謀交棒退休，由雙首長接任；聯電和格羅方德先後宣布停止先進製程發展；日月光獲中國政府點頭，合併矽品；中美貿易戰開打，中芯、華為旗下海思遭美方貿易制裁……。
+美國「華為禁令」生效後，華為不僅無法與美國企業有所往來，甚至不得利用任何含有美國技術，或以美國設備製造的零組件。
+值此國際局勢和產業環境多變難料的時期，台灣半導體產值在2020年突破3兆元，意義何在？
+回顧台灣半導體業第一個兆元產值里程碑，發生在2004年，花了10年，才在2014年跨越2兆元產值大關。然而，從2兆元推進到3兆元的高峰，只花了6年，可見半導體產業衝刺速度不斷加快。甚至，已有調研機構樂觀預期，台灣半導體產值要衝破5兆元大關，只要再花10年。
+晶圓代工模式，奠定產業鏈合作分工基礎
+台灣半導體之所以成為全球舉足輕重的產業聚落，主要可以歸因於我們在三大領域做到了世界頂尖：
+晶圓代工市占合計超過60％，穩居全球第一
+封測全球市占率超過30％，同樣位居世界第一
+IC設計則以21.7％的市占率，緊追美國、位居第二
+「擁有完整的供應鏈，成就了台灣半導體產業的世界地位。」DIGITIMES Research分析師陳澤嘉指出。
+而這條半導體產業鏈如今能如此縝密分工合作，台灣大學電機系講座教授、前科技部長陳良基認為，這必須回溯到張忠謀當年為台灣半導體帶來的一個新觀點：
+晶圓代工（Foundry）模式
+「大家都是從台灣看世界，他（張忠謀）則是把世界的經驗帶回台灣。」陳良基說。
+1987年，張忠謀成立台積電，觀察到當時台灣半導體產業生產線上的作業員，有著足夠的勤奮和常識，能接受領班教導，讓產品良率相對出色，因而打造出晶圓代工模式，奠定了日後台灣半導體產業鏈分工合作模式的基礎。
+在此之前，晶圓廠都是掌握在IBM及英特爾（Intel）等晶片業者手中，張忠謀則帶領企業不斷聚焦技術研發，創造晶圓代工產業的價值。
+然而，回顧台積電的發展，其實一路危機四伏，卻都憑著正確決策，順利挺過3個策略轉折點。
+2000年，半導體業為突破瓶頸，正從鋁製程跨入銅製程，技術掌握在IBM手上。不過，台積電並未與IBM合作，而是憑自身力量研發，成功生產0.13微米製程，就此拉開與其他晶圓代工廠距離。
+2010年，
+儘管景氣正陷於金融海嘯谷底，兼任執行長的張忠謀，
+看好未來行動裝置的發展，依舊下令加碼資本支出，來到59億美元（約新台幣1,770億元），大力投資先進製程
+當時台積電正在研發28奈米製程，有個關鍵技術必須在先閘極（Gate-first）與後閘極（Gate-last）之間抉擇，差異在於後閘極製作成本高、功耗低，能滿足接下來智慧型手機的應用需求。當時，三星（Samsung）和格羅方德（GlobalFoundries）都選擇先閘極，台積電則是選擇了後閘極。
+事後證明，台積電不僅成功量產，拉開與對手三星的技術差距，也奠基28奈米持續改版優勢。日後更靠著16奈米技術，搶走三星手中的蘋果訂單。28奈米一役，連張忠謀都認為為台積電開啟了新里程。
+台積電創辦人張忠謀帶來晶圓代工（Foundry）模式，奠定台灣半導體供應鏈分工發展基礎。
+「我很看重當時台積電研發出的28奈米製程，那是台灣晶圓代工技術的里程碑。」力晶創辦人黃崇仁激動地說。
+第三個拐點發生在
+2018年，正當英特爾卡關10奈米製程、遭遇良率問題，台積電以FinFET（鰭式場效電晶體）技術，率先量產7奈米
+，甚至在隔年導入EUV（極紫外光）技術讓N7＋製程正式量產，也是全球首個採用EUV技術並量產的企業。
+自此，台積電和英特爾地位互換，從追趕者成為領頭羊，甚至英特爾執行長史旺（Bob Swan）曾在今年7月指出，考慮將自家晶片製造委外，也意味過去20年半導體晶圓製造的競爭，將邁入新局。
+聚落效應發揮效率優勢，帶動IC設計起飛
+在晶圓代工之外，台灣的IC設計和封裝測試產業，也在過去20年產業專業分工下陸續茁壯。2020年合計產值超過1.4兆元，是晶圓代工之外，第二大半導體族群。
+根據工研院產科所預測，2020年IC設計的年產值將達到284億美元（約新台幣8,529億元）、年成長23.1％，是美國以外的第二大產值國；而IC封測則是84億美元（約新台幣5,520億元）、年成長約10.2％，穩居世界第一。
+「台灣晶圓代工和封測產業完整，對IC設計業最大的好處是溝通效率。」高速傳輸晶片業祥碩總經理林哲偉表示，若下單給格羅方德，光是技術溝通往返，恐怕就比同在台灣的台積電要複雜得多。
+2020年第2季統計，全球前10大晶圓廠中，有4家是台灣業者（台積電、聯電、世界先進、力積電）；全球前10大封測廠，有6家在台灣（日月光、矽品、力成、京元電、南茂、頎邦）；產業鏈完整優勢，也孵化出許多優異的IC設計業者，全球前10大IC設計公司中，台灣也入榜3家（聯發科、聯詠、瑞昱）。
+2020第二季全球前10大IC設計公司營收排名
+5G、AI、物聯網，構成強勁「矽需求」
+儘管半導體業一片榮景，2020年半導體產值貢獻台灣GDP（國民生產毛額）超過15％，也引來質疑聲浪：台灣經濟是否過分依賴單一產業？
+如果還在問我們是否要繼續依賴半導體來發展台灣的經濟，這真是個Stupid（愚蠢）的問題。
+」鈺創董事長盧超群直言，「最簡單的觀念就是：半導體應用面向非常廣，機會還很多。」
+5G、AI（人工智慧）等技術將改變未來世界樣貌，張忠謀也曾公開表示，物聯網（IoT）是下一個「big thing」，而這些技術背後的引擎都得靠半導體技術去實現，「半導體是原力，是啟動未來應用的技術關鍵。」陳良基說。
+研究機構集邦科技（TrendForce）指出，2020年全年智慧型手機生產總數12.43億支，其中5G手機將達到2.35億支、滲透率18.9％。聯電總經理簡山傑曾解釋，當手機從4G更換為5G，矽零件的需求量將提高2.5倍，是整個半導體產業的重大動能來源，而這還不包括5G基地台的布建。
+2020年5G手機將達2.35億支，矽零件的需求量也將從4G時代提高2.5倍，是半導體產業的重大動能來源。
+再從物聯網應用來看，市場調研機構Strategy Analytics預估，2030年全球聯網裝置將上看500億個，若再導入AI，讓每個物聯網裝置都具備運算能力，晶片需求將爆發性成長。
+不過，樂觀期許台灣半導體體產業再創輝煌之際，對於產業內外趨勢和環境，也必須審慎以對。
+首先是針對台灣產業的平衡發展。國際半導體產業協會（SEMI）全球行銷長暨台灣區總裁曹世綸指出，半導體如同台灣的「航空母艦」，已擁有航向世界的能力。接下來的挑戰是，
+我們是否準備好站在巨人的肩膀上，打造其他艦隊應戰？
+對此，陳良基舉例，PC產業雖然現在都移往中國生產，但是系統設備的製造能力依舊是台灣的專業。
+進入AI時代，台灣應該將重心轉向終端裝置的應用場景，立基於半導體技術優勢，仰賴IC設計能力，再配合PC產業的製造設計能力，共同發展出新的使用情境。
+另一個隱憂是，
+當半導體遲早面臨摩爾定律（Moore's law）的失效，屆時該如何應對？
+陳良基則認為，台積電製程發展到1奈米都不是問題，而
+目前業界解決摩爾定律的方式，都指向「異質整合」這條路，未來仍充滿機會
+至於仍未停歇的全球科技貿易戰，是否會成為台灣半導體發展的絆腳石？
+無論是陳良基、曹世綸乃至於產業大老，都一致認為，「矽」絕對是台灣最天然的屏障，只要持續維持技術領先、讓全球沒有台灣不行，台灣就仍能找到生存之道。
+讓矽島繼續榮耀，升級關鍵時刻來了
+「未來10年，台灣半導體的前景我還是相當看好的。」在兩岸都有投資發展半導體經驗的黃崇仁認為，台灣不只在技術製造和產業鏈生態上具有優勢，製造成本更具全球競爭力，「比中國便宜20％左右。」再加上台灣工程師性格細膩，有耐性突破製程瓶頸，這群默默耕耘的工程師過去功不可沒，未來也會再創佳績。
+台灣，僅占全球土地面積0.02％的蕞爾小島，憑著穩扎穩打的技術基礎和完整產業鏈，在全球半導體總產值強占19.7％。面對全球保護主義興起，各國發動科技貿易戰此起彼落，台灣這支半導體艦隊，將持續扮演全球科技不可或缺的存在。
+數位時代319期12月號《解析台灣半導體奇蹟！》封面故事
+責任編輯：林美欣</t>
+        </is>
+      </c>
+      <c r="I52" s="1" t="n">
+        <v>46244.62791032407</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>bd90c875dbc886701ec5a8dc8346cae00c3fed44eb24a6be853fd0628c329163</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AI 晶片引領半導體市場至 2030 年 - CIO Taiwan</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://www.cio.com.tw/ai-chips-lead-semiconductor-market-to-2030/</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>CIO Taiwan</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Tue, 03 Sep 2024 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>AI 晶片引領半導體市場至 2030 年 | CIO Taiwan
+查看所有結果
+◤SEMI 產業研究資深總監曾瑞榆指出，半導體市場有望於 2025 年呈現強勁復甦，2030 年 AI 半導體市場年複合成長率更將高達 24%。
+上一篇文章
+迎接 AI 三大挑戰  吳田玉：半導體要跨界合作
+下一篇文章
+英特爾落敗 大家可以學到什麼教訓？
+【專訪】中國信託商業銀行數位科技處處長王俊權：數據與 AI 治理體系，三層金字塔規模化
+【專訪】台達電子資訊長暨資安長曾立峰：企業架構思維，驅動全球營運
+匯豐銀行 AI 防堵金融犯罪的十年轉骨
+【編輯室札記】開源大模型讓 AI ROI 露曙光
+【專訪】萬事達卡台灣區董事總經理陳懿文：Agentic Commerce 時代 重塑金融信任架構
+直擊製造業 AI 轉型深水區！Dell Technologies、勤業眾信、BIG DATA 聯手推一站式 Agentic AI 架構，助攻企業從 PoC 邁向規模化生產
+臺安醫院重構數位韌性基石：攜手思科佈局零信任智慧醫療新階段
+邁向 Physical AI 無人載具成企業 AI、通訊韌性與資安整合新戰場
+經濟股市爆發 民眾無感如何解決？
+【金融業】金融犯罪偵測系統的十年演進 ─ HSBC 反洗錢系統的 AI 路徑
+FDE 前線部署工程師，讓 AI 真正落地的角色
+避免盲追流行，「主權 AI」徹底剖析
+未治理 AI 將付出代價
+從缺料、缺工到缺貨：企業為什麼需要 BCM 商業持續管理？
+邊 AI 邊裁員　企業正在重寫成長的規則
+供應商視野
+CIO 雜誌</t>
+        </is>
+      </c>
+      <c r="I53" s="1" t="n">
+        <v>46244.62846341435</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>e98a8767e4786e466eaaa5c9834f0f21606d38acb980d5eecfc2f80b6a3b8e68</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Navitas 與輝達開發的電源晶片有進展、股價飛天 - TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://finance.technews.tw/2025/10/15/navitas-nvidia-power-chip-development-progress-shares-soaring/</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Wed, 15 Oct 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>第三代半導體氮化鎵（GaN）功率 IC 領導大廠納微半導體（Navitas Semiconductor）宣布，與輝達（Nvidia）合作開發的 AI 基礎建設電源晶片取得進展，股價聞訊飆高。
+Barron’s報導，Navitas執行長Chris Allexandre 13日稍晚透過
+聲明稿表示
+，隨著輝達推動AI基礎設施轉型，該公司將藉由先進的氮化鎵（GaN）和碳化矽（SiC）電源解決方案，提供次世代資料中心所需的效率、可擴展性和可靠性。
+Navitas表示，最新裝置可讓輝達順利獲得次世代AI系統需要的800伏特電力，這項設計可直接為IT機櫃供電，無需額外的轉換器。
+根據Navitas說法，其為AI資料中心設計的先進800V高壓直流輸電（HVDC）架構，不但能提升效率及可擴展性，還可減少銅的用量。
+Navitas 14日聞訊飆漲26.08%、收12.57美元，創2022年1月11日以來收盤新高。
+Navitas 2025年5月就曾宣布獲得輝達訂單，帶動5月22日當天股價暴衝164.4%。
+MoneyDJ新聞
+授權轉載；首圖來源：shutterstock）
+延伸閱讀：
+納微打入 NVIDIA 供應鏈！高壓直流架構有望成 AI 資料中心趨勢
+文章看完覺得有幫助，何不給我們一個鼓勵
+請我們喝杯咖啡
+想請我們喝幾杯咖啡？
+每杯咖啡 65 元
+您的咖啡贊助將是讓我們持續走下去的動力
+總金額共新臺幣
+《關於請喝咖啡的 Q &amp; A》
+留給我們的話
+從這裡可透過《Google 新聞》追蹤 TechNews
+Navitas
+功率半導體</t>
+        </is>
+      </c>
+      <c r="I54" s="1" t="n">
+        <v>46245.69298417716</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/result.xlsx
+++ b/output/result.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U54"/>
+  <dimension ref="A1:U57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="I2" s="1" t="n">
-        <v>46244.62251445602</v>
+        <v>46247.58065633102</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>b3b4ad83b48702ce2ea2055f535e5d4b8ca5a70c50ef915e3c62756f15346df4</t>
+          <t>c892500cb00e9052a353b06c891bd622ea32067b72b66139cc189e69c86dfbd3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -626,92 +626,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>台灣IC設計產業：年營收破千億美元，蟄伏於供應鏈背後的全球王者 - 報新聞</t>
+          <t>半導體通膨趨勢成形，晶圓代工、IC 設計紛漲價 - TechNews 科技新報</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.contentplatform.info/articles/492757/taiwan-ic-design-industry-mediatek-realtek-novatek-ai-semiconductor/</t>
+          <t>https://finance.technews.tw/2026/05/01/semiconductor-inflation-trend-takes-shape-wafer-foundries-ic-design-price-hikes/</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>報新聞</t>
+          <t>TechNews 科技新報</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fri, 07 Aug 2026 17:23:43 GMT</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" s="1" t="n">
-        <v>46244.62257930556</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>c892500cb00e9052a353b06c891bd622ea32067b72b66139cc189e69c86dfbd3</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>IC semiconductor</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>半導體通膨趨勢成形，晶圓代工、IC 設計紛漲價 - TechNews 科技新報</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>https://finance.technews.tw/2026/05/01/semiconductor-inflation-trend-takes-shape-wafer-foundries-ic-design-price-hikes/</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>TechNews 科技新報</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
           <t>Fri, 01 May 2026 07:00:00 GMT</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>半導體通膨趨勢成形，因應成本高漲，包括晶圓代工及 IC 設計廠紛紛調漲價格，對於智慧手機等消費產品市場影響逐步顯現，智慧手機等今年出貨量恐面臨衰退壓力。
 半導體廠法人說明會陸續登場，成本壓力及產品價格策略成為法人關注的焦點。晶圓代工廠除將持續投入技術開發及擴充產能，中東緊張局勢也造成能源和物流等成本升高。
@@ -728,73 +661,73 @@
 繼記憶體價格飆漲後，晶圓代工和IC設計紛紛調漲價格，半導體通膨趨勢成形，使得智慧手機等消費產品市場，面臨成本升高的壓力進一步加劇。廠商除將資源集中於高階產品因應，需求也開始趨緩，聯發科預估，今年手機出貨量恐減少15%。漲價對市場需求的影響，未來是否進一步擴大，備受市場關注。</t>
         </is>
       </c>
-      <c r="I4" s="1" t="n">
-        <v>46244.62260273148</v>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="I3" s="1" t="n">
+        <v>46247.5806821875</v>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>Success</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>52c0d8de13d4498189dccc5889700320f4014f73509059f038d1c03499bc3134</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>IC semiconductor</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>NYCU and Purdue Launch Global Semiconductor Academy to Advance AI and Chip Talent Development - cna.com.tw</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>https://www.cna.com.tw/postwrite/eng/432806</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>cna.com.tw</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Thu, 07 May 2026 07:00:00 GMT</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Matsu’s “Blue Tears” Inspire NYCU Breakthrough in Next-Generation Luminescent Materials
 NYCU Partners with Kneron to Advance Edge AI Education and Real-World Deployment
@@ -822,8 +755,75 @@
 For more NYCU News, please visit the official NYCU website.</t>
         </is>
       </c>
+      <c r="I4" s="1" t="n">
+        <v>46247.58070892361</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>e43442dbc99bbd193fe79fe4ecba19bca7aec88192fb1e1a7218b1c867e007e6</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026 全球半導體展望報告：半導體與未來 - pwc.tw</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://www.pwc.tw/zh/publications/topic-report/semiconductor-and-beyond.html</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>pwc.tw</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tue, 27 Jan 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" s="1" t="n">
-        <v>46244.62263523148</v>
+        <v>46247.58073318287</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>e43442dbc99bbd193fe79fe4ecba19bca7aec88192fb1e1a7218b1c867e007e6</t>
+          <t>e4ac11cb4fcbfe85b0cee5b80deaf1b76ee2e40c21af99a317cd4a3a94cab310</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -870,92 +870,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026 全球半導體展望報告：半導體與未來 - pwc.tw</t>
+          <t>ICTGC競賽首登矽谷 進軍CES廣邀全球IC新創鏈結臺灣半導體生態鏈 - tca.org.tw</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.pwc.tw/zh/publications/topic-report/semiconductor-and-beyond.html</t>
+          <t>https://www.tca.org.tw/news_detail.php?n=2454&amp;t=h</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>pwc.tw</t>
+          <t>tca.org.tw</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 08:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" s="1" t="n">
-        <v>46244.62265920139</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>e4ac11cb4fcbfe85b0cee5b80deaf1b76ee2e40c21af99a317cd4a3a94cab310</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>IC semiconductor</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>ICTGC競賽首登矽谷 進軍CES廣邀全球IC新創鏈結臺灣半導體生態鏈 - tca.org.tw</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>https://www.tca.org.tw/news_detail.php?n=2454&amp;t=h</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>tca.org.tw</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
           <t>Fri, 02 Jan 2026 08:00:00 GMT</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>ICTGC競賽首登矽谷 進軍CES廣邀全球IC新創鏈結臺灣半導體生態鏈
 IC Taiwan Grand Challenge團隊於CES 2025展中之TTA國家館介紹競賽
@@ -984,73 +917,73 @@
 （發佈時間：2026-01-02）</t>
         </is>
       </c>
-      <c r="I7" s="1" t="n">
-        <v>46244.62278165509</v>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="I6" s="1" t="n">
+        <v>46247.58130280093</v>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>Success</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>858c62d825b27cd022cdc524a608aa9f87e352944400bbdf64555e4511a193c6</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>bcbcba2cd14a784917bf945b45c5eed6b5fd8877bb9dd71edbed7fafc4a03ae7</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>IC semiconductor</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>瑞昱半導體網通音訊IC領先 全球電子產品仰賴台灣實力 - 財經新聞 - PChome Online 新聞 - news.pchome.com.tw</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>瑞昱半導體網通音訊IC領先 全球電子產品仰賴台灣實力 - 財經新聞 - PChome Online 新聞 - PChome Online 新聞</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>https://news.pchome.com.tw/finance/sunmedia/20260330/index-77484256473773329003.html</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>news.pchome.com.tw</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>PChome Online 新聞</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 07:00:00 GMT</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>圖／本報資料庫
 ｜何映辰／台北報導
@@ -1065,8 +998,75 @@
 更多財經新聞 »</t>
         </is>
       </c>
+      <c r="I7" s="1" t="n">
+        <v>46247.58132935185</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>c26182506dccbffae3fbede2667f6b57b42e2b670d91e4b15a978b817696108b</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>美股焦點：ON Semiconductor(ON.US) | 23:32:11(GMT+8) - 台視全球資訊網</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://www.ttv.com.tw/finance/view/042026232332134174FF5E00432693B2142340DE48AAE792/587</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>台視全球資訊網</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fri, 24 Apr 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" s="1" t="n">
-        <v>46244.62280597222</v>
+        <v>46247.58135866898</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5e2150db004a7711293be698d35503f37f1430da74b1cbad0d35736d127bb684</t>
+          <t>c2c888cdc2d8914d55b2a9bb7e967671464e5d36db98adfd86fd9fe4d8cf4879</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>中國 IC 設計市佔已超車台灣！IDC 揭 2026 半導體十大趨勢：地緣政治如何重塑供應鏈？ - techorange.com</t>
+          <t>中國 IC 設計市佔已超車台灣！IDC 揭 2026 半導體十大趨勢：地緣政治如何重塑供應鏈？ - TechOrange 科技報橘</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>techorange.com</t>
+          <t>TechOrange 科技報橘</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="I9" s="1" t="n">
-        <v>46244.62283685185</v>
+        <v>46247.58138517361</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>c26182506dccbffae3fbede2667f6b57b42e2b670d91e4b15a978b817696108b</t>
+          <t>d84f3008927ac1e015d458406f982fc2df80fd7611be901e03542bf5b115c48e</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1207,92 +1207,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>美股焦點：ON Semiconductor(ON.US) | 23:32:11(GMT+8) - 台視全球資訊網</t>
+          <t>【即時新聞】這「1檔」半導體轉強，NVTS最新漲2.94%還能追嗎？ - CMoney投資網誌</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.ttv.com.tw/finance/view/042026232332134174FF5E00432693B2142340DE48AAE792/587</t>
+          <t>https://cmnews.com.tw/article/newsyoudeservetoknow-d463d065-3823-11f1-bf7c-8951ef46c39f</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>台視全球資訊網</t>
+          <t>CMoney投資網誌</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 07:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" s="1" t="n">
-        <v>46244.62286261574</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>5d1d6ef625a4bb9cd01eae5a76b6b531620f326d595b56bfffa47b317874bc2f</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>IC semiconductor</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>【即時新聞】這「1檔」半導體轉強，NVTS最新漲2.94%還能追嗎？ - CMoney投資網誌</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://cmnews.com.tw/article/newsyoudeservetoknow-d463d065-3823-11f1-bf7c-8951ef46c39f</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>CMoney投資網誌</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
           <t>Wed, 15 Apr 2026 07:00:00 GMT</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>【即時新聞】這「1檔」半導體轉強，NVTS最新漲2.94%還能追嗎？ | CMoney投資網誌
 【即時新聞】這「1檔」半導體轉強，NVTS最新漲2.94%還能追嗎？
@@ -1304,25 +1237,226 @@
 Top50美股新聞
 美股新聞快訊
 本文內容轉載
-【即時新聞】台達電(2308)直衝漲停！大戶搶卡位，這「4檔概念股」接棒上攻？
-【即時新聞】川湖(2059)EPS狂飆74元！資金排擠，這「2檔概念股」現分歧？
-兩個APP年代結束了！在美股K線上同時掌握台美股損益
+【即時新聞】星光美國住宅基金Starlight(SURF.UN:CA)公布最新Q2財報，物業營收大幅衰退41%！
+【即時新聞】Grupo Supervielle(SUPV)精簡人力奏效帶動獲利大爆發，不良貸款率低於同業！
+【即時新聞】Stereotaxis(STXS)導管營收狂飆近300%！新品供不應求拚明年獲利
+【台股盤後】大盤熄火震盪，資金先抬中小
 【股市爆料同學會專屬】－開戶領 30 天籌碼 K 線 VIP
+為什麼這檔配息12%的基金，全台灣只有7個人買？
 【每日簽到領獎】最高送 500 元超商禮券 + LINE Points
-【台股盤後】台積撐場等非農，加權多空搶月線
-【籌碼K線 1月登入禮】籌碼集中股(4)
-anhour ago
-非農爆冷點燃全球股市：從總經事件看台股AI供應鏈三雄
-國巨只是第一棒？MLCC搶貨、長約全來了，被動元件整排點火！
-4hours ago
-川湖連兩天攻漲停衝破1.2萬，GB300、ASIC還能推多高？
-5hours ago
+AI股修正資金急轉彎！大戶悄悄卡位不配息新興市場基金
+20minutes ago
+降息預期升溫！這檔不配息亞洲債券為何三年賺22%？
+21minutes ago
+通膨降溫引爆科技股！這檔不配息基金為何受青睞？
+37minutes ago
 要永久刪除文章嗎
 「」將被永久刪除，且這項操作無法復原。</t>
         </is>
       </c>
+      <c r="I10" s="1" t="n">
+        <v>46247.58141247685</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0863a493e946f0f3acee7ec785bce697a12dc30d667980b2ddf17abdadd19426</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026 AI on Chips：半導體前瞻趨勢論壇 - DIGITIMES</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://www.digitimes.com.tw/seminar/TechForum_20260820/</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>DIGITIMES</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 17:38:12 GMT</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>掌握次世代 AI 晶片戰略全貌​
+領航 2027 半導體關鍵契機
+站在 AI 指數化進步的轉折點：
+半導體生存法則​
+隨著人工智慧巨浪持續席捲全球，半導體產業正迎來前所未有的技術變革與版圖重塑。本屆「AI on Chips：半導體前瞻趨勢論壇」匯聚 DIGITIMES
+資深記者、分析師團隊、產業意見領袖及頂尖企業專家，將從供應鏈、製造、伺服器晶片、網路通訊到封裝測試，全方位解構 AI 晶片的最新動態與未來布局。
+09:00~09:30
+Section A
+Industry Overview
+09:30~10:00
+串連知識斷點：人工智慧時代的產業變革與資訊彙整框架
+DIGITIMES暨IC之音 董事長
+10:00~10:30
+材料創新成就AI未來
+應用材料 副總裁暨台灣區總裁
+10:30~10:45
+Section B
+AI Semiconductor
+10:45~11:15
+人工智慧運算架構與演進趨勢
+梁伯嵩博士
+聯發科技 資深處長
+11:15~11:45
+AI浪潮下的半導體產業轉變與商機
+DIGITIMES 副總監
+11:45~13:30
+Section C
+Server &amp; Agent AI Chip
+13:30~13:55
+2027年高階雲端AI加速器趨勢前瞻
+DIGITIMES 分析師
+13:55~14:20
+從雲端到邊緣AI，台系晶片設計產業動態解析
+14:20~14:45
+人形機器人浪潮襲來，多元算力處理器發展方興未艾​
+14:45~15:00
+Section D
+Networking Chip
+15:00~15:25
+打造Scale全棧式方案，伺服器連網晶片業者競爭升級
+15:25~15:50
+矽光子晶片業者的競合策略
+15:50~16:15
+CPO時代來臨，AI高速互連中長期技術演進與挑戰
+Section E
+AI Chip Supply Chain
+AI伺服器電源需求再升級，全球功率半導體齊攻HVDC 800V供應鏈
+記憶體漲勢不停，大廠策略解析
+AI趨勢下，扇出型面板級封裝技術的機會與挑戰
+Section F
+Panel
+15:00~15:40
+AI浪潮驅動全球半導體供應鏈重組：從晶圓代工、先進封裝到記憶體的新競局與新秩序
+主持人｜陳玉娟
+DIGITIMES 半導體首席記者
+與談人｜韓青秀
+與談人｜林俊吉
+DIGITIMES 資深分析師
+15:40~16:20
+美中休戰期，華為韜定律，星馬拼崛起，關鍵零件在台灣
+主持人｜何致中
+DIGITIMES 新聞中心主編
+與談人｜劉憲杰
+DIGITIMES 王牌記者
+與談人｜王嘉瑜
+與談人｜舒能翊
+【AI 晶片與網絡基礎】場
+2,000
+2,500 NTD
+(Section A、B、C、D)
+【半導體製造與產業地緣】場
+2,500
+(Section A、B、E、F)
+One Day Pass
+2,400
+3,000
+(Section A、B、C、D、E、F)
+報名報到即可領取
+Tech Forum Welcome Kit
+（限額200份）
+《天選·矽島》乙本
+7-11咖啡提貨券 乙張
+元大金融廣場 國際會議廳
+在資訊過載、訊號混雜的時代，多數人看見的是熱鬧，卻未必看懂方向。Tech Forum 的存在，正是為了把「雜訊」還原為「判斷」。
+由 DIGITIMES 明星分析師、王牌記者與科技領袖共同組成，Tech Forum
+不只是論壇，更是一座連接產業現場與決策核心的觀測站。從供應鏈脈動到大廠策略，從新品背後的技術邏輯到產業結構的轉變，我們以長期累積的資料與第一線洞察，拆解關鍵訊號，還原產業運行的真實軌跡。
+結合趨勢解析與交流討論，Tech Forum 協助與會者超越「看展」與資訊接收，建立對下一步科技發展的整體理解，將全球趨勢轉化為可思考、可行動的產業洞察。
+在這裡，資訊不是終點，而是決策的起點。
+Tech Forum，讓每一次理解，更接近未來。
+AI on Air
+COMPUTEX 前瞻趨勢論壇​
+AI 應用零距離
+CES 2026 科技洞察研討會
+Techtonic Shift
+展望2026年科技趨勢
+半導體產業
+2025 前瞻趨勢論壇
+COMPUTEX 2025 前瞻預測
+AI熱點深度解析
+直擊 CES 2025
+解析AI應用新風向
+GenAI X Geopolitics
+AI 加劇大國博弈 重啟供應鏈新變局
+活動參加辦法
+本活動僅提供「線上報名」方式，需完成報名及付款程序 。
+主辦單位保留最終審核權，並得依論壇主題及參與者屬性進行篩選。
+報名截止日為 2026 年 8月 17 日。主辦單位得視報名狀況調整截止時間。
+報名與資格審核
+本活動採事前線上報名制，所有報名資料將由主辦單位進行審核。
+通過審核者，將於活動前寄發「報到通知（含報到編號／QR Code）」至電子信箱，作為出席憑證。
+未通過審核者，亦將另行通知。如未收到任何通知，請至活動網站查詢報名狀態。
+請勿以不實或他人資料報名，以免觸法。
+線上信用卡付款：完成報名後，請依系統指示完成線上刷卡程序。
+若已報名者無法出席，可更換參加人員，並請事先通知主辦單位。
+取消與退費
+如需取消報名，請於活動前 3 天 以電話或 Email 通知，始得辦理退費。
+活動當日恕不接受取消或退費。
+未事先取消且未出席者，恕不退費。
+會員資格將視同使用一次權益。
+本活動採用電子發票：
+公司戶：提供電子發票 PDF
+個人：提供電子發票證明聯、手機載具或捐贈碼
+電子發票將於活動結束後 5–7 個工作日 寄送至報名信箱。如有特殊需求，請於活動前聯繫主辦單位。
+論壇講義（PDF）將於2026.08.20 19:00p.m. 寄送至您的報名信箱。
+惟因智慧財產權限制，部分講師內容恕不提供下載。
+「Section F : Panel」環節無提供講義。
+不可抗力因素
+如遇天災或不可抗力因素（如地震、颱風等），活動將延期舉辦，並另行公告。
+主辦單位保留調整活動內容、議程及講者之權利，恕不另行通知。
+DIGITIMES
+隱私權聲明</t>
+        </is>
+      </c>
       <c r="I11" s="1" t="n">
-        <v>46244.62335300926</v>
+        <v>46247.58143565973</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1389,7 +1523,7 @@
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" s="1" t="n">
-        <v>46244.62337538195</v>
+        <v>46247.58145766204</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1467,7 +1601,7 @@
         </is>
       </c>
       <c r="I13" s="1" t="n">
-        <v>46244.62340170139</v>
+        <v>46247.58148665509</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1562,7 +1696,7 @@
         </is>
       </c>
       <c r="I14" s="1" t="n">
-        <v>46244.62342738426</v>
+        <v>46247.58195819445</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1599,7 +1733,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>f19113e887dfbe08f3df29ee989d20774e0fa8193d0ee01d97cd2a0e74d647aa</t>
+          <t>06a59d3c3e353971851cc490c3a6838f45325e139ee3fd4dc77727eb2924eaf7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1609,7 +1743,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>通寶成Arm唯一注資台灣IC設計 鎖定無人機與機器人 - 科技新聞 - PChome Online 新聞 - news.pchome.com.tw</t>
+          <t>通寶成Arm唯一注資台灣IC設計 鎖定無人機與機器人 - 科技新聞 - PChome Online 新聞 - PChome Online 新聞</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1619,7 +1753,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>news.pchome.com.tw</t>
+          <t>PChome Online 新聞</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1652,7 +1786,7 @@
         </is>
       </c>
       <c r="I15" s="1" t="n">
-        <v>46244.6234515625</v>
+        <v>46247.58198270833</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1689,35 +1823,120 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>784c1b2acbfd3c05e8b785afa12e3ff56d4ffc5ba3ac6e855ca008c36246fbb0</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>30 人團隊搶下全球半壁江山，君曜科技如何成為橋接 IC 王者？ - TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://finance.technews.tw/2025/11/08/leading-bridging-chip-supplier-zeitec-semiconductor/</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sat, 08 Nov 2025 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>君曜科技靠自行研發的手機螢幕橋接晶片，成為橋接晶片供應商龍頭。證明以靈活的小團隊、貼近市場的策略，在競爭激烈的驅動 IC 市場，也可以找到一片天。
+一家員工不過30人、年營收從未達到10億元的IC設計公司，為何能在強敵環伺、價格殺到見骨的驅動IC戰場上穩健存活？答案是，洞察市場供需缺口，找出獨門生意。
+即將在年底上櫃的君曜科技，營收規模相較於聯詠、奇景等大廠，幾乎可用「微不足道」來形容，但它靠著自行研發的手機螢幕用橋接晶片，每年穩健獲利，如今在全球售後維修市場市占率已達五成，穩居橋接晶片供應商王座。
+根據法人推估，全球每年出貨約13億支智慧手機中，其中多達四億支會送進維修站。如果問題是螢幕故障，原本的OLED螢幕，可能會被成本較低的LCD螢幕取代，但置換上的LCD面板，因為廠牌、規格差異，常會出現螢幕訊號不相容或「黑邊」問題，此時就需要一顆專門轉換訊號的橋接晶片，讓螢幕功能維持正常。
+解決手機換螢幕黑邊問題
+招牌商品成維修必備元件
+這項維修必備的元件，正是由君曜率業界之先開發的招牌產品。
+2010年創立君曜之前，君曜科技董事長林澤琦曾任職台灣IC設計龍頭
+的電視晶片部門，但在大企業穩定晉升並非他的夢想，「我從小就想創業，不想每天坐辦公室」，32歲那年，他與朋友湊出1,000萬元創業，主攻因智慧手機和平板電腦興起而需求大增的觸控IC。
+▲ 君曜董事長林澤琦指出，研發團隊人雖少，但能快速決策和調整規格，適應市場多變需求，具有大型IC公司難以模仿的效率。
+剛成立不久，君曜推出的觸控IC就成功打入中國白牌平板市場與韓國SK集團等客戶，單月出貨突破百萬顆。這樣的成績立刻引起全球電子製造服務霸主
+注意，在2015年投資3,000萬元成為股東，並在多項產品中採用君曜晶片。
+然而，白牌平板市場2015年以後急速萎縮，再加上競爭者湧入、價格戰激烈，君曜因此力圖轉型，與鴻海合作開發高階觸控IC，計劃用於鴻海操刀的Nokia與InFocus智慧手機，但隨著相關產品開發進度停滯，也讓想藉著進入供應鏈翻身的君曜營運陷入困難。
+為求生存，林澤琦努力發掘新商機。2016年他注意到手機維修業者的零件來源，正從原本的「拆舊料」轉為「換新料」，因此嘗試與售後方案設計公司合作，提供觸控IC，勉強做到損益兩平。
+但林澤琦沒有輕易放棄，進一步調查後發現，手機維修還需橋接晶片因應新舊螢幕規格差異，利潤又高於觸控IC。且當時橋接晶片採取的開發技術難度高、價格又貴，幾乎沒有競爭者。但他有微控制器（MCU）設計經驗，自信可設計出成本可控的客製化晶片（ASIC）取而代之。</t>
+        </is>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>46247.58201081018</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>91843debf041fc741aba79dec6df216f652db20173c389f6278cae3a27ce0f85</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>IC semiconductor</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>通寶半導體獲 Arm 投資、完成 B 輪募資，規劃 Q426 申請上市 - TechNews 科技新報</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>https://finance.technews.tw/2026/03/03/qbit-semiconductor/</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>TechNews 科技新報</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Tue, 03 Mar 2026 08:00:00 GMT</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>台灣 IC 設計產業再添資本市場動態。通寶半導體（QBit Semiconductor）宣布完成 B 輪募資，並獲得 Arm Limited 參與投資，成為目前國內少數獲得 Arm 投資的 IC 設計業者之一。該公司同時規劃於 2026 年第四季向台灣證券交易所申請上市。
 據該公司說明，Arm 此次投資著眼於雙方在影像處理、控制與安全技術上的合作潛力，應用範圍涵蓋列印與影像相關市場。Arm 全球執行副總裁暨商務長 Will Abbey 指出，相關合作有助於擴展從高效能系統到成本導向裝置的技術應用，強化不同產品線的解決方案布局。
@@ -1739,93 +1958,8 @@
 從這裡可透過《Google 新聞》追蹤 TechNews</t>
         </is>
       </c>
-      <c r="I16" s="1" t="n">
-        <v>46244.62356418982</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>784c1b2acbfd3c05e8b785afa12e3ff56d4ffc5ba3ac6e855ca008c36246fbb0</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>IC semiconductor</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>30 人團隊搶下全球半壁江山，君曜科技如何成為橋接 IC 王者？ - TechNews 科技新報</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>https://finance.technews.tw/2025/11/08/leading-bridging-chip-supplier-zeitec-semiconductor/</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>TechNews 科技新報</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Sat, 08 Nov 2025 08:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>君曜科技靠自行研發的手機螢幕橋接晶片，成為橋接晶片供應商龍頭。證明以靈活的小團隊、貼近市場的策略，在競爭激烈的驅動 IC 市場，也可以找到一片天。
-一家員工不過30人、年營收從未達到10億元的IC設計公司，為何能在強敵環伺、價格殺到見骨的驅動IC戰場上穩健存活？答案是，洞察市場供需缺口，找出獨門生意。
-即將在年底上櫃的君曜科技，營收規模相較於聯詠、奇景等大廠，幾乎可用「微不足道」來形容，但它靠著自行研發的手機螢幕用橋接晶片，每年穩健獲利，如今在全球售後維修市場市占率已達五成，穩居橋接晶片供應商王座。
-根據法人推估，全球每年出貨約13億支智慧手機中，其中多達四億支會送進維修站。如果問題是螢幕故障，原本的OLED螢幕，可能會被成本較低的LCD螢幕取代，但置換上的LCD面板，因為廠牌、規格差異，常會出現螢幕訊號不相容或「黑邊」問題，此時就需要一顆專門轉換訊號的橋接晶片，讓螢幕功能維持正常。
-解決手機換螢幕黑邊問題
-招牌商品成維修必備元件
-這項維修必備的元件，正是由君曜率業界之先開發的招牌產品。
-2010年創立君曜之前，君曜科技董事長林澤琦曾任職台灣IC設計龍頭
-的電視晶片部門，但在大企業穩定晉升並非他的夢想，「我從小就想創業，不想每天坐辦公室」，32歲那年，他與朋友湊出1,000萬元創業，主攻因智慧手機和平板電腦興起而需求大增的觸控IC。
-▲ 君曜董事長林澤琦指出，研發團隊人雖少，但能快速決策和調整規格，適應市場多變需求，具有大型IC公司難以模仿的效率。
-剛成立不久，君曜推出的觸控IC就成功打入中國白牌平板市場與韓國SK集團等客戶，單月出貨突破百萬顆。這樣的成績立刻引起全球電子製造服務霸主
-注意，在2015年投資3,000萬元成為股東，並在多項產品中採用君曜晶片。
-然而，白牌平板市場2015年以後急速萎縮，再加上競爭者湧入、價格戰激烈，君曜因此力圖轉型，與鴻海合作開發高階觸控IC，計劃用於鴻海操刀的Nokia與InFocus智慧手機，但隨著相關產品開發進度停滯，也讓想藉著進入供應鏈翻身的君曜營運陷入困難。
-為求生存，林澤琦努力發掘新商機。2016年他注意到手機維修業者的零件來源，正從原本的「拆舊料」轉為「換新料」，因此嘗試與售後方案設計公司合作，提供觸控IC，勉強做到損益兩平。
-但林澤琦沒有輕易放棄，進一步調查後發現，手機維修還需橋接晶片因應新舊螢幕規格差異，利潤又高於觸控IC。且當時橋接晶片採取的開發技術難度高、價格又貴，幾乎沒有競爭者。但他有微控制器（MCU）設計經驗，自信可設計出成本可控的客製化晶片（ASIC）取而代之。</t>
-        </is>
-      </c>
       <c r="I17" s="1" t="n">
-        <v>46244.62358853009</v>
+        <v>46247.5820363426</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1917,7 +2051,7 @@
         </is>
       </c>
       <c r="I18" s="1" t="n">
-        <v>46244.62361392361</v>
+        <v>46247.5820612963</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1954,7 +2088,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>c5cd36811da64e7927563ac2608067d5e2031c9fded56cb75be6b7935f2fa6b3</t>
+          <t>fc89988ac380bea990e6415a7c7ed13a54ad8b53e884d7e640d64c325ff1f9f3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1964,218 +2098,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>中國急起直追，台灣2029年將失晶圓代工寶座？IDC揭半導體新變局 - 數位時代</t>
+          <t>台灣第一家！通寶半導體獲ARM 投資打造AI生態圈擬於2026年Q4申請上市 - 三立新聞</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://www.bnext.com.tw/article/85426/idc-2025-semiconductor-predict</t>
+          <t>https://inews.setn.com/news/1801759</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>數位時代</t>
+          <t>三立新聞</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fri, 12 Dec 2025 08:00:00 GMT</t>
+          <t>Tue, 03 Mar 2026 08:00:00 GMT</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
-        <is>
-          <t>AI NAS 何時才值得部署？QNAP 拆解地端 AI 的成本、算力與資料門檻
-2026.08.05
-AI與大數據
-sponsored
-威聯通科技股份有限公司
-當資料不能離開企業，運算就得靠近：AI 先改寫儲存架構
-AI 帶來的第一個變化，不只是運算能力提高，而是企業必須重新決定資料放在哪裡。
-儲存架構大致分為雲端與地端兩塊，QNAP 身為資料安全的守護者，長期發展的是地端網路儲存設備（NAS），並擴展至 25GbE、100GbE 高速網路交換器產品線，提供完整的儲存與高速網路基礎架構。威聯通科技（QNAP）總經理劉文義解釋，當資料因合規要求或敏感度不能上雲，就必須留在靠近使用者與應用的地方；運算需求一旦增加，承接資料的裝置也自然被推向地端 AI。
-不能上雲的名單比想像中長。醫療業持有大量醫療個資，金融與保險業受到合規與法規限制，部分大學院校與設計公司也不希望資料被雲端存取。對這些組織而言，問題並不是雲端好不好用，而是一開始就沒有把核心資料全面上雲的選項。
-威聯通科技（QNAP）總經理暨威強電集團（IEI）董事長 劉文義
-真正讓更多企業回頭計算的，則是長期成本。劉文義指出，資料上傳雲端可能免費，下載卻會按流量收費；當企業把一年、兩年、三年的費用加總回推，可能會發現，購買一台同等容量的 NAS，還能使用 7-10 年。資料規模愈大、存取愈頻繁，總持有成本的差距就愈值得評估。
-這並不代表雲端與地端只能二選一。雲端仍適合模型訓練、程式開發與波動大的工作負載；地端則較適合高頻存取、對延遲敏感，或不能離開企業邊界的資料。企業真正要回答的，是每一類資料與任務應該放在哪裡。
-依 QNAP 觀察，客戶過去關心的是需要幾 TB、幾 PB，或備份速度有多快；現在更常問的是，機器裡的資料要如何被 AI 活用。QNAP 也從 2021 年起，把公司發展定調在 AI 與高速網路的融合，試圖讓 NAS 從資料保存的位置，進一步成為資料被調用的位置。
-當資料量持續擴大，搜尋與管理方式也會跟著改變。「在 NAS 裡放入 AI Agent 會越來越不可或缺。」劉文義舉例，當照片累積到 10 萬、20 萬張，要找出其中幾張特定畫面，已不可能只靠人工翻找。此時，能理解內容、接受自然語言指令的 AI 工具，會從加分功能逐漸變成必要條件。
-從資料治理到地端推論：AI NAS 如何進入企業工作流？
-AI NAS 不是「多了 AI 功能的 NAS」，而是 NAS 在企業工作流裡換了位置。
-依 QNAP 觀察，目前客戶大致分布在一條導入光譜上。人數最多的一群，仍在把資料集中、分類、清理與建立權限。這一步看似與 AI 無關，卻決定後續系統能不能找到正確資料、辨識版本，並把答案交給有權限的人。
-中間一群開始建置私有的檢索增強生成（RAG）知識庫。RAG 並不是重新訓練一個模型，而是在模型回答前，先從企業的 SOP、合約、法規或技術文件中取回相關內容，再產生附有來源依據的答案。QNAP 以 Qsirch 的語意搜尋能力協助建構這類應用，協助企業建立私有知識庫；而走在最前面的少數企業，則已經嘗試地端推論與 AI Agent。
-模型的選擇權，QNAP 刻意留給客戶。知識庫背後採用哪一個模型，可由企業依需求決定，不綁定單一 AI 供應商。QNAP 也以 QuAgent AI 助理與模型情境協定（MCP）相關能力，讓管理者透過自然語言查詢狀態、調整設定，並讓 NAS 成為 AI Agent 可調用的資料節點。
-不過，劉文義沒有把這條路說得太容易。他坦言，目前 NAS 硬體的 AI 運算能力仍有限。一般企業期待的應用，可能需要約 300 到 800 TOPS，甚至 1,000 TOPS，因此多數方案會以 NVIDIA 顯示卡補足算力；一張卡約需新台幣 10 萬至 12 萬元，一張算不完，就得配置 2 張或 4 張。
-「整體成本可能是過去單獨一台 NAS 的 5 倍到 10 倍，並不是大部分中小企業都能接受。」除了硬體，使用者還需要 AI 應用的 Know-how、程式背景與開發資源，這些都是落地成本。
-QNAP 則是透過算力分級讓各規模與需求的企業都可以有適合的解決方案。在 Computex 2026 搶先亮相的 QNAP AI NAS 中，一類是採用含有 iGPU 與專屬 NPU 的處理器平台，以一百多 TOPS 的範圍，可順暢使用 AI 應用程式；另一類機種則可安裝 1 張或 2 張 NVIDIA 顯示卡，處理更大的運算量。
-同時 QNAP 也在軟體端也持續開發，目標是讓 NAS 裡的資料更有效率地被 AI 工具調用，讓資料成為有價值的知識。
-從規格走到現場：能源公司如何導入私有 LLM？
-本地 AI 實際落地部署會是什麼模樣？劉文義舉了一家約 50 多人的能源公司為例。這家公司原本想用 NAS 搭配雲端 AI 建置內部資料庫，但很快遇到兩個瓶頸：一是員工查詢時明顯出現卡頓；二是專利、技術與合約都高度敏感，高層不願上傳至公有雲，擔心機密資料會有外洩的疑慮。
-後來，該公司導入 QNAP AI NAS 的旗艦機種 QAI-h1290FX，搭配顯示卡與全快閃 SSD，在地端部署私有大型語言模型，把數十年來封存的靜態檔案交給 AI 調用，進行跨檔案摘要與精準搜尋。員工因此省下翻找合約與報告的時間，核心機密也能留在企業內部。
-這個案例說明，若任務範圍明確，有些應用不必動用雲端大型模型，地端運算量就可能足以支應。
-但不同企業的資料量、查詢方式與模型大小不同，導入前仍需要概念驗證（POC）與技術人員評估。
-而且，資料留在地端並不等於自動安全。企業仍要處理帳號權限、網路隔離、備份復原、漏洞修補與日常維運。地端的價值，是讓資料邊界與控制權回到企業手上；相對地，安全責任也會更直接地回到企業。
-哪些企業現在該做，哪些再等？先看重複性與三個條件
-能不能導入地端 AI，不只由產業標籤決定，也要看工作是否重複，以及場景能不能被清楚定義。劉文義觀察，第一批走進來的，除了受法規限制的醫療、金融與保險業，也包括利用地端 AI 加速資料處理的科技業，以及會計、律師等有大量重複文書工作的專業服務業，因為效益較容易被看見。
-工廠也是可預期的場景。一條生產線可能有　10　台、20　台機器，每台處理與儲存資料的 Protocol 都不同，需要相對應的儲存裝置；生產過程累積的影像與紀錄可能要保存 3 年到 5 年。當企業要跨設備調用這些資料，AI Agent 與地端資料節點就有發揮空間。
-「重複性資料處理越多，或重複性動作越多的產業，越容易透過導入 AI 提高工作效率。」反過來說，較傳統、人力密集，或仍高度依賴人工判斷的製造業，短期內未必能快速導入地端 AI。
-依 QNAP 提供的資料，企業也可用「高頻、大量、敏感」三個條件做第一輪判斷：資料是否被頻繁調用？規模是否大到雲端傳輸與長期費用開始變得明顯？內容是否涉及個資、法規、智慧財產或商業機密？三個條件愈集中，地端部署愈值得評估；三者都不成立時，使用雲端 API 往往更簡單，也可能更划算。
-可以先等的企業，大致也有三種。第一，資料仍分散、版本混亂、權限不清，急著上 AI 只會把混亂放大，先完成集中與治理，效率就可能先提升。第二，找不到一個具體且反覆發生的業務痛點，只因為「別人都在做」而採購，設備很可能變成昂貴的展示品。第三，使用量仍小、需求偶發，現階段雲端的彈性反而更有優勢。
-因此，POC 不應只驗證「模型答不答得出來」，還要回答三個問題：資料由誰負責，誰可以存取？導入後能節省多少查找時間、傳輸成本或人工作業？正式上線後，誰負責資料、模型與資安維運？只有當效益與責任都能被量化，才適合從展示走向正式部署。
-企業願意把部分資料留在自己的機房，動力最終仍回到資料主權。QNAP 的主要市場分布在歐洲、美洲與亞太，其中歐洲占比將近一半，而歐洲也正是全球推動資料主權的最大動力。
-QNAP 的產品已取得 ISO 27001、ISO 27017 與 ISO 27018 等多項認證，並滿足 GDPR、HIPAA 等資料保護與法規遵循需求；累積至今，已售出約數百萬台裝置，協助企業打造智慧、安全的儲存方案。
-至於普及時間點，劉文義提出一個明確的價格與效能交會點：地端應用若要順暢運作，運算量可能至少要達到 300 至 600 TOPS，甚至 800 TOPS，同時價格要落在新台幣 5 萬至 8 萬元。目前符合這些條件的硬體方案仍很有限。
-「AI NAS 不是多了 AI 功能，而是改寫了資料在工作流的位置。」威聯通科技總經理劉文義坦言，地端算力成本高昂，QNAP 透過「算力分級」與開放模型架構，助企業逐步建構私有 RAG 知識庫與 AI 團隊。
-「預測約兩、三年後，應該很快會看到符合一般大眾期待、具備合理 CP 值的產品。那個時間點，就會是 AI 落地最蓬勃發展的時候。」在此之前，企業真正能先做的，不是搶著買最大的模型或最昂貴的顯示卡，而是把資料治理、使用權限與高價值場景準備好。
-QNAP 以「資料煉油廠」比喻自己的角色：原油再多，沒有整理、提煉與配送的過程，也無法成為可用的能源。這個定位也點出地端 AI 的競賽條件——不是誰先買到算力，而是誰的資料先準備好被調用。模型會持續更換，但企業自己的資料層則會長期存在。
-AI NAS 不是把模型塞進儲存設備，而是在資料必須留在企業內時，讓搜尋、推論與管理靠近資料的地端節點。
-QNAP World Tour 2026 台北場將於 2026 年 9 月 18 日（五）舉行，現場將聚焦 AI 應用、儲存備份、網通產品、資安與監控，並安排 Live Demo，適合 IT 管理者、系統整合商與企業決策者參加。
-活動地點：新板希爾頓酒店｜如意 AB 廳
-活動時間：09:20–16:00
-地址：新北市板橋區民權路 88 號 2F
-立即報名：
-2026 QNAP 台灣企業資安韌性大調查，填問券抽好禮，倒數計時：
-即時熱門文章
-全球AI伺服器幾乎都靠台廠做！鴻海、廣達、緯穎⋯19檔AI基建概念股全拆解
-告別「極速迷思」！Opensignal 國際評比揭密：什麼才是 5G 時代的好網路？
-Gemini完整教學地圖！37篇實測整理，Notebooks、Spark、提示詞架構全打包
-黃仁勳再喊下一波AI浪潮是機器人！輝達Jetson Thor台鏈名單曝光，這些可望成受惠族群
-AI已經做得到20%的題目，反而不要碰！Google首席科學家給創業者的「1%法則」
-0到18歲成長津貼來了！可領多少？2027上路規劃、最新進度一次看</t>
-        </is>
-      </c>
-      <c r="I19" s="1" t="n">
-        <v>46244.6237478125</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>219376d9cb16ba8c93224bc86bce6e724c8062ef7fc9283f00ac3448736c22ba</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>IC semiconductor</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Nordic Semiconductor推出nRF54LV10A —— 一款突破性的低電壓藍牙低功耗系統單晶片，專為新一代醫療保健穿戴式設備設計_COMPOTECH ASIA - COMPOTECH Asia</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>https://www.compotechasia.com/a/new_product/2025/1209/62429.html</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>COMPOTECH Asia</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Tue, 09 Dec 2025 08:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" s="1" t="n">
-        <v>46244.62377064815</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>fc89988ac380bea990e6415a7c7ed13a54ad8b53e884d7e640d64c325ff1f9f3</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>IC semiconductor</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>台灣第一家！通寶半導體獲ARM 投資打造AI生態圈擬於2026年Q4申請上市 - 三立新聞</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>https://inews.setn.com/news/1801759</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>三立新聞</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Tue, 03 Mar 2026 08:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
         <is>
           <t>2026/03/03 14:56
 財經中心／綜合報導
@@ -2188,73 +2129,173 @@
 通寶SoC平台已獲國際一線印表機品牌採用，除多功能事務機（MFP）市場外，亦廣泛用於醫療印表機、相片印表機、掃描器、條碼印表機及工業印表機。未來，通寶半導體亦計畫將 SoC 開發拓展至互動式多媒體自動服務機（Kiosk）、機器人及無人機等新興應用領域。隨著募資完成與營運規模擴大，公司將依計畫於2026年第四季推進上市申請，邁向資本市場新里程碑。</t>
         </is>
       </c>
-      <c r="I21" s="1" t="n">
-        <v>46244.62379607639</v>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="I19" s="1" t="n">
+        <v>46247.58235446759</v>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>Success</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>a40adbc2c2b8875e017498c2b2e7e8a6a209d0b29298f9429681cdb2c86348cf</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>cebb3306715646c45de89d999c967a0b769f21ee1ca0ad9a81104e5263adaeab</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>IC semiconductor</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>MOSFET 是什麼？功率半導體崛起？為何近期熱度提升？安世事件帶來哪些利多？ - StockFeel 股感</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>中國急起直追，台灣2029年將失晶圓代工寶座？IDC揭半導體新變局 - 數位時代</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://www.bnext.com.tw/article/85426/idc-2025-semiconductor-predict</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>數位時代</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Fri, 12 Dec 2025 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>研究機構IDC（國際數據資訊公司）預估，2026年全球半導體市場規模將達8,900億美元，年成長率11%，在AI基礎建設投資支撐下，維持雙位數成長，並持續朝1兆美元大關前進。整體產業動能仍由AI伺服器、資料中心與先進製程驅動，但在地緣政治、產業政策與供應鏈重組交錯影響下，半導體版圖也正快速重組。
+對台灣而言，這一波趨勢「喜憂參半」。一方面，先進製程、CoWoS與封測仍站在全球供應鏈最前緣，直接受惠於AI晶片需求爆發，產業動能明確。另一方面，中國在成熟製程與IC設計領域的快速追趕，已實質改變區域競爭結構，甚至連台灣的晶圓代工霸主地位，都被IDC點名在2029年出現翻盤風險。
+IDC：台灣先進製程、先進封裝與封測持續領先
+在AI運算需求持續擴張之下，台灣半導體最具結構性優勢的戰場，仍然集中在先進製程、先進封裝與高階封測。從製程節點演進、CoWoS產能規模到封測市占結構，IDC的預測顯示，台灣在高階製造供應鏈的核心地位，短期內仍難以被取代，並將持續承接全球AI晶片擴產的主要動能。
+先進製程市場｜持續快速成長，2026年台積電市占73%
+隨著AI晶片算力需求呈指數型成長，市場對電晶體密度與能效的要求同步拉高，進一步推升3奈米與2奈米製程的採用率。4奈米以下先進製程將是2026年晶圓代工市場成長的核心引擎，預計帶動晶圓代工整體產值年增20%。
+主要晶圓代工廠正加速布局下一代技術節點，預期台積電市占率將攀升至73%，並擴充產能以因應強勁需求。至於三星與英特爾，則在歷經投資調整期後，轉為採取更精準的投資策略，未來將把資源集中於2奈米產能布局，以及1.4奈米製程的研發。
+CoWoS產能｜2025年成長113%，2026年再增72%
+IDC指出，2024年到2025年CoWoS產能年增113%，2025年到2026年將會再成長72%，但仍供不應求。2026年CoWoS需求結構中，輝達佔比高達57%，博通20%，AMD8%，Marvell與世芯各4%，聯發科約2%，世界約1%。
+台積電持續全力擴產，預計2026年全年CoWoS產能擴增至110萬片，但面對輝達、AMD與博通等大廠的龐大需求，市場仍存在供需缺口，溢出的訂單將成為各家封裝業者競逐的焦點。
+日月光、矽品憑藉FOCoS（（Fan-out Chip on Substrate））技術，預計開始承接外溢訂單；Amkor（艾克爾科技）則以韓國廠接單，並深耕美國亞利桑那州新廠；至於英特爾的EMIB技術，也有機會在良率穩定後，於雲端服務業者自研晶片市場取得更多比重。
+委外封測市場｜直到2029年台灣依然居首，市占42%
+在封測領域，IDC預估2026年全球OSAT市場成長率為10.9%。2025到2029年，台灣與美國OSAT市場年複合成長率皆為9.1%，中國約8.6%，其他地區約6.2%。以2029年市占來看，台灣以42%居首，其次是中國33%，美國16%，韓國約3%，其他地區合計6%。
+在「半導體自主化」政策推動下，中國晶圓代工成熟製程產能快速提升，下游OSAT（將晶片的封裝與測試外包）產業也隨之擴張，逐步形成完整的製造產業鏈。
+至於台灣與美國OSAT大廠，如日月光、矽品、京元電與Amkor，則在AI晶片需求帶動下，逐漸掌握輝達、AMD等高階晶片的外溢訂單，預計2025到2029年台美OSAT產值年複合成長率將達9%。
+成熟製程回溫，中國在設計與產能端急起直追
+相較於先進製程仍由台灣主導，真正出現結構性變化的領域，已開始轉向成熟製程、IC設計與整體產能版圖。
+在中美科技競逐與出口管制持續收緊的背景下，中國加速將產業資源導向受限制較小的成熟製程與本土IC設計，形成另一條快速放量的成長路徑，也直接改變亞太區半導體競爭結構。
+目前台灣在IC設計市占已落居中國之後，IDC進一步預測，至2029年，中國晶圓代工產能占比有機會超過台灣。
+成熟製程市場｜12吋與8吋產能利用率回溫，升至8成以上
+成熟製程歷經兩年調整後已走出谷底。2025年下半年受惠於關稅避險與供應鏈預防性備貨，產能利用率明顯回穩。展望2026年，受惠於AI資料中心對矽光子、矽鍺（SiGe）等高速傳輸晶片，以及高效能電源管理IC（PMIC）的強勁需求，預計平均產能利用率將穩定維持在80%以上。
+其中，12吋成熟製程平均產能利用率自2024年第一季約75%，一路回升到2025年第四季84%，2026年最高約85%，全年維持在83%左右的高檔。8吋成熟製程則從2024年第一季約66%，在2025年第三季回到81%，2026年可穩定維持在81%到82%區間。
+IC設計市場｜臺灣退居全球第三，中國2026年市占45%
+IDC預測，亞太區IC設計市場2026年將成長11%，但區內結構已出現明顯變化。中國在國家政策與本土市場需求帶動下，IC設計產值已於2025年正式超越臺灣，2026年市占率將進一步擴大到45%，台灣則調整至40%。
+消長主因在於中國近年在本土AI晶片與高階手機處理器上的技術突破，加上大量新創公司切入邊緣運算與物聯網晶片市場，帶動整體營收呈現倍數成長。
+IDC也直指，台灣排名下滑的關鍵，在於「缺乏自主研發的AI晶片」，目前除了聯發科之外，多數IC設計業者仍缺乏來自AI晶片的營收貢獻；即使將世芯、創意等IC設計服務業者一併納入計算，整體市占規模仍難以追上中國。
+晶圓代工市場｜2029年中國超越台灣登頂，產能占37%
+在美國出口管制限制先進製程設備的情況下，中國轉而集中資源擴充受限制較小的成熟製程，並扶植本土設備與材料供應鏈，確保電動車、工控與物聯網等關鍵晶片的自主供應。美國則透過台積電亞利桑那廠等新建案強化在地製造能力，Fab21P2A預計於2027年量產3奈米。日本除台積電熊本廠外，也加碼支持Rapidus在2027年挑戰2奈米量產。
+IDC預測，2029年中國將握有全球37%的晶圓代工產能，台灣為35%，美國占8%，日本與歐洲各約3%，並將在2028年超越臺灣，成為全球最大晶圓代工產地。從2025到2029年的產能複合成長率來看，中國約9.8%，日本10.0%，美國8.4%，臺灣則約2.8%。
+整體來看，AI需求仍是驅動半導體產業成長的最核心動能。IDC也觀察到，隨著雲端業者加速導入自研晶片，AI伺服器加速器正快速朝ASIC傾斜，帶動整體算力基礎建設的投資結構出現變化；另一方面，從晶圓代工、非記憶體IDM、封測到光罩的「Foundry 2.0」生態系，也正同步擴產成形。</t>
+        </is>
+      </c>
+      <c r="I20" s="1" t="n">
+        <v>46247.58238840278</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2cb4efa6ba789db37bc3eae445adb19fba8a09218fc569246d6288280316a8e9</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>MOSFET 是什麼？功率半導體崛起？為何近期熱度提升？安世事件帶來哪些利多？ - stockfeel.com.tw</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>https://www.stockfeel.com.tw/mosfet-%E6%87%89%E7%94%A8-%E6%A6%82%E5%BF%B5%E8%82%A1/</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>StockFeel 股感</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>stockfeel.com.tw</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>Wed, 27 May 2026 07:00:00 GMT</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>MOSFET 的全稱為，「金屬氧化物半導體場效電晶體」（Metal-Oxide-Semiconductor Field-Effect Transistor ，以下簡稱 MOSFET），是現代電子工業中應用最為廣泛的基礎元件之一。無論是在複雜的積體電路（IC）設計中，還是在終端的電路板（PCB）應用上，重要性不可替代。特別是在大功率半導體，MOSFET 可以精準的控制電源電子，可以直觀的理解成電子電路中的「精密開關」。但為何近期 Mosfet 的熱度如此之高呢？
 MOSFET 是什麼？
@@ -2433,8 +2474,82 @@
 270666</t>
         </is>
       </c>
+      <c r="I21" s="1" t="n">
+        <v>46247.58241835648</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>9f5b70d46fc79e391d0e4ff25f7a3115cf981a49dae222a377ae133cce6cffca</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>【獨家專訪】SAPIEN Semiconductors：從大型Micro LED 顯示器到近眼顯示裝置的全方位解決方案 - LEDinside</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://www.ledinside.com.tw/interview/20251017-40226.html</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>LEDinside</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Fri, 17 Oct 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>SAPIEN Semiconductors致力於與全球 Micro LED 顯示器產業的關鍵客戶緊密合作，提供創新的解決方案。此外，該公司在2024年成功於韓國KOSDAQ掛牌上市，創下79.9億韓元的營收佳績，年成長率高達149%。SAPIEN Semiconductors為了更完善服務客戶也在矽谷設立辦公室，而客戶們也包含多家美國科技巨頭。TrendForce 很榮幸與 SAPIEN Semiconductors執行長李明熙（Myunghee Lee）及策略長 Ethan Jin 進行電話專訪。他們分享了對 Micro LED 市場展望的寶貴見解，並討論了公司目前的發展狀況。
+SAPIEN Semiconductors Inc. 成立於 2017 年，是一家無廠半導體設計公司，專注於為 Micro LED 顯示驅動器開發客製化 ASIC 產品與解決方案。該公司運用創新且已經在矽晶圓片上驗證的設計IP，為客戶提供完整為客戶提供涵蓋各種Micro LED顯示解析度及尺寸的完整解決方案。這些解決方案適用於從元宇宙到大型顯示器等各類應用領域。根據 SAPIEN Semiconductors 的專利組合，在近眼顯示應用中採用具備 PWM 的主動驅動 CMOS 架構，可有效降低功耗。此外，就大型顯示器而言，採用具備 PWM 驅動的Micro IC，不僅能更容易點亮 LED，還能避免驅動電流過低的問題。
+李明熙表示，SAPIEN Semiconductors已成功提供標準化與客製化的 CMOS 產品，以滿足不同客戶的需求。例如，該公司目前已向市場提供採用 28nm 節點的標準全彩 CMOS產品，以及採用 22nm／28nm 節點的客製化單色 CMOS 背板 IC，支援 2.5µm 的像素間距，解析度達 800×600 至最高 2K。未來，公司規劃突破22nm製程節點與2µm像素間距的技術門檻，以實現1280x720 或更高的 FHD解析度。針對大型顯示器，SAPIEN Semiconductors正致力開發Micro IC，為美國主要科技公司提供具附加價值的解決方案，產品主要鎖定新一代筆電顯示器應用。這些解決方案旨在提升亮度均勻性、提高對比度並降低功耗，從而實現更卓越的靜態與動態畫質。
+李明熙認為，Micro LED 技術結合 CMOS 可廣泛應用於近眼顯示、筆電顯示、車用顯示與大型顯示器，將引領新一代顯示技術進入非凡的新時代。</t>
+        </is>
+      </c>
       <c r="I22" s="1" t="n">
-        <v>46244.6238288426</v>
+        <v>46247.58245107639</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -2471,7 +2586,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>f6fd556ce7e06082903a08836771552e9a863fb20d553ec3baa79b6b22fca37d</t>
+          <t>a3d45bbf4d495defa3ef30d0256c941f40a24dd9df1c36a67b73873107a9ee15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2481,99 +2596,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>【獨家專訪】SAPIEN Semiconductors：從大型Micro LED 顯示器到近眼顯示裝置的全方位解決方案 - ledinside.com.tw</t>
+          <t>Arm 首度在台領投！專家分析：通寶半導體憑尖端技術獲全球矽智財IP龍頭入股 - ETtoday財經雲</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://www.ledinside.com.tw/interview/20251017-40226.html</t>
+          <t>https://finance.ettoday.net/news/3129203</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ledinside.com.tw</t>
+          <t>ETtoday財經雲</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fri, 17 Oct 2025 07:00:00 GMT</t>
+          <t>Mon, 09 Mar 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
-        <is>
-          <t>SAPIEN Semiconductors致力於與全球 Micro LED 顯示器產業的關鍵客戶緊密合作，提供創新的解決方案。此外，該公司在2024年成功於韓國KOSDAQ掛牌上市，創下79.9億韓元的營收佳績，年成長率高達149%。SAPIEN Semiconductors為了更完善服務客戶也在矽谷設立辦公室，而客戶們也包含多家美國科技巨頭。TrendForce 很榮幸與 SAPIEN Semiconductors執行長李明熙（Myunghee Lee）及策略長 Ethan Jin 進行電話專訪。他們分享了對 Micro LED 市場展望的寶貴見解，並討論了公司目前的發展狀況。
-SAPIEN Semiconductors Inc. 成立於 2017 年，是一家無廠半導體設計公司，專注於為 Micro LED 顯示驅動器開發客製化 ASIC 產品與解決方案。該公司運用創新且已經在矽晶圓片上驗證的設計IP，為客戶提供完整為客戶提供涵蓋各種Micro LED顯示解析度及尺寸的完整解決方案。這些解決方案適用於從元宇宙到大型顯示器等各類應用領域。根據 SAPIEN Semiconductors 的專利組合，在近眼顯示應用中採用具備 PWM 的主動驅動 CMOS 架構，可有效降低功耗。此外，就大型顯示器而言，採用具備 PWM 驅動的Micro IC，不僅能更容易點亮 LED，還能避免驅動電流過低的問題。
-李明熙表示，SAPIEN Semiconductors已成功提供標準化與客製化的 CMOS 產品，以滿足不同客戶的需求。例如，該公司目前已向市場提供採用 28nm 節點的標準全彩 CMOS產品，以及採用 22nm／28nm 節點的客製化單色 CMOS 背板 IC，支援 2.5µm 的像素間距，解析度達 800×600 至最高 2K。未來，公司規劃突破22nm製程節點與2µm像素間距的技術門檻，以實現1280x720 或更高的 FHD解析度。針對大型顯示器，SAPIEN Semiconductors正致力開發Micro IC，為美國主要科技公司提供具附加價值的解決方案，產品主要鎖定新一代筆電顯示器應用。這些解決方案旨在提升亮度均勻性、提高對比度並降低功耗，從而實現更卓越的靜態與動態畫質。
-李明熙認為，Micro LED 技術結合 CMOS 可廣泛應用於近眼顯示、筆電顯示、車用顯示與大型顯示器，將引領新一代顯示技術進入非凡的新時代。</t>
-        </is>
-      </c>
-      <c r="I23" s="1" t="n">
-        <v>46244.6238612963</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>840706a5bdb3730b7ee331116b12d747e3b5e516c12211f189d3480622602686</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>IC semiconductor</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Arm 首度在台領投！專家分析：通寶半導體憑尖端技術獲全球矽智財IP龍頭入股 - ETtoday財經雲</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>https://finance.ettoday.net/news/3129203</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>ETtoday財經雲</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Mon, 09 Mar 2026 07:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
         <is>
           <t>▲通寶半導體憑尖端技術獲全球矽智財IP龍頭入股 。（圖／通寶提供）
 記者陳弘修／台北報導
@@ -2583,110 +2624,76 @@
 通寶半導體的專業優勢，有助於 Arm 在特定垂直領域（如列印、掃描、影像辨識、AI 生態圈） 開發出更具成本競爭力的產品。此次投資不僅代表 Arm 對通寶技術積澱的肯定，更象徵雙方將共同為未來的影像處理精密控制市場奠定堅實的基礎，開創台灣 IC 設計走向全球戰略合作的新模式。
 ▲通寶半導體公司董事長暨執行長沈軾榮。
 財經專家汪潔民在廣播節目中也表示，全球矽智財IP龍頭Arm正式投資通寶半導體，這不僅是 Arm 在台灣的首例直接投資案，更顯示出台灣在特殊應用領域（SoC &amp; ASIC）的研發實力已獲國際頂尖大廠認可。
-汪潔民分析，Arm過去並未投資台灣任何一家公司，為何特別選擇通寶，關鍵在於通寶具備「可怕的先進影像處理技術」。通寶是全球極少數能自主開發並成功整合以下三大核心技術的公司：AI 智慧影像處理運算、精密動件控制、節能感知管理，特別是在多功能事務機（MFP）產業，晶片設計必須同時應對極其複雜的影像還原、精密機構運作及高度資安防護，技術壁壘極高。通寶憑藉先進影像處理功能，在競爭激烈的 IC 設計市場中脫穎而出。
-※本文版權所有，非經授權，不得轉載。
-[ETtoday著作權聲明]
-A-Lin誇曾國城「下麵好吃」　狂開車他笑瘋：你在說什麼
-快訊／台積電開獎！　7月、前7月營收雙創紀錄
-晶圓代工龍頭台積電（2330）今日公佈 2026 年 7 月營收報告。台積電 7 月合併營收約為新台幣 4,675 億 8,000 萬元，較上月增加了 5.6%，較去年同期增加了 44.7%，續創單月歷史新高。
-2026-08-10 13:42
-國票金副董年薪2千萬掀波　大股東一銀出手！2聲明促檢討薪酬
-國票金（2889）副董事長年薪高達2,000萬元引發爭議，身為大股東之一的第一銀行今（10）日出手表態，針對國票金高階主管薪酬議題提出2項聲明，除已促請所推舉董事透過董事會檢討國票金及子公司薪酬結構合理性，也要求持續精進公司治理，以保障股東權益。
-2026-08-10 14:09
-記憶體缺貨兩樣情！3檔亮燈漲停　千金股勤誠挫6%
-記憶體缺貨題材今（10）日呈現兩樣情，上游記憶體族群買氣火熱，南亞科（2408）、華邦電（2344）、巨虹（8084）盤中一度亮燈漲停，旺宏（2337）漲逾8%，晶豪科（3006）更大漲9.75%、距離漲停僅一步之遙；相較之下，下游通路族群走勢偏弱，威剛（3260）、十銓（4967）、宇瞻（8271）、創見（2451）股價全面走疲，千金股勤誠（8210）也受記憶體缺料、營收認列遞延影響，盤中跌幅一度達6.73%。
-2026-08-10 11:47
-2.5兆股利放大術！0050橫掃3世代　2檔主動式ETF擠進前10強
-上市櫃企業獲利創高帶動下，今年現金股利發放規模可望突破2.5兆，凱基證券觀察，愈來愈多投資人已不再將股利視為一次性的收入，而是把股利再投入，經統計元大台灣50（0050）成為所有年齡層股利再投入主要標的，尤其Z世代（19～30歲）投入占比高達29%，展現年輕族群「先存市值、再談收益」的理財觀念。
-2026-08-10 11:35
-禾伸堂處置出關奔漲停　被動元件5檔齊亮燈
-處置股新制於今（10）日上路，禾伸堂（3026）處置提前解禁，股價跳空直奔588元漲停，其他遭處置被動元件全數恢復正常交易，日電貿（3090）、天二科技（6834）、光頡（3624）、雷科（6207）、富致（6642）等五檔一度亮燈攻漲停，國巨*（2327）漲幅逾半根停板。
-2026-08-10 11:10
-處置新制來了！南電明提前出關今漲逾半根　景碩、欣興紅盤同慶
-台股處置新制今（10）日正式上路，ABF載板景碩（3189）、欣興（3037）、因股價波動過大，每2分鐘撮合一次，處置至8月14日止，欣興漲逾3%，來到985元，景碩則是漲逾1%，南電（8046）適用銜接制度提前明（11）日出關結束處置，股價開高走高，漲逾半根停板，上攻1150元，突破季線，臻鼎-KY（4958）則是盤上震盪。
-2026-08-10 10:20
-台股6千金齊亮燈　權值股台達電帶旺指數漲近千點
-台股今（10）日在權值股、高價股奮力上攻下，多頭信心滿滿，特別是權值股「三哥」台達電（2308）、萬金股后川湖（2059）等6檔亮燈漲停，開盤1小時後加權指數漲近千點。
-2026-08-10 10:18
-面板雙雄齊亮燈！台積電遭爆搶購友達廠房　公司：不回應傳聞
-護國神山台積電（2330）爆出有意向面板廠購地擴廠，受此消息影響，面板股友達（2409）、群創（3481）早盤雙雙亮燈漲停，開盤不到半小時皆湧入逾18萬張成交量，居成交排行前2大。
-2026-08-10 10:14
-川湖處置首日再飆漲停！一張爽賺111萬　本土投顧喊17500元
-伺服器滑軌大廠、股后川湖（2059）今（10）日迎來處置首日，股價開盤直攻漲停價12,220元，連續2個交易日亮燈漲停，再刷掛牌以來歷史天價，盤中一度大漲1,110元，等於每張帳面多賺111萬元。不過漲停並未鎖牢，開盤約10分鐘後打開，漲幅快速收斂。
-2026-08-10 09:17
-首檔聚焦PCB供應鏈龍頭的ETF　 009828於8／17開募
-隨著AI伺服器、高速運算及資料中心建置需求持續升溫，市場投資焦點正由晶片與伺服器，逐步擴散至PCB、載板及高階材料等關鍵供應鏈，瞄準此趨勢，中國信託投信推出國內首檔聚焦PCB供應鏈的「中信台日韓PCB ETF（009828）將於8月17日至20日展開募集，助投資人一次布局台灣、日本及韓國PCB產業龍頭，掌握AI硬體規格升級所帶動的長期成長商機。
-2026-08-10 14:31
-我也要留言，快前往新聞雲App！</t>
-        </is>
-      </c>
-      <c r="I24" s="1" t="n">
-        <v>46244.62388615741</v>
-      </c>
-      <c r="J24" t="inlineStr">
+汪潔民分析，Arm過去並未投資台灣任何一家公司，為何特別選擇通寶，關鍵在於通寶具備「可怕的先進影像處理技術」。通寶是全球極少數能自主開發並成功整合以下三大核心技術的公司：AI 智慧影像處理運算、精密動件控制、節能感知管理，特別是在多功能事務機（MFP）產業，晶片設計必須同時應對極其複雜的影像還原、精密機構運作及高度資安防護，技術壁壘極高。通寶憑藉先進影像處理功能，在競爭激烈的 IC 設計市場中脫穎而出。</t>
+        </is>
+      </c>
+      <c r="I23" s="1" t="n">
+        <v>46247.58292116898</v>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>Success</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>6707a17d53879fe3227e2c9c22edabb69bbb83ed41f96e0833d8927ec8c45514</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>IC semiconductor</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>AI x 半導體下的新契機，《AI核心驅動全球半導體競局》研討會成功解密 - TechNews 科技新報</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>https://technews.tw/2026/04/13/trendforce-2026-hsinchu-semiconductor-forum/</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>TechNews 科技新報</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 07:00:00 GMT</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>集邦科技與科技新報於 2026 年 3 月 31 日假新竹暐順國際會議中心盛大舉辦《AI核心驅動全球半導體競局》研討會。來自產官學研的專家們嘗試從半導體新聚落、晶圓代工、半導體價值鏈升級、邊緣 AI 落地、DRAM 創新、CPO 新趨勢等專題發表，共同探索在 AI 算力掛帥時代下，半導體產業得以致勝的關鍵下一步。
 AI 成為晶圓代工主要驅動力，強勁 PMIC 需求拉高 8 吋廠利用率
@@ -2717,73 +2724,73 @@
 從這裡可透過《Google 新聞》追蹤 TechNews</t>
         </is>
       </c>
-      <c r="I25" s="1" t="n">
-        <v>46244.62435674768</v>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="I24" s="1" t="n">
+        <v>46247.58294769676</v>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>Success</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>795c8f4a6a73a784ae2822b9bedadb516b4a30d0253d2c61ba9e16b5dfbaedd3</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>IC semiconductor</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>「落後國際 5~10 年」，中國半導體高層罕見坦承 AI 晶片差距 - TechNews 科技新報</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>https://technews.tw/2026/03/31/china-semiconductor-ai-chip-tech-lags-5-10-years-equipment-talent-bottlenecks-worsen/</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>TechNews 科技新報</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 07:00:00 GMT</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>在今年 3 月 25 日至 27 日於上海舉行的 SEMICON China 2026 相關論壇上，多位中國半導體業界高層罕見坦言，當地在 AI 資料中心晶片領域與國際領先者之間仍有約五到十年的差距。與此同時，AI 應用快速擴張也正把設備、被動元件與人才供應推向緊繃狀態。
 根據與會者說法，AI 熱潮雖然推動晶片技術與投資持續升溫，但下一階段的突破更仰賴半導體製造設備的進展。ACM Research 執行長 David Wang 表示，AI 浪潮帶動了晶片進步，但未來運算效能的演進路徑，很大程度上將由新一代製造設備決定，而目前這些下一代工具尚未開發完成。
@@ -2805,8 +2812,86 @@
 AI 資料中心</t>
         </is>
       </c>
+      <c r="I25" s="1" t="n">
+        <v>46247.58297268519</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>53512cade5a320ced692e64e9c3e60fdbb3a454e36090ce659facdece4b3225a</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>砸近8億元取得8吋晶圓廠！新唐終止與以色列大廠合資 旗下子公司完全持有TPSCo - ftnn.com.tw</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://www.ftnn.com.tw/news/533337</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ftnn.com.tw</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Thu, 26 Mar 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>記者張書翰／綜合報導
+記憶體巨頭華邦電（2344）旗下半導體暨IC設計大廠新唐（4919）昨（25）日發布重訊，公告董事會決議通過對由子公司Nuvoton Technology Corporation Japan（NTCJ）與以色列商Tower Semiconductor（高塔半導體）合資之Tower Partners Semiconductor Co., Ltd.（TPSCo）進行策略性業務重組，並終止合資關係。
+新唐宣布旗下子公司NTCJ將取得TPSCo公司100%股權。（示意圖／截取自新唐官網影片）
+新唐表示，TPSCo營運項目包含12吋及8吋晶圓廠相關業務。目前由新唐旗下子公司NTCJ持有49%股權計49,539股，以色列商Tower則持有51%股權；當交易完成後預計累積持有TPSCo公司100%股份共101,100股。
+廣告 更多內容請繼續往下閱讀
+新唐說明，該公司與Tower計畫對TPSCo進行策略性業務重組，並結束與Tower之合資安排；新唐指出，重組後Tower將取得TPSCo之12吋晶圓廠及相關業務，TPSCo之8吋晶圓廠及相關業務將由TPSCo持續經營，並成為NTCJ之全資子公司，NTCJ將於交易完成日支付2500萬美元（約新台幣7.98億元）予Tower作為對價。該交易預計於2027年4月1日完成，惟仍須符合相關交割條件及主管機關核准。
+今日新唐開高後一路震盪，最終翻黑下跌7.8元，以93.2元作收，跌幅7.72%，成交量來到1萬7276張。
+◎《FTNN新聞網》提醒您：本資料僅供參考，投資人應獨立判斷，審慎評估並自負投資風險。</t>
+        </is>
+      </c>
       <c r="I26" s="1" t="n">
-        <v>46244.62438107639</v>
+        <v>46247.58300320602</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2882,7 +2967,7 @@
         </is>
       </c>
       <c r="I27" s="1" t="n">
-        <v>46244.62440524306</v>
+        <v>46247.58302579861</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2949,7 +3034,7 @@
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" s="1" t="n">
-        <v>46244.62454228009</v>
+        <v>46247.58308003472</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2986,7 +3071,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>470674249962a799c89eb1334da0c3195b7d7f00248425e72020ce9da2b6f162</t>
+          <t>9a7dc224540514f6744339f4ebfa33b103459d718bf62dec876901a104efd077</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2996,113 +3081,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>工研院先進半導體研發基地破土，台積電捐助設備定 2027 年完工 - TechNews 科技新報</t>
+          <t>功率半導體(Power Semiconductor)-8 一文看懂，先進功率半導體技術路線圖：SiC、GaN與先進封裝| 科技 - 鉅亨號</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://technews.tw/2026/02/10/the-industrial-technology-research-institute-itri-advanced-semiconductor-rd-base-broke-ground/</t>
+          <t>https://hao.cnyes.com/post/256845</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TechNews 科技新報</t>
+          <t>鉅亨號</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 08:00:00 GMT</t>
+          <t>Mon, 29 Jun 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
-        <is>
-          <t>經濟部攜手國發會、國科會共同打造的「先進半導體研發基地」，10 日於工研院中興院區正式動土、藉由晶創台灣方案的支持，基地內將設有「先進半導體試產線」，2027 年底完工後，將提供「IC 設計創新試產驗證」、「先進半導體製程開發」、「設備材料在地化驗證」三項服務，有效降低中小型 IC 設計公司與新創公司的驗證門檻，協助國內材料及設備業者強化競爭力，並超前部署 AI 晶片、矽光子、量子等前瞻技術，開創半導體創新研發生態系，並強化台灣在全球半導體產業的關鍵地位。
-當場致詞的行政院院長卓榮泰表示，AI驅動下使得半導體需求激增，半導體不僅是當前世界各國全力爭取發展的產業，也是台灣連結世界的關鍵樞紐，同時更是總統賴清德提出的AI新十大建設、五大信賴產業政策的核心項目。隨著 算力需求越來越大，政府積極打造台灣從「半導體製造大國」升級為「AI智慧島」，在基礎建設上超前部署，而這座「先進半導體研發基地」，就是國家戰略拼圖中不可或缺的一塊，同時，政府也會扮演產業最強力的後盾，確保產業在研發創新的路上，沒有後顧之憂。
-經濟部部長龔明鑫表示，面對國際局勢變動與全球供應鏈重組，在全球賽跑中持續領先的關鍵就在於強化研發韌性與自主技術，經濟部積極推動「先進半導體研發基地」，有三大亮點，第一是培育生態系、鎖定中小型IC設計公司、新創，或本土設備、材料商，提供新材料、設備、製程反覆驗證機會，例如少量多樣、可彈性調整之「新型態晶圓共乘服務」、縮短研發週期、加快商品化。讓產業生態系更完整、更有韌性。
-第二是技術多樣性，將鎖定目前應用最廣、需求最穩定的 28 到 90 奈米市場，也是AI 邊緣運算(Edge Al)與高效能運算需求最迫切的節點。突破、助攻AI 百工百業。第三是研發更前瞻，智慧醫療、自駕車、工廠自動化都需要特殊製程晶片，在工研院研發團隊全力配合下，基地將超前部署 AI晶片、矽光子、量子科技的尖端開發，扮演百工百業數位轉型的核心引擎，此外要特別感謝
-，不僅慷慨捐贈關鍵半導體設備，還派出專業團隊，提供最頂尖的建廠諮詢與技術指導，充分展現台灣半導體產業最珍貴的共好精神。
-經濟部長期深耕高階半導體技術研發，從材料、元件、製程、晶片設計、封裝到測試完整布局，積極建構我國半導體產業上中下游的一條龍開發能量，在晶創台灣方案政策推動下，已設置 3DIC 先進封裝試產線、八吋次微米感測晶片兩大試產線，並設置「檢量測驗證實驗室」，協助業界進行技術驗證與快速試製。現在進一步建設「先進半導體研發基地」，為國內研究機構首座新形態高科技半導體廠房，設有十二吋先進半導體後製程試產線，並升級現有八吋產線，預計2027年底完工。
-未來，基地將提供28至90奈米後段製程的研發與試產服務，串聯晶片設計、製造與封裝試量產，及測試驗證一條龍服務，協助中小型IC設計業者、半導體業者將產品開發時程縮短30%，並支援量子運算、矽光子、客製化晶片(ASIC)、整合型 3D 架構與下世代記憶體等前瞻技術。國內廠商可於本地完成研發、驗證、迭代的完整流程，強化半導體供應鏈的自主性與韌性；基地也將促進與大專校院合作，協助學生熟悉製程與業界需求，提升半導體人才量能與競爭力。期盼透過三大試產線與一座實驗室的整合，超前部署基礎建設，打造下世代半導體創新研發生態系。
-(首圖來源：科技新報攝)
-文章看完覺得有幫助，何不給我們一個鼓勵
-請我們喝杯咖啡
-想請我們喝幾杯咖啡？
-每杯咖啡 65 元
-您的咖啡贊助將是讓我們持續走下去的動力
-總金額共新臺幣
-《關於請喝咖啡的 Q &amp; A》
-留給我們的話
-從這裡可透過《Google 新聞》追蹤 TechNews
-先進半導體</t>
-        </is>
-      </c>
-      <c r="I29" s="1" t="n">
-        <v>46244.62456527778</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>9a7dc224540514f6744339f4ebfa33b103459d718bf62dec876901a104efd077</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>IC semiconductor</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>功率半導體(Power Semiconductor)-8 一文看懂，先進功率半導體技術路線圖：SiC、GaN與先進封裝| 科技 - 鉅亨號</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>https://hao.cnyes.com/post/256845</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>鉅亨號</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Mon, 29 Jun 2026 07:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
         <is>
           <t>功率半導體(Power Semiconductor)-8 一文看懂，先進功率半導體技術路線圖：SiC、GaN與先進封裝
 2026/06/29
@@ -3448,155 +3445,75 @@
 (半導體先進技術與模擬)</t>
         </is>
       </c>
-      <c r="I30" s="1" t="n">
-        <v>46244.62459576389</v>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="I29" s="1" t="n">
+        <v>46247.58319033564</v>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>Success</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
     </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>99282990254295f23b6069f22bd9729761bc9de2ce214a4cd8fa8522ae22fb79</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ded80b8888d084d44b525e7bc9a7629b2906606a0a38a0d0acd8e8c3dfc957c5</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>IC semiconductor</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>砸近8億元取得8吋晶圓廠！新唐終止與以色列大廠合資 旗下子公司完全持有TPSCo - FTNN 新聞網</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>https://www.ftnn.com.tw/news/533337</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>FTNN 新聞網</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Thu, 26 Mar 2026 07:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>記者張書翰／綜合報導
-記憶體巨頭華邦電（2344）旗下半導體暨IC設計大廠新唐（4919）昨（25）日發布重訊，公告董事會決議通過對由子公司Nuvoton Technology Corporation Japan（NTCJ）與以色列商Tower Semiconductor（高塔半導體）合資之Tower Partners Semiconductor Co., Ltd.（TPSCo）進行策略性業務重組，並終止合資關係。
-新唐宣布旗下子公司NTCJ將取得TPSCo公司100%股權。（示意圖／截取自新唐官網影片）
-新唐表示，TPSCo營運項目包含12吋及8吋晶圓廠相關業務。目前由新唐旗下子公司NTCJ持有49%股權計49,539股，以色列商Tower則持有51%股權；當交易完成後預計累積持有TPSCo公司100%股份共101,100股。
-廣告 更多內容請繼續往下閱讀
-新唐說明，該公司與Tower計畫對TPSCo進行策略性業務重組，並結束與Tower之合資安排；新唐指出，重組後Tower將取得TPSCo之12吋晶圓廠及相關業務，TPSCo之8吋晶圓廠及相關業務將由TPSCo持續經營，並成為NTCJ之全資子公司，NTCJ將於交易完成日支付2500萬美元（約新台幣7.98億元）予Tower作為對價。該交易預計於2027年4月1日完成，惟仍須符合相關交割條件及主管機關核准。
-今日新唐開高後一路震盪，最終翻黑下跌7.8元，以93.2元作收，跌幅7.72%，成交量來到1萬7276張。
-◎《FTNN新聞網》提醒您：本資料僅供參考，投資人應獨立判斷，審慎評估並自負投資風險。</t>
-        </is>
-      </c>
-      <c r="I31" s="1" t="n">
-        <v>46244.62462010416</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>651cba9a1261da00ca71b45d4f40eb85f6e1966de0791d4e8479969fe09c67e1</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>IC semiconductor</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>聯發科半導體、人工智慧及通訊領域論文 入選全球頂尖學術會議 - 自由財經</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>聯發科半導體、人工智慧及通訊領域論文 入選全球頂尖學術會議 - ec.ltn.com.tw</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
         <is>
           <t>https://ec.ltn.com.tw/article/breakingnews/5257196</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>自由財經</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ec.ltn.com.tw</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>Tue, 25 Nov 2025 08:00:00 GMT</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>台股收盤》記憶體領逾1300家同樂 指數收漲702點
-台積電7月營收4675億元 月增5.6％再飆新高
-聯發科半導體、人工智慧及通訊領域論文 入選全球頂尖學術會議
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>聯發科半導體、人工智慧及通訊領域論文 入選全球頂尖學術會議
 2025/11/25 12:52
 聯發科半導體、人工智慧及通訊領域論文入選全球頂尖學術會議。（記者卓怡君攝）
 〔記者卓怡君／台北報導〕IC設計龍頭聯發科（2454）今日宣布，今年旗下多篇論文入選ISSCC、NeurIPS、CVPR、ICLR、ICML、ICC、GLOBECOM等全球半導體、人工智慧及通訊領域的頂尖國際學術會議。其中，入選有IC設計界奧林匹克之稱的ISSCC 2026論文中，有兩篇由台灣總部研發團隊發表，這也讓聯發科成為台灣業界唯一連續23年累計超過百篇論文入選的企業，展現深厚的技術實力。此外，聯發科副董事長暨執行長蔡力行也受邀於明年二月在美國舊金山舉行的ISSCC 2026，以「拓展AI新視野：半導體創新觀點」（Advancing Horizons for AI: Perspectives on Semiconductor Innovations）為題，分享如何持續透過半導體技術創新，推動AI邁向新境界。
@@ -3612,8 +3529,163 @@
 今日熱門新聞</t>
         </is>
       </c>
+      <c r="I30" s="1" t="n">
+        <v>46247.58321657407</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>470674249962a799c89eb1334da0c3195b7d7f00248425e72020ce9da2b6f162</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>工研院先進半導體研發基地破土，台積電捐助設備定 2027 年完工 - TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://technews.tw/2026/02/10/the-industrial-technology-research-institute-itri-advanced-semiconductor-rd-base-broke-ground/</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tue, 10 Feb 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>經濟部攜手國發會、國科會共同打造的「先進半導體研發基地」，10 日於工研院中興院區正式動土、藉由晶創台灣方案的支持，基地內將設有「先進半導體試產線」，2027 年底完工後，將提供「IC 設計創新試產驗證」、「先進半導體製程開發」、「設備材料在地化驗證」三項服務，有效降低中小型 IC 設計公司與新創公司的驗證門檻，協助國內材料及設備業者強化競爭力，並超前部署 AI 晶片、矽光子、量子等前瞻技術，開創半導體創新研發生態系，並強化台灣在全球半導體產業的關鍵地位。
+當場致詞的行政院院長卓榮泰表示，AI驅動下使得半導體需求激增，半導體不僅是當前世界各國全力爭取發展的產業，也是台灣連結世界的關鍵樞紐，同時更是總統賴清德提出的AI新十大建設、五大信賴產業政策的核心項目。隨著 算力需求越來越大，政府積極打造台灣從「半導體製造大國」升級為「AI智慧島」，在基礎建設上超前部署，而這座「先進半導體研發基地」，就是國家戰略拼圖中不可或缺的一塊，同時，政府也會扮演產業最強力的後盾，確保產業在研發創新的路上，沒有後顧之憂。
+經濟部部長龔明鑫表示，面對國際局勢變動與全球供應鏈重組，在全球賽跑中持續領先的關鍵就在於強化研發韌性與自主技術，經濟部積極推動「先進半導體研發基地」，有三大亮點，第一是培育生態系、鎖定中小型IC設計公司、新創，或本土設備、材料商，提供新材料、設備、製程反覆驗證機會，例如少量多樣、可彈性調整之「新型態晶圓共乘服務」、縮短研發週期、加快商品化。讓產業生態系更完整、更有韌性。
+第二是技術多樣性，將鎖定目前應用最廣、需求最穩定的 28 到 90 奈米市場，也是AI 邊緣運算(Edge Al)與高效能運算需求最迫切的節點。突破、助攻AI 百工百業。第三是研發更前瞻，智慧醫療、自駕車、工廠自動化都需要特殊製程晶片，在工研院研發團隊全力配合下，基地將超前部署 AI晶片、矽光子、量子科技的尖端開發，扮演百工百業數位轉型的核心引擎，此外要特別感謝
+，不僅慷慨捐贈關鍵半導體設備，還派出專業團隊，提供最頂尖的建廠諮詢與技術指導，充分展現台灣半導體產業最珍貴的共好精神。
+經濟部長期深耕高階半導體技術研發，從材料、元件、製程、晶片設計、封裝到測試完整布局，積極建構我國半導體產業上中下游的一條龍開發能量，在晶創台灣方案政策推動下，已設置 3DIC 先進封裝試產線、八吋次微米感測晶片兩大試產線，並設置「檢量測驗證實驗室」，協助業界進行技術驗證與快速試製。現在進一步建設「先進半導體研發基地」，為國內研究機構首座新形態高科技半導體廠房，設有十二吋先進半導體後製程試產線，並升級現有八吋產線，預計2027年底完工。
+未來，基地將提供28至90奈米後段製程的研發與試產服務，串聯晶片設計、製造與封裝試量產，及測試驗證一條龍服務，協助中小型IC設計業者、半導體業者將產品開發時程縮短30%，並支援量子運算、矽光子、客製化晶片(ASIC)、整合型 3D 架構與下世代記憶體等前瞻技術。國內廠商可於本地完成研發、驗證、迭代的完整流程，強化半導體供應鏈的自主性與韌性；基地也將促進與大專校院合作，協助學生熟悉製程與業界需求，提升半導體人才量能與競爭力。期盼透過三大試產線與一座實驗室的整合，超前部署基礎建設，打造下世代半導體創新研發生態系。
+(首圖來源：科技新報攝)
+文章看完覺得有幫助，何不給我們一個鼓勵
+請我們喝杯咖啡
+想請我們喝幾杯咖啡？
+每杯咖啡 65 元
+您的咖啡贊助將是讓我們持續走下去的動力
+總金額共新臺幣
+《關於請喝咖啡的 Q &amp; A》
+留給我們的話
+從這裡可透過《Google 新聞》追蹤 TechNews
+先進半導體</t>
+        </is>
+      </c>
+      <c r="I31" s="1" t="n">
+        <v>46247.58324986111</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>9d26820d0d4c5cdd0ffcee101e09a8a4420b68665a736989844872b104470034</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Cadence 攜手台積電擴大 AI 半導體創新，範圍涵蓋 N3、N2、A16 及 A14 先進製程 - TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://technews.tw/2026/05/12/cadence-partners-with-tsmc-to-expand-ai-semiconductor-innovation/</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" s="1" t="n">
-        <v>46244.62473276621</v>
+        <v>46247.58327538194</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -3650,7 +3722,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>9d26820d0d4c5cdd0ffcee101e09a8a4420b68665a736989844872b104470034</t>
+          <t>e98a8767e4786e466eaaa5c9834f0f21606d38acb980d5eecfc2f80b6a3b8e68</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3660,12 +3732,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cadence 攜手台積電擴大 AI 半導體創新，範圍涵蓋 N3、N2、A16 及 A14 先進製程 - TechNews 科技新報</t>
+          <t>Navitas 與輝達開發的電源晶片有進展、股價飛天 - TechNews 科技新報</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://technews.tw/2026/05/12/cadence-partners-with-tsmc-to-expand-ai-semiconductor-innovation/</t>
+          <t>https://finance.technews.tw/2025/10/15/navitas-nvidia-power-chip-development-progress-shares-soaring/</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3675,12 +3747,38 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tue, 12 May 2026 07:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>Wed, 15 Oct 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>第三代半導體氮化鎵（GaN）功率 IC 領導大廠納微半導體（Navitas Semiconductor）宣布，與輝達（Nvidia）合作開發的 AI 基礎建設電源晶片取得進展，股價聞訊飆高。
+Barron’s報導，Navitas執行長Chris Allexandre 13日稍晚透過
+聲明稿表示
+，隨著輝達推動AI基礎設施轉型，該公司將藉由先進的氮化鎵（GaN）和碳化矽（SiC）電源解決方案，提供次世代資料中心所需的效率、可擴展性和可靠性。
+Navitas表示，最新裝置可讓輝達順利獲得次世代AI系統需要的800伏特電力，這項設計可直接為IT機櫃供電，無需額外的轉換器。
+根據Navitas說法，其為AI資料中心設計的先進800V高壓直流輸電（HVDC）架構，不但能提升效率及可擴展性，還可減少銅的用量。
+Navitas 14日聞訊飆漲26.08%、收12.57美元，創2022年1月11日以來收盤新高。
+Navitas 2025年5月就曾宣布獲得輝達訂單，帶動5月22日當天股價暴衝164.4%。
+MoneyDJ新聞
+授權轉載；首圖來源：shutterstock）
+延伸閱讀：
+納微打入 NVIDIA 供應鏈！高壓直流架構有望成 AI 資料中心趨勢
+文章看完覺得有幫助，何不給我們一個鼓勵
+請我們喝杯咖啡
+想請我們喝幾杯咖啡？
+每杯咖啡 65 元
+您的咖啡贊助將是讓我們持續走下去的動力
+總金額共新臺幣
+《關於請喝咖啡的 Q &amp; A》
+留給我們的話
+從這裡可透過《Google 新聞》追蹤 TechNews
+Navitas
+功率半導體</t>
+        </is>
+      </c>
       <c r="I33" s="1" t="n">
-        <v>46244.62476368056</v>
+        <v>46247.58330166667</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -3717,7 +3815,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2db8fa800bbc0eeb8c86f4b71d8c7b7711dc2003bcf334ace465b6abc3f9ff37</t>
+          <t>2e90d7ae07c2ea69d243f32f7fbd103c001b9299aaef6e8d30aa12e4a015bf00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3727,27 +3825,53 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>為何印度理工人才不願來台？ 台IC設計業者揭背後原因 - digitimes.com.tw</t>
+          <t>Dialog Semiconductor成為AST＆Science先進通訊客製IC的首選供應商 - CIO Taiwan</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://www.digitimes.com.tw/tech/dt/n/shwnws.asp?id=0000733683_OB45OBTN9ZSIJS26YI5IY</t>
+          <t>https://www.cio.com.tw/dialog-semiconductors-as-preferred-provider-for-asts-advanced-communications-custom-ic/</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>digitimes.com.tw</t>
+          <t>CIO Taiwan</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Wed, 08 Oct 2025 07:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Thu, 17 Dec 2020 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Dialog Semiconductor成為AST＆Science先進通訊客製IC的首選供應商 | CIO Taiwan
+查看所有結果
+上一篇文章
+專訪光田綜合醫院總院長王乃弘
+下一篇文章
+Toppan投資 iDGate (蓋特資訊)深化其在數位ID領域的全球領先地位
+工廠停工誰負責？掌握資產真相，別讓 OT 治理變成一場紙上談兵
+連資產真相都掌握不住，OT 治理多半只會停在紙面
+決策不能重來？揭秘技術領導者如何用 AI 買回商業世界的「生存選擇權」！
+【下載包】跨境資安風險升高 公務設備「出國前、期間、返國後」三階段防護
+從 AI 購物管家到頂級體驗 萬事達卡加速布局新消費場景
+直擊製造業 AI 轉型深水區！Dell Technologies、勤業眾信、BIG DATA 聯手推一站式 Agentic AI 架構，助攻企業從 PoC 邁向規模化生產
+合規管理×智慧防護　台塑網雙引擎捍衛營業秘密
+【專訪】中國信託商業銀行數位科技處處長王俊權：數據與 AI 治理體系，三層金字塔規模化
+【專訪】台達電子資訊長暨資安長曾立峰：企業架構思維，驅動全球營運
+【金融業】金融犯罪偵測系統的十年演進 ─ HSBC 反洗錢系統的 AI 路徑
+【專訪】鴻海科技集團 B 事業群總經理姜志雄
+邁向 Physical AI 無人載具成企業 AI、通訊韌性與資安整合新戰場
+醫療 AI 進入規模化時代 應用創新邁向平台治理
+從幣圈到內控：虛擬資產專法通過後，企業要補上的治理能力
+FDE 前線部署工程師，讓 AI 真正落地的角色
+供應商視野
+CIO 雜誌</t>
+        </is>
+      </c>
       <c r="I34" s="1" t="n">
-        <v>46244.62480554398</v>
+        <v>46247.5834075463</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -3784,7 +3908,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>60b0ca63494564649596daa2b53702c6954758a16f0563a75662e3b53ad89dd4</t>
+          <t>41fa99a30b4653f2e09824373cea6b9080e72bc96a09d726f765675c71bfd52e</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3794,53 +3918,27 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Dialog Semiconductor成為AST＆Science先進通訊客製IC的首選供應商 - CIO Taiwan</t>
+          <t>Semiconductor sector output forecast to rise by double digits in 2025|English News - ocacnews.net</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://www.cio.com.tw/dialog-semiconductors-as-preferred-provider-for-asts-advanced-communications-custom-ic/</t>
+          <t>https://ocacnews.net/article/398583</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CIO Taiwan</t>
+          <t>ocacnews.net</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Thu, 17 Dec 2020 08:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Dialog Semiconductor成為AST＆Science先進通訊客製IC的首選供應商 | CIO Taiwan
-查看所有結果
-上一篇文章
-專訪光田綜合醫院總院長王乃弘
-下一篇文章
-Toppan投資 iDGate (蓋特資訊)深化其在數位ID領域的全球領先地位
-【專訪】中國信託商業銀行數位科技處處長王俊權：數據與 AI 治理體系，三層金字塔規模化
-【專訪】台達電子資訊長暨資安長曾立峰：企業架構思維，驅動全球營運
-匯豐銀行 AI 防堵金融犯罪的十年轉骨
-【編輯室札記】開源大模型讓 AI ROI 露曙光
-【專訪】萬事達卡台灣區董事總經理陳懿文：Agentic Commerce 時代 重塑金融信任架構
-直擊製造業 AI 轉型深水區！Dell Technologies、勤業眾信、BIG DATA 聯手推一站式 Agentic AI 架構，助攻企業從 PoC 邁向規模化生產
-臺安醫院重構數位韌性基石：攜手思科佈局零信任智慧醫療新階段
-邁向 Physical AI 無人載具成企業 AI、通訊韌性與資安整合新戰場
-經濟股市爆發 民眾無感如何解決？
-【金融業】金融犯罪偵測系統的十年演進 ─ HSBC 反洗錢系統的 AI 路徑
-FDE 前線部署工程師，讓 AI 真正落地的角色
-未治理 AI 將付出代價
-避免盲追流行，「主權 AI」徹底剖析
-從缺料、缺工到缺貨：企業為什麼需要 BCM 商業持續管理？
-邊 AI 邊裁員　企業正在重寫成長的規則
-供應商視野
-CIO 雜誌</t>
-        </is>
-      </c>
+          <t>Tue, 20 May 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" s="1" t="n">
-        <v>46244.62483115741</v>
+        <v>46247.58344548611</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -3877,7 +3975,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>41fa99a30b4653f2e09824373cea6b9080e72bc96a09d726f765675c71bfd52e</t>
+          <t>bef16fabb298f3831569573533c5522478a9db9044a02e0dcd049f99ad6e8ccb</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3887,12 +3985,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Semiconductor sector output forecast to rise by double digits in 2025|English News - ocacnews.net</t>
+          <t>Taiwan ranked No. 1 semiconductor material buyer in 2022|English News - ocacnews.net</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://ocacnews.net/article/398583</t>
+          <t>https://ocacnews.net/article/342674</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3902,12 +4000,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tue, 20 May 2025 07:00:00 GMT</t>
+          <t>Sat, 17 Jun 2023 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" s="1" t="n">
-        <v>46244.62487055556</v>
+        <v>46247.58346916667</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -4000,7 +4098,7 @@
         </is>
       </c>
       <c r="I37" s="1" t="n">
-        <v>46244.62489186342</v>
+        <v>46247.58349108796</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -4037,7 +4135,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>bef16fabb298f3831569573533c5522478a9db9044a02e0dcd049f99ad6e8ccb</t>
+          <t>911b56f42cecaa50b9187146b6f3bfec0ac4b2893b908dad5f7a530d2f0b995e</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4047,12 +4145,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Taiwan ranked No. 1 semiconductor material buyer in 2022|English News - ocacnews.net</t>
+          <t>ITRI raises output growth forecast for Taiwan semiconductors|English News - ocacnews.net</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://ocacnews.net/article/342674</t>
+          <t>https://ocacnews.net/article/405790</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4062,12 +4160,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sat, 17 Jun 2023 07:00:00 GMT</t>
+          <t>Sat, 16 Aug 2025 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" s="1" t="n">
-        <v>46244.62491994213</v>
+        <v>46247.58351814815</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -4104,7 +4202,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>911b56f42cecaa50b9187146b6f3bfec0ac4b2893b908dad5f7a530d2f0b995e</t>
+          <t>639f8ebbece786f86813e938d0ccf98ab3d08bba30540e5b1f9592b0b65641fc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4114,92 +4212,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ITRI raises output growth forecast for Taiwan semiconductors|English News - ocacnews.net</t>
+          <t>IC Taiwan Grand Challenge 攜手國際新創InnoVEX亮相技術發表會熱鬧登場展現跨國創新能量 - tca.org.tw</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://ocacnews.net/article/405790</t>
+          <t>https://www.tca.org.tw/news_detail.php?n=2334&amp;t=h</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ocacnews.net</t>
+          <t>tca.org.tw</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sat, 16 Aug 2025 07:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" s="1" t="n">
-        <v>46244.62494292824</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>639f8ebbece786f86813e938d0ccf98ab3d08bba30540e5b1f9592b0b65641fc</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>IC semiconductor</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>IC Taiwan Grand Challenge 攜手國際新創InnoVEX亮相技術發表會熱鬧登場展現跨國創新能量 - tca.org.tw</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>https://www.tca.org.tw/news_detail.php?n=2334&amp;t=h</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>tca.org.tw</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
           <t>Thu, 22 May 2025 07:00:00 GMT</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>IC Taiwan Grand Challenge 攜手國際新創 InnoVEX亮相 技術發表會熱鬧登場 展現跨國創新能量
 行政院卓榮泰院長參觀IC Taiwan Grand Challenge主題館
@@ -4222,8 +4253,75 @@
 （發佈時間：2025-05-22）</t>
         </is>
       </c>
+      <c r="I39" s="1" t="n">
+        <v>46247.58354550926</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>03ea2e084138cc326cdd2524ea646239092663a5223569afb7f4c05e0fa286c6</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TSMC's Liu expects Taiwan IC output to grow by over 24% in 2021 - ocacnews.net</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://ocacnews.net/article/294059</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>ocacnews.net</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Fri, 29 Oct 2021 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" s="1" t="n">
-        <v>46244.62496851852</v>
+        <v>46247.58356972222</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -4260,7 +4358,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>03ea2e084138cc326cdd2524ea646239092663a5223569afb7f4c05e0fa286c6</t>
+          <t>e6463873826fb94a191b4a836c5e9734eb7ef992a4b6ff21161e8df2865f04b9</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4270,175 +4368,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>TSMC's Liu expects Taiwan IC output to grow by over 24% in 2021 - ocacnews.net</t>
+          <t>半導體產業趨勢的反轉（1）：從垂直整合到價值鏈的解構 - DIGITIMES</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://ocacnews.net/article/294059</t>
+          <t>https://www.digitimes.com.tw/col/article/?id=15760</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ocacnews.net</t>
+          <t>DIGITIMES</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fri, 29 Oct 2021 07:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" s="1" t="n">
-        <v>46244.62499065972</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>90510c2b81ff073ff963d951442ba7ac0475f9f3eecbaafc3dbd4e9297962780</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>IC semiconductor</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>CT Semiconductor 完成組裝、測試和封裝 (ATP) 半導體晶片的首期「種子培訓」課程 - globenewswire.com</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>https://www.globenewswire.com/news-release/2025/01/25/3015182/0/zh-hant/ct-semiconductor-%E5%AE%8C%E6%88%90%E7%B5%84%E8%A3%9D-%E6%B8%AC%E8%A9%A6%E5%92%8C%E5%B0%81%E8%A3%9D-atp-%E5%8D%8A%E5%B0%8E%E9%AB%94%E6%99%B6%E7%89%87%E7%9A%84%E9%A6%96%E6%9C%9F-%E7%A8%AE%E5%AD%90%E5%9F%B9%E8%A8%93-%E8%AA%B2%E7%A8%8B.html</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>globenewswire.com</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Sat, 25 Jan 2025 08:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>河內，越南, Jan. 25, 2025 (GLOBE NEWSWIRE) -- CT Group 旗下的 CT Semiconductor 正式結束了組裝、測試和封裝 (ATP) 半導體晶片的首期「種子培訓 - 培訓導師」課程。 該課程於 2025 年 1 月 13 日至 19 日在河內國家創新中心 (NIC) 舉行。
-主辦方開設該課程的宗旨是與政府合作，培養半導體產業的優秀人才。 這個項目遵循總理第 1018/QD-TTg 號決定。該決定概述了越南半導體產業從現在到 2030 年期間的發展策略，以及展望至 2050 年的願景。
-CT Semiconductor 的「種子培訓 - 培訓導師」課程
-該課程由擁有 20 多年行業經驗的外國專家設計並提供直接指導。 課程的亮點之一，是所有參與者都獲得了
-CT Semiconductor
-的全力支持，包括學費、生活費和交通費。 這顯示該公司堅定致力為越南半導體產業的可持續發展作出貢獻，同時緊貼政府的產業發展策略。
-Le Xuan Luc 博士 (越南河內國立大學 - 工程技術大學，奈米資訊科技融合工程博士) 表示：
-「我參加了『種子培訓 - 培訓導師』首期課程，覺得這門課程非常有意義。 CT Semiconductor 具有無畏的開創性視野，為培養測試、組裝和封裝 IC 晶片的高水平實踐型學生而提供支援，這是一項長期策略，在全國範圍內推動越南半導體生態系統蓬勃發展。 自越南確立科技是國家發展核心以來，這是為業界帶來重大效益的實際舉措。」
-國家創新中心 (NIC) 的代表分享說：
-「像『種子培訓 - 培訓導師』這樣的課程，是培養技術熟練的人才隊伍的第一步，以滿足國內外半導體產業的龐大需求。 CT Semiconductor 在人力資源培訓計劃方面發揮領導作用，有助實現國家設立的目標：到 2030 年，將有 50,000 名工程師和本科生為半導體行業服務。」
-CT Semiconductor 的代表補充說：
-「我們明白，人力資源是關鍵，以實現『越南成為地區性領先的半導體技術中心』的願景。 透過這項課程，CT Semiconductor 不僅滿足了我們廠房的人力需求，更可為外國半導體公司在越南投資和擴展業務而提供支援。 這是長期策略的一部分，旨在確保越南不僅是投資項目的理想地點，而且還能提供符合國際標準的優秀人才。」
-CT Semiconductor 開設課程是為越南半導體產業培養優秀人才邁出了策略性的一步。 CT Semiconductor 大力投資於教育和技術開發，致力為半導體產業打好可持續發展的基礎，與各界人士攜手合作，逐步將越南打造為地區性及全球的重要半導體技術中心。</t>
-        </is>
-      </c>
-      <c r="I42" s="1" t="n">
-        <v>46244.62556239584</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>d9516ceb392700aba05ac3588dda0bad4b7cb2b4b9dfd03d00b1e349a1f310cf</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>IC semiconductor</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>半導體產業趨勢的反轉（1）：從垂直整合到價值鏈的解構 - digitimes.com.tw</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>https://www.digitimes.com.tw/col/article/?id=15760</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>digitimes.com.tw</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
           <t>Wed, 19 Feb 2025 08:00:00 GMT</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>在半導體產業發展迄今的70幾個年頭，有一甲子的時間整個產業的動向是解構產業價值鏈，變成單獨的價值鏈節點（value chain node）。
 在1950~70年代，最早期的半導體公司如仙童半導體（Fairchild Semiconductor；1957）、美國無線電公司（RCA Semiconductor；1960s）、通用儀器（General Instrument；1960s）、德州儀器（Texas Instrument；1951）、摩托羅拉半導體（Motorola Semiconductor；1949）等，這些公司在今日半導體產業的分類都是清一色的整合設備製造商（IDM；Integrated Device Manufacturer）。
@@ -4456,8 +4404,142 @@
 裂解垂直整合的價值鏈成為各自獨立的價值鏈節點還能取得更高效率的運作和利潤，自有它的深層技術原因：此時的半導體發展在核心的環節如設計、製造、封測等都還留有相當的物性和電性的餘裕，各相鄰的價值節點之間可以靠共同約定的標準介面來協作，毋需太多額外的溝通，因此獨立、專注的價值節點經營可行，並且可以建立規模經濟，特別是在技術研發方面。這一點對於以後產業型態的發展持續佔有重要的影響力。</t>
         </is>
       </c>
+      <c r="I41" s="1" t="n">
+        <v>46247.58414957176</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>48d605b54fce7180a1174c7d39c71f52500f46950e0f62787045acf849ce26b2</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Manufacturing sector's Q2 fixed asset investments up on IC expansion|English News - ocacnews.net</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://ocacnews.net/article/408310</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>ocacnews.net</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Thu, 18 Sep 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" s="1" t="n">
+        <v>46247.58417225695</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>f84824d4d97b46a78bcb3d2aa4262369827025f0d1503af80fdd981ca4bc1c21</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>【2025最新】半導體業平均薪資前10揭曉！瑞昱年薪475萬奪冠、台積電排第9｜工作機會 - 104職場力</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://blog.104.com.tw/top-10-semiconductor-industry-salary-2024/</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>104職場力</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Wed, 04 Jun 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" s="1" t="n">
-        <v>46244.62560547454</v>
+        <v>46247.5846419213</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -4494,7 +4576,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>48d605b54fce7180a1174c7d39c71f52500f46950e0f62787045acf849ce26b2</t>
+          <t>cf227a2c8d065c9423155b9660e657159b2ae3801c130ba1c9d46cbf3370b37f</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4504,226 +4586,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Manufacturing sector's Q2 fixed asset investments up on IC expansion|English News - ocacnews.net</t>
+          <t>鴻海研究院研發先進晶片獲IEEE ISPSD肯定 突破AI伺服器關鍵技術 - 鴻海科技集團</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://ocacnews.net/article/408310</t>
+          <t>https://www.foxconn.com/zh-tw/press-center/press-releases/latest-news/1769</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ocacnews.net</t>
+          <t>鴻海科技集團</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Thu, 18 Sep 2025 07:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" s="1" t="n">
-        <v>46244.62562869213</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>f0d83ebd3a8f068f24b94463dfedca4e4d5ff26f56c07a1a491ba6fce3d2fda6</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>IC semiconductor</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2023年半導體平均月薪5.6萬元年增幅3.1% 高薪職務出列！挑戰月薪上看10萬 - 104職場力</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>https://blog.104.com.tw/104data-2023-semiconductor-salary/</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>104職場力</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Tue, 05 Sep 2023 07:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" s="1" t="n">
-        <v>46244.6257383449</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>f84824d4d97b46a78bcb3d2aa4262369827025f0d1503af80fdd981ca4bc1c21</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>IC semiconductor</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>【2025最新】半導體業平均薪資前10揭曉！瑞昱年薪475萬奪冠、台積電排第9｜工作機會 - 104職場力</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>https://blog.104.com.tw/top-10-semiconductor-industry-salary-2024/</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>104職場力</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Wed, 04 Jun 2025 07:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" s="1" t="n">
-        <v>46244.62576335648</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>cf227a2c8d065c9423155b9660e657159b2ae3801c130ba1c9d46cbf3370b37f</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>IC semiconductor</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>鴻海研究院研發先進晶片獲IEEE ISPSD肯定 突破AI伺服器關鍵技術 - 鴻海科技集團</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>https://www.foxconn.com/zh-tw/press-center/press-releases/latest-news/1769</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>鴻海科技集團</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
           <t>Mon, 16 Jun 2025 07:00:00 GMT</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>鴻海研究院研發先進晶片獲IEEE ISPSD肯定 突破AI伺服器關鍵技術
 2025/06/16
@@ -4786,8 +4667,299 @@
 www.honhai.com</t>
         </is>
       </c>
+      <c r="I44" s="1" t="n">
+        <v>46247.58476510417</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>bf9f997c98c4f8af770c67d8042ac9bde341a39bc5031f517ed9bb9044aec41e</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ALPHA &amp; OMEGA SEMICONDUCTOR Ltd SEC 10-Q Report - TradingView</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://tw.tradingview.com/news/tradingview:fab2a8ac8fb12:0-alpha-omega-semiconductor-ltd-sec-10-q-report/</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Thu, 05 Feb 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>ALPHA &amp; OMEGA SEMICONDUCTOR Ltd SEC 10-Q Report
+Alpha &amp; Omega Semiconductor Ltd, a leading provider of power semiconductors, has released its Form 10-Q report for the second quarter of fiscal year 2026. The report highlights the company's financial performance and operational activities, reflecting the challenges and strategic initiatives undertaken during the period.
+Financial Highlights
+Business Highlights
+SEC Filing:
+ALPHA &amp; OMEGA SEMICONDUCTOR Ltd [ AOSL ] - 10-Q - Feb. 05, 2026
+TradingView
+來自 TradingView 的更多新聞</t>
+        </is>
+      </c>
+      <c r="I45" s="1" t="n">
+        <v>46247.5847996875</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>dc74c2edc22c1b22e6eeea02d48cb561d61918edfe005fcff817a913e2828802</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2023 年全球前十大 IC 設計業者營收合計年增 12%，NVIDIA 首度奪冠 - TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://finance.technews.tw/2024/05/09/total-revenue-of-the-worlds-top-ten-ic-design-companies-in-2023/</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>TechNews 科技新報</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Thu, 09 May 2024 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" s="1" t="n">
+        <v>46247.58633684028</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>73b37e02765619429a5b5d2e549303e455c335ffc7f29e9d7b5386833b067002</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>【專欄】中芯國際7奈米真抄襲台積電？被爆早用挖礦專用IC「練兵」 - 數位時代</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://www.bnext.com.tw/article/70875/smic-7nm</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>數位時代</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Thu, 28 Jul 2022 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>一文看懂 AI 電視可以幹嘛？不只有 AI 演算法，頂級硬體帶來高畫質表現
+2026.08.07
+sponsored
+台灣索尼股份有限公司
+火熱的 AI 風潮掀起客廳革命，到底 AI 電視可以幹嘛？簡單來說，AI 電視透過 AI 處理器與演算法，即時進行 AI 畫質優化、音效調整、智慧語音搜尋和極致的個人化推薦，全面顛覆傳統智慧電視。在 AI 電視功能中，最讓消費者有感的是 AI 畫質優化，但許多人往往忽略了，畫質提升不只關乎演算法，更取決於底層的背光、色彩與控光技術。Sony BRAVIA True RGB LED 電視，正是將軟體思維與硬體工藝深度結合的最好示範。透過創新的 XR 認知智慧處理器搭配 True RGB 技術，精準呈現 AI 電視的畫質優化能力。
+AI 電視是什麼？不只是能上網看串流的智慧電視
+要理解 AI 電視可以幹嘛，首先必須釐清 AI 電視與一般智慧電視的差異。傳統智慧電視是為電視接上網路，讓使用者單向觀看連網影音。AI 電視則是在智慧電視的基礎上，導入了 AI 處理器與先進演算法，讓智慧電視具備「主動分析與學習」的能力，可即時判斷每一幀影像的畫質特徵、聲音頻率、觀看環境（如白天強光或夜晚暗光），甚至是家庭成員的使用習慣，進而動態調整視聽呈現。簡單來說，傳統智慧電視解決的是「能不能連網看內容」的問題，而 AI 電視解決的是「如何讓內容呈現得最好」的體驗問題。
+但當 AI 演算法分析出最佳的畫面設定後，如果硬體無法精準跟上，優化效果就會大打折扣。這也是為什麼高階顯示技術 True RGB 開始受到市場矚目，確保 AI 算出的極致色彩與對比，能精準落地在觀眾眼前。
+傳統電視容易出現暗部發灰或亮處過曝。Sony BRAVIA 9 II 透過 True RGB 三色獨立背光，能將 AI 算出的極致對比與飽和色彩精準落地。
+AI 電視可以幹嘛？從畫質、場景、音效到個人化推薦的四大核心進化
+面對消費者的核心疑問「AI 電視可以幹嘛？」，可從四大 AI 電視功能深入拆解。
+AI 畫質升頻與降噪：讓低解析度內容更清晰
+透過 AI 升頻與降噪技術，可分析解析度較低或經過壓縮的影音內容，改善線條、紋理與雜訊，使畫面在 4K 螢幕上呈現得更清晰。True RGB 則能協助 AI 優化後的畫面亮度、色彩與對比度精準呈現。不過實際效果仍會受到原始片源解析度與壓縮品質影響。
+智慧場景辨識：依電影、球賽、遊戲自動調整畫面
+AI 電視能即時辨識播放內容，自動調整畫面呈現，比如看電影時調整為劇院感色溫、看球賽即時插幀消除動態殘影、玩遊戲時自動切換至低延遲模式。在不同場景轉換時，True RGB 讓亮度與色彩對比表現依然精準自然。
+左圖為電影模式，右圖為遊戲模式。智慧場景辨識功能會根據電影、球賽或遊戲自動切換最佳模式。搭配 True RGB 技術，即使在動態或暗部場景下，色彩依然自然不失真。
+AI 音效優化：讓人聲與環境音更清楚
+AI 音效演算法能分離出人聲對白與背景音效。看動作大片時，能放大環繞立體感；看新聞時，則優化人聲頻率，甚至能根據客廳結構進行空間音效校正。
+除了頂級畫質，Sony 將 AI 音效演算法與機身背部揚聲器深度結合，能根據客廳結構進行空間校正，分離出清晰人聲與震撼環繞音效。
+語音互動與個人化推薦：減少尋找內容時間
+AI 語音互動更能理解複雜語意，當你說出「我想看適合週末晚上的搞笑電影」時，AI 便會結合使用者的觀看偏好推薦清單，真正做到懂你所想。
+整體而言，在眾多 AI 電視功能中，消費者最能直觀感受到的是 AI 畫質升頻與場景優化。但不論軟體演算法如何強大，都需要有對應的硬體執行力，而 True RGB 正是讓這些高階 AI 畫質能精準落地的關鍵技術。
+AI 畫質優化的關鍵：不只靠演算法，硬體也是決勝點
+在討論 AI 電視時，大眾常有一種迷思，認為只要電視內建強大的 AI 處理器和演算法就行，事實上，AI 電視的畫質優化不是靠單一演算法完成，而是包含「AI 判斷」與「硬體呈現」兩大層次：
+首先由 AI 負責辨識畫面中的主體物件、人眼焦點、光影分佈及動態物體的移動軌跡等。根據 AI 判斷結果，演算法在底層即時計算出一套優化藍圖，決定哪些區域需要進行 AI 升頻、降噪、提高畫質、調整亮度、對比或色彩飽和度等。而硬體則負責最終畫面呈現，包含電視的背光、面板、控光技術與色彩控制技術，才是真正決定這張優化藍圖能被實現到什麼程度的關鍵。
+而 Sony BRAVIA True RGB LED 電視便精準示範，硬體如何賦予 AI 電視極致表現。傳統 LED 電視使用單一藍色 LED，再搭配濾光片混色的方式，容易產生色彩混濁或亮度減損，True RGB 技術則以獨立驅動紅（Red）、綠（Green）、藍（Blue）三原色 LED 作為背光源，當 XR 認知智慧處理器分析影像內容，發出畫面調整指令後，True RGB 能精準響應，讓紅、綠、藍三色背光以極高精度進行獨立控光，將 AI 畫面調整的判斷精準呈現。
+一般智慧電視、AI 電視、搭載 True RGB 的 AI 電視差在哪？
+跳脫複雜的規格參數，一次搞懂三代智慧電視有何不同。簡單來說，一般 AI 電視可以做到升頻、降噪與場景辨識；搭載 True RGB 的 AI 電視則進一步把 AI 判斷延伸到背光與色彩控制，真實還原亮度、色彩與對比。
+一般智慧電視
+搭載 True RGB 的 AI 電視
+解決「連網與內容獲取」
+解決「基礎畫面自動優化」
+解決「極致高階畫質精準執行」
+畫質處理能力
+支援基本的數位降噪，無法因應訊號源差而改善
+具備 AI 升頻技術，能動態辨識場景並優化低解析度影片
+結合 XR 認知智慧處理器與硬體優勢，進行深度的 AI 畫面優化
+傳統常亮背光，容易產生漏光與局部發灰現象
+具備區域控光，但演算法與硬體匹配度較為普遍
+採用 True RGB 三色獨立背光，控光精準度極高，無溢光與色偏
+色彩與亮度表現
+色彩表現較為平淡，高亮處易過曝，暗部細節容易丟失
+色彩飽和度高，但有時因演算法過度補償而顯得不夠自然
+實現豐富飽和的色彩表現層次，精準還原真實色彩
+主要適合情境
+看第四台、日常追劇
+看 4K 串流，希望電視能自動適應不同影音內容
+追求劇院級體驗，喜歡高畫質影音、球賽、遊戲的用戶
+跳脫傳統電視容易漏光與發灰的痛點，Sony BRAVIA 9 II 結合旗艦級 XR 認知智慧處理器與 True RGB 背光技術，從底座美學到內在核心，皆為追求劇院級體驗的頂級用戶而生。
+買 AI 電視時，真正該看哪些規格？
+當你準備為家裡添購 AI 電視時，除了關心它是否支援智慧語音、刷新率有多高、個人化推薦好不好用之外，以下四個核心 AI 電視功能才是決定長期觀看品質的關鍵指標：
+AI 處理器
+大腦優劣決定電視表現，挑選時認準旗艦級的 AI 處理器，如 Sony 的 XR 認知智慧處理器，不只單純堆疊算力，而能模擬人類大腦的認知方式，打造身歷其境的畫面真實感。
+AI 升頻能力
+優秀的 AI 升頻能力應能精準區分「影像噪訊」與「畫面原生紋理」，在去除雜訊的同時保留皮膚毛孔、衣服編織等細節，而非一味抹平。
+背光與控光技術
+若重視高階畫質，True RGB 可作為判斷 AI 畫質能否精準呈現的重要顯示技術，徹底告別傳統畫面暗部發灰、亮部慘白的通病。
+不能只看標榜的 HDR 規格，更要檢視硬體能否真實呈現。True RGB 能賦予 AI 電視更強悍的畫面執行力，銳利呈現 AI 算出的明暗對比與色彩飽和度。
+關於 AI 電視與 True RGB 的常見問答
+Q1：AI 電視適合哪些人？
+AI 電視適合所有對影音品質有追求的人。不論你是愛看高畫質影音的追劇族、追求畫面流暢不殘影的運動迷、重視高刷新率與低延遲的遊戲玩家，AI 電視都能大幅提升觀影體驗。
+Q2：AI 升頻會把影片變成 4K 嗎？
+無法完全等同原生 4K，但能讓畫面更接近高解析度的觀看效果。AI 升頻利用比對與像素補插，將原本模糊線條變得銳利清晰，結合 True RGB 的高精細控光後，視覺表現會非常接近 4K 原生畫質。
+Q3：買 AI 電視時，只看 AI 處理器夠嗎？
+絕對不夠。演算法算出的完美畫面需要顯示硬體來執行，電視的背光技術、控光與色彩管理能力（如 True RGB）同樣重要。軟硬完美結合，才是高畫質的保障。
+Q4：AI 電視對看球賽或玩遊戲有什麼差別？
+AI 電視能根據不同場景優化畫面表現，觀看球賽時，能動態識別高速移動對象，即時插幀消除動態殘影；玩遊戲時，能自動切換至低延遲模式和強化暗部細節。
+Q5：白天和晚上看電視，AI 電視會自動切換不同的畫質設定嗎？
+Sony 搭載 True RGB 的 AI 電視內建環境光感測器，能根據環境光線變化動態調節畫面呈現，在白天明亮時自動增亮、晚上變暗時調降亮度並柔化對比，省去手動切換的麻煩。
+即時熱門文章
+影音｜台灣新首富解密：川湖林聰吉國小畢業、黑手出身，如何靠滑軌卡住AI伺服器命門？
+長壽的關鍵在於「空腹」？揭開諾貝爾獎認證的細胞再生長壽法
+Gemini簡報可以編輯了！3步驟教學：Canvas模式一鍵生成，加碼6招Google簡報實用技巧
+AI NAS 何時才值得部署？QNAP 拆解地端 AI 的成本、算力與資料門檻
+宜得利海外首座商場落腳圓山！創辦人27歲赴美被「嚇到」，低價哲學從此開始
+幣安被列入台灣VASP警示名單，不得提供虛擬資產服務！加密市場監管再度升溫</t>
+        </is>
+      </c>
       <c r="I47" s="1" t="n">
-        <v>46244.6258053588</v>
+        <v>46247.58645581018</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -4824,7 +4996,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>e097dd1868ea3b466a96ee9b8ac9699a142d2a30879e7b14e8aedad5cf8be7e8</t>
+          <t>1f7959be4e79052bd73b42e07ba195c024481f6108ff06ec931a2ea06a77832d</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4834,36 +5006,27 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>「全球IC設計供應商大展」首度增闢臺北場 - iThome</t>
+          <t>2024全球前十大IC設計公司最新排名！NVIDIA市占50％稱霸、聯發科排第5 - 財訊</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://www.ithome.com.tw/news/24694</t>
+          <t>https://www.wealth.com.tw/articles/86af32a3-c705-48de-b242-0ebfbc657f0f</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>iThome</t>
+          <t>財訊</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Thu, 30 Sep 2021 07:36:05 GMT</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>繼去年10月宣布擴大在亞太地區的布局之後，由全球主要IC設計業者組成的全球IC設計與委外代工協會（Fabless Semiconductor Association；簡稱FSA）又有最新決議，該協會日前宣布，今年11月11日將在臺北舉辦一場「全球IC設計供應商大展」，同時並舉行「半導體領域論壇」，會中更擬邀請聯發科技董事長蔡明介進行專題演講。
-「全球IC設計供應商大展」是FSA每年例行的大型展覽活動，在美國已經連續舉辦了7年，今年第8屆的展覽活動將於10月舉行。緊接著在11月，針對亞太地區的業者，另外增闢一場同樣類型的展覽及論壇活動，這是該協會第1次在其它區域增闢展覽場次。
-至於為何選擇在臺北舉辦，FSA亞太地區執行長王智立表示：「最主要是因為臺灣目前是僅次於美國第2大的IC設計大國，臺灣佔有全球IC設計25％的產值，而且還在逐漸成長當中，是一個非常重要的IC設計重鎮。」除此之外，也是為了服務臺灣的IC設計及半導體業者，因為每年「全球IC設計供應商大展」在美國舉辦時，業者能派去參觀這個展覽的人數有限，如果在臺北展出，則可以參與的人將會有更多。
-去年美國的「全球IC設計供應商大展」，總共吸引了917家公司參與了這個活動，參觀人數約有1800人。IC產業的中高階主管、工程師及業務行銷人員佔了絕大多數。今年臺北的首場展覽，佔地面積有150攤位，預計吸引1500名參觀者。
-FSA目前共有450個會員公司，亞太區有29家業者，亞太會員數近來成長快速，王智立表示，今年6月亞太會員將達到55個公司。臺灣業者包括聯發科、鈺創、揚智、凌陽、威盛等多家知名IC業者都是會員。
-鈺創董事長盧超群指出，在半導體業界有許多大大小小的協會，他認為大略可分成3個體系，一個是以半導體製造業者為主的半導體協會，如：美國半導體協會（SIA），另一個是是學術與業界結合的IEEE，負責業界標準的制訂等工作。另外一股勢力就是由IC設計業者組成的FSA，而FSA在業界希望能達到整合上下游供應練資源的功能。</t>
-        </is>
-      </c>
+          <t>Tue, 18 Mar 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" s="1" t="n">
-        <v>46244.62583908565</v>
+        <v>46247.58700811343</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -4900,7 +5063,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>dc74c2edc22c1b22e6eeea02d48cb561d61918edfe005fcff817a913e2828802</t>
+          <t>d0455bacbf23a7968e443b7e65e45901fa7e104e12e9c57e7c10bb6e85228895</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4910,285 +5073,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2023 年全球前十大 IC 設計業者營收合計年增 12%，NVIDIA 首度奪冠 - TechNews 科技新報</t>
+          <t>一顆IC、3兆產值！解析台灣半導體大軍創下的全球奇蹟 - 數位時代</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://finance.technews.tw/2024/05/09/total-revenue-of-the-worlds-top-ten-ic-design-companies-in-2023/</t>
+          <t>https://www.bnext.com.tw/article/60280/taiwan%27s-semiconductor-industry</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>TechNews 科技新報</t>
+          <t>數位時代</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Thu, 09 May 2024 07:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" s="1" t="n">
-        <v>46244.62586155093</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>c8ccdc5fe4b9178247a1974381170690c33b6fb683d74a9ca93d1c289751896b</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>IC semiconductor</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>【專欄】中芯國際7奈米真抄襲台積電？被爆早用挖礦專用IC「練兵」 - 數位時代</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>https://www.bnext.com.tw/article/70875/smic-7nm</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>數位時代</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Thu, 28 Jul 2022 07:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>AI NAS 何時才值得部署？QNAP 拆解地端 AI 的成本、算力與資料門檻
-2026.08.05
-AI與大數據
-sponsored
-威聯通科技股份有限公司
-當資料不能離開企業，運算就得靠近：AI 先改寫儲存架構
-AI 帶來的第一個變化，不只是運算能力提高，而是企業必須重新決定資料放在哪裡。
-儲存架構大致分為雲端與地端兩塊，QNAP 身為資料安全的守護者，長期發展的是地端網路儲存設備（NAS），並擴展至 25GbE、100GbE 高速網路交換器產品線，提供完整的儲存與高速網路基礎架構。威聯通科技（QNAP）總經理劉文義解釋，當資料因合規要求或敏感度不能上雲，就必須留在靠近使用者與應用的地方；運算需求一旦增加，承接資料的裝置也自然被推向地端 AI。
-不能上雲的名單比想像中長。醫療業持有大量醫療個資，金融與保險業受到合規與法規限制，部分大學院校與設計公司也不希望資料被雲端存取。對這些組織而言，問題並不是雲端好不好用，而是一開始就沒有把核心資料全面上雲的選項。
-威聯通科技（QNAP）總經理暨威強電集團（IEI）董事長 劉文義
-真正讓更多企業回頭計算的，則是長期成本。劉文義指出，資料上傳雲端可能免費，下載卻會按流量收費；當企業把一年、兩年、三年的費用加總回推，可能會發現，購買一台同等容量的 NAS，還能使用 7-10 年。資料規模愈大、存取愈頻繁，總持有成本的差距就愈值得評估。
-這並不代表雲端與地端只能二選一。雲端仍適合模型訓練、程式開發與波動大的工作負載；地端則較適合高頻存取、對延遲敏感，或不能離開企業邊界的資料。企業真正要回答的，是每一類資料與任務應該放在哪裡。
-依 QNAP 觀察，客戶過去關心的是需要幾 TB、幾 PB，或備份速度有多快；現在更常問的是，機器裡的資料要如何被 AI 活用。QNAP 也從 2021 年起，把公司發展定調在 AI 與高速網路的融合，試圖讓 NAS 從資料保存的位置，進一步成為資料被調用的位置。
-當資料量持續擴大，搜尋與管理方式也會跟著改變。「在 NAS 裡放入 AI Agent 會越來越不可或缺。」劉文義舉例，當照片累積到 10 萬、20 萬張，要找出其中幾張特定畫面，已不可能只靠人工翻找。此時，能理解內容、接受自然語言指令的 AI 工具，會從加分功能逐漸變成必要條件。
-從資料治理到地端推論：AI NAS 如何進入企業工作流？
-AI NAS 不是「多了 AI 功能的 NAS」，而是 NAS 在企業工作流裡換了位置。
-依 QNAP 觀察，目前客戶大致分布在一條導入光譜上。人數最多的一群，仍在把資料集中、分類、清理與建立權限。這一步看似與 AI 無關，卻決定後續系統能不能找到正確資料、辨識版本，並把答案交給有權限的人。
-中間一群開始建置私有的檢索增強生成（RAG）知識庫。RAG 並不是重新訓練一個模型，而是在模型回答前，先從企業的 SOP、合約、法規或技術文件中取回相關內容，再產生附有來源依據的答案。QNAP 以 Qsirch 的語意搜尋能力協助建構這類應用，協助企業建立私有知識庫；而走在最前面的少數企業，則已經嘗試地端推論與 AI Agent。
-模型的選擇權，QNAP 刻意留給客戶。知識庫背後採用哪一個模型，可由企業依需求決定，不綁定單一 AI 供應商。QNAP 也以 QuAgent AI 助理與模型情境協定（MCP）相關能力，讓管理者透過自然語言查詢狀態、調整設定，並讓 NAS 成為 AI Agent 可調用的資料節點。
-不過，劉文義沒有把這條路說得太容易。他坦言，目前 NAS 硬體的 AI 運算能力仍有限。一般企業期待的應用，可能需要約 300 到 800 TOPS，甚至 1,000 TOPS，因此多數方案會以 NVIDIA 顯示卡補足算力；一張卡約需新台幣 10 萬至 12 萬元，一張算不完，就得配置 2 張或 4 張。
-「整體成本可能是過去單獨一台 NAS 的 5 倍到 10 倍，並不是大部分中小企業都能接受。」除了硬體，使用者還需要 AI 應用的 Know-how、程式背景與開發資源，這些都是落地成本。
-QNAP 則是透過算力分級讓各規模與需求的企業都可以有適合的解決方案。在 Computex 2026 搶先亮相的 QNAP AI NAS 中，一類是採用含有 iGPU 與專屬 NPU 的處理器平台，以一百多 TOPS 的範圍，可順暢使用 AI 應用程式；另一類機種則可安裝 1 張或 2 張 NVIDIA 顯示卡，處理更大的運算量。
-同時 QNAP 也在軟體端也持續開發，目標是讓 NAS 裡的資料更有效率地被 AI 工具調用，讓資料成為有價值的知識。
-從規格走到現場：能源公司如何導入私有 LLM？
-本地 AI 實際落地部署會是什麼模樣？劉文義舉了一家約 50 多人的能源公司為例。這家公司原本想用 NAS 搭配雲端 AI 建置內部資料庫，但很快遇到兩個瓶頸：一是員工查詢時明顯出現卡頓；二是專利、技術與合約都高度敏感，高層不願上傳至公有雲，擔心機密資料會有外洩的疑慮。
-後來，該公司導入 QNAP AI NAS 的旗艦機種 QAI-h1290FX，搭配顯示卡與全快閃 SSD，在地端部署私有大型語言模型，把數十年來封存的靜態檔案交給 AI 調用，進行跨檔案摘要與精準搜尋。員工因此省下翻找合約與報告的時間，核心機密也能留在企業內部。
-這個案例說明，若任務範圍明確，有些應用不必動用雲端大型模型，地端運算量就可能足以支應。
-但不同企業的資料量、查詢方式與模型大小不同，導入前仍需要概念驗證（POC）與技術人員評估。
-而且，資料留在地端並不等於自動安全。企業仍要處理帳號權限、網路隔離、備份復原、漏洞修補與日常維運。地端的價值，是讓資料邊界與控制權回到企業手上；相對地，安全責任也會更直接地回到企業。
-哪些企業現在該做，哪些再等？先看重複性與三個條件
-能不能導入地端 AI，不只由產業標籤決定，也要看工作是否重複，以及場景能不能被清楚定義。劉文義觀察，第一批走進來的，除了受法規限制的醫療、金融與保險業，也包括利用地端 AI 加速資料處理的科技業，以及會計、律師等有大量重複文書工作的專業服務業，因為效益較容易被看見。
-工廠也是可預期的場景。一條生產線可能有　10　台、20　台機器，每台處理與儲存資料的 Protocol 都不同，需要相對應的儲存裝置；生產過程累積的影像與紀錄可能要保存 3 年到 5 年。當企業要跨設備調用這些資料，AI Agent 與地端資料節點就有發揮空間。
-「重複性資料處理越多，或重複性動作越多的產業，越容易透過導入 AI 提高工作效率。」反過來說，較傳統、人力密集，或仍高度依賴人工判斷的製造業，短期內未必能快速導入地端 AI。
-依 QNAP 提供的資料，企業也可用「高頻、大量、敏感」三個條件做第一輪判斷：資料是否被頻繁調用？規模是否大到雲端傳輸與長期費用開始變得明顯？內容是否涉及個資、法規、智慧財產或商業機密？三個條件愈集中，地端部署愈值得評估；三者都不成立時，使用雲端 API 往往更簡單，也可能更划算。
-可以先等的企業，大致也有三種。第一，資料仍分散、版本混亂、權限不清，急著上 AI 只會把混亂放大，先完成集中與治理，效率就可能先提升。第二，找不到一個具體且反覆發生的業務痛點，只因為「別人都在做」而採購，設備很可能變成昂貴的展示品。第三，使用量仍小、需求偶發，現階段雲端的彈性反而更有優勢。
-因此，POC 不應只驗證「模型答不答得出來」，還要回答三個問題：資料由誰負責，誰可以存取？導入後能節省多少查找時間、傳輸成本或人工作業？正式上線後，誰負責資料、模型與資安維運？只有當效益與責任都能被量化，才適合從展示走向正式部署。
-企業願意把部分資料留在自己的機房，動力最終仍回到資料主權。QNAP 的主要市場分布在歐洲、美洲與亞太，其中歐洲占比將近一半，而歐洲也正是全球推動資料主權的最大動力。
-QNAP 的產品已取得 ISO 27001、ISO 27017 與 ISO 27018 等多項認證，並滿足 GDPR、HIPAA 等資料保護與法規遵循需求；累積至今，已售出約數百萬台裝置，協助企業打造智慧、安全的儲存方案。
-至於普及時間點，劉文義提出一個明確的價格與效能交會點：地端應用若要順暢運作，運算量可能至少要達到 300 至 600 TOPS，甚至 800 TOPS，同時價格要落在新台幣 5 萬至 8 萬元。目前符合這些條件的硬體方案仍很有限。
-「AI NAS 不是多了 AI 功能，而是改寫了資料在工作流的位置。」威聯通科技總經理劉文義坦言，地端算力成本高昂，QNAP 透過「算力分級」與開放模型架構，助企業逐步建構私有 RAG 知識庫與 AI 團隊。
-「預測約兩、三年後，應該很快會看到符合一般大眾期待、具備合理 CP 值的產品。那個時間點，就會是 AI 落地最蓬勃發展的時候。」在此之前，企業真正能先做的，不是搶著買最大的模型或最昂貴的顯示卡，而是把資料治理、使用權限與高價值場景準備好。
-QNAP 以「資料煉油廠」比喻自己的角色：原油再多，沒有整理、提煉與配送的過程，也無法成為可用的能源。這個定位也點出地端 AI 的競賽條件——不是誰先買到算力，而是誰的資料先準備好被調用。模型會持續更換，但企業自己的資料層則會長期存在。
-AI NAS 不是把模型塞進儲存設備，而是在資料必須留在企業內時，讓搜尋、推論與管理靠近資料的地端節點。
-QNAP World Tour 2026 台北場將於 2026 年 9 月 18 日（五）舉行，現場將聚焦 AI 應用、儲存備份、網通產品、資安與監控，並安排 Live Demo，適合 IT 管理者、系統整合商與企業決策者參加。
-活動地點：新板希爾頓酒店｜如意 AB 廳
-活動時間：09:20–16:00
-地址：新北市板橋區民權路 88 號 2F
-立即報名：
-2026 QNAP 台灣企業資安韌性大調查，填問券抽好禮，倒數計時：
-即時熱門文章
-全球AI伺服器幾乎都靠台廠做！鴻海、廣達、緯穎⋯19檔AI基建概念股全拆解
-告別「極速迷思」！Opensignal 國際評比揭密：什麼才是 5G 時代的好網路？
-Gemini完整教學地圖！37篇實測整理，Notebooks、Spark、提示詞架構全打包
-黃仁勳再喊下一波AI浪潮是機器人！輝達Jetson Thor台鏈名單曝光，這些可望成受惠族群
-AI已經做得到20%的題目，反而不要碰！Google首席科學家給創業者的「1%法則」
-0到18歲成長津貼來了！可領多少？2027上路規劃、最新進度一次看</t>
-        </is>
-      </c>
-      <c r="I50" s="1" t="n">
-        <v>46244.62739863426</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>b25ce6310ea574f011477b6dbe960921afda78558d82c5931236c24dac4a08f2</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>IC semiconductor</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2024全球前十大IC設計公司最新排名！NVIDIA市占50％稱霸、聯發科排第5 - wealth.com.tw</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>https://www.wealth.com.tw/articles/86af32a3-c705-48de-b242-0ebfbc657f0f</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>wealth.com.tw</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Tue, 18 Mar 2025 07:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" s="1" t="n">
-        <v>46244.62742038194</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>d0455bacbf23a7968e443b7e65e45901fa7e104e12e9c57e7c10bb6e85228895</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>IC semiconductor</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>一顆IC、3兆產值！解析台灣半導體大軍創下的全球奇蹟 - 數位時代</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>https://www.bnext.com.tw/article/60280/taiwan%27s-semiconductor-industry</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>數位時代</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
           <t>Tue, 01 Dec 2020 08:00:00 GMT</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>根據世界半導體貿易統計組織（WSTS）預估，雖受到疫情干擾，但仍樂觀預估2020年全球半導體產值約4,260億美元（約新台幣12.78兆元），增幅3.3％；相較之下，台灣因疫情控制得宜產能未受影響，工研院產科國際所（IEK）更上修今年台灣半導體產值年成長高達20.7％，並將首度突破新台幣3兆元大關，在暌違3年後，重奪全球第2大半導體產值國地位。
 過去3年，也是台灣半導體產業風起雲湧的關鍵時期：台積電創辦人張忠謀交棒退休，由雙首長接任；聯電和格羅方德先後宣布停止先進製程發展；日月光獲中國政府點頭，合併矽品；中美貿易戰開打，中芯、華為旗下海思遭美方貿易制裁……。
@@ -5251,8 +5154,209 @@
 責任編輯：林美欣</t>
         </is>
       </c>
+      <c r="I49" s="1" t="n">
+        <v>46247.58703892361</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>b3b4ad83b48702ce2ea2055f535e5d4b8ca5a70c50ef915e3c62756f15346df4</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>台灣IC設計產業：年營收破千億美元，蟄伏於供應鏈背後的全球王者 - 報新聞</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://www.contentplatform.info/articles/492757/taiwan-ic-design-industry-mediatek-realtek-novatek-ai-semiconductor/</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>報新聞</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:23:43 GMT</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" s="1" t="n">
+        <v>46248.81641684028</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>219376d9cb16ba8c93224bc86bce6e724c8062ef7fc9283f00ac3448736c22ba</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Nordic Semiconductor推出nRF54LV10A —— 一款突破性的低電壓藍牙低功耗系統單晶片，專為新一代醫療保健穿戴式設備設計_COMPOTECH ASIA - COMPOTECH Asia</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://www.compotechasia.com/a/new_product/2025/1209/62429.html</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>COMPOTECH Asia</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Tue, 09 Dec 2025 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" s="1" t="n">
+        <v>46248.81875958334</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>270a8d5c521f48eb74af322becee4bae4f5524cb64222b8a70de16c1de207d73</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Elevation Semiconductor 推出兩款用於反激式轉換器的新型離線 AC-DC 初級側 PWM 控制器 - COMPOTECH Asia</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://compotechasia.com/a/new_product/2022/0928/52283.html</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>COMPOTECH Asia</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Wed, 28 Sep 2022 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" s="1" t="n">
-        <v>46244.62791032407</v>
+        <v>46248.82103641204</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -5289,7 +5393,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>bd90c875dbc886701ec5a8dc8346cae00c3fed44eb24a6be853fd0628c329163</t>
+          <t>8d89c3fcf96a44fd659d0fa2aa9fbe3897042676fe3c978226a851d7de3a2f43</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -5299,54 +5403,33 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>AI 晶片引領半導體市場至 2030 年 - CIO Taiwan</t>
+          <t>FSA首度在台舉行IC設計供應商大展 - ctimes.com.tw</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://www.cio.com.tw/ai-chips-lead-semiconductor-market-to-2030/</t>
+          <t>https://ctimes.com.tw/DispArt/tw/FSA/04111018239R.shtml</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CIO Taiwan</t>
+          <t>ctimes.com.tw</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tue, 03 Sep 2024 07:00:00 GMT</t>
+          <t>Thu, 13 Aug 2026 20:43:27 GMT</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>AI 晶片引領半導體市場至 2030 年 | CIO Taiwan
-查看所有結果
-◤SEMI 產業研究資深總監曾瑞榆指出，半導體市場有望於 2025 年呈現強勁復甦，2030 年 AI 半導體市場年複合成長率更將高達 24%。
-上一篇文章
-迎接 AI 三大挑戰  吳田玉：半導體要跨界合作
-下一篇文章
-英特爾落敗 大家可以學到什麼教訓？
-【專訪】中國信託商業銀行數位科技處處長王俊權：數據與 AI 治理體系，三層金字塔規模化
-【專訪】台達電子資訊長暨資安長曾立峰：企業架構思維，驅動全球營運
-匯豐銀行 AI 防堵金融犯罪的十年轉骨
-【編輯室札記】開源大模型讓 AI ROI 露曙光
-【專訪】萬事達卡台灣區董事總經理陳懿文：Agentic Commerce 時代 重塑金融信任架構
-直擊製造業 AI 轉型深水區！Dell Technologies、勤業眾信、BIG DATA 聯手推一站式 Agentic AI 架構，助攻企業從 PoC 邁向規模化生產
-臺安醫院重構數位韌性基石：攜手思科佈局零信任智慧醫療新階段
-邁向 Physical AI 無人載具成企業 AI、通訊韌性與資安整合新戰場
-經濟股市爆發 民眾無感如何解決？
-【金融業】金融犯罪偵測系統的十年演進 ─ HSBC 反洗錢系統的 AI 路徑
-FDE 前線部署工程師，讓 AI 真正落地的角色
-避免盲追流行，「主權 AI」徹底剖析
-未治理 AI 將付出代價
-從缺料、缺工到缺貨：企業為什麼需要 BCM 商業持續管理？
-邊 AI 邊裁員　企業正在重寫成長的規則
-供應商視野
-CIO 雜誌</t>
+          <t>無晶圓廠IC設計協會（Fabless Semiconductor Association；FSA）將於11日起在台北舉行IC設計供應商大展（2004 FSA Suppliers Expo Taiwan），此次展覽是FSA繼去年在台成立亞太區總部後，首次在亞洲舉行IC設計供應商大展。展覽並將同時舉行半導體領袖論壇，將有許多產業界重量級人士出席。
+據了解，FSA的IC設計供應商大展中除有台積電董事長張忠謀發表專題演講，台北市長馬英九與FSA執行長Jodi Shelton、FSA董事會副主席兼科勝訊董事長Dwight Decker、FSA亞洲領袖議會主席兼鈺創董事長盧超群、蔡明介、益華執行董事長RayBingham等人也將出席。
+FSA表示，這項為期一天的活動將結合IC設計業者與相關供應商、整合元件製造商、OEM業者等，促進供應商與業者的合作，會場並展出IC設計相關工具、服務和先進技術，參展業者將包括封裝、測試、設計軟體、設備、光罩和晶圓製造業等。</t>
         </is>
       </c>
       <c r="I53" s="1" t="n">
-        <v>46244.62846341435</v>
+        <v>46249.55234271991</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -5383,7 +5466,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>e98a8767e4786e466eaaa5c9834f0f21606d38acb980d5eecfc2f80b6a3b8e68</t>
+          <t>29dbc757af71a5225f8899cb337bee432ae4f1edb143f20a1f0b1cf0e1c3855f</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -5393,12 +5476,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Navitas 與輝達開發的電源晶片有進展、股價飛天 - TechNews 科技新報</t>
+          <t>偉詮電靠「護國神山」牽線的併購，Q1 獲利狂飆 475% 通吃 AI 散熱大單 - TechNews 科技新報</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://finance.technews.tw/2025/10/15/navitas-nvidia-power-chip-development-progress-shares-soaring/</t>
+          <t>https://finance.technews.tw/2026/07/18/weltrend-semiconductor-inc/</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -5408,38 +5491,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Wed, 15 Oct 2025 07:00:00 GMT</t>
+          <t>Sat, 18 Jul 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>第三代半導體氮化鎵（GaN）功率 IC 領導大廠納微半導體（Navitas Semiconductor）宣布，與輝達（Nvidia）合作開發的 AI 基礎建設電源晶片取得進展，股價聞訊飆高。
-Barron’s報導，Navitas執行長Chris Allexandre 13日稍晚透過
-聲明稿表示
-，隨著輝達推動AI基礎設施轉型，該公司將藉由先進的氮化鎵（GaN）和碳化矽（SiC）電源解決方案，提供次世代資料中心所需的效率、可擴展性和可靠性。
-Navitas表示，最新裝置可讓輝達順利獲得次世代AI系統需要的800伏特電力，這項設計可直接為IT機櫃供電，無需額外的轉換器。
-根據Navitas說法，其為AI資料中心設計的先進800V高壓直流輸電（HVDC）架構，不但能提升效率及可擴展性，還可減少銅的用量。
-Navitas 14日聞訊飆漲26.08%、收12.57美元，創2022年1月11日以來收盤新高。
-Navitas 2025年5月就曾宣布獲得輝達訂單，帶動5月22日當天股價暴衝164.4%。
-MoneyDJ新聞
-授權轉載；首圖來源：shutterstock）
-延伸閱讀：
-納微打入 NVIDIA 供應鏈！高壓直流架構有望成 AI 資料中心趨勢
-文章看完覺得有幫助，何不給我們一個鼓勵
-請我們喝杯咖啡
-想請我們喝幾杯咖啡？
-每杯咖啡 65 元
-您的咖啡贊助將是讓我們持續走下去的動力
-總金額共新臺幣
-《關於請喝咖啡的 Q &amp; A》
-留給我們的話
-從這裡可透過《Google 新聞》追蹤 TechNews
-Navitas
-功率半導體</t>
+          <t>當多數 IC 設計業者仍苦於價格戰，
+靠一場併購翻轉命運。
+由「護國神山」牽線，成功切入AI資料中心生態系，走出成熟製程紅海困局。
+由「護國神山」牽線的併購案，讓老牌IC設計公司偉詮電，得以切入全球資料中心生態系，在消費性電子產品疲軟不振之際，逆勢突圍，今年上半年營收創下歷史新高，第一季稅後淨利成長幅度更高達475％。
+成立於1989年的偉詮電，過去的強項是Type-C快充設備的電力傳輸控制晶片，以及筆電及遊戲機電源管理晶片。然而，不少產品近年皆面臨中國對手低價競爭。
+「台灣雖有兩百多家IC設計公司，但上有超級強勢的晶圓代工廠，下有台灣系統大廠的壓力，我們被夾在中間，議價能力非常弱勢。」2014年加入公司的偉詮電執行長林崇燾直言不諱。
+身為董事長林錫銘之子、同時擁有外資分析師背景的林崇燾，幾年來一直積極尋覓轉型路徑，並鎖定併購規模較小且具備獲利能力的台灣晶片同業，在共用台灣供應鏈的前提下擴大客戶規模，偉詮電才能發揮綜效、持續成長。
+併購陞達科保密到家，產品市占率大幅提升
+機會，在2022年新冠疫情期間降臨。
+當年，團隊規模僅50人的
+，面臨拿不到晶圓產能，也找不到研發人才的困境。台灣半導體業「護國神山」，看準陞達科這家客戶的技術含金量高，主動將它介紹給另一家長期客戶偉詮電。
+林崇燾分析後認為，偉詮電與陞達科的客戶群重疊度不高，且當時偉詮電也在發展以MCU為主的馬達控制IC，主攻高階市場，陞達科則在研發用於伺服器氣冷散熱的馬達風扇控制IC，以ASIC晶片方式出貨、供應中低階市場，雙方市場高度互補。
+由於偉詮電過去曾有洽談併購時，因消息提前走漏而導致被併購方股價大漲、收購成本大幅拉高，最終破局的慘痛教訓，林崇燾這次出手前保密到家，「宣布併購前，整家公司只有我、董事長還有財務長三個人知道」，他回憶。
+因此林崇燾說服陞達科大股東
+後，先買下陞達科51％股權；2025年再透過換股方式，將陞達科收購下市。
+兩家公司合併後綜效明顯，雙方在馬達風扇控制IC的市占率，從17％一路躍升至四成左右，不僅為公司創造全新的成長動能，也大幅強化產品議價能力。
+「2025年營收成長15％、獲利近乎翻倍……今年第一季散熱風扇馬達控制 IC年增率高達七成，就是受惠AI硬體建置的投資，抵銷我們在電源的小幅衰退。」林崇燾分析合併效益。</t>
         </is>
       </c>
       <c r="I54" s="1" t="n">
-        <v>46245.69298417716</v>
+        <v>46249.55427341435</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -5469,6 +5546,254 @@
       </c>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>62</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>5bb0491f325ca3a081ba6eed47c7e6cc711a57f61118343571bec094be896941</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>觀點｜台灣又背鍋！川普再提「台灣搶晶片生意論」：從市占率來看，這話有公道嗎？ - 數位時代</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://www.bnext.com.tw/article/85177/trump-criticizes-taiwan-chip-industry-american-semiconductor-revival</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>數位時代</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Thu, 20 Nov 2025 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>11月17日，美國總統川普再度提到台灣。他表示，美國曾「愚蠢地」把晶片生意拱手讓給台灣；不過如今晶片將回到美國生產，美國預計在接下來的幾年內取得很大部分的晶片市場。川普並稱，他認為美國可能在很短時間內生產世界上大多數的晶片。
+川普聲稱，台灣目前幾乎生產製造了「100%」的晶片，這實在很「丟臉」，但好消息是，它們即將「回流」到美國。他又說，美國透過關稅保護產業，以防止像晶片產業那樣遭到「襲擊」。
+川普表示，美國曾經占「百分之百」的晶片生意，如今全都轉往台灣與南韓，且大多數在台灣。
+政治人物經常以與事實有明顯落差的聳動論點，來彰顯自身的偉大並宣揚政績。川普對晶片市場的發言偏離事實太遠，其目的在於凸顯他的關稅政策能扭轉乾坤，將過去的「錯誤」導回正軌。
+台灣晶圓廠產能，2010年已達世界最多
+美國是半導體的發明地。1950、1960年代，美國曾是半導體「唯一」的生產國；其後歐洲、日本加入，形成三足鼎立的態勢。
+1990年，歐洲半導體產能占全球44%，居第一；美國以37%居第二；日本以19%居第三。
+到2000年，台灣、韓國加入半導體生產行列，歐洲半導體的產能占比退至24%，仍居全球第一。
+後起之秀台灣在大舉興建8吋晶圓廠下，半導體產能全球占比躍升至22%，居第二。
+美國以19%的晶圓廠產能占比退居第三；日本占16%，居第四；韓國占13%，居第五。
+2010年，台灣晶圓廠產能占全球22%，高居第一，主要動能來自晶圓代工。
+日本占18%，居第二；韓國占15%，居第三；美國與歐洲占比大幅下滑，雙雙跌至13%，並列第四。
+在政府政策全力支持下，中國半導體產業快速發展；中國晶圓廠產能占全球11%，居第五。
+2020年，台灣晶圓廠產能占全球19%，仍居第一。同年，日本、韓國、中國的晶圓廠產能占比皆為18%，並列第二；可見中國大力興建晶圓廠、產能快速擴充。
+2020年，美國晶圓廠產能占全球12%，居第三；歐洲占7%，居第四。
+論IC設計，美國才是半導體龍頭
+歐美原為半導體產業的先進區域。美國雖在IC設計獨霸全球，但在晶圓製造方面落後亞太地區；歐洲更是每況愈下。
+在新冠疫情肆虐下，晶片一度成為全球焦點，美、歐、日競相祭出優惠政策，鼓勵在地建設晶圓廠。
+美國推動「晶片法案」，鼓勵在美國興建晶圓廠；估計2022至2032年，美國晶圓廠產能將激增203%，同期間全球平均增幅為108%。
+美國雖在半導體產能上落後，然而在半導體市場仍居領先。
+2024年，總部設於美國的半導體公司營收以50.4%的市占率高居全球第一
+；韓國以21.1%居第二，與美國差距顯著。
+總部設於美國的半導體公司營收，以50.4%的市占率高居全球第一；圖為輝達美國總部，僅為示意圖。
+歐洲市占率為9.2%，居第三；日本8.2%，居第四；台灣6.5%，居第五；中國4.5%，居第六。
+台灣雖在晶圓代工獨霸全球，但半導體「市場市占率」以半導體成品計算，故整體市占率並不高。
+半導體製程回流美國，台灣是關鍵角色
+早在競選期間，川普就曾對台灣晶片產業發表不友善言論，指稱台灣「100%奪走美國的晶片事業」。時至今日，川普老調重彈，須留意他可能施壓台積電，要求擴大投資並加速量產。
+不過，川普也已接獲台積電在美國成功量產4奈米晶片的資訊。預計在明年底或2027年，台積電美國廠將量產3奈米，快速推進美國先進製程的產能。
+美國半導體公司縱橫全球、占據市場「半壁江山」。目前的短板在於美國本土晶圓廠產能較台灣、韓國、中國為少。不過，
+隨台積電投資1650億美元在美國興建先進晶圓廠與封裝廠，美國10奈米以下先進製程產能至2030年預估將躍升至全球28%，僅次於台灣的45%，居第二。
+在如此前景下，期望川普不要再酸台灣。畢竟，台灣很可能成為促成先進半導體製程回流美國製造的關鍵功臣。
+延伸閱讀：
+觀點｜解讀「AI投資大時代」背後的隱憂：如果電力不再是算力天花板，接下來呢？
+觀點｜盧特尼克的嘴，騙人的鬼？從台積電產能看真相：台美「晶片五五分」為何根本不可能
+責任編輯：李先泰</t>
+        </is>
+      </c>
+      <c r="I55" s="1" t="n">
+        <v>46250.56509642361</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>63</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>e097dd1868ea3b466a96ee9b8ac9699a142d2a30879e7b14e8aedad5cf8be7e8</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>「全球IC設計供應商大展」首度增闢臺北場 - iThome</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://www.ithome.com.tw/news/24694</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>iThome</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Thu, 30 Sep 2021 07:36:05 GMT</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>繼去年10月宣布擴大在亞太地區的布局之後，由全球主要IC設計業者組成的全球IC設計與委外代工協會（Fabless Semiconductor Association；簡稱FSA）又有最新決議，該協會日前宣布，今年11月11日將在臺北舉辦一場「全球IC設計供應商大展」，同時並舉行「半導體領域論壇」，會中更擬邀請聯發科技董事長蔡明介進行專題演講。
+「全球IC設計供應商大展」是FSA每年例行的大型展覽活動，在美國已經連續舉辦了7年，今年第8屆的展覽活動將於10月舉行。緊接著在11月，針對亞太地區的業者，另外增闢一場同樣類型的展覽及論壇活動，這是該協會第1次在其它區域增闢展覽場次。
+至於為何選擇在臺北舉辦，FSA亞太地區執行長王智立表示：「最主要是因為臺灣目前是僅次於美國第2大的IC設計大國，臺灣佔有全球IC設計25％的產值，而且還在逐漸成長當中，是一個非常重要的IC設計重鎮。」除此之外，也是為了服務臺灣的IC設計及半導體業者，因為每年「全球IC設計供應商大展」在美國舉辦時，業者能派去參觀這個展覽的人數有限，如果在臺北展出，則可以參與的人將會有更多。
+去年美國的「全球IC設計供應商大展」，總共吸引了917家公司參與了這個活動，參觀人數約有1800人。IC產業的中高階主管、工程師及業務行銷人員佔了絕大多數。今年臺北的首場展覽，佔地面積有150攤位，預計吸引1500名參觀者。
+FSA目前共有450個會員公司，亞太區有29家業者，亞太會員數近來成長快速，王智立表示，今年6月亞太會員將達到55個公司。臺灣業者包括聯發科、鈺創、揚智、凌陽、威盛等多家知名IC業者都是會員。
+鈺創董事長盧超群指出，在半導體業界有許多大大小小的協會，他認為大略可分成3個體系，一個是以半導體製造業者為主的半導體協會，如：美國半導體協會（SIA），另一個是是學術與業界結合的IEEE，負責業界標準的制訂等工作。另外一股勢力就是由IC設計業者組成的FSA，而FSA在業界希望能達到整合上下游供應練資源的功能。</t>
+        </is>
+      </c>
+      <c r="I56" s="1" t="n">
+        <v>46250.56588189815</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>64</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>f0d83ebd3a8f068f24b94463dfedca4e4d5ff26f56c07a1a491ba6fce3d2fda6</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2023年半導體平均月薪5.6萬元年增幅3.1% 高薪職務出列！挑戰月薪上看10萬 - 104職場力</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://blog.104.com.tw/104data-2023-semiconductor-salary/</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>104職場力</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Tue, 05 Sep 2023 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" s="1" t="n">
+        <v>46250.56753127315</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/result.xlsx
+++ b/output/result.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U57"/>
+  <dimension ref="A1:U62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5795,6 +5795,434 @@
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
     </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>66</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>df3f5e636daa45107d35475009ed5e4fbffe1503d52eb91981ee34c59ca4a6a4</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>【2026最新】半導體業平均薪資出爐！日月光投控628萬奪冠、台積電破400萬 - 104職場力</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://blog.104.com.tw/top-10-semiconductor-industry-salary-2025/</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>104職場力</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Wed, 03 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" s="1" t="n">
+        <v>46252.80205401662</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>67</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>a0e5c4996be3fa353c6c653650971b467627207c9509a31d4e70eb5429f914ec</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026/08/11 Sony Semiconductor Solutions and TSMC Agreed to Establish Joint Venture for Next-Generation Image Sensors</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://pr.tsmc.com/english/news/3333</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>TSMC</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sony Semiconductor Solutions and TSMC Agreed to Establish Joint Venture for Next-Generation Image Sensors
+Issued by: TSMC
+Issued on:
+2026/08/11
+HSINCHU, Taiwan, R.O.C. and ATSUGI, Japan, August 11, 2026 -
+Sony Semiconductor Solutions Corporation (“Sony”) and Taiwan Semiconductor Manufacturing Company Limited (“TSMC”) (TWSE: 2330, NYSE: TSM) today announced the execution of a legally binding definitive agreement for the establishment of Advanced Vision Semiconductor Manufacturing Corporation as a joint venture (“JV”) in Koshi City, Kumamoto Prefecture, Japan. The JV will serve as a core hub for the development and manufacturing activities required for the volume production of image sensors for smartphones utilizing advanced manufacturing process technology. The JV is expected to commence volume production in 2029.
+Sony will be the sole controlling shareholder and the JV is planned to operate as a consolidated subsidiary of Sony Group Corporation. The Representative Director of the JV is planned to be appointed by Sony.
+Pursuant to the definitive agreement, Sony plans to contribute approximately 465 billion yen to the JV through a combination of cash contributions and the transfer of its assets* through a company split. TSMC plans to make cash contributions of approximately 282 billion yen. These capital contributions are expected to be made in phases based on market demand and other relevant business conditions. In addition to these capital contributions by Sony and TSMC, investments required to realize the production capacity planned by the JV are being considered on the premise that they would receive support from the Japanese government.
+Under the strategic partnership, Sony intends to take a leading role in the development of core image sensor technologies, as well as product planning and product design. The JV plans to leverage TSMC’s advanced process technology and manufacturing expertise to drive development and manufacturing activities required for the volume production. Through this collaboration, the companies intend to accelerate the commercialization of image sensor products driven by customer needs while advancing technological innovation and strengthening manufacturing capacity.
+The establishment of the JV and completion of the transaction are subject to the receipt of required regulatory approvals and the satisfaction of other customary closing conditions.
+All other aspects of the partnership remain unchanged from the announcement by Sony and TSMC titled “Sony Semiconductor Solutions and TSMC Enter Preliminary Agreement for Next-Generation Image Sensor Strategic Partnership” issued on May 8, 2026.
+* Sony’s newly constructed fab in Koshi City, Kumamoto Prefecture, Japan, in which Sony has already invested.
+TSMC Spokesperson
+Wendell Huang
+Senior Vice President &amp; Chief Financial Officer
+TSMC Deputy Spokesperson
+Nina Kao
+Public Relations Division
+TSMC Media Contact</t>
+        </is>
+      </c>
+      <c r="I59" s="1" t="n">
+        <v>46252.80282093724</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>68</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>33a6723168a7b53184d89698b6359e00ea6cdcda94022f36fa13b7fd632bee65</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026/05/15 TSMC to Sell 8.1% of Vanguard International Semiconductor</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://pr.tsmc.com/english/news/3314</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>TSMC</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>TSMC to Sell 8.1% of Vanguard International Semiconductor
+Issued by: TSMC
+Issued on:
+2026/05/15
+HSINCHU, Taiwan, R.O.C., May 15, 2026 –
+TSMC (TWSE: 2330, NYSE: TSM) plans to execute the sale of up to 152.0 million common shares of Vanguard International Semiconductor Corporation (“VIS”), or approximately 8.1% of VIS’ fully-diluted paid-in-capital through a block trade to financial institutional investors.
+The proposed share sale will not affect TSMC’s strategic relations with VIS, including outsourcing of interposer production and licensing of GaN technology to VIS. The proposed share sale is part of TSMC’s plan to focus its resources on core business activities. In June 2024, TSMC ceased to have representation on VIS’ board of directors.
+TSMC currently holds approximately 27.1% of VIS shares on a fully diluted basis. Upon the completion of this share sale, TSMC expects to reduce its shareholding in VIS to approximately 19%. TSMC has no plan to sell more VIS shares in the foreseeable future.
+TSMC Spokesperson
+Wendell Huang
+Senior Vice President &amp; Chief Financial Officer
+TSMC Deputy Spokesperson
+Nina Kao
+Public Relations Division
+TSMC Media Contact</t>
+        </is>
+      </c>
+      <c r="I60" s="1" t="n">
+        <v>46252.80286494823</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>69</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>80bb08a00be68949140e3b543787a768fc20fed0be49f04b3b3a8eb00e31c914</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026/05/08 Sony Semiconductor Solutions and TSMC Enter Preliminary Agreement for Next-Generation Image Sensor Strategic Partnership</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://pr.tsmc.com/english/news/3308</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>TSMC</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sony Semiconductor Solutions and TSMC Enter Preliminary Agreement for Next-Generation Image Sensor Strategic Partnership
+Issued by: Sony Semiconductor Solutions Corporation and TSMC
+Issued on:
+2026/05/08
+Hsinchu, Taiwan, R.O.C., May 8, 2026 -
+Sony Semiconductor Solutions Corporation (“Sony”) and TSMC (TWSE: 2330, NYSE: TSM) today announced the signing of a non-binding memorandum of understanding (“MOU”) to form a strategic partnership for the development and manufacturing of next-generation image sensors.
+Under the proposed partnership, Sony and TSMC intend to establish a joint venture (“JV”), with Sony being the majority and controlling shareholder, to set up development and production lines in Sony’s newly constructed fab in Koshi City, Kumamoto Prefecture. Through the JV, both companies expect to leverage Sony's expertise in sensor design alongside TSMC’s strengths in process technology and manufacturing excellence as part of a broader collaboration aimed at enhancing image sensor performance.
+With the MOU signed, Sony and TSMC are discussing potential investments by the JV. These investments, along with new capital investment by Sony in its existing plant in Nagasaki, are being considered on the premise that they would be implemented in phases based on market demand, and that they would receive support from the Japanese government.
+This partnership also seeks to explore and address emerging opportunities in physical AI applications, such as automotive and robotics, paving the way for future innovations and expanded technological advancements. The establishment of the JV remains subject to the execution of a definitive legally binding agreement regarding the partnership and the satisfaction of customary closing conditions.
+“Building on the trust cultivated through our long-standing collaboration with TSMC, I am delighted that we have reached an agreement to advance our partnership to a new stage,” said Shinji Sashida, President and CEO of Sony Semiconductor Solutions Corporation. “This JV is a significant initiative that brings together the strengths of both companies and aims to drive further advancement in technology and business within the next-generation image sensor field. Building on this JV, Sony intends to further strengthen its business operations with a focus on creating high added value. Rooted in the Sony Spirit that has guided us since our founding, we intend to continue to take on the challenge of creating new markets through unprecedented ideas and distinctive technologies.”
+“Sony has been our long-time partner in the CMOS image sensor business. We are excited to elevate our collaboration to the next level, which represents a key step forward in driving future sensing technology in the AI era,” said TSMC Senior Vice President and Deputy Co-COO, Dr. Kevin Zhang. “This partnership underscores our shared commitment and mutual vision of leveraging cutting-edge technologies and innovative solutions to deliver leading sensing technology and products. We look forward to working closely together to achieve impactful results and create lasting value for all stakeholders.”
+TSMC Spokesperson
+Wendell Huang
+Senior Vice President &amp; Chief Financial Officer
+TSMC Deputy Spokesperson
+Nina Kao
+Public Relations Division
+TSMC Media Contact</t>
+        </is>
+      </c>
+      <c r="I61" s="1" t="n">
+        <v>46252.80290519664</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>70</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>fc0c6a277e289c6215faee30099dbc75fc8b6fc7aafc2efee48020b4189e8c37</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>IC semiconductor</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026/04/23 TSMC Debuts A13 Technology at 2026 North America Technology Symposium</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://pr.tsmc.com/english/news/3302</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>TSMC</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>TSMC Debuts A13 Technology at 2026 North America Technology Symposium
+Newest Node Pushes Density Scaling and Energy Efficiency to New Heights to Address Industry’s Most Demanding Applications
+Issued by: TSMC
+Issued on:
+2026/04/23
+SANTA CLARA, CA, Apr. 22, 2026 --
+TSMC (TWSE: 2330, NYSE: TSM) today debuted its latest innovation in its most advanced process technology at the Company’s 2026 North America Technology Symposium. TSMC’s new A13 process is a direct shrink of its industry-leading A14 node announced in 2025, enabling even more compact and efficient designs to address insatiable customer demand in computational requirements for next-generation artificial intelligence, high performance computing (HPC), and mobile applications.
+Representing TSMC’s commitment to continuous improvement, A13 provides 6% area savings from A14. Design rules are fully backward compatible with A14, enabling customers to quickly migrate their designs to TSMC’s latest nanosheet transistor technology. In addition, A13 delivers increased power efficiency and performance gains through design-technology co-optimization, and is scheduled to enter production in 2029, one year after A14.
+A13 was one of many technology innovations highlighted at TSMC’s North America Technology Symposium in Santa Clara, California, which kicks off the event series around the world in the coming months. With the theme of “Expanding AI with Leadership Silicon,” the technology symposiums are TSMC’s largest annual customer events, showcasing the Company’s breakthroughs in technology development and manufacturing service.
+“At TSMC, we understand our customers are always looking ahead to their next innovation and they come to us for a reliable stream of new silicon technologies, like A13, meticulously engineered to be ready for high-volume production right when their visionary new designs demand them,” said TSMC Chairman and CEO Dr. C.C. Wei. “TSMC’s advanced process technologies lead the industry in density, performance and power efficiency, and we continually strive to make them even better for our customers’ future products, ensuring customers’ success as their most reliable technological partner."
+Other new technologies unveiled at the North America Technology Symposium include:
+Advanced Logic
+At the event, TSMC is also previewing its A14 platform enhancement
+, which features Super Power Rail technology to provide backside power delivery for AI and HPC applications. A12 is also scheduled to enter production in 2029.
+TSMC continues to advance its 2nm platform with the introduction of
+, which employs design-technology co-optimization to reach speed gains of 3-4% or power reduction of 8-10% and a 1.02-1.03X logic density improvement from N2P. A balanced option for AI, HPC, and mobile applications leveraging the process maturity and strong yield performance of the 2nm technology platform, N2U is scheduled for production in 2028.
+TSMC 3DFabric
+Advanced Packaging and 3D Silicon Stacking
+To support AI demand for more computing power and memory in a single package, TSMC continues to expand its Chip on Wafer on Substrate (CoWoS
+) technology to integrate more silicon. The Company is now producing 5.5-reticle size CoWoS and planning for even larger versions. A
+14-reticle size CoWoS
+, capable of integrating approximately 10 large compute dies and 20 HBM stacks, is slated for production in 2028. This will be followed by an expansion to beyond 14 reticles in 2029. These new offerings provide customers with more options for AI compute scaling and complement TSMC’s 40-reticle size SoW-X System-on-Wafer technology also expected in 2029.
+TSMC is also offering its TSMC-SoIC
+3D chip stacking technology on its most advanced technology platform, with
+A14-to-A14 SoIC
+set to be available for production in 2029. It will provide 1.8X higher die-to-die I/O density compared with N2-on-N2 SoIC, supporting higher bandwidth of data transfer between stacked chips.
+TSMC’s Compact Universal Photonic Engine (TSMC-COUPE™) is set to reach a key milestone with a true co-packaged optics solution using
+COUPE on substrate
+beginning production in 2026. By integrating the COUPE optical engine directly inside the package, TSMC achieves 2X power efficiency and 10X latency reduction versus a pluggable version on the circuit board. The technology is featured in a 200Gbps micro-ring modulator, a highly compact and energy-efficient solution to move data between racks in data centers.
+Automotive and Robotics
+Advanced Driver Assistance Systems (ADAS) and autonomous vehicles require leading-edge technologies along with stringent quality and reliability standards. Physical AI applications, such as humanoid robots, are adopting similarly demanding requirements. To address these needs, TSMC announced
+, the first automotive-grade process technology with nanosheet transistors. N2A provides 15-20% speed gain at the same power compared with N3A and is scheduled to complete AEC-Q100 qualification in 2028. Furthermore, TSMC is making “Auto-Use” design kits available within its N2P process design kit (PDK), enabling customers to factor in automotive usage conditions in the design. This allows customers an earlier design start before N2A process is fully qualified.
+TSMC’s efforts to speed up automotive product cycles are already paying off for customers as
+enters production in 2026. With the N3 “Auto Early” program, customers were able to start designs in 2023, and today more than 10 products are planned on N3A technology to make automobiles smarter, greener, and safer for consumers.
+Specialty Technology
+TSMC is the first to bring high voltage technology into the FinFET era in 2026 with its
+N16HV
+process aimed at display driver applications. For smartphone display drivers, N16HV will increase gate density by 41% and reduce power by 35% compared to TSMC’s N28HV process. For near-eye displays, N16HV can shrink die area by 40% and reduce power by over 20%, enhancing the usability of applications such as smart glasses.
+TSMC Spokesperson
+Wendell Huang
+Senior Vice President &amp; Chief Financial Officer
+TSMC Deputy Spokesperson
+Nina Kao
+Public Relations Division
+TSMC Media Contact</t>
+        </is>
+      </c>
+      <c r="I62" s="1" t="n">
+        <v>46252.80295300022</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
